--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{708CBE13-F23B-4B4B-9375-D8F60A13F2C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C444EA68-009E-4A7F-B529-AA5E968D6040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$702</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$712</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7714" uniqueCount="1430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7889" uniqueCount="1444">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -4396,6 +4396,48 @@
   </si>
   <si>
     <t>FERNANDO YUPANQUI</t>
+  </si>
+  <si>
+    <t>C000386</t>
+  </si>
+  <si>
+    <t>C000391</t>
+  </si>
+  <si>
+    <t>C000392</t>
+  </si>
+  <si>
+    <t>C000393</t>
+  </si>
+  <si>
+    <t>C000394</t>
+  </si>
+  <si>
+    <t>C000395</t>
+  </si>
+  <si>
+    <t>C000396</t>
+  </si>
+  <si>
+    <t>12/07/2026</t>
+  </si>
+  <si>
+    <t>C000397</t>
+  </si>
+  <si>
+    <t>C000398</t>
+  </si>
+  <si>
+    <t>C000399</t>
+  </si>
+  <si>
+    <t>OFERTA EXPORTABLE DE PRODUCTOS TEXTILES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTIVIDAD 4.3 ASISTENCIA TÉCNICA ESPECÍFICA EN DISEÑO DE ENVASES Y EMPAQUES. </t>
+  </si>
+  <si>
+    <t>ACTIVIDAD 4.3 DISEÑO DE EMPAQUES Y/O ENVASES EN PRODUCTOS TEXTILES CON CORTE LÁSER EN MATERIAL MDF: LUXURY PACKAGING</t>
   </si>
 </sst>
 </file>
@@ -4486,7 +4528,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4509,6 +4551,7 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4849,7 +4892,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:P702"/>
+  <dimension ref="A1:P718"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -12769,7 +12812,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>911</v>
       </c>
@@ -12819,7 +12862,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>913</v>
       </c>
@@ -12869,7 +12912,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>914</v>
       </c>
@@ -12919,7 +12962,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>915</v>
       </c>
@@ -12969,7 +13012,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>916</v>
       </c>
@@ -13019,7 +13062,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>917</v>
       </c>
@@ -13069,7 +13112,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>918</v>
       </c>
@@ -13119,7 +13162,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>919</v>
       </c>
@@ -13169,7 +13212,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>920</v>
       </c>
@@ -13219,7 +13262,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>921</v>
       </c>
@@ -13269,7 +13312,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>922</v>
       </c>
@@ -13319,7 +13362,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>923</v>
       </c>
@@ -13369,7 +13412,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>924</v>
       </c>
@@ -13419,7 +13462,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>925</v>
       </c>
@@ -13469,7 +13512,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>926</v>
       </c>
@@ -13519,7 +13562,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>927</v>
       </c>
@@ -13569,7 +13612,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>928</v>
       </c>
@@ -13619,7 +13662,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>929</v>
       </c>
@@ -13669,7 +13712,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>930</v>
       </c>
@@ -13719,7 +13762,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>931</v>
       </c>
@@ -13769,7 +13812,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>932</v>
       </c>
@@ -13819,7 +13862,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>933</v>
       </c>
@@ -13869,7 +13912,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>934</v>
       </c>
@@ -13919,7 +13962,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>935</v>
       </c>
@@ -13969,7 +14012,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>936</v>
       </c>
@@ -14019,7 +14062,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>937</v>
       </c>
@@ -14069,7 +14112,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>938</v>
       </c>
@@ -14119,7 +14162,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>939</v>
       </c>
@@ -14169,7 +14212,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>940</v>
       </c>
@@ -14219,7 +14262,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>941</v>
       </c>
@@ -14269,7 +14312,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>942</v>
       </c>
@@ -14319,7 +14362,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>943</v>
       </c>
@@ -14369,7 +14412,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>944</v>
       </c>
@@ -14419,7 +14462,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>945</v>
       </c>
@@ -14469,7 +14512,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>946</v>
       </c>
@@ -14519,7 +14562,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>947</v>
       </c>
@@ -14569,7 +14612,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>948</v>
       </c>
@@ -14619,7 +14662,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>949</v>
       </c>
@@ -14669,7 +14712,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>950</v>
       </c>
@@ -14719,7 +14762,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>951</v>
       </c>
@@ -14769,7 +14812,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>952</v>
       </c>
@@ -14819,7 +14862,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>953</v>
       </c>
@@ -14869,7 +14912,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>954</v>
       </c>
@@ -14919,7 +14962,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>955</v>
       </c>
@@ -14969,7 +15012,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>956</v>
       </c>
@@ -15019,7 +15062,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>957</v>
       </c>
@@ -15069,7 +15112,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>958</v>
       </c>
@@ -15119,7 +15162,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>959</v>
       </c>
@@ -15169,7 +15212,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>960</v>
       </c>
@@ -15219,7 +15262,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>961</v>
       </c>
@@ -15269,7 +15312,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>962</v>
       </c>
@@ -15319,7 +15362,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>963</v>
       </c>
@@ -15369,7 +15412,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>964</v>
       </c>
@@ -15419,7 +15462,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>965</v>
       </c>
@@ -15469,7 +15512,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>966</v>
       </c>
@@ -15519,7 +15562,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>967</v>
       </c>
@@ -15569,7 +15612,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>968</v>
       </c>
@@ -16982,7 +17025,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>969</v>
       </c>
@@ -17032,7 +17075,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>970</v>
       </c>
@@ -17082,7 +17125,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>971</v>
       </c>
@@ -17132,7 +17175,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>972</v>
       </c>
@@ -17182,7 +17225,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>973</v>
       </c>
@@ -17232,7 +17275,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>974</v>
       </c>
@@ -17282,7 +17325,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>975</v>
       </c>
@@ -17332,7 +17375,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>976</v>
       </c>
@@ -17382,7 +17425,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>977</v>
       </c>
@@ -17432,7 +17475,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>978</v>
       </c>
@@ -17482,7 +17525,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>979</v>
       </c>
@@ -17532,7 +17575,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>980</v>
       </c>
@@ -17582,7 +17625,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>981</v>
       </c>
@@ -17632,7 +17675,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>982</v>
       </c>
@@ -17682,7 +17725,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>983</v>
       </c>
@@ -17732,7 +17775,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>984</v>
       </c>
@@ -17782,7 +17825,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>985</v>
       </c>
@@ -17832,7 +17875,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>986</v>
       </c>
@@ -17882,7 +17925,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>987</v>
       </c>
@@ -17932,7 +17975,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>988</v>
       </c>
@@ -17982,7 +18025,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>989</v>
       </c>
@@ -18032,7 +18075,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>990</v>
       </c>
@@ -18082,7 +18125,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>991</v>
       </c>
@@ -18132,7 +18175,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>992</v>
       </c>
@@ -18182,7 +18225,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>993</v>
       </c>
@@ -18232,7 +18275,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>994</v>
       </c>
@@ -18282,7 +18325,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>995</v>
       </c>
@@ -18332,7 +18375,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>996</v>
       </c>
@@ -18382,7 +18425,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>997</v>
       </c>
@@ -18432,7 +18475,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>998</v>
       </c>
@@ -18482,7 +18525,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>999</v>
       </c>
@@ -18532,7 +18575,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>1000</v>
       </c>
@@ -18582,7 +18625,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>1001</v>
       </c>
@@ -18632,7 +18675,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>1002</v>
       </c>
@@ -18682,7 +18725,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>1003</v>
       </c>
@@ -18732,7 +18775,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>1004</v>
       </c>
@@ -18782,7 +18825,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>1005</v>
       </c>
@@ -18832,7 +18875,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>1006</v>
       </c>
@@ -18882,7 +18925,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>1007</v>
       </c>
@@ -18932,7 +18975,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>1008</v>
       </c>
@@ -18982,7 +19025,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>1009</v>
       </c>
@@ -19032,7 +19075,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>1010</v>
       </c>
@@ -19082,7 +19125,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>1011</v>
       </c>
@@ -19602,7 +19645,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>1012</v>
       </c>
@@ -19652,7 +19695,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>1013</v>
       </c>
@@ -19702,7 +19745,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>1014</v>
       </c>
@@ -19752,7 +19795,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>1015</v>
       </c>
@@ -19802,7 +19845,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>1016</v>
       </c>
@@ -19852,7 +19895,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1017</v>
       </c>
@@ -19902,7 +19945,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1018</v>
       </c>
@@ -19952,7 +19995,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>1019</v>
       </c>
@@ -20002,7 +20045,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>1020</v>
       </c>
@@ -20052,7 +20095,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1021</v>
       </c>
@@ -20102,7 +20145,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>1022</v>
       </c>
@@ -20152,7 +20195,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>1023</v>
       </c>
@@ -20202,7 +20245,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>1024</v>
       </c>
@@ -20252,7 +20295,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>1025</v>
       </c>
@@ -20302,7 +20345,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>1026</v>
       </c>
@@ -20352,7 +20395,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>1027</v>
       </c>
@@ -20402,7 +20445,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>1028</v>
       </c>
@@ -20452,7 +20495,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>1029</v>
       </c>
@@ -20502,7 +20545,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1030</v>
       </c>
@@ -20552,7 +20595,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>1031</v>
       </c>
@@ -20602,7 +20645,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>1032</v>
       </c>
@@ -20652,7 +20695,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>1033</v>
       </c>
@@ -20702,7 +20745,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>1034</v>
       </c>
@@ -20752,7 +20795,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>1035</v>
       </c>
@@ -20802,7 +20845,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>1036</v>
       </c>
@@ -20852,7 +20895,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>1037</v>
       </c>
@@ -20902,7 +20945,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>1038</v>
       </c>
@@ -20952,7 +20995,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>1039</v>
       </c>
@@ -21002,7 +21045,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>1040</v>
       </c>
@@ -21052,7 +21095,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>1041</v>
       </c>
@@ -21102,7 +21145,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>1042</v>
       </c>
@@ -21152,7 +21195,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>1043</v>
       </c>
@@ -21202,7 +21245,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>1044</v>
       </c>
@@ -21252,7 +21295,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>1045</v>
       </c>
@@ -21302,7 +21345,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>1046</v>
       </c>
@@ -21352,7 +21395,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1047</v>
       </c>
@@ -21402,7 +21445,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1048</v>
       </c>
@@ -21452,7 +21495,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>1049</v>
       </c>
@@ -21502,7 +21545,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>1050</v>
       </c>
@@ -21552,7 +21595,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1051</v>
       </c>
@@ -21602,7 +21645,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>1052</v>
       </c>
@@ -21652,7 +21695,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>1053</v>
       </c>
@@ -21702,7 +21745,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>1054</v>
       </c>
@@ -21752,7 +21795,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>1055</v>
       </c>
@@ -21802,7 +21845,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>1056</v>
       </c>
@@ -21852,7 +21895,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>1057</v>
       </c>
@@ -21902,7 +21945,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>1058</v>
       </c>
@@ -21952,7 +21995,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>1059</v>
       </c>
@@ -22002,7 +22045,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>1060</v>
       </c>
@@ -22052,7 +22095,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>1061</v>
       </c>
@@ -22102,7 +22145,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>1062</v>
       </c>
@@ -22152,7 +22195,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>1063</v>
       </c>
@@ -22202,7 +22245,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>1064</v>
       </c>
@@ -22252,7 +22295,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>1065</v>
       </c>
@@ -22302,7 +22345,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1066</v>
       </c>
@@ -22352,7 +22395,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1067</v>
       </c>
@@ -22402,7 +22445,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>1068</v>
       </c>
@@ -22452,7 +22495,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>1069</v>
       </c>
@@ -22502,7 +22545,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1070</v>
       </c>
@@ -22552,7 +22595,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1071</v>
       </c>
@@ -22602,7 +22645,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>1072</v>
       </c>
@@ -22652,7 +22695,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1073</v>
       </c>
@@ -22702,7 +22745,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1074</v>
       </c>
@@ -22752,7 +22795,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>1075</v>
       </c>
@@ -22802,7 +22845,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1076</v>
       </c>
@@ -22852,7 +22895,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1077</v>
       </c>
@@ -22902,7 +22945,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1078</v>
       </c>
@@ -22952,7 +22995,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>1079</v>
       </c>
@@ -23002,7 +23045,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>1080</v>
       </c>
@@ -23052,7 +23095,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1081</v>
       </c>
@@ -23102,7 +23145,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>1082</v>
       </c>
@@ -23152,7 +23195,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>1083</v>
       </c>
@@ -23202,7 +23245,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1084</v>
       </c>
@@ -23252,7 +23295,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1085</v>
       </c>
@@ -23302,7 +23345,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1086</v>
       </c>
@@ -23352,7 +23395,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1087</v>
       </c>
@@ -23402,7 +23445,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1088</v>
       </c>
@@ -23452,7 +23495,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>1089</v>
       </c>
@@ -23502,7 +23545,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1090</v>
       </c>
@@ -23552,7 +23595,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1091</v>
       </c>
@@ -23602,7 +23645,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1092</v>
       </c>
@@ -23652,7 +23695,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1093</v>
       </c>
@@ -23702,7 +23745,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1094</v>
       </c>
@@ -23752,7 +23795,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1095</v>
       </c>
@@ -23802,7 +23845,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1096</v>
       </c>
@@ -23852,7 +23895,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1097</v>
       </c>
@@ -23902,7 +23945,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1098</v>
       </c>
@@ -23952,7 +23995,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1099</v>
       </c>
@@ -24002,7 +24045,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1100</v>
       </c>
@@ -24052,7 +24095,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1101</v>
       </c>
@@ -24102,7 +24145,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1102</v>
       </c>
@@ -24152,7 +24195,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1103</v>
       </c>
@@ -24202,7 +24245,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1104</v>
       </c>
@@ -24252,7 +24295,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1105</v>
       </c>
@@ -24302,7 +24345,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1106</v>
       </c>
@@ -24352,7 +24395,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1107</v>
       </c>
@@ -24402,7 +24445,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1108</v>
       </c>
@@ -24452,7 +24495,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1109</v>
       </c>
@@ -24502,7 +24545,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1110</v>
       </c>
@@ -24552,7 +24595,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1111</v>
       </c>
@@ -24602,7 +24645,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1112</v>
       </c>
@@ -24652,7 +24695,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>1113</v>
       </c>
@@ -24702,7 +24745,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1114</v>
       </c>
@@ -24752,7 +24795,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1115</v>
       </c>
@@ -24802,7 +24845,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1116</v>
       </c>
@@ -24852,7 +24895,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1117</v>
       </c>
@@ -24902,7 +24945,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1118</v>
       </c>
@@ -24952,7 +24995,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1119</v>
       </c>
@@ -25002,7 +25045,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1120</v>
       </c>
@@ -25052,7 +25095,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1121</v>
       </c>
@@ -25102,7 +25145,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1122</v>
       </c>
@@ -25152,7 +25195,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1123</v>
       </c>
@@ -25202,7 +25245,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1124</v>
       </c>
@@ -25252,7 +25295,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1125</v>
       </c>
@@ -25302,7 +25345,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1126</v>
       </c>
@@ -25352,7 +25395,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1127</v>
       </c>
@@ -25402,7 +25445,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1128</v>
       </c>
@@ -25452,7 +25495,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1129</v>
       </c>
@@ -25502,7 +25545,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>1130</v>
       </c>
@@ -25552,7 +25595,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1131</v>
       </c>
@@ -25602,7 +25645,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1132</v>
       </c>
@@ -25652,7 +25695,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1151</v>
       </c>
@@ -25702,7 +25745,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1152</v>
       </c>
@@ -25752,7 +25795,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>1153</v>
       </c>
@@ -25802,7 +25845,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>1154</v>
       </c>
@@ -25852,7 +25895,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>1155</v>
       </c>
@@ -25902,7 +25945,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>1156</v>
       </c>
@@ -25952,7 +25995,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>1157</v>
       </c>
@@ -26002,7 +26045,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>1158</v>
       </c>
@@ -26052,7 +26095,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>1159</v>
       </c>
@@ -26102,7 +26145,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>1160</v>
       </c>
@@ -26152,7 +26195,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>1161</v>
       </c>
@@ -26169,7 +26212,7 @@
         <v>195</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>1140</v>
+        <v>564</v>
       </c>
       <c r="G439" s="1">
         <v>10240067566</v>
@@ -26202,7 +26245,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>1162</v>
       </c>
@@ -26219,7 +26262,7 @@
         <v>195</v>
       </c>
       <c r="F440" s="1" t="s">
-        <v>1140</v>
+        <v>564</v>
       </c>
       <c r="G440" s="1">
         <v>10240067566</v>
@@ -26252,7 +26295,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>1163</v>
       </c>
@@ -26302,7 +26345,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>1164</v>
       </c>
@@ -26352,7 +26395,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>1165</v>
       </c>
@@ -26402,7 +26445,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>1166</v>
       </c>
@@ -26452,7 +26495,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>1167</v>
       </c>
@@ -26469,7 +26512,7 @@
         <v>195</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>1140</v>
+        <v>564</v>
       </c>
       <c r="G445" s="1">
         <v>10247060931</v>
@@ -31613,7 +31656,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>1195</v>
       </c>
@@ -31663,7 +31706,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>1196</v>
       </c>
@@ -31713,7 +31756,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>1197</v>
       </c>
@@ -31763,7 +31806,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>1198</v>
       </c>
@@ -31813,7 +31856,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>1199</v>
       </c>
@@ -31863,7 +31906,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>1200</v>
       </c>
@@ -31913,7 +31956,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>1201</v>
       </c>
@@ -31963,7 +32006,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>1202</v>
       </c>
@@ -32013,7 +32056,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>1203</v>
       </c>
@@ -32063,7 +32106,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>1204</v>
       </c>
@@ -32113,7 +32156,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>1205</v>
       </c>
@@ -32163,7 +32206,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>1206</v>
       </c>
@@ -32213,7 +32256,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>1207</v>
       </c>
@@ -32263,7 +32306,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>1208</v>
       </c>
@@ -32363,7 +32406,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>1210</v>
       </c>
@@ -32463,7 +32506,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>1212</v>
       </c>
@@ -32563,7 +32606,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>1214</v>
       </c>
@@ -32663,7 +32706,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>1216</v>
       </c>
@@ -32763,7 +32806,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>1218</v>
       </c>
@@ -32863,7 +32906,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>1220</v>
       </c>
@@ -32963,7 +33006,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>1222</v>
       </c>
@@ -33063,7 +33106,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>1224</v>
       </c>
@@ -33163,7 +33206,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>1226</v>
       </c>
@@ -33263,7 +33306,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>1228</v>
       </c>
@@ -33363,7 +33406,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>1230</v>
       </c>
@@ -33463,7 +33506,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>1232</v>
       </c>
@@ -33563,7 +33606,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>1234</v>
       </c>
@@ -33663,7 +33706,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>1236</v>
       </c>
@@ -33763,7 +33806,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>1238</v>
       </c>
@@ -33963,7 +34006,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>1242</v>
       </c>
@@ -34013,7 +34056,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>1243</v>
       </c>
@@ -34063,7 +34106,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>1244</v>
       </c>
@@ -34113,7 +34156,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>1245</v>
       </c>
@@ -34163,7 +34206,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>1246</v>
       </c>
@@ -34213,7 +34256,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>1247</v>
       </c>
@@ -34263,7 +34306,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>1247</v>
       </c>
@@ -34454,7 +34497,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="612" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>1277</v>
       </c>
@@ -38073,7 +38116,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="689" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
         <v>1387</v>
       </c>
@@ -38120,7 +38163,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="690" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
         <v>1388</v>
       </c>
@@ -38167,7 +38210,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="691" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
         <v>1389</v>
       </c>
@@ -38214,7 +38257,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="692" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
         <v>1390</v>
       </c>
@@ -38261,7 +38304,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="693" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
         <v>1391</v>
       </c>
@@ -38308,7 +38351,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="694" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
         <v>1392</v>
       </c>
@@ -38355,7 +38398,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="695" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
         <v>1393</v>
       </c>
@@ -38402,7 +38445,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="696" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
         <v>1394</v>
       </c>
@@ -38449,7 +38492,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="697" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
         <v>1395</v>
       </c>
@@ -38496,7 +38539,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="698" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
         <v>1396</v>
       </c>
@@ -38543,7 +38586,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="699" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
         <v>1397</v>
       </c>
@@ -38590,7 +38633,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="700" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
         <v>1398</v>
       </c>
@@ -38637,7 +38680,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="701" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
         <v>1399</v>
       </c>
@@ -38684,7 +38727,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="702" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
         <v>1400</v>
       </c>
@@ -38731,16 +38774,811 @@
         <v>50</v>
       </c>
     </row>
+    <row r="703" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A703" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B703" s="7" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C703" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D703" s="1">
+        <v>6</v>
+      </c>
+      <c r="E703" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F703" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="G703" s="10">
+        <v>10403881363</v>
+      </c>
+      <c r="H703" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I703" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="J703" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K703" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L703" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="M703" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N703" s="1">
+        <v>1</v>
+      </c>
+      <c r="O703" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P703" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="704" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A704" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B704" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C704" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D704" s="1">
+        <v>7</v>
+      </c>
+      <c r="E704" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F704" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="G704" s="10">
+        <v>10417044227</v>
+      </c>
+      <c r="H704" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I704" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J704" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K704" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L704" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M704" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N704" s="1">
+        <v>1</v>
+      </c>
+      <c r="O704" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P704" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="705" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A705" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B705" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C705" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D705" s="1">
+        <v>7</v>
+      </c>
+      <c r="E705" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F705" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="G705" s="10">
+        <v>10409054086</v>
+      </c>
+      <c r="H705" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="I705" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J705" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K705" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L705" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M705" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N705" s="1">
+        <v>1</v>
+      </c>
+      <c r="O705" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P705" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="706" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A706" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B706" s="7" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C706" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D706" s="1">
+        <v>7</v>
+      </c>
+      <c r="E706" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F706" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="G706" s="10">
+        <v>10239802872</v>
+      </c>
+      <c r="H706" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I706" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J706" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K706" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L706" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M706" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N706" s="1">
+        <v>1</v>
+      </c>
+      <c r="O706" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P706" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="707" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A707" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B707" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C707" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D707" s="1">
+        <v>7</v>
+      </c>
+      <c r="E707" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F707" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="G707" s="10">
+        <v>10239478676</v>
+      </c>
+      <c r="H707" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="I707" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J707" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K707" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L707" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M707" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N707" s="1">
+        <v>1</v>
+      </c>
+      <c r="O707" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P707" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="708" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A708" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B708" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C708" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D708" s="1">
+        <v>7</v>
+      </c>
+      <c r="E708" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F708" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="G708" s="10">
+        <v>10239118211</v>
+      </c>
+      <c r="H708" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I708" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="J708" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K708" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L708" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M708" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N708" s="1">
+        <v>1</v>
+      </c>
+      <c r="O708" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P708" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="709" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A709" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B709" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C709" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D709" s="1">
+        <v>7</v>
+      </c>
+      <c r="E709" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F709" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="G709" s="10">
+        <v>10013070585</v>
+      </c>
+      <c r="H709" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I709" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J709" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K709" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L709" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="M709" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N709" s="1">
+        <v>1</v>
+      </c>
+      <c r="O709" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P709" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="710" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A710" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B710" s="7" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C710" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D710" s="1">
+        <v>7</v>
+      </c>
+      <c r="E710" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F710" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G710" s="10">
+        <v>10404750432</v>
+      </c>
+      <c r="H710" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I710" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J710" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K710" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L710" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="M710" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N710" s="1">
+        <v>1</v>
+      </c>
+      <c r="O710" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P710" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="711" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A711" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B711" s="7" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C711" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D711" s="1">
+        <v>7</v>
+      </c>
+      <c r="E711" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F711" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G711" s="1">
+        <v>10403471645</v>
+      </c>
+      <c r="H711" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I711" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J711" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K711" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L711" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="M711" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N711" s="1">
+        <v>1</v>
+      </c>
+      <c r="O711" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P711" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="712" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A712" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B712" s="8">
+        <v>46216</v>
+      </c>
+      <c r="C712" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D712" s="1">
+        <v>7</v>
+      </c>
+      <c r="E712" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F712" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="G712" s="10">
+        <v>10403478488</v>
+      </c>
+      <c r="H712" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I712" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J712" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K712" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L712" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="M712" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N712" s="1">
+        <v>1</v>
+      </c>
+      <c r="O712" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P712" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="713" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A713" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B713" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C713" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D713" s="1">
+        <v>7</v>
+      </c>
+      <c r="E713" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F713" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G713" s="10">
+        <v>10430636931</v>
+      </c>
+      <c r="H713" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I713" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J713" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K713" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L713" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="M713" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N713" s="1">
+        <v>1</v>
+      </c>
+      <c r="O713" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P713" s="2">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="714" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A714" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B714" s="7" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C714" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D714" s="1">
+        <v>7</v>
+      </c>
+      <c r="E714" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F714" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G714" s="10">
+        <v>10430636931</v>
+      </c>
+      <c r="H714" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I714" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J714" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K714" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L714" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="M714" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N714" s="1">
+        <v>1</v>
+      </c>
+      <c r="O714" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P714" s="2">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="715" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A715" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B715" s="7" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C715" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D715" s="1">
+        <v>7</v>
+      </c>
+      <c r="E715" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F715" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G715" s="10">
+        <v>10401531284</v>
+      </c>
+      <c r="H715" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I715" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J715" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K715" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L715" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="M715" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N715" s="1">
+        <v>1</v>
+      </c>
+      <c r="O715" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P715" s="2">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="716" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A716" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B716" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C716" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D716" s="1">
+        <v>7</v>
+      </c>
+      <c r="E716" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F716" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G716" s="10">
+        <v>10401531284</v>
+      </c>
+      <c r="H716" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I716" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J716" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K716" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L716" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="M716" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N716" s="1">
+        <v>1</v>
+      </c>
+      <c r="O716" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P716" s="2">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="717" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A717" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B717" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C717" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D717" s="1">
+        <v>7</v>
+      </c>
+      <c r="E717" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F717" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G717" s="10">
+        <v>10239223431</v>
+      </c>
+      <c r="H717" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I717" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J717" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K717" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L717" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="M717" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N717" s="1">
+        <v>1</v>
+      </c>
+      <c r="O717" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P717" s="2">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="718" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A718" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B718" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C718" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D718" s="1">
+        <v>7</v>
+      </c>
+      <c r="E718" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F718" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G718" s="10">
+        <v>10239223431</v>
+      </c>
+      <c r="H718" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="I718" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="J718" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K718" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="L718" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="M718" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="N718" s="1">
+        <v>1</v>
+      </c>
+      <c r="O718" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="P718" s="2">
+        <v>4.3</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P702" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
-    <filterColumn colId="3">
+  <autoFilter ref="A1:P712" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
+    <filterColumn colId="4">
       <filters>
-        <filter val="7"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="9">
-      <filters>
-        <filter val="2. Diseño y/o desarrollo de productos"/>
+        <filter val="CdD-FEST"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C444EA68-009E-4A7F-B529-AA5E968D6040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F83D7E-E69B-49D4-98C4-01D1A68F6B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$712</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$718</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4528,7 +4528,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4551,7 +4551,6 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12812,7 +12811,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>911</v>
       </c>
@@ -12862,7 +12861,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>913</v>
       </c>
@@ -12912,7 +12911,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>914</v>
       </c>
@@ -12962,7 +12961,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>915</v>
       </c>
@@ -13012,7 +13011,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>916</v>
       </c>
@@ -13062,7 +13061,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>917</v>
       </c>
@@ -13112,7 +13111,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>918</v>
       </c>
@@ -13162,7 +13161,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>919</v>
       </c>
@@ -13212,7 +13211,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>920</v>
       </c>
@@ -13262,7 +13261,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>921</v>
       </c>
@@ -13312,7 +13311,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>922</v>
       </c>
@@ -13362,7 +13361,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>923</v>
       </c>
@@ -13412,7 +13411,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>924</v>
       </c>
@@ -13462,7 +13461,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>925</v>
       </c>
@@ -13512,7 +13511,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>926</v>
       </c>
@@ -13562,7 +13561,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>927</v>
       </c>
@@ -13612,7 +13611,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>928</v>
       </c>
@@ -13662,7 +13661,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>929</v>
       </c>
@@ -13712,7 +13711,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>930</v>
       </c>
@@ -13762,7 +13761,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>931</v>
       </c>
@@ -13812,7 +13811,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>932</v>
       </c>
@@ -13862,7 +13861,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>933</v>
       </c>
@@ -13912,7 +13911,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>934</v>
       </c>
@@ -13962,7 +13961,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>935</v>
       </c>
@@ -14012,7 +14011,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>936</v>
       </c>
@@ -14062,7 +14061,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>937</v>
       </c>
@@ -14112,7 +14111,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>938</v>
       </c>
@@ -14162,7 +14161,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>939</v>
       </c>
@@ -14212,7 +14211,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>940</v>
       </c>
@@ -14262,7 +14261,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>941</v>
       </c>
@@ -14312,7 +14311,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>942</v>
       </c>
@@ -14362,7 +14361,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>943</v>
       </c>
@@ -14412,7 +14411,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>944</v>
       </c>
@@ -14462,7 +14461,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>945</v>
       </c>
@@ -14512,7 +14511,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>946</v>
       </c>
@@ -14562,7 +14561,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>947</v>
       </c>
@@ -14612,7 +14611,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>948</v>
       </c>
@@ -14662,7 +14661,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>949</v>
       </c>
@@ -14712,7 +14711,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>950</v>
       </c>
@@ -14762,7 +14761,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>951</v>
       </c>
@@ -14812,7 +14811,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>952</v>
       </c>
@@ -14862,7 +14861,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>953</v>
       </c>
@@ -14912,7 +14911,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>954</v>
       </c>
@@ -14962,7 +14961,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>955</v>
       </c>
@@ -15012,7 +15011,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>956</v>
       </c>
@@ -15062,7 +15061,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>957</v>
       </c>
@@ -15112,7 +15111,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>958</v>
       </c>
@@ -15162,7 +15161,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>959</v>
       </c>
@@ -15212,7 +15211,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>960</v>
       </c>
@@ -15262,7 +15261,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>961</v>
       </c>
@@ -15312,7 +15311,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>962</v>
       </c>
@@ -15362,7 +15361,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>963</v>
       </c>
@@ -15412,7 +15411,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>964</v>
       </c>
@@ -15462,7 +15461,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>965</v>
       </c>
@@ -15512,7 +15511,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>966</v>
       </c>
@@ -15562,7 +15561,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>967</v>
       </c>
@@ -15612,7 +15611,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>968</v>
       </c>
@@ -17025,7 +17024,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>969</v>
       </c>
@@ -17075,7 +17074,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>970</v>
       </c>
@@ -17125,7 +17124,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>971</v>
       </c>
@@ -17175,7 +17174,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>972</v>
       </c>
@@ -17225,7 +17224,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>973</v>
       </c>
@@ -17275,7 +17274,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>974</v>
       </c>
@@ -17325,7 +17324,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>975</v>
       </c>
@@ -17375,7 +17374,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>976</v>
       </c>
@@ -17425,7 +17424,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>977</v>
       </c>
@@ -17475,7 +17474,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>978</v>
       </c>
@@ -17525,7 +17524,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>979</v>
       </c>
@@ -17575,7 +17574,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>980</v>
       </c>
@@ -17625,7 +17624,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>981</v>
       </c>
@@ -17675,7 +17674,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>982</v>
       </c>
@@ -17725,7 +17724,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>983</v>
       </c>
@@ -17775,7 +17774,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>984</v>
       </c>
@@ -17825,7 +17824,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>985</v>
       </c>
@@ -17875,7 +17874,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>986</v>
       </c>
@@ -17925,7 +17924,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>987</v>
       </c>
@@ -17975,7 +17974,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>988</v>
       </c>
@@ -18025,7 +18024,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>989</v>
       </c>
@@ -18075,7 +18074,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>990</v>
       </c>
@@ -18125,7 +18124,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>991</v>
       </c>
@@ -18175,7 +18174,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>992</v>
       </c>
@@ -18225,7 +18224,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>993</v>
       </c>
@@ -18275,7 +18274,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>994</v>
       </c>
@@ -18325,7 +18324,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>995</v>
       </c>
@@ -18425,7 +18424,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>997</v>
       </c>
@@ -18475,7 +18474,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>998</v>
       </c>
@@ -18525,7 +18524,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>999</v>
       </c>
@@ -18575,7 +18574,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>1000</v>
       </c>
@@ -18625,7 +18624,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>1001</v>
       </c>
@@ -18675,7 +18674,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>1002</v>
       </c>
@@ -18725,7 +18724,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>1003</v>
       </c>
@@ -18825,7 +18824,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>1005</v>
       </c>
@@ -18875,7 +18874,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>1006</v>
       </c>
@@ -18925,7 +18924,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>1007</v>
       </c>
@@ -18975,7 +18974,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>1008</v>
       </c>
@@ -19025,7 +19024,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>1009</v>
       </c>
@@ -19075,7 +19074,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>1010</v>
       </c>
@@ -19125,7 +19124,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>1011</v>
       </c>
@@ -19645,7 +19644,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>1012</v>
       </c>
@@ -19695,7 +19694,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>1013</v>
       </c>
@@ -19745,7 +19744,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>1014</v>
       </c>
@@ -19795,7 +19794,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>1015</v>
       </c>
@@ -19845,7 +19844,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>1016</v>
       </c>
@@ -19895,7 +19894,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1017</v>
       </c>
@@ -19945,7 +19944,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1018</v>
       </c>
@@ -19995,7 +19994,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>1019</v>
       </c>
@@ -20045,7 +20044,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>1020</v>
       </c>
@@ -20095,7 +20094,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1021</v>
       </c>
@@ -20145,7 +20144,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>1022</v>
       </c>
@@ -20245,7 +20244,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>1024</v>
       </c>
@@ -20295,7 +20294,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>1025</v>
       </c>
@@ -20345,7 +20344,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>1026</v>
       </c>
@@ -20395,7 +20394,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>1027</v>
       </c>
@@ -20495,7 +20494,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>1029</v>
       </c>
@@ -20545,7 +20544,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1030</v>
       </c>
@@ -20595,7 +20594,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>1031</v>
       </c>
@@ -20695,7 +20694,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>1033</v>
       </c>
@@ -20745,7 +20744,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>1034</v>
       </c>
@@ -20795,7 +20794,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>1035</v>
       </c>
@@ -20845,7 +20844,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>1036</v>
       </c>
@@ -20895,7 +20894,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>1037</v>
       </c>
@@ -20945,7 +20944,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>1038</v>
       </c>
@@ -20995,7 +20994,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>1039</v>
       </c>
@@ -21012,7 +21011,7 @@
         <v>195</v>
       </c>
       <c r="F335" s="1" t="s">
-        <v>565</v>
+        <v>1140</v>
       </c>
       <c r="G335" s="1">
         <v>10238589458</v>
@@ -21045,7 +21044,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>1040</v>
       </c>
@@ -21095,7 +21094,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>1041</v>
       </c>
@@ -21145,7 +21144,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>1042</v>
       </c>
@@ -21195,7 +21194,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>1043</v>
       </c>
@@ -21245,7 +21244,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>1044</v>
       </c>
@@ -21295,7 +21294,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>1045</v>
       </c>
@@ -21345,7 +21344,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>1046</v>
       </c>
@@ -21395,7 +21394,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1047</v>
       </c>
@@ -21445,7 +21444,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1048</v>
       </c>
@@ -21495,7 +21494,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>1049</v>
       </c>
@@ -21545,7 +21544,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>1050</v>
       </c>
@@ -21595,7 +21594,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1051</v>
       </c>
@@ -21645,7 +21644,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>1052</v>
       </c>
@@ -21695,7 +21694,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>1053</v>
       </c>
@@ -21745,7 +21744,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>1054</v>
       </c>
@@ -21795,7 +21794,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>1055</v>
       </c>
@@ -21845,7 +21844,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>1056</v>
       </c>
@@ -21895,7 +21894,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>1057</v>
       </c>
@@ -21945,7 +21944,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>1058</v>
       </c>
@@ -21995,7 +21994,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>1059</v>
       </c>
@@ -22045,7 +22044,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>1060</v>
       </c>
@@ -22095,7 +22094,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>1061</v>
       </c>
@@ -22145,7 +22144,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>1062</v>
       </c>
@@ -22195,7 +22194,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>1063</v>
       </c>
@@ -22245,7 +22244,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>1064</v>
       </c>
@@ -22295,7 +22294,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>1065</v>
       </c>
@@ -22345,7 +22344,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1066</v>
       </c>
@@ -22395,7 +22394,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1067</v>
       </c>
@@ -22445,7 +22444,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>1068</v>
       </c>
@@ -22495,7 +22494,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>1069</v>
       </c>
@@ -22545,7 +22544,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1070</v>
       </c>
@@ -22595,7 +22594,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1071</v>
       </c>
@@ -22645,7 +22644,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>1072</v>
       </c>
@@ -22695,7 +22694,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1073</v>
       </c>
@@ -22745,7 +22744,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1074</v>
       </c>
@@ -22795,7 +22794,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>1075</v>
       </c>
@@ -22845,7 +22844,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1076</v>
       </c>
@@ -22895,7 +22894,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1077</v>
       </c>
@@ -22945,7 +22944,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1078</v>
       </c>
@@ -22995,7 +22994,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>1079</v>
       </c>
@@ -23045,7 +23044,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>1080</v>
       </c>
@@ -23095,7 +23094,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1081</v>
       </c>
@@ -23195,7 +23194,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>1083</v>
       </c>
@@ -23245,7 +23244,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1084</v>
       </c>
@@ -23295,7 +23294,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1085</v>
       </c>
@@ -23345,7 +23344,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1086</v>
       </c>
@@ -23395,7 +23394,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1087</v>
       </c>
@@ -23445,7 +23444,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1088</v>
       </c>
@@ -23495,7 +23494,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>1089</v>
       </c>
@@ -23545,7 +23544,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1090</v>
       </c>
@@ -23595,7 +23594,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1091</v>
       </c>
@@ -23645,7 +23644,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1092</v>
       </c>
@@ -23695,7 +23694,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1093</v>
       </c>
@@ -23745,7 +23744,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1094</v>
       </c>
@@ -23795,7 +23794,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1095</v>
       </c>
@@ -23845,7 +23844,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1096</v>
       </c>
@@ -23895,7 +23894,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1097</v>
       </c>
@@ -23945,7 +23944,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1098</v>
       </c>
@@ -23995,7 +23994,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1099</v>
       </c>
@@ -24045,7 +24044,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1100</v>
       </c>
@@ -24095,7 +24094,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1101</v>
       </c>
@@ -24145,7 +24144,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1102</v>
       </c>
@@ -24195,7 +24194,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1103</v>
       </c>
@@ -24245,7 +24244,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1104</v>
       </c>
@@ -24295,7 +24294,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1105</v>
       </c>
@@ -24345,7 +24344,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1106</v>
       </c>
@@ -24395,7 +24394,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1107</v>
       </c>
@@ -24445,7 +24444,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1108</v>
       </c>
@@ -24495,7 +24494,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1109</v>
       </c>
@@ -24545,7 +24544,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1110</v>
       </c>
@@ -24595,7 +24594,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1111</v>
       </c>
@@ -24645,7 +24644,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1112</v>
       </c>
@@ -24695,7 +24694,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>1113</v>
       </c>
@@ -24745,7 +24744,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1114</v>
       </c>
@@ -24795,7 +24794,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1115</v>
       </c>
@@ -24845,7 +24844,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1116</v>
       </c>
@@ -24895,7 +24894,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1117</v>
       </c>
@@ -24945,7 +24944,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1118</v>
       </c>
@@ -24995,7 +24994,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1119</v>
       </c>
@@ -25045,7 +25044,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1120</v>
       </c>
@@ -25095,7 +25094,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1121</v>
       </c>
@@ -25145,7 +25144,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1122</v>
       </c>
@@ -25195,7 +25194,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1123</v>
       </c>
@@ -25245,7 +25244,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1124</v>
       </c>
@@ -25295,7 +25294,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1125</v>
       </c>
@@ -25345,7 +25344,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1126</v>
       </c>
@@ -25395,7 +25394,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1127</v>
       </c>
@@ -25445,7 +25444,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1128</v>
       </c>
@@ -25495,7 +25494,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1129</v>
       </c>
@@ -25545,7 +25544,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>1130</v>
       </c>
@@ -25595,7 +25594,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1131</v>
       </c>
@@ -25645,7 +25644,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1132</v>
       </c>
@@ -25695,7 +25694,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1151</v>
       </c>
@@ -25745,7 +25744,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1152</v>
       </c>
@@ -25795,7 +25794,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>1153</v>
       </c>
@@ -25845,7 +25844,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>1154</v>
       </c>
@@ -25895,7 +25894,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>1155</v>
       </c>
@@ -25945,7 +25944,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>1156</v>
       </c>
@@ -25995,7 +25994,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>1157</v>
       </c>
@@ -26045,7 +26044,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>1158</v>
       </c>
@@ -26095,7 +26094,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>1159</v>
       </c>
@@ -26145,7 +26144,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="438" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>1160</v>
       </c>
@@ -26195,7 +26194,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>1161</v>
       </c>
@@ -26245,7 +26244,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="440" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>1162</v>
       </c>
@@ -26295,7 +26294,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>1163</v>
       </c>
@@ -26312,7 +26311,7 @@
         <v>195</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>1140</v>
+        <v>564</v>
       </c>
       <c r="G441" s="1">
         <v>10238698362</v>
@@ -26345,7 +26344,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>1164</v>
       </c>
@@ -26362,7 +26361,7 @@
         <v>195</v>
       </c>
       <c r="F442" s="1" t="s">
-        <v>1140</v>
+        <v>564</v>
       </c>
       <c r="G442" s="1">
         <v>10238698362</v>
@@ -26395,7 +26394,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>1165</v>
       </c>
@@ -26412,7 +26411,7 @@
         <v>195</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>1140</v>
+        <v>564</v>
       </c>
       <c r="G443" s="1">
         <v>10409054086</v>
@@ -26445,7 +26444,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>1166</v>
       </c>
@@ -26462,7 +26461,7 @@
         <v>195</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>1140</v>
+        <v>564</v>
       </c>
       <c r="G444" s="1">
         <v>10409054086</v>
@@ -26495,7 +26494,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>1167</v>
       </c>
@@ -31656,7 +31655,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>1195</v>
       </c>
@@ -31706,7 +31705,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>1196</v>
       </c>
@@ -31756,7 +31755,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="557" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>1197</v>
       </c>
@@ -31806,7 +31805,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>1198</v>
       </c>
@@ -31856,7 +31855,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="559" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>1199</v>
       </c>
@@ -31906,7 +31905,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="560" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>1200</v>
       </c>
@@ -31956,7 +31955,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>1201</v>
       </c>
@@ -32006,7 +32005,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>1202</v>
       </c>
@@ -32056,7 +32055,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>1203</v>
       </c>
@@ -32106,7 +32105,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>1204</v>
       </c>
@@ -32156,7 +32155,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>1205</v>
       </c>
@@ -32206,7 +32205,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>1206</v>
       </c>
@@ -32256,7 +32255,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>1207</v>
       </c>
@@ -32306,7 +32305,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>1208</v>
       </c>
@@ -32356,7 +32355,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>1209</v>
       </c>
@@ -32406,7 +32405,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>1210</v>
       </c>
@@ -32456,7 +32455,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>1211</v>
       </c>
@@ -32506,7 +32505,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>1212</v>
       </c>
@@ -32556,7 +32555,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>1213</v>
       </c>
@@ -32606,7 +32605,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>1214</v>
       </c>
@@ -32656,7 +32655,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>1215</v>
       </c>
@@ -32706,7 +32705,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>1216</v>
       </c>
@@ -32756,7 +32755,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>1217</v>
       </c>
@@ -32806,7 +32805,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>1218</v>
       </c>
@@ -32856,7 +32855,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>1219</v>
       </c>
@@ -32906,7 +32905,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>1220</v>
       </c>
@@ -32956,7 +32955,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="581" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>1221</v>
       </c>
@@ -33006,7 +33005,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>1222</v>
       </c>
@@ -33056,7 +33055,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="583" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>1223</v>
       </c>
@@ -33106,7 +33105,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>1224</v>
       </c>
@@ -33156,7 +33155,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>1225</v>
       </c>
@@ -33206,7 +33205,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>1226</v>
       </c>
@@ -33256,7 +33255,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>1227</v>
       </c>
@@ -33306,7 +33305,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>1228</v>
       </c>
@@ -33356,7 +33355,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>1229</v>
       </c>
@@ -33406,7 +33405,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>1230</v>
       </c>
@@ -33456,7 +33455,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="591" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>1231</v>
       </c>
@@ -33506,7 +33505,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>1232</v>
       </c>
@@ -33556,7 +33555,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>1233</v>
       </c>
@@ -33606,7 +33605,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="594" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>1234</v>
       </c>
@@ -33656,7 +33655,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="595" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>1235</v>
       </c>
@@ -33706,7 +33705,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="596" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>1236</v>
       </c>
@@ -33756,7 +33755,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="597" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>1237</v>
       </c>
@@ -33806,7 +33805,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="598" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>1238</v>
       </c>
@@ -33856,7 +33855,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="599" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>1239</v>
       </c>
@@ -33906,7 +33905,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="600" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>1240</v>
       </c>
@@ -33956,7 +33955,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="601" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>1241</v>
       </c>
@@ -34006,7 +34005,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="602" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>1242</v>
       </c>
@@ -34056,7 +34055,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="603" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>1243</v>
       </c>
@@ -34106,7 +34105,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="604" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>1244</v>
       </c>
@@ -34156,7 +34155,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="605" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>1245</v>
       </c>
@@ -34206,7 +34205,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="606" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>1246</v>
       </c>
@@ -34256,7 +34255,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="607" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>1247</v>
       </c>
@@ -34306,7 +34305,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="608" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>1247</v>
       </c>
@@ -38774,7 +38773,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="703" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
         <v>1430</v>
       </c>
@@ -38793,7 +38792,7 @@
       <c r="F703" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G703" s="10">
+      <c r="G703" s="1">
         <v>10403881363</v>
       </c>
       <c r="H703" s="1" t="s">
@@ -38824,7 +38823,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="704" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
         <v>1431</v>
       </c>
@@ -38843,7 +38842,7 @@
       <c r="F704" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G704" s="10">
+      <c r="G704" s="1">
         <v>10417044227</v>
       </c>
       <c r="H704" s="1" t="s">
@@ -38874,7 +38873,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="705" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
         <v>1432</v>
       </c>
@@ -38893,7 +38892,7 @@
       <c r="F705" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G705" s="10">
+      <c r="G705" s="1">
         <v>10409054086</v>
       </c>
       <c r="H705" s="1" t="s">
@@ -38924,7 +38923,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="706" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
         <v>1433</v>
       </c>
@@ -38943,7 +38942,7 @@
       <c r="F706" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G706" s="10">
+      <c r="G706" s="1">
         <v>10239802872</v>
       </c>
       <c r="H706" s="1" t="s">
@@ -38974,7 +38973,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="707" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
         <v>1434</v>
       </c>
@@ -38993,7 +38992,7 @@
       <c r="F707" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G707" s="10">
+      <c r="G707" s="1">
         <v>10239478676</v>
       </c>
       <c r="H707" s="1" t="s">
@@ -39024,7 +39023,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="708" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
         <v>1435</v>
       </c>
@@ -39043,7 +39042,7 @@
       <c r="F708" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G708" s="10">
+      <c r="G708" s="1">
         <v>10239118211</v>
       </c>
       <c r="H708" s="1" t="s">
@@ -39074,7 +39073,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="709" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
         <v>1436</v>
       </c>
@@ -39093,7 +39092,7 @@
       <c r="F709" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="G709" s="10">
+      <c r="G709" s="1">
         <v>10013070585</v>
       </c>
       <c r="H709" s="1" t="s">
@@ -39143,7 +39142,7 @@
       <c r="F710" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="G710" s="10">
+      <c r="G710" s="1">
         <v>10404750432</v>
       </c>
       <c r="H710" s="1" t="s">
@@ -39243,7 +39242,7 @@
       <c r="F712" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="G712" s="10">
+      <c r="G712" s="1">
         <v>10403478488</v>
       </c>
       <c r="H712" s="1" t="s">
@@ -39274,7 +39273,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="713" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
         <v>1440</v>
       </c>
@@ -39293,7 +39292,7 @@
       <c r="F713" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="G713" s="10">
+      <c r="G713" s="1">
         <v>10430636931</v>
       </c>
       <c r="H713" s="1" t="s">
@@ -39324,7 +39323,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="714" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
         <v>1440</v>
       </c>
@@ -39343,7 +39342,7 @@
       <c r="F714" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="G714" s="10">
+      <c r="G714" s="1">
         <v>10430636931</v>
       </c>
       <c r="H714" s="1" t="s">
@@ -39374,7 +39373,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="715" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
         <v>1440</v>
       </c>
@@ -39393,7 +39392,7 @@
       <c r="F715" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="G715" s="10">
+      <c r="G715" s="1">
         <v>10401531284</v>
       </c>
       <c r="H715" s="1" t="s">
@@ -39424,7 +39423,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="716" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
         <v>1440</v>
       </c>
@@ -39443,7 +39442,7 @@
       <c r="F716" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="G716" s="10">
+      <c r="G716" s="1">
         <v>10401531284</v>
       </c>
       <c r="H716" s="1" t="s">
@@ -39474,7 +39473,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="717" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
         <v>1440</v>
       </c>
@@ -39493,7 +39492,7 @@
       <c r="F717" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="G717" s="10">
+      <c r="G717" s="1">
         <v>10239223431</v>
       </c>
       <c r="H717" s="1" t="s">
@@ -39524,7 +39523,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="718" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
         <v>1440</v>
       </c>
@@ -39543,7 +39542,7 @@
       <c r="F718" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="G718" s="10">
+      <c r="G718" s="1">
         <v>10239223431</v>
       </c>
       <c r="H718" s="1" t="s">
@@ -39575,10 +39574,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P712" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
+  <autoFilter ref="A1:P718" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
     <filterColumn colId="4">
       <filters>
         <filter val="CdD-FEST"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="15">
+      <filters>
+        <filter val="5.1"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{648FBB4C-B2AF-4BF9-8556-53750E4AECD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDB6A13-2D32-4AE2-913E-344ABE34E997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13101,10 +13101,10 @@
         <v>575</v>
       </c>
       <c r="G174" s="1">
-        <v>10247060931</v>
+        <v>10240067566</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>201</v>
+        <v>136</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>515</v>
@@ -13154,7 +13154,7 @@
         <v>10478372073</v>
       </c>
       <c r="H175" s="1" t="s">
-        <v>136</v>
+        <v>201</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>515</v>
@@ -14251,7 +14251,7 @@
         <v>575</v>
       </c>
       <c r="G197" s="1">
-        <v>10240067566</v>
+        <v>10247060931</v>
       </c>
       <c r="H197" s="1" t="s">
         <v>213</v>
@@ -21384,7 +21384,7 @@
         <v>824</v>
       </c>
       <c r="G342" s="1">
-        <v>10478372073</v>
+        <v>10240067566</v>
       </c>
       <c r="H342" s="1" t="s">
         <v>136</v>
@@ -22084,7 +22084,7 @@
         <v>576</v>
       </c>
       <c r="G356" s="1">
-        <v>10478372073</v>
+        <v>10240067566</v>
       </c>
       <c r="H356" s="1" t="s">
         <v>136</v>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDB6A13-2D32-4AE2-913E-344ABE34E997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACA6770-532E-44F5-BF45-CAB1BFAFC10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,6 +43,7 @@
     <author>tc={CE24220F-9884-4515-949C-9773C2AB6CD7}</author>
     <author>tc={CC2010E8-F445-4468-8B38-512A71CE0E30}</author>
     <author>tc={8D189750-CB69-4720-9438-68E8E26098F2}</author>
+    <author>tc={1FED0FA3-1881-4474-876E-0AE471879AA2}</author>
   </authors>
   <commentList>
     <comment ref="B27" authorId="0" shapeId="0" xr:uid="{388AD7C4-BD45-408C-9C25-D76BA7C147BF}">
@@ -101,12 +102,20 @@
     01/07/2026</t>
       </text>
     </comment>
+    <comment ref="A719" authorId="7" shapeId="0" xr:uid="{1FED0FA3-1881-4474-876E-0AE471879AA2}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    No se refleja en el archivo de DESE</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7889" uniqueCount="1451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7899" uniqueCount="1453">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -4459,13 +4468,19 @@
   </si>
   <si>
     <t>C000717</t>
+  </si>
+  <si>
+    <t>Desarrollo de un bioplaguicida microencapsulado de liberación controlada mediante la valorización de merma de fibra de alpaca para el control del gusano cogollero (Spodoptera frugiperda) en el cultivo de maíz del distrito de Taray, Cusco.</t>
+  </si>
+  <si>
+    <t>C000718</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4524,6 +4539,11 @@
       <color theme="9" tint="-0.249977111117893"/>
       <name val="Aptos Display"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4906,12 +4926,15 @@
   <threadedComment ref="B521" dT="2026-08-04T22:28:59.52" personId="{4AFC30EF-3D5B-4D86-B079-7855968373AE}" id="{8D189750-CB69-4720-9438-68E8E26098F2}">
     <text>01/07/2026</text>
   </threadedComment>
+  <threadedComment ref="A719" dT="2026-08-25T17:21:34.22" personId="{4AFC30EF-3D5B-4D86-B079-7855968373AE}" id="{1FED0FA3-1881-4474-876E-0AE471879AA2}">
+    <text>No se refleja en el archivo de DESE</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
-  <dimension ref="A1:P718"/>
+  <dimension ref="A1:P719"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -39593,6 +39616,53 @@
         <v>50</v>
       </c>
     </row>
+    <row r="719" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A719" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B719" s="8">
+        <v>46225</v>
+      </c>
+      <c r="C719" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D719" s="1">
+        <v>7</v>
+      </c>
+      <c r="E719" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F719" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G719" s="1">
+        <v>20172474501</v>
+      </c>
+      <c r="H719" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="I719" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="J719" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K719" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="L719" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="M719" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="N719" s="1">
+        <v>1</v>
+      </c>
+      <c r="O719" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P718">
     <sortCondition ref="D1:D718"/>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACA6770-532E-44F5-BF45-CAB1BFAFC10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E64F64E-0B73-4B3E-93DD-125CEB9263FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7899" uniqueCount="1453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8611" uniqueCount="1594">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -4474,13 +4474,436 @@
   </si>
   <si>
     <t>C000718</t>
+  </si>
+  <si>
+    <t>CARAZAS PEREIRA GRIMALDINA</t>
+  </si>
+  <si>
+    <t>Grabado laser</t>
+  </si>
+  <si>
+    <t>diseño de productos en tejido de punto con fibra de alpaca , acorde a la demnada actual con enfoque en sostenibilidad</t>
+  </si>
+  <si>
+    <t>Diseño y modelaje de productos textiles con enfoque en Economia circular</t>
+  </si>
+  <si>
+    <t>Diseño y modelaje de productos textiles en fibra de alpaca con enfoque de Economia Circular</t>
+  </si>
+  <si>
+    <t>Diseño de Logotipos</t>
+  </si>
+  <si>
+    <t>C000719</t>
+  </si>
+  <si>
+    <t>C000720</t>
+  </si>
+  <si>
+    <t>C000721</t>
+  </si>
+  <si>
+    <t>C000722</t>
+  </si>
+  <si>
+    <t>C000723</t>
+  </si>
+  <si>
+    <t>03/08/2026</t>
+  </si>
+  <si>
+    <t>07/08/2026</t>
+  </si>
+  <si>
+    <t>Calculadora de la Circularidad</t>
+  </si>
+  <si>
+    <t>Calculadora de la Circuladora</t>
+  </si>
+  <si>
+    <t>Aprovechamiento de recursos textiles para generar productos exportables</t>
+  </si>
+  <si>
+    <t>ECONOMIA CIRCULAR COMO ESTRATEGIA DE COMPETITIVIDAD PARA LA EXPORTACION</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Aprovechamiento eficiente de las materias primas en la produccion</t>
+  </si>
+  <si>
+    <t>C000724</t>
+  </si>
+  <si>
+    <t>C000725</t>
+  </si>
+  <si>
+    <t>C000726</t>
+  </si>
+  <si>
+    <t>C000727</t>
+  </si>
+  <si>
+    <t>C000728</t>
+  </si>
+  <si>
+    <t>C000729</t>
+  </si>
+  <si>
+    <t>12/08/2026</t>
+  </si>
+  <si>
+    <t>11/08/2026</t>
+  </si>
+  <si>
+    <t>04/08/2026</t>
+  </si>
+  <si>
+    <t>24/08/2026</t>
+  </si>
+  <si>
+    <t>23/08/2026</t>
+  </si>
+  <si>
+    <t>CAPACITACION ESPECIALIZADA EN PRODUCCION SOSTENIBLE Y ECONOMIA CIRCULAR PARA LA EXPORTACION IV</t>
+  </si>
+  <si>
+    <t>CAPACITACION ESPECIALIZADA EN PRODUCCION SOSTENIBLE Y ECONOMIA CIRCULAR PARA LA EXPORTACION - ESPINAR</t>
+  </si>
+  <si>
+    <t>ECONOMÍA CIRCULAR COMO ESTRATEGIA DE FORMALIZACIÓN Y GESTIÓN EMPRESARIAL PARA LA EXPORTACIÓN (OCCOPATA)</t>
+  </si>
+  <si>
+    <t>QUISPE BEJAR JUSTINA</t>
+  </si>
+  <si>
+    <t>CONDORI CUITO MARCIA</t>
+  </si>
+  <si>
+    <t>HUALLPAYUNCA CARAZAS LOURDES LISBETH</t>
+  </si>
+  <si>
+    <t>LUPO DE PAUCAR SEBASTIANA MERCEDES</t>
+  </si>
+  <si>
+    <t>PEÑALOZA DE GAMARRA LIDIA MARINA</t>
+  </si>
+  <si>
+    <t>QUISPE ORUE MARILU</t>
+  </si>
+  <si>
+    <t>QUISPE CONDO VIRGINIA</t>
+  </si>
+  <si>
+    <t>PAUCAR RODRIGUEZ CRISTINA</t>
+  </si>
+  <si>
+    <t>QUISPE BEJAR CARMELA</t>
+  </si>
+  <si>
+    <t>TURPO YUCRA RENALDO</t>
+  </si>
+  <si>
+    <t>ACROTA OROSCO JUAN CANCIO</t>
+  </si>
+  <si>
+    <t>GUILLEN FERRO EULALIA</t>
+  </si>
+  <si>
+    <t>HERRERA QUISPE MARGOT</t>
+  </si>
+  <si>
+    <t>FLORES SUYO ROXANA</t>
+  </si>
+  <si>
+    <t>SICOS ALMANZA JAVIER WUALTER</t>
+  </si>
+  <si>
+    <t>SOTO MENDOZA APOLINAR</t>
+  </si>
+  <si>
+    <t>PILARES CCANCHI CASIANO</t>
+  </si>
+  <si>
+    <t>PRIETO GONGORA GINO JOHN</t>
+  </si>
+  <si>
+    <t>FARFAN QUISPE CARMEN ELENA</t>
+  </si>
+  <si>
+    <t>VELASQUEZ TACURI THALIA FRESSIA</t>
+  </si>
+  <si>
+    <t>PRIETO ANGULO DIMAS</t>
+  </si>
+  <si>
+    <t>CCALLA PARICAHUA NELLY</t>
+  </si>
+  <si>
+    <t>CASTILLO VEGA RAQUEL FRANCISCA</t>
+  </si>
+  <si>
+    <t>BALDERRAMA SICOS SONIA</t>
+  </si>
+  <si>
+    <t>PANOCCA MERMA CLAUDIO ZENOBIO</t>
+  </si>
+  <si>
+    <t>POCCORI PUMA WILLIAN</t>
+  </si>
+  <si>
+    <t>MINA QUISPE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>SUMIRE SILVA VIRGINIA MYRIAN</t>
+  </si>
+  <si>
+    <t>TAPIA LLANTA FLORA</t>
+  </si>
+  <si>
+    <t>CORDOVA SAICO EUFEMIA</t>
+  </si>
+  <si>
+    <t>SAICO CORDOVA RINA</t>
+  </si>
+  <si>
+    <t>SALAZAR ARIAS JENNIFER</t>
+  </si>
+  <si>
+    <t>SECCA QUISPE RUBEN</t>
+  </si>
+  <si>
+    <t>SECCA QUISPE SANTOS</t>
+  </si>
+  <si>
+    <t>SECCA QUISPE NANCY</t>
+  </si>
+  <si>
+    <t>CABEZA CHECCA YSABEL</t>
+  </si>
+  <si>
+    <t>SECCA QUISPE FLORA</t>
+  </si>
+  <si>
+    <t>QUISPE ARIAS FABIANA</t>
+  </si>
+  <si>
+    <t>HUILLCA RAMOS LEONARDO</t>
+  </si>
+  <si>
+    <t>ARIAS CHECCA LIZ ANTONIETA</t>
+  </si>
+  <si>
+    <t>NOA NOA VILMA</t>
+  </si>
+  <si>
+    <t>SALAZAR ARIAS ALEXANDRA</t>
+  </si>
+  <si>
+    <t>NOA ARIAS HAYDEE</t>
+  </si>
+  <si>
+    <t>SECCA QUISPE RICARDINA</t>
+  </si>
+  <si>
+    <t>SECCA QUISPE MARLENY</t>
+  </si>
+  <si>
+    <t>CABEZA CHECCA ROSA MARIA</t>
+  </si>
+  <si>
+    <t>ARIAS CHECCA GISELA</t>
+  </si>
+  <si>
+    <t>C000730</t>
+  </si>
+  <si>
+    <t>C000731</t>
+  </si>
+  <si>
+    <t>C000732</t>
+  </si>
+  <si>
+    <t>C000733</t>
+  </si>
+  <si>
+    <t>C000734</t>
+  </si>
+  <si>
+    <t>C000735</t>
+  </si>
+  <si>
+    <t>C000736</t>
+  </si>
+  <si>
+    <t>C000737</t>
+  </si>
+  <si>
+    <t>C000738</t>
+  </si>
+  <si>
+    <t>C000739</t>
+  </si>
+  <si>
+    <t>C000740</t>
+  </si>
+  <si>
+    <t>C000741</t>
+  </si>
+  <si>
+    <t>C000742</t>
+  </si>
+  <si>
+    <t>C000743</t>
+  </si>
+  <si>
+    <t>C000744</t>
+  </si>
+  <si>
+    <t>C000745</t>
+  </si>
+  <si>
+    <t>C000746</t>
+  </si>
+  <si>
+    <t>C000747</t>
+  </si>
+  <si>
+    <t>C000748</t>
+  </si>
+  <si>
+    <t>C000749</t>
+  </si>
+  <si>
+    <t>C000750</t>
+  </si>
+  <si>
+    <t>C000751</t>
+  </si>
+  <si>
+    <t>C000752</t>
+  </si>
+  <si>
+    <t>C000753</t>
+  </si>
+  <si>
+    <t>C000754</t>
+  </si>
+  <si>
+    <t>C000755</t>
+  </si>
+  <si>
+    <t>C000756</t>
+  </si>
+  <si>
+    <t>C000757</t>
+  </si>
+  <si>
+    <t>C000758</t>
+  </si>
+  <si>
+    <t>C000759</t>
+  </si>
+  <si>
+    <t>C000760</t>
+  </si>
+  <si>
+    <t>C000761</t>
+  </si>
+  <si>
+    <t>C000762</t>
+  </si>
+  <si>
+    <t>C000763</t>
+  </si>
+  <si>
+    <t>C000764</t>
+  </si>
+  <si>
+    <t>C000765</t>
+  </si>
+  <si>
+    <t>C000766</t>
+  </si>
+  <si>
+    <t>C000767</t>
+  </si>
+  <si>
+    <t>C000768</t>
+  </si>
+  <si>
+    <t>C000769</t>
+  </si>
+  <si>
+    <t>C000770</t>
+  </si>
+  <si>
+    <t>C000771</t>
+  </si>
+  <si>
+    <t>C000772</t>
+  </si>
+  <si>
+    <t>C000773</t>
+  </si>
+  <si>
+    <t>C000774</t>
+  </si>
+  <si>
+    <t>C000775</t>
+  </si>
+  <si>
+    <t>C000776</t>
+  </si>
+  <si>
+    <t>C000777</t>
+  </si>
+  <si>
+    <t>C000778</t>
+  </si>
+  <si>
+    <t>C000779</t>
+  </si>
+  <si>
+    <t>C000780</t>
+  </si>
+  <si>
+    <t>C000781</t>
+  </si>
+  <si>
+    <t>C000782</t>
+  </si>
+  <si>
+    <t>C000783</t>
+  </si>
+  <si>
+    <t>C000784</t>
+  </si>
+  <si>
+    <t>C000785</t>
+  </si>
+  <si>
+    <t>C000786</t>
+  </si>
+  <si>
+    <t>C000787</t>
+  </si>
+  <si>
+    <t>C000788</t>
+  </si>
+  <si>
+    <t>C000789</t>
+  </si>
+  <si>
+    <t>25/08/2026</t>
+  </si>
+  <si>
+    <t>18/08/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4540,11 +4963,6 @@
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -4569,7 +4987,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4592,6 +5010,7 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4934,7 +5353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
-  <dimension ref="A1:P719"/>
+  <dimension ref="A1:P790"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -39663,6 +40082,3136 @@
         <v>529</v>
       </c>
     </row>
+    <row r="720" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A720" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B720" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C720" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D720" s="1">
+        <v>8</v>
+      </c>
+      <c r="E720" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F720" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G720" s="10">
+        <v>10239470209</v>
+      </c>
+      <c r="H720" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I720" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="J720" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K720" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="L720" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="M720" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N720" s="1">
+        <v>10</v>
+      </c>
+      <c r="O720" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="721" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A721" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B721" s="7" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C721" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D721" s="1">
+        <v>8</v>
+      </c>
+      <c r="E721" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F721" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="G721" s="10">
+        <v>24867908</v>
+      </c>
+      <c r="H721" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J721" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K721" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L721" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="M721" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N721" s="1">
+        <v>3</v>
+      </c>
+      <c r="O721" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="722" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A722" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B722" s="7" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C722" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D722" s="1">
+        <v>8</v>
+      </c>
+      <c r="E722" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F722" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="G722" s="10">
+        <v>23980287</v>
+      </c>
+      <c r="H722" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J722" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K722" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L722" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="M722" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N722" s="1">
+        <v>3</v>
+      </c>
+      <c r="O722" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="723" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A723" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B723" s="7" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C723" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D723" s="1">
+        <v>8</v>
+      </c>
+      <c r="E723" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F723" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="G723" s="10">
+        <v>40388136</v>
+      </c>
+      <c r="H723" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="J723" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K723" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L723" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="M723" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N723" s="1">
+        <v>3</v>
+      </c>
+      <c r="O723" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="724" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A724" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B724" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C724" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D724" s="1">
+        <v>8</v>
+      </c>
+      <c r="E724" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F724" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="G724" s="10">
+        <v>10239470209</v>
+      </c>
+      <c r="H724" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I724" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="J724" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K724" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="L724" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="M724" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N724" s="1">
+        <v>10</v>
+      </c>
+      <c r="O724" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="725" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A725" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B725" s="7" t="s">
+        <v>1477</v>
+      </c>
+      <c r="C725" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D725" s="1">
+        <v>8</v>
+      </c>
+      <c r="E725" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F725" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G725" s="10">
+        <v>10403881363</v>
+      </c>
+      <c r="H725" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J725" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K725" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L725" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="M725" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N725" s="1">
+        <v>1</v>
+      </c>
+      <c r="O725" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="726" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A726" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B726" s="7" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C726" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D726" s="1">
+        <v>8</v>
+      </c>
+      <c r="E726" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F726" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G726" s="10">
+        <v>10248679081</v>
+      </c>
+      <c r="H726" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J726" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K726" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L726" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="M726" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N726" s="1">
+        <v>1</v>
+      </c>
+      <c r="O726" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="727" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A727" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B727" s="7" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C727" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D727" s="1">
+        <v>8</v>
+      </c>
+      <c r="E727" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F727" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G727" s="10">
+        <v>10403471645</v>
+      </c>
+      <c r="H727" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J727" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K727" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L727" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="M727" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N727" s="1">
+        <v>1</v>
+      </c>
+      <c r="O727" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="728" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A728" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B728" s="7" t="s">
+        <v>1479</v>
+      </c>
+      <c r="C728" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D728" s="1">
+        <v>8</v>
+      </c>
+      <c r="E728" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F728" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G728" s="10">
+        <v>10444412823</v>
+      </c>
+      <c r="H728" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="J728" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K728" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L728" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="M728" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N728" s="1">
+        <v>1</v>
+      </c>
+      <c r="O728" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="729" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A729" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B729" s="7" t="s">
+        <v>1480</v>
+      </c>
+      <c r="C729" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D729" s="1">
+        <v>8</v>
+      </c>
+      <c r="E729" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F729" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G729" s="10">
+        <v>10239802821</v>
+      </c>
+      <c r="H729" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J729" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K729" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L729" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="M729" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N729" s="1">
+        <v>1</v>
+      </c>
+      <c r="O729" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="730" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A730" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B730" s="7" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C730" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D730" s="1">
+        <v>8</v>
+      </c>
+      <c r="E730" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F730" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G730" s="10">
+        <v>10403881363</v>
+      </c>
+      <c r="H730" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J730" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K730" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L730" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="M730" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N730" s="1">
+        <v>1</v>
+      </c>
+      <c r="O730" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="731" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A731" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B731" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C731" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D731" s="1">
+        <v>8</v>
+      </c>
+      <c r="E731" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F731" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G731" s="10">
+        <v>23952707</v>
+      </c>
+      <c r="H731" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="J731" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K731" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L731" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M731" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N731" s="1">
+        <v>1</v>
+      </c>
+      <c r="O731" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="732" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A732" s="1" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B732" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C732" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D732" s="1">
+        <v>8</v>
+      </c>
+      <c r="E732" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F732" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G732" s="10">
+        <v>23958294</v>
+      </c>
+      <c r="H732" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="J732" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K732" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L732" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M732" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N732" s="1">
+        <v>1</v>
+      </c>
+      <c r="O732" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="733" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A733" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B733" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C733" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D733" s="1">
+        <v>8</v>
+      </c>
+      <c r="E733" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F733" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G733" s="10">
+        <v>46412224</v>
+      </c>
+      <c r="H733" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="J733" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K733" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L733" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M733" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N733" s="1">
+        <v>1</v>
+      </c>
+      <c r="O733" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="734" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A734" s="1" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B734" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C734" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D734" s="1">
+        <v>8</v>
+      </c>
+      <c r="E734" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F734" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G734" s="10">
+        <v>23914748</v>
+      </c>
+      <c r="H734" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="J734" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K734" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L734" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M734" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N734" s="1">
+        <v>1</v>
+      </c>
+      <c r="O734" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="735" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A735" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B735" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C735" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D735" s="1">
+        <v>8</v>
+      </c>
+      <c r="E735" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F735" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G735" s="10">
+        <v>23806437</v>
+      </c>
+      <c r="H735" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="J735" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K735" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L735" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M735" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N735" s="1">
+        <v>1</v>
+      </c>
+      <c r="O735" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="736" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A736" s="1" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B736" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C736" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D736" s="1">
+        <v>8</v>
+      </c>
+      <c r="E736" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F736" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G736" s="10">
+        <v>23938763</v>
+      </c>
+      <c r="H736" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="J736" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K736" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L736" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M736" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N736" s="1">
+        <v>1</v>
+      </c>
+      <c r="O736" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="737" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A737" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B737" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C737" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D737" s="1">
+        <v>8</v>
+      </c>
+      <c r="E737" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F737" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G737" s="10">
+        <v>24707629</v>
+      </c>
+      <c r="H737" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="J737" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K737" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L737" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M737" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N737" s="1">
+        <v>1</v>
+      </c>
+      <c r="O737" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="738" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A738" s="1" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B738" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C738" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D738" s="1">
+        <v>8</v>
+      </c>
+      <c r="E738" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F738" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G738" s="10">
+        <v>23939680</v>
+      </c>
+      <c r="H738" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="J738" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K738" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L738" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M738" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N738" s="1">
+        <v>1</v>
+      </c>
+      <c r="O738" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="739" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A739" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B739" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C739" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D739" s="1">
+        <v>8</v>
+      </c>
+      <c r="E739" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F739" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G739" s="10">
+        <v>40152636</v>
+      </c>
+      <c r="H739" s="1" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J739" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K739" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L739" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M739" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N739" s="1">
+        <v>1</v>
+      </c>
+      <c r="O739" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="740" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A740" s="1" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B740" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C740" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D740" s="1">
+        <v>8</v>
+      </c>
+      <c r="E740" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F740" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G740" s="10">
+        <v>23982106</v>
+      </c>
+      <c r="H740" s="1" t="s">
+        <v>1494</v>
+      </c>
+      <c r="J740" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K740" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L740" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M740" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N740" s="1">
+        <v>1</v>
+      </c>
+      <c r="O740" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="741" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A741" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B741" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C741" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D741" s="1">
+        <v>8</v>
+      </c>
+      <c r="E741" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F741" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G741" s="10">
+        <v>24884262</v>
+      </c>
+      <c r="H741" s="1" t="s">
+        <v>1495</v>
+      </c>
+      <c r="J741" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K741" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L741" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M741" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N741" s="1">
+        <v>1</v>
+      </c>
+      <c r="O741" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="742" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A742" s="1" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B742" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C742" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D742" s="1">
+        <v>8</v>
+      </c>
+      <c r="E742" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F742" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G742" s="10">
+        <v>23844225</v>
+      </c>
+      <c r="H742" s="1" t="s">
+        <v>1496</v>
+      </c>
+      <c r="J742" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K742" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L742" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M742" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N742" s="1">
+        <v>1</v>
+      </c>
+      <c r="O742" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="743" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A743" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B743" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C743" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D743" s="1">
+        <v>8</v>
+      </c>
+      <c r="E743" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F743" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G743" s="10">
+        <v>24006558</v>
+      </c>
+      <c r="H743" s="1" t="s">
+        <v>1497</v>
+      </c>
+      <c r="J743" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K743" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L743" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M743" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N743" s="1">
+        <v>1</v>
+      </c>
+      <c r="O743" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="744" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A744" s="1" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B744" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C744" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D744" s="1">
+        <v>8</v>
+      </c>
+      <c r="E744" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F744" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G744" s="10">
+        <v>23928091</v>
+      </c>
+      <c r="H744" s="1" t="s">
+        <v>1498</v>
+      </c>
+      <c r="J744" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K744" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L744" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M744" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N744" s="1">
+        <v>1</v>
+      </c>
+      <c r="O744" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="745" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A745" s="1" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B745" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C745" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D745" s="1">
+        <v>8</v>
+      </c>
+      <c r="E745" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F745" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G745" s="10">
+        <v>43584124</v>
+      </c>
+      <c r="H745" s="1" t="s">
+        <v>1499</v>
+      </c>
+      <c r="J745" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K745" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L745" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M745" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N745" s="1">
+        <v>1</v>
+      </c>
+      <c r="O745" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="746" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A746" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B746" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C746" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D746" s="1">
+        <v>8</v>
+      </c>
+      <c r="E746" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F746" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G746" s="10">
+        <v>23877092</v>
+      </c>
+      <c r="H746" s="1" t="s">
+        <v>1500</v>
+      </c>
+      <c r="J746" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K746" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L746" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M746" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N746" s="1">
+        <v>1</v>
+      </c>
+      <c r="O746" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="747" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A747" s="1" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B747" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C747" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D747" s="1">
+        <v>8</v>
+      </c>
+      <c r="E747" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F747" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G747" s="10">
+        <v>23846625</v>
+      </c>
+      <c r="H747" s="1" t="s">
+        <v>1501</v>
+      </c>
+      <c r="J747" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K747" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L747" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M747" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N747" s="1">
+        <v>1</v>
+      </c>
+      <c r="O747" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="748" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A748" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B748" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C748" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D748" s="1">
+        <v>8</v>
+      </c>
+      <c r="E748" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F748" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G748" s="10">
+        <v>23987971</v>
+      </c>
+      <c r="H748" s="1" t="s">
+        <v>1502</v>
+      </c>
+      <c r="J748" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K748" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L748" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M748" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N748" s="1">
+        <v>1</v>
+      </c>
+      <c r="O748" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="749" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A749" s="1" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B749" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C749" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D749" s="1">
+        <v>8</v>
+      </c>
+      <c r="E749" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F749" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G749" s="10">
+        <v>80193430</v>
+      </c>
+      <c r="H749" s="1" t="s">
+        <v>1503</v>
+      </c>
+      <c r="J749" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K749" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L749" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M749" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N749" s="1">
+        <v>1</v>
+      </c>
+      <c r="O749" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="750" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A750" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B750" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C750" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D750" s="1">
+        <v>8</v>
+      </c>
+      <c r="E750" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F750" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G750" s="10">
+        <v>48605004</v>
+      </c>
+      <c r="H750" s="1" t="s">
+        <v>1504</v>
+      </c>
+      <c r="J750" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K750" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L750" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M750" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N750" s="1">
+        <v>1</v>
+      </c>
+      <c r="O750" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="751" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A751" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B751" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C751" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D751" s="1">
+        <v>8</v>
+      </c>
+      <c r="E751" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F751" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G751" s="10">
+        <v>23997448</v>
+      </c>
+      <c r="H751" s="1" t="s">
+        <v>1505</v>
+      </c>
+      <c r="J751" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K751" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L751" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M751" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N751" s="1">
+        <v>1</v>
+      </c>
+      <c r="O751" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="752" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A752" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B752" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C752" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D752" s="1">
+        <v>8</v>
+      </c>
+      <c r="E752" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F752" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G752" s="10">
+        <v>80015290</v>
+      </c>
+      <c r="H752" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="J752" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K752" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L752" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M752" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N752" s="1">
+        <v>1</v>
+      </c>
+      <c r="O752" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="753" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A753" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B753" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C753" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D753" s="1">
+        <v>8</v>
+      </c>
+      <c r="E753" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F753" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G753" s="10">
+        <v>23879056</v>
+      </c>
+      <c r="H753" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="J753" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K753" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L753" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M753" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N753" s="1">
+        <v>1</v>
+      </c>
+      <c r="O753" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="754" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A754" s="1" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B754" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C754" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D754" s="1">
+        <v>8</v>
+      </c>
+      <c r="E754" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F754" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G754" s="10">
+        <v>24720830</v>
+      </c>
+      <c r="H754" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="J754" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K754" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L754" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M754" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N754" s="1">
+        <v>1</v>
+      </c>
+      <c r="O754" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="755" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A755" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B755" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C755" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D755" s="1">
+        <v>8</v>
+      </c>
+      <c r="E755" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F755" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G755" s="10">
+        <v>23951746</v>
+      </c>
+      <c r="H755" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="J755" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K755" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L755" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M755" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N755" s="1">
+        <v>1</v>
+      </c>
+      <c r="O755" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="756" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A756" s="1" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B756" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C756" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D756" s="1">
+        <v>8</v>
+      </c>
+      <c r="E756" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F756" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G756" s="10">
+        <v>45721278</v>
+      </c>
+      <c r="H756" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="J756" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K756" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L756" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M756" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N756" s="1">
+        <v>1</v>
+      </c>
+      <c r="O756" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="757" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A757" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B757" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C757" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D757" s="1">
+        <v>8</v>
+      </c>
+      <c r="E757" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F757" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G757" s="10">
+        <v>23949979</v>
+      </c>
+      <c r="H757" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="J757" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K757" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L757" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M757" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N757" s="1">
+        <v>1</v>
+      </c>
+      <c r="O757" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="758" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A758" s="1" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B758" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C758" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D758" s="1">
+        <v>8</v>
+      </c>
+      <c r="E758" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F758" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G758" s="10">
+        <v>42047719</v>
+      </c>
+      <c r="H758" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="J758" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K758" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L758" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M758" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N758" s="1">
+        <v>1</v>
+      </c>
+      <c r="O758" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="759" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A759" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B759" s="7" t="s">
+        <v>1592</v>
+      </c>
+      <c r="C759" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D759" s="1">
+        <v>8</v>
+      </c>
+      <c r="E759" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F759" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G759" s="10">
+        <v>41845783</v>
+      </c>
+      <c r="H759" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="J759" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K759" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L759" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="M759" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N759" s="1">
+        <v>1</v>
+      </c>
+      <c r="O759" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="760" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A760" s="1" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B760" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C760" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D760" s="1">
+        <v>8</v>
+      </c>
+      <c r="E760" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F760" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G760" s="10">
+        <v>45087670</v>
+      </c>
+      <c r="H760" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J760" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K760" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L760" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M760" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N760" s="1">
+        <v>1</v>
+      </c>
+      <c r="O760" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="761" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A761" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B761" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C761" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D761" s="1">
+        <v>8</v>
+      </c>
+      <c r="E761" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F761" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G761" s="10">
+        <v>47614294</v>
+      </c>
+      <c r="H761" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="J761" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K761" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L761" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M761" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N761" s="1">
+        <v>1</v>
+      </c>
+      <c r="O761" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="762" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A762" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B762" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C762" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D762" s="1">
+        <v>8</v>
+      </c>
+      <c r="E762" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F762" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G762" s="10">
+        <v>24873839</v>
+      </c>
+      <c r="H762" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="J762" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K762" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L762" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M762" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N762" s="1">
+        <v>1</v>
+      </c>
+      <c r="O762" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="763" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A763" s="1" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B763" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C763" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D763" s="1">
+        <v>8</v>
+      </c>
+      <c r="E763" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F763" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G763" s="10">
+        <v>47656632</v>
+      </c>
+      <c r="H763" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="J763" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K763" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L763" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M763" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N763" s="1">
+        <v>1</v>
+      </c>
+      <c r="O763" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="764" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A764" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B764" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C764" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D764" s="1">
+        <v>8</v>
+      </c>
+      <c r="E764" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F764" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G764" s="10">
+        <v>43150763</v>
+      </c>
+      <c r="H764" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="J764" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K764" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L764" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M764" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N764" s="1">
+        <v>1</v>
+      </c>
+      <c r="O764" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="765" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A765" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B765" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C765" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D765" s="1">
+        <v>8</v>
+      </c>
+      <c r="E765" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F765" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G765" s="10">
+        <v>42566234</v>
+      </c>
+      <c r="H765" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="J765" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K765" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L765" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M765" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N765" s="1">
+        <v>1</v>
+      </c>
+      <c r="O765" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="766" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A766" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B766" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C766" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D766" s="1">
+        <v>8</v>
+      </c>
+      <c r="E766" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F766" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G766" s="10">
+        <v>46258399</v>
+      </c>
+      <c r="H766" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="J766" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K766" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L766" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M766" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N766" s="1">
+        <v>1</v>
+      </c>
+      <c r="O766" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="767" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A767" s="1" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B767" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C767" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D767" s="1">
+        <v>8</v>
+      </c>
+      <c r="E767" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F767" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G767" s="10">
+        <v>73870421</v>
+      </c>
+      <c r="H767" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="J767" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K767" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L767" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M767" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N767" s="1">
+        <v>1</v>
+      </c>
+      <c r="O767" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="768" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A768" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B768" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C768" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D768" s="1">
+        <v>8</v>
+      </c>
+      <c r="E768" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F768" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G768" s="10">
+        <v>46314028</v>
+      </c>
+      <c r="H768" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="J768" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K768" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L768" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M768" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N768" s="1">
+        <v>1</v>
+      </c>
+      <c r="O768" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="769" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A769" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B769" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C769" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D769" s="1">
+        <v>8</v>
+      </c>
+      <c r="E769" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F769" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G769" s="10">
+        <v>45625853</v>
+      </c>
+      <c r="H769" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="J769" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K769" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L769" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M769" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N769" s="1">
+        <v>1</v>
+      </c>
+      <c r="O769" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="770" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A770" s="1" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B770" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C770" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D770" s="1">
+        <v>8</v>
+      </c>
+      <c r="E770" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F770" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G770" s="10">
+        <v>40040306</v>
+      </c>
+      <c r="H770" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="J770" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K770" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L770" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M770" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N770" s="1">
+        <v>1</v>
+      </c>
+      <c r="O770" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="771" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A771" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B771" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C771" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D771" s="1">
+        <v>8</v>
+      </c>
+      <c r="E771" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F771" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G771" s="10">
+        <v>46474063</v>
+      </c>
+      <c r="H771" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="J771" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K771" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L771" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M771" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N771" s="1">
+        <v>1</v>
+      </c>
+      <c r="O771" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="772" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A772" s="1" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B772" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C772" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D772" s="1">
+        <v>8</v>
+      </c>
+      <c r="E772" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F772" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G772" s="10">
+        <v>47925279</v>
+      </c>
+      <c r="H772" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="J772" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K772" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L772" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M772" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N772" s="1">
+        <v>1</v>
+      </c>
+      <c r="O772" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="773" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A773" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B773" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C773" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D773" s="1">
+        <v>8</v>
+      </c>
+      <c r="E773" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F773" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G773" s="10">
+        <v>42150509</v>
+      </c>
+      <c r="H773" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="J773" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K773" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L773" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M773" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N773" s="1">
+        <v>1</v>
+      </c>
+      <c r="O773" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="774" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A774" s="1" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B774" s="7" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C774" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D774" s="1">
+        <v>8</v>
+      </c>
+      <c r="E774" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F774" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G774" s="10">
+        <v>45431690</v>
+      </c>
+      <c r="H774" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="J774" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K774" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L774" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="M774" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N774" s="1">
+        <v>1</v>
+      </c>
+      <c r="O774" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="775" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A775" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B775" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C775" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D775" s="1">
+        <v>8</v>
+      </c>
+      <c r="E775" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F775" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G775" s="10">
+        <v>60925074</v>
+      </c>
+      <c r="H775" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="J775" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K775" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L775" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M775" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N775" s="1">
+        <v>1</v>
+      </c>
+      <c r="O775" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="776" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A776" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B776" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C776" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D776" s="1">
+        <v>8</v>
+      </c>
+      <c r="E776" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F776" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G776" s="10">
+        <v>44396874</v>
+      </c>
+      <c r="H776" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="J776" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K776" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L776" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M776" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N776" s="1">
+        <v>1</v>
+      </c>
+      <c r="O776" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="777" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A777" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B777" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C777" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D777" s="1">
+        <v>8</v>
+      </c>
+      <c r="E777" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F777" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G777" s="10">
+        <v>44010946</v>
+      </c>
+      <c r="H777" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="J777" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K777" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L777" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M777" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N777" s="1">
+        <v>1</v>
+      </c>
+      <c r="O777" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="778" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A778" s="1" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B778" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C778" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D778" s="1">
+        <v>8</v>
+      </c>
+      <c r="E778" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F778" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G778" s="10">
+        <v>73570769</v>
+      </c>
+      <c r="H778" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="J778" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K778" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L778" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M778" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N778" s="1">
+        <v>1</v>
+      </c>
+      <c r="O778" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="779" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A779" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B779" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C779" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D779" s="1">
+        <v>8</v>
+      </c>
+      <c r="E779" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F779" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G779" s="10">
+        <v>73597255</v>
+      </c>
+      <c r="H779" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="J779" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K779" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L779" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M779" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N779" s="1">
+        <v>1</v>
+      </c>
+      <c r="O779" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="780" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A780" s="1" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B780" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C780" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D780" s="1">
+        <v>8</v>
+      </c>
+      <c r="E780" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F780" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G780" s="10">
+        <v>42426721</v>
+      </c>
+      <c r="H780" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="J780" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K780" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L780" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M780" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N780" s="1">
+        <v>1</v>
+      </c>
+      <c r="O780" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="781" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A781" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B781" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C781" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D781" s="1">
+        <v>8</v>
+      </c>
+      <c r="E781" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F781" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G781" s="10">
+        <v>23916286</v>
+      </c>
+      <c r="H781" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="J781" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K781" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L781" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M781" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N781" s="1">
+        <v>1</v>
+      </c>
+      <c r="O781" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="782" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A782" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B782" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C782" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D782" s="1">
+        <v>8</v>
+      </c>
+      <c r="E782" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F782" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G782" s="10">
+        <v>45355866</v>
+      </c>
+      <c r="H782" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="J782" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K782" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L782" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M782" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N782" s="1">
+        <v>1</v>
+      </c>
+      <c r="O782" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="783" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A783" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B783" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C783" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D783" s="1">
+        <v>8</v>
+      </c>
+      <c r="E783" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F783" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G783" s="10">
+        <v>61401694</v>
+      </c>
+      <c r="H783" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="J783" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K783" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L783" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M783" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N783" s="1">
+        <v>1</v>
+      </c>
+      <c r="O783" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="784" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A784" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B784" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C784" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D784" s="1">
+        <v>8</v>
+      </c>
+      <c r="E784" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F784" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G784" s="10">
+        <v>45146935</v>
+      </c>
+      <c r="H784" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="J784" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K784" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L784" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M784" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N784" s="1">
+        <v>1</v>
+      </c>
+      <c r="O784" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="785" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A785" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B785" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C785" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D785" s="1">
+        <v>8</v>
+      </c>
+      <c r="E785" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F785" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G785" s="10">
+        <v>47188247</v>
+      </c>
+      <c r="H785" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="J785" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K785" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L785" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M785" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N785" s="1">
+        <v>1</v>
+      </c>
+      <c r="O785" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="786" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A786" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B786" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C786" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D786" s="1">
+        <v>8</v>
+      </c>
+      <c r="E786" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F786" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G786" s="10">
+        <v>23958774</v>
+      </c>
+      <c r="H786" s="1" t="s">
+        <v>1527</v>
+      </c>
+      <c r="J786" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K786" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L786" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M786" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N786" s="1">
+        <v>1</v>
+      </c>
+      <c r="O786" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="787" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A787" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B787" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C787" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D787" s="1">
+        <v>8</v>
+      </c>
+      <c r="E787" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F787" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G787" s="10">
+        <v>46756737</v>
+      </c>
+      <c r="H787" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="J787" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K787" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L787" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M787" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N787" s="1">
+        <v>1</v>
+      </c>
+      <c r="O787" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="788" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A788" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B788" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C788" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D788" s="1">
+        <v>8</v>
+      </c>
+      <c r="E788" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F788" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G788" s="10">
+        <v>75771143</v>
+      </c>
+      <c r="H788" s="1" t="s">
+        <v>1529</v>
+      </c>
+      <c r="J788" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K788" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L788" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M788" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N788" s="1">
+        <v>1</v>
+      </c>
+      <c r="O788" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="789" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A789" s="1" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B789" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C789" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D789" s="1">
+        <v>8</v>
+      </c>
+      <c r="E789" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F789" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G789" s="10">
+        <v>45652745</v>
+      </c>
+      <c r="H789" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="J789" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K789" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L789" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M789" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N789" s="1">
+        <v>1</v>
+      </c>
+      <c r="O789" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="790" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A790" s="1" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B790" s="7" t="s">
+        <v>1593</v>
+      </c>
+      <c r="C790" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D790" s="1">
+        <v>8</v>
+      </c>
+      <c r="E790" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F790" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G790" s="10">
+        <v>73200292</v>
+      </c>
+      <c r="H790" s="1" t="s">
+        <v>1531</v>
+      </c>
+      <c r="J790" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K790" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L790" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="M790" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N790" s="1">
+        <v>1</v>
+      </c>
+      <c r="O790" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P718">
     <sortCondition ref="D1:D718"/>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E64F64E-0B73-4B3E-93DD-125CEB9263FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EA044F-0733-463E-B1BE-47F2D1FB9CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8611" uniqueCount="1594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8644" uniqueCount="1597">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -4897,6 +4897,15 @@
   </si>
   <si>
     <t>18/08/2026</t>
+  </si>
+  <si>
+    <t>C000790</t>
+  </si>
+  <si>
+    <t>C000791</t>
+  </si>
+  <si>
+    <t>C000792</t>
   </si>
 </sst>
 </file>
@@ -5353,7 +5362,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
-  <dimension ref="A1:P790"/>
+  <dimension ref="A1:P793"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -40101,7 +40110,7 @@
       <c r="F720" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G720" s="10">
+      <c r="G720" s="1">
         <v>10239470209</v>
       </c>
       <c r="H720" s="1" t="s">
@@ -40148,7 +40157,7 @@
       <c r="F721" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G721" s="10">
+      <c r="G721" s="1">
         <v>24867908</v>
       </c>
       <c r="H721" s="1" t="s">
@@ -40192,7 +40201,7 @@
       <c r="F722" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G722" s="10">
+      <c r="G722" s="1">
         <v>23980287</v>
       </c>
       <c r="H722" s="1" t="s">
@@ -40236,7 +40245,7 @@
       <c r="F723" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G723" s="10">
+      <c r="G723" s="1">
         <v>40388136</v>
       </c>
       <c r="H723" s="1" t="s">
@@ -40280,7 +40289,7 @@
       <c r="F724" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G724" s="10">
+      <c r="G724" s="1">
         <v>10239470209</v>
       </c>
       <c r="H724" s="1" t="s">
@@ -40327,7 +40336,7 @@
       <c r="F725" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="G725" s="10">
+      <c r="G725" s="1">
         <v>10403881363</v>
       </c>
       <c r="H725" s="1" t="s">
@@ -40371,7 +40380,7 @@
       <c r="F726" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="G726" s="10">
+      <c r="G726" s="1">
         <v>10248679081</v>
       </c>
       <c r="H726" s="1" t="s">
@@ -40415,7 +40424,7 @@
       <c r="F727" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="G727" s="10">
+      <c r="G727" s="1">
         <v>10403471645</v>
       </c>
       <c r="H727" s="1" t="s">
@@ -40459,7 +40468,7 @@
       <c r="F728" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G728" s="10">
+      <c r="G728" s="1">
         <v>10444412823</v>
       </c>
       <c r="H728" s="1" t="s">
@@ -40503,7 +40512,7 @@
       <c r="F729" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G729" s="10">
+      <c r="G729" s="1">
         <v>10239802821</v>
       </c>
       <c r="H729" s="1" t="s">
@@ -40547,7 +40556,7 @@
       <c r="F730" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G730" s="10">
+      <c r="G730" s="1">
         <v>10403881363</v>
       </c>
       <c r="H730" s="1" t="s">
@@ -40591,7 +40600,7 @@
       <c r="F731" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G731" s="10">
+      <c r="G731" s="1">
         <v>23952707</v>
       </c>
       <c r="H731" s="1" t="s">
@@ -40635,7 +40644,7 @@
       <c r="F732" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G732" s="10">
+      <c r="G732" s="1">
         <v>23958294</v>
       </c>
       <c r="H732" s="1" t="s">
@@ -40679,7 +40688,7 @@
       <c r="F733" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G733" s="10">
+      <c r="G733" s="1">
         <v>46412224</v>
       </c>
       <c r="H733" s="1" t="s">
@@ -40723,7 +40732,7 @@
       <c r="F734" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G734" s="10">
+      <c r="G734" s="1">
         <v>23914748</v>
       </c>
       <c r="H734" s="1" t="s">
@@ -40767,7 +40776,7 @@
       <c r="F735" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G735" s="10">
+      <c r="G735" s="1">
         <v>23806437</v>
       </c>
       <c r="H735" s="1" t="s">
@@ -40811,7 +40820,7 @@
       <c r="F736" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G736" s="10">
+      <c r="G736" s="1">
         <v>23938763</v>
       </c>
       <c r="H736" s="1" t="s">
@@ -40855,7 +40864,7 @@
       <c r="F737" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G737" s="10">
+      <c r="G737" s="1">
         <v>24707629</v>
       </c>
       <c r="H737" s="1" t="s">
@@ -40899,7 +40908,7 @@
       <c r="F738" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G738" s="10">
+      <c r="G738" s="1">
         <v>23939680</v>
       </c>
       <c r="H738" s="1" t="s">
@@ -40943,7 +40952,7 @@
       <c r="F739" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G739" s="10">
+      <c r="G739" s="1">
         <v>40152636</v>
       </c>
       <c r="H739" s="1" t="s">
@@ -40987,7 +40996,7 @@
       <c r="F740" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G740" s="10">
+      <c r="G740" s="1">
         <v>23982106</v>
       </c>
       <c r="H740" s="1" t="s">
@@ -41031,7 +41040,7 @@
       <c r="F741" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G741" s="10">
+      <c r="G741" s="1">
         <v>24884262</v>
       </c>
       <c r="H741" s="1" t="s">
@@ -41075,7 +41084,7 @@
       <c r="F742" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G742" s="10">
+      <c r="G742" s="1">
         <v>23844225</v>
       </c>
       <c r="H742" s="1" t="s">
@@ -41119,7 +41128,7 @@
       <c r="F743" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G743" s="10">
+      <c r="G743" s="1">
         <v>24006558</v>
       </c>
       <c r="H743" s="1" t="s">
@@ -41163,7 +41172,7 @@
       <c r="F744" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G744" s="10">
+      <c r="G744" s="1">
         <v>23928091</v>
       </c>
       <c r="H744" s="1" t="s">
@@ -41207,7 +41216,7 @@
       <c r="F745" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G745" s="10">
+      <c r="G745" s="1">
         <v>43584124</v>
       </c>
       <c r="H745" s="1" t="s">
@@ -41251,7 +41260,7 @@
       <c r="F746" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G746" s="10">
+      <c r="G746" s="1">
         <v>23877092</v>
       </c>
       <c r="H746" s="1" t="s">
@@ -41295,7 +41304,7 @@
       <c r="F747" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G747" s="10">
+      <c r="G747" s="1">
         <v>23846625</v>
       </c>
       <c r="H747" s="1" t="s">
@@ -41339,7 +41348,7 @@
       <c r="F748" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G748" s="10">
+      <c r="G748" s="1">
         <v>23987971</v>
       </c>
       <c r="H748" s="1" t="s">
@@ -41383,7 +41392,7 @@
       <c r="F749" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G749" s="10">
+      <c r="G749" s="1">
         <v>80193430</v>
       </c>
       <c r="H749" s="1" t="s">
@@ -41427,7 +41436,7 @@
       <c r="F750" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G750" s="10">
+      <c r="G750" s="1">
         <v>48605004</v>
       </c>
       <c r="H750" s="1" t="s">
@@ -41471,7 +41480,7 @@
       <c r="F751" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G751" s="10">
+      <c r="G751" s="1">
         <v>23997448</v>
       </c>
       <c r="H751" s="1" t="s">
@@ -41515,7 +41524,7 @@
       <c r="F752" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G752" s="10">
+      <c r="G752" s="1">
         <v>80015290</v>
       </c>
       <c r="H752" s="1" t="s">
@@ -41559,7 +41568,7 @@
       <c r="F753" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G753" s="10">
+      <c r="G753" s="1">
         <v>23879056</v>
       </c>
       <c r="H753" s="1" t="s">
@@ -41603,7 +41612,7 @@
       <c r="F754" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G754" s="10">
+      <c r="G754" s="1">
         <v>24720830</v>
       </c>
       <c r="H754" s="1" t="s">
@@ -41647,7 +41656,7 @@
       <c r="F755" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G755" s="10">
+      <c r="G755" s="1">
         <v>23951746</v>
       </c>
       <c r="H755" s="1" t="s">
@@ -41691,7 +41700,7 @@
       <c r="F756" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G756" s="10">
+      <c r="G756" s="1">
         <v>45721278</v>
       </c>
       <c r="H756" s="1" t="s">
@@ -41735,7 +41744,7 @@
       <c r="F757" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G757" s="10">
+      <c r="G757" s="1">
         <v>23949979</v>
       </c>
       <c r="H757" s="1" t="s">
@@ -41779,7 +41788,7 @@
       <c r="F758" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G758" s="10">
+      <c r="G758" s="1">
         <v>42047719</v>
       </c>
       <c r="H758" s="1" t="s">
@@ -41823,7 +41832,7 @@
       <c r="F759" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G759" s="10">
+      <c r="G759" s="1">
         <v>41845783</v>
       </c>
       <c r="H759" s="1" t="s">
@@ -41867,7 +41876,7 @@
       <c r="F760" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G760" s="10">
+      <c r="G760" s="1">
         <v>45087670</v>
       </c>
       <c r="H760" s="1" t="s">
@@ -41911,7 +41920,7 @@
       <c r="F761" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G761" s="10">
+      <c r="G761" s="1">
         <v>47614294</v>
       </c>
       <c r="H761" s="1" t="s">
@@ -41955,7 +41964,7 @@
       <c r="F762" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G762" s="10">
+      <c r="G762" s="1">
         <v>24873839</v>
       </c>
       <c r="H762" s="1" t="s">
@@ -41999,7 +42008,7 @@
       <c r="F763" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G763" s="10">
+      <c r="G763" s="1">
         <v>47656632</v>
       </c>
       <c r="H763" s="1" t="s">
@@ -42043,7 +42052,7 @@
       <c r="F764" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G764" s="10">
+      <c r="G764" s="1">
         <v>43150763</v>
       </c>
       <c r="H764" s="1" t="s">
@@ -42087,7 +42096,7 @@
       <c r="F765" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G765" s="10">
+      <c r="G765" s="1">
         <v>42566234</v>
       </c>
       <c r="H765" s="1" t="s">
@@ -42131,7 +42140,7 @@
       <c r="F766" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G766" s="10">
+      <c r="G766" s="1">
         <v>46258399</v>
       </c>
       <c r="H766" s="1" t="s">
@@ -42175,7 +42184,7 @@
       <c r="F767" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G767" s="10">
+      <c r="G767" s="1">
         <v>73870421</v>
       </c>
       <c r="H767" s="1" t="s">
@@ -42219,7 +42228,7 @@
       <c r="F768" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G768" s="10">
+      <c r="G768" s="1">
         <v>46314028</v>
       </c>
       <c r="H768" s="1" t="s">
@@ -42263,7 +42272,7 @@
       <c r="F769" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G769" s="10">
+      <c r="G769" s="1">
         <v>45625853</v>
       </c>
       <c r="H769" s="1" t="s">
@@ -42307,7 +42316,7 @@
       <c r="F770" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G770" s="10">
+      <c r="G770" s="1">
         <v>40040306</v>
       </c>
       <c r="H770" s="1" t="s">
@@ -42351,7 +42360,7 @@
       <c r="F771" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G771" s="10">
+      <c r="G771" s="1">
         <v>46474063</v>
       </c>
       <c r="H771" s="1" t="s">
@@ -42395,7 +42404,7 @@
       <c r="F772" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G772" s="10">
+      <c r="G772" s="1">
         <v>47925279</v>
       </c>
       <c r="H772" s="1" t="s">
@@ -42439,7 +42448,7 @@
       <c r="F773" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G773" s="10">
+      <c r="G773" s="1">
         <v>42150509</v>
       </c>
       <c r="H773" s="1" t="s">
@@ -42483,7 +42492,7 @@
       <c r="F774" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G774" s="10">
+      <c r="G774" s="1">
         <v>45431690</v>
       </c>
       <c r="H774" s="1" t="s">
@@ -42527,7 +42536,7 @@
       <c r="F775" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G775" s="10">
+      <c r="G775" s="1">
         <v>60925074</v>
       </c>
       <c r="H775" s="1" t="s">
@@ -42571,7 +42580,7 @@
       <c r="F776" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G776" s="10">
+      <c r="G776" s="1">
         <v>44396874</v>
       </c>
       <c r="H776" s="1" t="s">
@@ -42615,7 +42624,7 @@
       <c r="F777" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G777" s="10">
+      <c r="G777" s="1">
         <v>44010946</v>
       </c>
       <c r="H777" s="1" t="s">
@@ -42659,7 +42668,7 @@
       <c r="F778" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G778" s="10">
+      <c r="G778" s="1">
         <v>73570769</v>
       </c>
       <c r="H778" s="1" t="s">
@@ -42703,7 +42712,7 @@
       <c r="F779" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G779" s="10">
+      <c r="G779" s="1">
         <v>73597255</v>
       </c>
       <c r="H779" s="1" t="s">
@@ -42747,7 +42756,7 @@
       <c r="F780" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G780" s="10">
+      <c r="G780" s="1">
         <v>42426721</v>
       </c>
       <c r="H780" s="1" t="s">
@@ -42791,7 +42800,7 @@
       <c r="F781" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G781" s="10">
+      <c r="G781" s="1">
         <v>23916286</v>
       </c>
       <c r="H781" s="1" t="s">
@@ -42835,7 +42844,7 @@
       <c r="F782" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G782" s="10">
+      <c r="G782" s="1">
         <v>45355866</v>
       </c>
       <c r="H782" s="1" t="s">
@@ -42879,7 +42888,7 @@
       <c r="F783" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G783" s="10">
+      <c r="G783" s="1">
         <v>61401694</v>
       </c>
       <c r="H783" s="1" t="s">
@@ -42923,7 +42932,7 @@
       <c r="F784" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G784" s="10">
+      <c r="G784" s="1">
         <v>45146935</v>
       </c>
       <c r="H784" s="1" t="s">
@@ -42948,7 +42957,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="785" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
         <v>1586</v>
       </c>
@@ -42967,7 +42976,7 @@
       <c r="F785" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G785" s="10">
+      <c r="G785" s="1">
         <v>47188247</v>
       </c>
       <c r="H785" s="1" t="s">
@@ -42992,7 +43001,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="786" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
         <v>1587</v>
       </c>
@@ -43011,7 +43020,7 @@
       <c r="F786" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G786" s="10">
+      <c r="G786" s="1">
         <v>23958774</v>
       </c>
       <c r="H786" s="1" t="s">
@@ -43036,7 +43045,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="787" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
         <v>1588</v>
       </c>
@@ -43055,7 +43064,7 @@
       <c r="F787" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G787" s="10">
+      <c r="G787" s="1">
         <v>46756737</v>
       </c>
       <c r="H787" s="1" t="s">
@@ -43080,7 +43089,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="788" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
         <v>1589</v>
       </c>
@@ -43099,7 +43108,7 @@
       <c r="F788" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G788" s="10">
+      <c r="G788" s="1">
         <v>75771143</v>
       </c>
       <c r="H788" s="1" t="s">
@@ -43124,7 +43133,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="789" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A789" s="1" t="s">
         <v>1590</v>
       </c>
@@ -43143,7 +43152,7 @@
       <c r="F789" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G789" s="10">
+      <c r="G789" s="1">
         <v>45652745</v>
       </c>
       <c r="H789" s="1" t="s">
@@ -43168,7 +43177,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="790" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A790" s="1" t="s">
         <v>1591</v>
       </c>
@@ -43187,7 +43196,7 @@
       <c r="F790" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G790" s="10">
+      <c r="G790" s="1">
         <v>73200292</v>
       </c>
       <c r="H790" s="1" t="s">
@@ -43210,6 +43219,156 @@
       </c>
       <c r="O790" s="1" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="791" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A791" s="1" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B791" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="C791" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D791" s="1">
+        <v>7</v>
+      </c>
+      <c r="E791" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F791" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="G791" s="10">
+        <v>10430636931</v>
+      </c>
+      <c r="H791" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I791" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="J791" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K791" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L791" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="M791" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N791" s="1">
+        <v>1</v>
+      </c>
+      <c r="O791" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="P791" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="792" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A792" s="1" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B792" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="C792" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D792" s="1">
+        <v>7</v>
+      </c>
+      <c r="E792" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F792" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="G792" s="10">
+        <v>10444412823</v>
+      </c>
+      <c r="H792" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="I792" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="J792" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K792" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L792" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="M792" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N792" s="1">
+        <v>1</v>
+      </c>
+      <c r="O792" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="P792" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="793" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A793" s="1" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B793" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="C793" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D793" s="1">
+        <v>7</v>
+      </c>
+      <c r="E793" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F793" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="G793" s="1">
+        <v>10403881363</v>
+      </c>
+      <c r="H793" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I793" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="J793" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K793" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L793" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="M793" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N793" s="1">
+        <v>1</v>
+      </c>
+      <c r="O793" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="P793" s="2">
+        <v>4.0999999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EA044F-0733-463E-B1BE-47F2D1FB9CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD88101E-05FB-435A-A324-F1AFC043EAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$718</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$793</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,6 +42,7 @@
     <author>tc={280F0341-12E0-4EAD-B947-F8812C2A93A9}</author>
     <author>tc={CE24220F-9884-4515-949C-9773C2AB6CD7}</author>
     <author>tc={CC2010E8-F445-4468-8B38-512A71CE0E30}</author>
+    <author>tc={4E3C9A9E-14E5-43AA-8B1F-779CDCC8D0F5}</author>
     <author>tc={8D189750-CB69-4720-9438-68E8E26098F2}</author>
     <author>tc={1FED0FA3-1881-4474-876E-0AE471879AA2}</author>
   </authors>
@@ -94,7 +95,15 @@
     25/03/2026</t>
       </text>
     </comment>
-    <comment ref="B521" authorId="6" shapeId="0" xr:uid="{8D189750-CB69-4720-9438-68E8E26098F2}">
+    <comment ref="F263" authorId="6" shapeId="0" xr:uid="{4E3C9A9E-14E5-43AA-8B1F-779CDCC8D0F5}">
+      <text>
+        <t>[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    LUIS VALENCIA</t>
+      </text>
+    </comment>
+    <comment ref="B521" authorId="7" shapeId="0" xr:uid="{8D189750-CB69-4720-9438-68E8E26098F2}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -102,7 +111,7 @@
     01/07/2026</t>
       </text>
     </comment>
-    <comment ref="A719" authorId="7" shapeId="0" xr:uid="{1FED0FA3-1881-4474-876E-0AE471879AA2}">
+    <comment ref="A719" authorId="8" shapeId="0" xr:uid="{1FED0FA3-1881-4474-876E-0AE471879AA2}">
       <text>
         <t>[Comentario encadenado]
 Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -115,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8644" uniqueCount="1597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8643" uniqueCount="1597">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -4912,7 +4921,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4970,6 +4979,12 @@
       <sz val="10"/>
       <color theme="9" tint="-0.249977111117893"/>
       <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -5351,6 +5366,9 @@
   <threadedComment ref="B254" dT="2026-08-04T21:23:39.27" personId="{4AFC30EF-3D5B-4D86-B079-7855968373AE}" id="{CC2010E8-F445-4468-8B38-512A71CE0E30}">
     <text>25/03/2026</text>
   </threadedComment>
+  <threadedComment ref="F263" dT="2026-09-01T15:17:41.55" personId="{4AFC30EF-3D5B-4D86-B079-7855968373AE}" id="{4E3C9A9E-14E5-43AA-8B1F-779CDCC8D0F5}">
+    <text>LUIS VALENCIA</text>
+  </threadedComment>
   <threadedComment ref="B521" dT="2026-08-04T22:28:59.52" personId="{4AFC30EF-3D5B-4D86-B079-7855968373AE}" id="{8D189750-CB69-4720-9438-68E8E26098F2}">
     <text>01/07/2026</text>
   </threadedComment>
@@ -5362,6 +5380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P793"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5433,7 +5452,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>596</v>
       </c>
@@ -5480,7 +5499,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>598</v>
       </c>
@@ -5527,7 +5546,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>599</v>
       </c>
@@ -5574,7 +5593,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>600</v>
       </c>
@@ -5621,7 +5640,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>601</v>
       </c>
@@ -5668,7 +5687,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>602</v>
       </c>
@@ -5715,7 +5734,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>603</v>
       </c>
@@ -5762,7 +5781,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>604</v>
       </c>
@@ -5809,7 +5828,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>605</v>
       </c>
@@ -5856,7 +5875,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>606</v>
       </c>
@@ -5903,7 +5922,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>607</v>
       </c>
@@ -5950,7 +5969,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>608</v>
       </c>
@@ -5997,7 +6016,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>609</v>
       </c>
@@ -6044,7 +6063,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>610</v>
       </c>
@@ -6091,7 +6110,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>611</v>
       </c>
@@ -6138,7 +6157,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>612</v>
       </c>
@@ -6185,7 +6204,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>613</v>
       </c>
@@ -6232,7 +6251,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>614</v>
       </c>
@@ -6279,7 +6298,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>615</v>
       </c>
@@ -6326,7 +6345,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>616</v>
       </c>
@@ -6373,7 +6392,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>617</v>
       </c>
@@ -6420,7 +6439,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>618</v>
       </c>
@@ -6467,7 +6486,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>619</v>
       </c>
@@ -6514,7 +6533,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>620</v>
       </c>
@@ -6561,7 +6580,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>621</v>
       </c>
@@ -6608,7 +6627,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>622</v>
       </c>
@@ -6655,7 +6674,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>623</v>
       </c>
@@ -6702,7 +6721,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>624</v>
       </c>
@@ -6749,7 +6768,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>625</v>
       </c>
@@ -6796,7 +6815,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>626</v>
       </c>
@@ -6843,7 +6862,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>627</v>
       </c>
@@ -6890,7 +6909,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>628</v>
       </c>
@@ -6937,7 +6956,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>629</v>
       </c>
@@ -6984,7 +7003,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>630</v>
       </c>
@@ -7031,7 +7050,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>631</v>
       </c>
@@ -7078,7 +7097,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>632</v>
       </c>
@@ -7125,7 +7144,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>633</v>
       </c>
@@ -7172,7 +7191,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>634</v>
       </c>
@@ -7219,7 +7238,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>635</v>
       </c>
@@ -7266,7 +7285,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>636</v>
       </c>
@@ -7313,7 +7332,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>637</v>
       </c>
@@ -7360,7 +7379,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>638</v>
       </c>
@@ -7407,7 +7426,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>639</v>
       </c>
@@ -7454,7 +7473,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>640</v>
       </c>
@@ -7501,7 +7520,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>641</v>
       </c>
@@ -7548,7 +7567,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>642</v>
       </c>
@@ -7595,7 +7614,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>643</v>
       </c>
@@ -7642,7 +7661,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>644</v>
       </c>
@@ -7689,7 +7708,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>645</v>
       </c>
@@ -7736,7 +7755,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>646</v>
       </c>
@@ -7783,7 +7802,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>647</v>
       </c>
@@ -7830,7 +7849,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>648</v>
       </c>
@@ -7877,7 +7896,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>649</v>
       </c>
@@ -7924,7 +7943,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>650</v>
       </c>
@@ -7971,7 +7990,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>651</v>
       </c>
@@ -8018,7 +8037,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>652</v>
       </c>
@@ -8065,7 +8084,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>653</v>
       </c>
@@ -8112,7 +8131,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>654</v>
       </c>
@@ -8159,7 +8178,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>655</v>
       </c>
@@ -8206,7 +8225,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>656</v>
       </c>
@@ -8253,7 +8272,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>657</v>
       </c>
@@ -8300,7 +8319,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>658</v>
       </c>
@@ -8347,7 +8366,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>659</v>
       </c>
@@ -8394,7 +8413,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>660</v>
       </c>
@@ -8441,7 +8460,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>661</v>
       </c>
@@ -8488,7 +8507,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>662</v>
       </c>
@@ -8535,7 +8554,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>663</v>
       </c>
@@ -8582,7 +8601,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>664</v>
       </c>
@@ -8629,7 +8648,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>665</v>
       </c>
@@ -8676,7 +8695,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>666</v>
       </c>
@@ -8723,7 +8742,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>667</v>
       </c>
@@ -8770,7 +8789,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>668</v>
       </c>
@@ -8817,7 +8836,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>669</v>
       </c>
@@ -8864,7 +8883,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>670</v>
       </c>
@@ -8911,7 +8930,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>671</v>
       </c>
@@ -8958,7 +8977,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>672</v>
       </c>
@@ -9005,7 +9024,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>673</v>
       </c>
@@ -9052,7 +9071,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>674</v>
       </c>
@@ -9099,7 +9118,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>675</v>
       </c>
@@ -9146,7 +9165,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>676</v>
       </c>
@@ -9193,7 +9212,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>677</v>
       </c>
@@ -9240,7 +9259,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>678</v>
       </c>
@@ -9287,7 +9306,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>679</v>
       </c>
@@ -9334,7 +9353,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>680</v>
       </c>
@@ -9381,7 +9400,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>681</v>
       </c>
@@ -9428,7 +9447,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>682</v>
       </c>
@@ -9475,7 +9494,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>683</v>
       </c>
@@ -9522,7 +9541,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>684</v>
       </c>
@@ -9569,7 +9588,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>685</v>
       </c>
@@ -9616,7 +9635,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>686</v>
       </c>
@@ -9663,7 +9682,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>687</v>
       </c>
@@ -9710,7 +9729,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>688</v>
       </c>
@@ -9757,7 +9776,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>689</v>
       </c>
@@ -9804,7 +9823,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>690</v>
       </c>
@@ -9851,7 +9870,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>691</v>
       </c>
@@ -9898,7 +9917,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>692</v>
       </c>
@@ -9945,7 +9964,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>693</v>
       </c>
@@ -9992,7 +10011,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>694</v>
       </c>
@@ -10039,7 +10058,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>695</v>
       </c>
@@ -10086,7 +10105,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>696</v>
       </c>
@@ -10133,7 +10152,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>697</v>
       </c>
@@ -10180,7 +10199,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>698</v>
       </c>
@@ -10227,7 +10246,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>699</v>
       </c>
@@ -10274,7 +10293,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>700</v>
       </c>
@@ -10321,7 +10340,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>701</v>
       </c>
@@ -10368,7 +10387,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>702</v>
       </c>
@@ -10415,7 +10434,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>703</v>
       </c>
@@ -10462,7 +10481,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>704</v>
       </c>
@@ -10509,7 +10528,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>705</v>
       </c>
@@ -10556,7 +10575,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>706</v>
       </c>
@@ -10603,7 +10622,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>707</v>
       </c>
@@ -10650,7 +10669,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>708</v>
       </c>
@@ -10697,7 +10716,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>709</v>
       </c>
@@ -10744,7 +10763,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>710</v>
       </c>
@@ -10791,7 +10810,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>711</v>
       </c>
@@ -10838,7 +10857,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>712</v>
       </c>
@@ -10932,7 +10951,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>714</v>
       </c>
@@ -10979,7 +10998,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>715</v>
       </c>
@@ -11026,7 +11045,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>716</v>
       </c>
@@ -11073,7 +11092,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>717</v>
       </c>
@@ -11120,7 +11139,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>718</v>
       </c>
@@ -11167,7 +11186,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>719</v>
       </c>
@@ -11214,7 +11233,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>720</v>
       </c>
@@ -11261,7 +11280,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>721</v>
       </c>
@@ -11308,7 +11327,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>722</v>
       </c>
@@ -11355,7 +11374,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>723</v>
       </c>
@@ -11402,7 +11421,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>724</v>
       </c>
@@ -11449,7 +11468,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>725</v>
       </c>
@@ -11496,7 +11515,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>726</v>
       </c>
@@ -11543,7 +11562,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>727</v>
       </c>
@@ -11590,7 +11609,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>728</v>
       </c>
@@ -11637,7 +11656,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>729</v>
       </c>
@@ -11684,7 +11703,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>730</v>
       </c>
@@ -11731,7 +11750,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>731</v>
       </c>
@@ -11778,7 +11797,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>732</v>
       </c>
@@ -11825,7 +11844,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>733</v>
       </c>
@@ -11872,7 +11891,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>734</v>
       </c>
@@ -11919,7 +11938,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>735</v>
       </c>
@@ -11966,7 +11985,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>736</v>
       </c>
@@ -12013,7 +12032,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>737</v>
       </c>
@@ -12060,7 +12079,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>738</v>
       </c>
@@ -12107,7 +12126,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>739</v>
       </c>
@@ -12154,7 +12173,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>740</v>
       </c>
@@ -12201,7 +12220,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>741</v>
       </c>
@@ -12248,7 +12267,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>742</v>
       </c>
@@ -12295,7 +12314,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>743</v>
       </c>
@@ -12342,7 +12361,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>744</v>
       </c>
@@ -12389,7 +12408,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>745</v>
       </c>
@@ -12436,7 +12455,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>746</v>
       </c>
@@ -12483,7 +12502,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>747</v>
       </c>
@@ -12530,7 +12549,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>748</v>
       </c>
@@ -12577,7 +12596,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>749</v>
       </c>
@@ -12624,7 +12643,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>750</v>
       </c>
@@ -12671,7 +12690,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>751</v>
       </c>
@@ -12718,7 +12737,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>752</v>
       </c>
@@ -12765,7 +12784,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>753</v>
       </c>
@@ -12812,7 +12831,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>754</v>
       </c>
@@ -12859,7 +12878,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>755</v>
       </c>
@@ -12906,7 +12925,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>756</v>
       </c>
@@ -12953,7 +12972,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>757</v>
       </c>
@@ -13000,7 +13019,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>758</v>
       </c>
@@ -13047,7 +13066,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>759</v>
       </c>
@@ -13094,7 +13113,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>760</v>
       </c>
@@ -13141,7 +13160,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>761</v>
       </c>
@@ -13188,7 +13207,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>762</v>
       </c>
@@ -13235,7 +13254,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>763</v>
       </c>
@@ -13282,7 +13301,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>764</v>
       </c>
@@ -13332,7 +13351,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>765</v>
       </c>
@@ -13382,7 +13401,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>766</v>
       </c>
@@ -13432,7 +13451,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>767</v>
       </c>
@@ -13482,7 +13501,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>768</v>
       </c>
@@ -13532,7 +13551,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>769</v>
       </c>
@@ -13582,7 +13601,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>770</v>
       </c>
@@ -13632,7 +13651,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>771</v>
       </c>
@@ -13682,7 +13701,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>772</v>
       </c>
@@ -13732,7 +13751,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>773</v>
       </c>
@@ -13782,7 +13801,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>774</v>
       </c>
@@ -13832,7 +13851,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>775</v>
       </c>
@@ -13882,7 +13901,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>776</v>
       </c>
@@ -13932,7 +13951,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>777</v>
       </c>
@@ -13982,7 +14001,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>778</v>
       </c>
@@ -14032,7 +14051,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>779</v>
       </c>
@@ -14082,7 +14101,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>780</v>
       </c>
@@ -14132,7 +14151,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>781</v>
       </c>
@@ -14182,7 +14201,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>782</v>
       </c>
@@ -14282,7 +14301,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>784</v>
       </c>
@@ -14332,7 +14351,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>785</v>
       </c>
@@ -14382,7 +14401,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>786</v>
       </c>
@@ -14432,7 +14451,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>787</v>
       </c>
@@ -14482,7 +14501,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>788</v>
       </c>
@@ -14532,7 +14551,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>789</v>
       </c>
@@ -14582,7 +14601,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>790</v>
       </c>
@@ -14632,7 +14651,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>791</v>
       </c>
@@ -14682,7 +14701,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>792</v>
       </c>
@@ -14732,7 +14751,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>793</v>
       </c>
@@ -14782,7 +14801,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>794</v>
       </c>
@@ -14832,7 +14851,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>795</v>
       </c>
@@ -14882,7 +14901,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>796</v>
       </c>
@@ -14932,7 +14951,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>797</v>
       </c>
@@ -14982,7 +15001,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>798</v>
       </c>
@@ -15032,7 +15051,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>799</v>
       </c>
@@ -15082,7 +15101,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>800</v>
       </c>
@@ -15132,7 +15151,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>801</v>
       </c>
@@ -15182,7 +15201,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>802</v>
       </c>
@@ -15232,7 +15251,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>803</v>
       </c>
@@ -15282,7 +15301,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>804</v>
       </c>
@@ -15332,7 +15351,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>805</v>
       </c>
@@ -15382,7 +15401,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>806</v>
       </c>
@@ -15432,7 +15451,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>807</v>
       </c>
@@ -15482,7 +15501,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>808</v>
       </c>
@@ -15532,7 +15551,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>809</v>
       </c>
@@ -15582,7 +15601,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>810</v>
       </c>
@@ -15632,7 +15651,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>811</v>
       </c>
@@ -15682,7 +15701,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>812</v>
       </c>
@@ -15732,7 +15751,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>813</v>
       </c>
@@ -15782,7 +15801,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>814</v>
       </c>
@@ -15832,7 +15851,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>815</v>
       </c>
@@ -15882,7 +15901,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>816</v>
       </c>
@@ -15932,7 +15951,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>817</v>
       </c>
@@ -15982,7 +16001,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>836</v>
       </c>
@@ -16032,7 +16051,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>837</v>
       </c>
@@ -16082,7 +16101,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>838</v>
       </c>
@@ -16132,7 +16151,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>839</v>
       </c>
@@ -16179,7 +16198,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>840</v>
       </c>
@@ -16226,7 +16245,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>841</v>
       </c>
@@ -16273,7 +16292,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>842</v>
       </c>
@@ -16320,7 +16339,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>843</v>
       </c>
@@ -16367,7 +16386,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>844</v>
       </c>
@@ -16414,7 +16433,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>845</v>
       </c>
@@ -16461,7 +16480,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>846</v>
       </c>
@@ -16508,7 +16527,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>847</v>
       </c>
@@ -16555,7 +16574,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>848</v>
       </c>
@@ -16602,7 +16621,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>849</v>
       </c>
@@ -16649,7 +16668,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>850</v>
       </c>
@@ -16696,7 +16715,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>851</v>
       </c>
@@ -16743,7 +16762,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>852</v>
       </c>
@@ -16790,7 +16809,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>880</v>
       </c>
@@ -16837,7 +16856,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>881</v>
       </c>
@@ -16884,7 +16903,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>882</v>
       </c>
@@ -16931,7 +16950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>883</v>
       </c>
@@ -16978,7 +16997,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>884</v>
       </c>
@@ -17025,7 +17044,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>885</v>
       </c>
@@ -17072,7 +17091,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>886</v>
       </c>
@@ -17119,7 +17138,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>887</v>
       </c>
@@ -17166,7 +17185,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>888</v>
       </c>
@@ -17213,7 +17232,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>889</v>
       </c>
@@ -17260,7 +17279,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>890</v>
       </c>
@@ -17307,7 +17326,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>891</v>
       </c>
@@ -17354,7 +17373,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>892</v>
       </c>
@@ -17401,7 +17420,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>893</v>
       </c>
@@ -17448,7 +17467,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>894</v>
       </c>
@@ -17495,7 +17514,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>895</v>
       </c>
@@ -17545,7 +17564,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>896</v>
       </c>
@@ -17595,7 +17614,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>897</v>
       </c>
@@ -17645,7 +17664,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>898</v>
       </c>
@@ -17695,7 +17714,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>899</v>
       </c>
@@ -17745,7 +17764,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>900</v>
       </c>
@@ -17795,7 +17814,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>901</v>
       </c>
@@ -17845,7 +17864,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>902</v>
       </c>
@@ -17911,9 +17930,6 @@
       <c r="E263" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F263" s="1" t="s">
-        <v>575</v>
-      </c>
       <c r="G263" s="1">
         <v>10435553881</v>
       </c>
@@ -17995,7 +18011,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>905</v>
       </c>
@@ -18045,7 +18061,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>906</v>
       </c>
@@ -18095,7 +18111,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>907</v>
       </c>
@@ -18145,7 +18161,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>908</v>
       </c>
@@ -18195,7 +18211,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>909</v>
       </c>
@@ -18245,7 +18261,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>910</v>
       </c>
@@ -18295,7 +18311,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>911</v>
       </c>
@@ -18345,7 +18361,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>912</v>
       </c>
@@ -18395,7 +18411,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>913</v>
       </c>
@@ -18445,7 +18461,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>914</v>
       </c>
@@ -18495,7 +18511,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>915</v>
       </c>
@@ -18545,7 +18561,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>916</v>
       </c>
@@ -18595,7 +18611,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>917</v>
       </c>
@@ -18645,7 +18661,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>918</v>
       </c>
@@ -18695,7 +18711,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>919</v>
       </c>
@@ -18745,7 +18761,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>920</v>
       </c>
@@ -18795,7 +18811,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>921</v>
       </c>
@@ -18845,7 +18861,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>922</v>
       </c>
@@ -18895,7 +18911,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>923</v>
       </c>
@@ -18945,7 +18961,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>924</v>
       </c>
@@ -18995,7 +19011,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>925</v>
       </c>
@@ -19045,7 +19061,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>926</v>
       </c>
@@ -19095,7 +19111,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>927</v>
       </c>
@@ -19145,7 +19161,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>928</v>
       </c>
@@ -19195,7 +19211,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>929</v>
       </c>
@@ -19245,7 +19261,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>930</v>
       </c>
@@ -19295,7 +19311,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>931</v>
       </c>
@@ -19345,7 +19361,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>932</v>
       </c>
@@ -19395,7 +19411,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>959</v>
       </c>
@@ -19445,7 +19461,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>960</v>
       </c>
@@ -19495,7 +19511,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>961</v>
       </c>
@@ -19545,7 +19561,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>962</v>
       </c>
@@ -19595,7 +19611,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>963</v>
       </c>
@@ -19645,7 +19661,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>964</v>
       </c>
@@ -19692,7 +19708,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>965</v>
       </c>
@@ -19739,7 +19755,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>966</v>
       </c>
@@ -19786,7 +19802,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>967</v>
       </c>
@@ -19833,7 +19849,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>968</v>
       </c>
@@ -19880,7 +19896,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>969</v>
       </c>
@@ -19927,7 +19943,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>1003</v>
       </c>
@@ -19974,7 +19990,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>1004</v>
       </c>
@@ -20021,7 +20037,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>1005</v>
       </c>
@@ -20068,7 +20084,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>1006</v>
       </c>
@@ -20115,7 +20131,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>1007</v>
       </c>
@@ -20165,7 +20181,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>1008</v>
       </c>
@@ -20215,7 +20231,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>1009</v>
       </c>
@@ -20265,7 +20281,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>1010</v>
       </c>
@@ -20315,7 +20331,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>1011</v>
       </c>
@@ -20365,7 +20381,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1012</v>
       </c>
@@ -20415,7 +20431,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1013</v>
       </c>
@@ -20465,7 +20481,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>1014</v>
       </c>
@@ -20515,7 +20531,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>1015</v>
       </c>
@@ -20565,7 +20581,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1016</v>
       </c>
@@ -20615,7 +20631,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>1017</v>
       </c>
@@ -20665,7 +20681,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>1018</v>
       </c>
@@ -20715,7 +20731,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>1019</v>
       </c>
@@ -20765,7 +20781,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>1020</v>
       </c>
@@ -20815,7 +20831,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>1021</v>
       </c>
@@ -20865,7 +20881,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>1022</v>
       </c>
@@ -20915,7 +20931,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>1023</v>
       </c>
@@ -20965,7 +20981,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>1024</v>
       </c>
@@ -21015,7 +21031,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1025</v>
       </c>
@@ -21065,7 +21081,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>1026</v>
       </c>
@@ -21115,7 +21131,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>1027</v>
       </c>
@@ -21165,7 +21181,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>1028</v>
       </c>
@@ -21215,7 +21231,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>1029</v>
       </c>
@@ -21265,7 +21281,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>1030</v>
       </c>
@@ -21315,7 +21331,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>1031</v>
       </c>
@@ -21365,7 +21381,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>1032</v>
       </c>
@@ -21415,7 +21431,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>1033</v>
       </c>
@@ -21465,7 +21481,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>1034</v>
       </c>
@@ -21515,7 +21531,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>1035</v>
       </c>
@@ -21565,7 +21581,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>1036</v>
       </c>
@@ -21615,7 +21631,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>1037</v>
       </c>
@@ -21665,7 +21681,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>1038</v>
       </c>
@@ -21715,7 +21731,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>1039</v>
       </c>
@@ -21765,7 +21781,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>1040</v>
       </c>
@@ -21815,7 +21831,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>1041</v>
       </c>
@@ -21865,7 +21881,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1042</v>
       </c>
@@ -21915,7 +21931,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1043</v>
       </c>
@@ -21965,7 +21981,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>1044</v>
       </c>
@@ -22015,7 +22031,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>1045</v>
       </c>
@@ -22065,7 +22081,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1046</v>
       </c>
@@ -22115,7 +22131,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>1047</v>
       </c>
@@ -22165,7 +22181,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>1048</v>
       </c>
@@ -22215,7 +22231,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>1049</v>
       </c>
@@ -22265,7 +22281,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>1050</v>
       </c>
@@ -22315,7 +22331,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>1051</v>
       </c>
@@ -22365,7 +22381,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>1052</v>
       </c>
@@ -22415,7 +22431,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>1053</v>
       </c>
@@ -22465,7 +22481,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>1054</v>
       </c>
@@ -22515,7 +22531,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>1055</v>
       </c>
@@ -22565,7 +22581,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>1056</v>
       </c>
@@ -22615,7 +22631,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>1057</v>
       </c>
@@ -22665,7 +22681,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>1058</v>
       </c>
@@ -22715,7 +22731,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>1059</v>
       </c>
@@ -22765,7 +22781,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>1060</v>
       </c>
@@ -22815,7 +22831,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1061</v>
       </c>
@@ -22865,7 +22881,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1062</v>
       </c>
@@ -22915,7 +22931,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>1063</v>
       </c>
@@ -23015,7 +23031,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1065</v>
       </c>
@@ -23065,7 +23081,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1066</v>
       </c>
@@ -23115,7 +23131,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>1067</v>
       </c>
@@ -23165,7 +23181,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1068</v>
       </c>
@@ -23215,7 +23231,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1069</v>
       </c>
@@ -23265,7 +23281,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>1070</v>
       </c>
@@ -23315,7 +23331,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1071</v>
       </c>
@@ -23365,7 +23381,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1072</v>
       </c>
@@ -23415,7 +23431,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1073</v>
       </c>
@@ -23465,7 +23481,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>1074</v>
       </c>
@@ -23515,7 +23531,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>1075</v>
       </c>
@@ -23565,7 +23581,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1076</v>
       </c>
@@ -23615,7 +23631,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>1077</v>
       </c>
@@ -23665,7 +23681,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>1078</v>
       </c>
@@ -23715,7 +23731,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1079</v>
       </c>
@@ -23765,7 +23781,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1080</v>
       </c>
@@ -23815,7 +23831,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1081</v>
       </c>
@@ -23865,7 +23881,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1082</v>
       </c>
@@ -23915,7 +23931,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1083</v>
       </c>
@@ -23965,7 +23981,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>1084</v>
       </c>
@@ -24015,7 +24031,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1085</v>
       </c>
@@ -24065,7 +24081,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1115</v>
       </c>
@@ -24115,7 +24131,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1129</v>
       </c>
@@ -24165,7 +24181,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1130</v>
       </c>
@@ -24215,7 +24231,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1131</v>
       </c>
@@ -24265,7 +24281,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1132</v>
       </c>
@@ -24315,7 +24331,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1116</v>
       </c>
@@ -24365,7 +24381,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1117</v>
       </c>
@@ -24415,7 +24431,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1118</v>
       </c>
@@ -24465,7 +24481,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1119</v>
       </c>
@@ -24515,7 +24531,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1120</v>
       </c>
@@ -24565,7 +24581,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1121</v>
       </c>
@@ -24615,7 +24631,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1123</v>
       </c>
@@ -24665,7 +24681,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1124</v>
       </c>
@@ -24715,7 +24731,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1125</v>
       </c>
@@ -24765,7 +24781,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1133</v>
       </c>
@@ -24815,7 +24831,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1134</v>
       </c>
@@ -24865,7 +24881,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1135</v>
       </c>
@@ -24915,7 +24931,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1136</v>
       </c>
@@ -24965,7 +24981,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1137</v>
       </c>
@@ -25015,7 +25031,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1138</v>
       </c>
@@ -25065,7 +25081,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1139</v>
       </c>
@@ -25115,7 +25131,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1140</v>
       </c>
@@ -25165,7 +25181,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>1141</v>
       </c>
@@ -25215,7 +25231,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1142</v>
       </c>
@@ -25265,7 +25281,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1143</v>
       </c>
@@ -25315,7 +25331,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1144</v>
       </c>
@@ -25365,7 +25381,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1145</v>
       </c>
@@ -25415,7 +25431,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1146</v>
       </c>
@@ -25465,7 +25481,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1147</v>
       </c>
@@ -25515,7 +25531,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1148</v>
       </c>
@@ -25565,7 +25581,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1149</v>
       </c>
@@ -25615,7 +25631,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1150</v>
       </c>
@@ -25665,7 +25681,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1151</v>
       </c>
@@ -25715,7 +25731,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1152</v>
       </c>
@@ -25765,7 +25781,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1153</v>
       </c>
@@ -25815,7 +25831,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1154</v>
       </c>
@@ -25865,7 +25881,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1155</v>
       </c>
@@ -25915,7 +25931,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1156</v>
       </c>
@@ -25965,7 +25981,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1157</v>
       </c>
@@ -26015,7 +26031,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>1158</v>
       </c>
@@ -26065,7 +26081,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1159</v>
       </c>
@@ -26115,7 +26131,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1160</v>
       </c>
@@ -26165,7 +26181,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1161</v>
       </c>
@@ -26215,7 +26231,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1162</v>
       </c>
@@ -26265,7 +26281,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>1163</v>
       </c>
@@ -26315,7 +26331,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>1164</v>
       </c>
@@ -26415,7 +26431,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>1166</v>
       </c>
@@ -26465,7 +26481,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>1167</v>
       </c>
@@ -26565,7 +26581,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>1169</v>
       </c>
@@ -26615,7 +26631,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="438" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>1170</v>
       </c>
@@ -26665,7 +26681,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>1171</v>
       </c>
@@ -26715,7 +26731,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="440" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>1172</v>
       </c>
@@ -26765,7 +26781,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>1173</v>
       </c>
@@ -26815,7 +26831,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>1174</v>
       </c>
@@ -26865,7 +26881,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>1175</v>
       </c>
@@ -26915,7 +26931,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>1176</v>
       </c>
@@ -26965,7 +26981,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>1177</v>
       </c>
@@ -27015,7 +27031,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="446" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>1178</v>
       </c>
@@ -27065,7 +27081,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="447" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>1179</v>
       </c>
@@ -27112,7 +27128,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="448" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>1180</v>
       </c>
@@ -27159,7 +27175,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>1181</v>
       </c>
@@ -27206,7 +27222,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>1182</v>
       </c>
@@ -27253,7 +27269,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>1183</v>
       </c>
@@ -27300,7 +27316,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>1184</v>
       </c>
@@ -27347,7 +27363,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>1185</v>
       </c>
@@ -27394,7 +27410,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>1186</v>
       </c>
@@ -27441,7 +27457,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>1187</v>
       </c>
@@ -27488,7 +27504,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>1188</v>
       </c>
@@ -27535,7 +27551,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>1189</v>
       </c>
@@ -27629,7 +27645,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>1191</v>
       </c>
@@ -27676,7 +27692,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>1192</v>
       </c>
@@ -27723,7 +27739,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>1193</v>
       </c>
@@ -27770,7 +27786,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>1194</v>
       </c>
@@ -27817,7 +27833,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>1195</v>
       </c>
@@ -27864,7 +27880,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>1196</v>
       </c>
@@ -27911,7 +27927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>1197</v>
       </c>
@@ -27958,7 +27974,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>1198</v>
       </c>
@@ -28005,7 +28021,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>1199</v>
       </c>
@@ -28052,7 +28068,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>1200</v>
       </c>
@@ -28099,7 +28115,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>1201</v>
       </c>
@@ -28146,7 +28162,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>1202</v>
       </c>
@@ -28193,7 +28209,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>1203</v>
       </c>
@@ -28240,7 +28256,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>1204</v>
       </c>
@@ -28287,7 +28303,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>1205</v>
       </c>
@@ -28334,7 +28350,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>1206</v>
       </c>
@@ -28381,7 +28397,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>1207</v>
       </c>
@@ -28428,7 +28444,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>1208</v>
       </c>
@@ -28475,7 +28491,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>1209</v>
       </c>
@@ -28522,7 +28538,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>1210</v>
       </c>
@@ -28569,7 +28585,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>1211</v>
       </c>
@@ -28616,7 +28632,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>1212</v>
       </c>
@@ -28663,7 +28679,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>1213</v>
       </c>
@@ -28710,7 +28726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>1214</v>
       </c>
@@ -28757,7 +28773,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>1215</v>
       </c>
@@ -28804,7 +28820,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>1216</v>
       </c>
@@ -28851,7 +28867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>1217</v>
       </c>
@@ -28898,7 +28914,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>1218</v>
       </c>
@@ -28945,7 +28961,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>1219</v>
       </c>
@@ -28992,7 +29008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>1220</v>
       </c>
@@ -29039,7 +29055,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>1221</v>
       </c>
@@ -29086,7 +29102,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>1222</v>
       </c>
@@ -29133,7 +29149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>1223</v>
       </c>
@@ -29180,7 +29196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>1224</v>
       </c>
@@ -29227,7 +29243,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>1225</v>
       </c>
@@ -29274,7 +29290,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>1226</v>
       </c>
@@ -29321,7 +29337,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>1227</v>
       </c>
@@ -29368,7 +29384,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>1228</v>
       </c>
@@ -29415,7 +29431,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>1229</v>
       </c>
@@ -29462,7 +29478,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>1230</v>
       </c>
@@ -29509,7 +29525,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>1231</v>
       </c>
@@ -29556,7 +29572,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>1232</v>
       </c>
@@ -29603,7 +29619,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>1233</v>
       </c>
@@ -29650,7 +29666,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>1234</v>
       </c>
@@ -29697,7 +29713,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>1235</v>
       </c>
@@ -29744,7 +29760,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>1236</v>
       </c>
@@ -29791,7 +29807,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>1237</v>
       </c>
@@ -29838,7 +29854,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>1238</v>
       </c>
@@ -29885,7 +29901,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>1239</v>
       </c>
@@ -29932,7 +29948,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>1240</v>
       </c>
@@ -29979,7 +29995,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>1241</v>
       </c>
@@ -30026,7 +30042,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>1242</v>
       </c>
@@ -30073,7 +30089,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>1243</v>
       </c>
@@ -30120,7 +30136,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>1244</v>
       </c>
@@ -30167,7 +30183,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>1245</v>
       </c>
@@ -30214,7 +30230,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>1246</v>
       </c>
@@ -30261,7 +30277,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>1247</v>
       </c>
@@ -30308,7 +30324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>1248</v>
       </c>
@@ -30355,7 +30371,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>1249</v>
       </c>
@@ -30402,7 +30418,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>1250</v>
       </c>
@@ -30449,7 +30465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>1251</v>
       </c>
@@ -30496,7 +30512,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>1252</v>
       </c>
@@ -30543,7 +30559,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>1253</v>
       </c>
@@ -30590,7 +30606,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>1254</v>
       </c>
@@ -30637,7 +30653,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>1255</v>
       </c>
@@ -30684,7 +30700,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>1256</v>
       </c>
@@ -30731,7 +30747,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>1257</v>
       </c>
@@ -30778,7 +30794,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>1258</v>
       </c>
@@ -30825,7 +30841,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>1259</v>
       </c>
@@ -30872,7 +30888,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>1260</v>
       </c>
@@ -30919,7 +30935,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="529" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>1261</v>
       </c>
@@ -30966,7 +30982,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="530" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>1262</v>
       </c>
@@ -31013,7 +31029,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="531" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>1263</v>
       </c>
@@ -31057,7 +31073,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>1264</v>
       </c>
@@ -31101,7 +31117,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="533" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>1265</v>
       </c>
@@ -31148,7 +31164,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="534" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>1266</v>
       </c>
@@ -31195,7 +31211,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="535" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>1267</v>
       </c>
@@ -31242,7 +31258,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="536" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>1268</v>
       </c>
@@ -31289,7 +31305,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="537" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>1269</v>
       </c>
@@ -31336,7 +31352,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="538" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>1270</v>
       </c>
@@ -31383,7 +31399,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>1271</v>
       </c>
@@ -31427,7 +31443,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="540" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>1272</v>
       </c>
@@ -31471,7 +31487,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="541" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>1273</v>
       </c>
@@ -31518,7 +31534,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>1274</v>
       </c>
@@ -31565,7 +31581,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>1275</v>
       </c>
@@ -31612,7 +31628,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="544" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>1276</v>
       </c>
@@ -31659,7 +31675,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>1277</v>
       </c>
@@ -31706,7 +31722,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>1278</v>
       </c>
@@ -31753,7 +31769,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>1279</v>
       </c>
@@ -31800,7 +31816,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>1280</v>
       </c>
@@ -31847,7 +31863,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>1281</v>
       </c>
@@ -31894,7 +31910,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="550" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>1282</v>
       </c>
@@ -31941,7 +31957,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="551" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>1283</v>
       </c>
@@ -31988,7 +32004,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="552" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>1284</v>
       </c>
@@ -32035,7 +32051,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="553" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>1285</v>
       </c>
@@ -32082,7 +32098,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="554" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>1286</v>
       </c>
@@ -32129,7 +32145,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>1287</v>
       </c>
@@ -32176,7 +32192,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>1288</v>
       </c>
@@ -32226,7 +32242,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="557" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>1289</v>
       </c>
@@ -32276,7 +32292,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>1290</v>
       </c>
@@ -32326,7 +32342,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="559" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>1291</v>
       </c>
@@ -32376,7 +32392,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="560" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>1292</v>
       </c>
@@ -32426,7 +32442,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>1293</v>
       </c>
@@ -32476,7 +32492,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>1294</v>
       </c>
@@ -32526,7 +32542,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>1295</v>
       </c>
@@ -32576,7 +32592,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>1296</v>
       </c>
@@ -32626,7 +32642,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>1297</v>
       </c>
@@ -32676,7 +32692,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>1298</v>
       </c>
@@ -32726,7 +32742,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>1299</v>
       </c>
@@ -32776,7 +32792,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>1300</v>
       </c>
@@ -32826,7 +32842,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>1301</v>
       </c>
@@ -32876,7 +32892,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>1302</v>
       </c>
@@ -32926,7 +32942,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>1303</v>
       </c>
@@ -32976,7 +32992,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>1304</v>
       </c>
@@ -33026,7 +33042,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>1305</v>
       </c>
@@ -33076,7 +33092,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>1306</v>
       </c>
@@ -33126,7 +33142,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>1307</v>
       </c>
@@ -33176,7 +33192,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>1308</v>
       </c>
@@ -33226,7 +33242,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>1309</v>
       </c>
@@ -33276,7 +33292,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>1310</v>
       </c>
@@ -33326,7 +33342,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>1311</v>
       </c>
@@ -33376,7 +33392,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>1312</v>
       </c>
@@ -33426,7 +33442,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="581" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>1313</v>
       </c>
@@ -33476,7 +33492,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>1314</v>
       </c>
@@ -33526,7 +33542,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="583" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>1315</v>
       </c>
@@ -33576,7 +33592,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>1316</v>
       </c>
@@ -33626,7 +33642,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>1317</v>
       </c>
@@ -33676,7 +33692,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>1318</v>
       </c>
@@ -33726,7 +33742,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>1319</v>
       </c>
@@ -33776,7 +33792,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>1320</v>
       </c>
@@ -33826,7 +33842,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>1321</v>
       </c>
@@ -33876,7 +33892,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>1322</v>
       </c>
@@ -33926,7 +33942,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="591" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>1323</v>
       </c>
@@ -33976,7 +33992,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>1324</v>
       </c>
@@ -34026,7 +34042,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>1325</v>
       </c>
@@ -34076,7 +34092,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="594" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>1326</v>
       </c>
@@ -34126,7 +34142,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="595" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>1327</v>
       </c>
@@ -34176,7 +34192,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="596" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>1328</v>
       </c>
@@ -34226,7 +34242,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="597" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>1329</v>
       </c>
@@ -34276,7 +34292,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="598" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>1330</v>
       </c>
@@ -34326,7 +34342,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="599" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>1331</v>
       </c>
@@ -34376,7 +34392,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="600" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>1332</v>
       </c>
@@ -34426,7 +34442,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="601" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>1333</v>
       </c>
@@ -34476,7 +34492,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="602" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>1334</v>
       </c>
@@ -34526,7 +34542,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="603" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>1335</v>
       </c>
@@ -34576,7 +34592,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="604" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>1336</v>
       </c>
@@ -34626,7 +34642,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="605" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>1337</v>
       </c>
@@ -34676,7 +34692,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="606" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>1338</v>
       </c>
@@ -34726,7 +34742,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="607" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>1339</v>
       </c>
@@ -34776,7 +34792,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="608" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>1340</v>
       </c>
@@ -34826,7 +34842,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="609" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>1341</v>
       </c>
@@ -34876,7 +34892,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="610" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>1342</v>
       </c>
@@ -34926,7 +34942,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="611" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>1343</v>
       </c>
@@ -34976,7 +34992,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="612" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>1344</v>
       </c>
@@ -35026,7 +35042,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="613" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>1345</v>
       </c>
@@ -35076,7 +35092,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="614" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>1346</v>
       </c>
@@ -35126,7 +35142,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="615" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>1347</v>
       </c>
@@ -35176,7 +35192,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="616" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>1348</v>
       </c>
@@ -35226,7 +35242,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="617" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>1349</v>
       </c>
@@ -35276,7 +35292,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="618" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>1350</v>
       </c>
@@ -35326,7 +35342,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="619" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>1351</v>
       </c>
@@ -35376,7 +35392,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="620" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>1352</v>
       </c>
@@ -35426,7 +35442,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="621" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>1353</v>
       </c>
@@ -35476,7 +35492,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="622" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>1354</v>
       </c>
@@ -35526,7 +35542,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="623" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>1355</v>
       </c>
@@ -35576,7 +35592,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="624" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>1356</v>
       </c>
@@ -35626,7 +35642,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>1357</v>
       </c>
@@ -35673,7 +35689,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>1358</v>
       </c>
@@ -35720,7 +35736,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>1359</v>
       </c>
@@ -35767,7 +35783,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>1360</v>
       </c>
@@ -35814,7 +35830,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>1361</v>
       </c>
@@ -35861,7 +35877,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>1362</v>
       </c>
@@ -35908,7 +35924,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>1363</v>
       </c>
@@ -35955,7 +35971,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>1364</v>
       </c>
@@ -36002,7 +36018,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>1365</v>
       </c>
@@ -36049,7 +36065,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>1366</v>
       </c>
@@ -36096,7 +36112,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>1367</v>
       </c>
@@ -36143,7 +36159,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>1368</v>
       </c>
@@ -36190,7 +36206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>1369</v>
       </c>
@@ -36237,7 +36253,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>1370</v>
       </c>
@@ -36284,7 +36300,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>1371</v>
       </c>
@@ -36331,7 +36347,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>1372</v>
       </c>
@@ -36378,7 +36394,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>1373</v>
       </c>
@@ -36425,7 +36441,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>1374</v>
       </c>
@@ -36472,7 +36488,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>1375</v>
       </c>
@@ -36519,7 +36535,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>1376</v>
       </c>
@@ -36566,7 +36582,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>1377</v>
       </c>
@@ -36613,7 +36629,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>1378</v>
       </c>
@@ -36660,7 +36676,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>1379</v>
       </c>
@@ -36707,7 +36723,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>1380</v>
       </c>
@@ -36754,7 +36770,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>1381</v>
       </c>
@@ -36801,7 +36817,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>1382</v>
       </c>
@@ -36848,7 +36864,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>1383</v>
       </c>
@@ -36895,7 +36911,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>1384</v>
       </c>
@@ -36942,7 +36958,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="653" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
         <v>1385</v>
       </c>
@@ -36989,7 +37005,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="654" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
         <v>1386</v>
       </c>
@@ -37036,7 +37052,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
         <v>1387</v>
       </c>
@@ -37083,7 +37099,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
         <v>1388</v>
       </c>
@@ -37130,7 +37146,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
         <v>1389</v>
       </c>
@@ -37177,7 +37193,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
         <v>1390</v>
       </c>
@@ -37224,7 +37240,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
         <v>1391</v>
       </c>
@@ -37271,7 +37287,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
         <v>1392</v>
       </c>
@@ -37318,7 +37334,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
         <v>1393</v>
       </c>
@@ -37365,7 +37381,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
         <v>1394</v>
       </c>
@@ -37412,7 +37428,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="663" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
         <v>1395</v>
       </c>
@@ -37459,7 +37475,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="664" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
         <v>1396</v>
       </c>
@@ -37506,7 +37522,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
         <v>1397</v>
       </c>
@@ -37553,7 +37569,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="666" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
         <v>1398</v>
       </c>
@@ -37600,7 +37616,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="667" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
         <v>1399</v>
       </c>
@@ -37647,7 +37663,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="668" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
         <v>1400</v>
       </c>
@@ -37694,7 +37710,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="669" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
         <v>1401</v>
       </c>
@@ -37741,7 +37757,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="670" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
         <v>1402</v>
       </c>
@@ -37788,7 +37804,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="671" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
         <v>1403</v>
       </c>
@@ -37835,7 +37851,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="672" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
         <v>1404</v>
       </c>
@@ -37882,7 +37898,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="673" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
         <v>1405</v>
       </c>
@@ -37929,7 +37945,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="674" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
         <v>1406</v>
       </c>
@@ -37976,7 +37992,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="675" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
         <v>1407</v>
       </c>
@@ -38023,7 +38039,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="676" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
         <v>1408</v>
       </c>
@@ -38070,7 +38086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="677" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
         <v>1409</v>
       </c>
@@ -38117,7 +38133,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="678" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
         <v>1410</v>
       </c>
@@ -38164,7 +38180,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="679" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
         <v>1411</v>
       </c>
@@ -38211,7 +38227,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="680" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
         <v>1412</v>
       </c>
@@ -38258,7 +38274,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="681" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
         <v>1413</v>
       </c>
@@ -38305,7 +38321,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="682" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
         <v>1414</v>
       </c>
@@ -38352,7 +38368,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="683" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
         <v>1415</v>
       </c>
@@ -38399,7 +38415,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
         <v>1416</v>
       </c>
@@ -38446,7 +38462,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
         <v>1417</v>
       </c>
@@ -38493,7 +38509,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
         <v>1418</v>
       </c>
@@ -38540,7 +38556,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
         <v>1419</v>
       </c>
@@ -38587,7 +38603,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="688" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
         <v>1420</v>
       </c>
@@ -38634,7 +38650,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="689" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
         <v>1421</v>
       </c>
@@ -38681,7 +38697,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="690" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
         <v>1422</v>
       </c>
@@ -38728,7 +38744,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
         <v>1423</v>
       </c>
@@ -38775,7 +38791,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
         <v>1424</v>
       </c>
@@ -38822,7 +38838,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
         <v>1425</v>
       </c>
@@ -38869,7 +38885,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
         <v>1426</v>
       </c>
@@ -38916,7 +38932,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
         <v>1427</v>
       </c>
@@ -38963,7 +38979,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="696" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
         <v>1428</v>
       </c>
@@ -39010,7 +39026,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="697" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
         <v>1429</v>
       </c>
@@ -39057,7 +39073,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
         <v>1430</v>
       </c>
@@ -39104,7 +39120,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
         <v>1431</v>
       </c>
@@ -39151,7 +39167,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
         <v>1432</v>
       </c>
@@ -39198,7 +39214,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
         <v>1433</v>
       </c>
@@ -39245,7 +39261,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
         <v>1434</v>
       </c>
@@ -39292,7 +39308,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="703" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
         <v>1435</v>
       </c>
@@ -39339,7 +39355,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="704" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
         <v>1436</v>
       </c>
@@ -39386,7 +39402,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="705" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
         <v>1437</v>
       </c>
@@ -39433,7 +39449,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="706" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
         <v>1438</v>
       </c>
@@ -39480,7 +39496,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="707" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
         <v>1439</v>
       </c>
@@ -39527,7 +39543,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="708" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
         <v>1440</v>
       </c>
@@ -39574,7 +39590,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="709" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
         <v>1441</v>
       </c>
@@ -39621,7 +39637,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="710" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
         <v>1442</v>
       </c>
@@ -39668,7 +39684,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="711" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
         <v>1443</v>
       </c>
@@ -39715,7 +39731,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="712" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
         <v>1444</v>
       </c>
@@ -39762,7 +39778,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="713" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
         <v>1445</v>
       </c>
@@ -39809,7 +39825,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="714" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
         <v>1446</v>
       </c>
@@ -39856,7 +39872,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="715" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
         <v>1447</v>
       </c>
@@ -39903,7 +39919,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="716" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
         <v>1448</v>
       </c>
@@ -39950,7 +39966,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="717" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
         <v>1449</v>
       </c>
@@ -39997,7 +40013,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="718" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
         <v>1450</v>
       </c>
@@ -40044,7 +40060,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="719" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
         <v>1452</v>
       </c>
@@ -40091,7 +40107,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="720" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
         <v>1459</v>
       </c>
@@ -40138,7 +40154,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="721" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
         <v>1460</v>
       </c>
@@ -40182,7 +40198,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="722" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
         <v>1461</v>
       </c>
@@ -40226,7 +40242,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="723" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
         <v>1462</v>
       </c>
@@ -40270,7 +40286,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="724" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
         <v>1463</v>
       </c>
@@ -40317,7 +40333,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="725" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
         <v>1471</v>
       </c>
@@ -40361,7 +40377,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="726" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
         <v>1472</v>
       </c>
@@ -40405,7 +40421,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="727" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
         <v>1473</v>
       </c>
@@ -40449,7 +40465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="728" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
         <v>1474</v>
       </c>
@@ -40493,7 +40509,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="729" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
         <v>1475</v>
       </c>
@@ -40537,7 +40553,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="730" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
         <v>1476</v>
       </c>
@@ -40581,7 +40597,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="731" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
         <v>1532</v>
       </c>
@@ -40625,7 +40641,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="732" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
         <v>1533</v>
       </c>
@@ -40669,7 +40685,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="733" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
         <v>1534</v>
       </c>
@@ -40713,7 +40729,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="734" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
         <v>1535</v>
       </c>
@@ -40757,7 +40773,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="735" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
         <v>1536</v>
       </c>
@@ -40801,7 +40817,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="736" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
         <v>1537</v>
       </c>
@@ -40845,7 +40861,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="737" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
         <v>1538</v>
       </c>
@@ -40889,7 +40905,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="738" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
         <v>1539</v>
       </c>
@@ -40933,7 +40949,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="739" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
         <v>1540</v>
       </c>
@@ -40977,7 +40993,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="740" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
         <v>1541</v>
       </c>
@@ -41021,7 +41037,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="741" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
         <v>1542</v>
       </c>
@@ -41065,7 +41081,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="742" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
         <v>1543</v>
       </c>
@@ -41109,7 +41125,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="743" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
         <v>1544</v>
       </c>
@@ -41153,7 +41169,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="744" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
         <v>1545</v>
       </c>
@@ -41197,7 +41213,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="745" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
         <v>1546</v>
       </c>
@@ -41241,7 +41257,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="746" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
         <v>1547</v>
       </c>
@@ -41285,7 +41301,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="747" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
         <v>1548</v>
       </c>
@@ -41329,7 +41345,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="748" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
         <v>1549</v>
       </c>
@@ -41373,7 +41389,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="749" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
         <v>1550</v>
       </c>
@@ -41417,7 +41433,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="750" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
         <v>1551</v>
       </c>
@@ -41461,7 +41477,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="751" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
         <v>1552</v>
       </c>
@@ -41505,7 +41521,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="752" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
         <v>1553</v>
       </c>
@@ -41549,7 +41565,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="753" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
         <v>1554</v>
       </c>
@@ -41593,7 +41609,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="754" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
         <v>1555</v>
       </c>
@@ -41637,7 +41653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="755" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
         <v>1556</v>
       </c>
@@ -41681,7 +41697,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="756" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
         <v>1557</v>
       </c>
@@ -41725,7 +41741,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="757" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
         <v>1558</v>
       </c>
@@ -41769,7 +41785,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="758" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
         <v>1559</v>
       </c>
@@ -41813,7 +41829,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="759" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
         <v>1560</v>
       </c>
@@ -41857,7 +41873,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="760" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
         <v>1561</v>
       </c>
@@ -41901,7 +41917,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="761" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
         <v>1562</v>
       </c>
@@ -41945,7 +41961,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="762" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
         <v>1563</v>
       </c>
@@ -41989,7 +42005,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="763" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
         <v>1564</v>
       </c>
@@ -42033,7 +42049,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="764" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
         <v>1565</v>
       </c>
@@ -42077,7 +42093,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="765" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
         <v>1566</v>
       </c>
@@ -42121,7 +42137,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="766" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
         <v>1567</v>
       </c>
@@ -42165,7 +42181,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="767" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
         <v>1568</v>
       </c>
@@ -42209,7 +42225,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
         <v>1569</v>
       </c>
@@ -42253,7 +42269,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
         <v>1570</v>
       </c>
@@ -42297,7 +42313,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="770" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
         <v>1571</v>
       </c>
@@ -42341,7 +42357,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="771" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
         <v>1572</v>
       </c>
@@ -42385,7 +42401,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="772" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
         <v>1573</v>
       </c>
@@ -42429,7 +42445,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="773" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
         <v>1574</v>
       </c>
@@ -42473,7 +42489,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="774" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
         <v>1575</v>
       </c>
@@ -42517,7 +42533,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="775" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
         <v>1576</v>
       </c>
@@ -42561,7 +42577,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="776" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
         <v>1577</v>
       </c>
@@ -42605,7 +42621,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
         <v>1578</v>
       </c>
@@ -42649,7 +42665,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="778" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
         <v>1579</v>
       </c>
@@ -42693,7 +42709,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="779" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
         <v>1580</v>
       </c>
@@ -42737,7 +42753,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="780" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
         <v>1581</v>
       </c>
@@ -42781,7 +42797,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="781" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
         <v>1582</v>
       </c>
@@ -42825,7 +42841,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="782" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
         <v>1583</v>
       </c>
@@ -42869,7 +42885,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="783" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
         <v>1584</v>
       </c>
@@ -42913,7 +42929,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="784" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
         <v>1585</v>
       </c>
@@ -42957,7 +42973,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="785" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
         <v>1586</v>
       </c>
@@ -43001,7 +43017,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="786" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
         <v>1587</v>
       </c>
@@ -43045,7 +43061,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="787" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
         <v>1588</v>
       </c>
@@ -43089,7 +43105,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="788" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
         <v>1589</v>
       </c>
@@ -43133,7 +43149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="789" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" s="1" t="s">
         <v>1590</v>
       </c>
@@ -43177,7 +43193,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="790" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" s="1" t="s">
         <v>1591</v>
       </c>
@@ -43221,7 +43237,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="791" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" s="1" t="s">
         <v>1594</v>
       </c>
@@ -43271,7 +43287,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="792" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" s="1" t="s">
         <v>1595</v>
       </c>
@@ -43321,7 +43337,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="793" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
         <v>1596</v>
       </c>
@@ -43372,6 +43388,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P793" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="CUSILAYME APAZA MARILUZ"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P718">
     <sortCondition ref="D1:D718"/>
   </sortState>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD88101E-05FB-435A-A324-F1AFC043EAD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D4BF37-D8D1-4286-BAB3-D50BD68F2433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4921,7 +4921,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4981,12 +4981,6 @@
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -5011,7 +5005,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5034,7 +5028,6 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5380,7 +5373,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:P793"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5452,7 +5444,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>596</v>
       </c>
@@ -5499,7 +5491,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>598</v>
       </c>
@@ -5546,7 +5538,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>599</v>
       </c>
@@ -5593,7 +5585,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>600</v>
       </c>
@@ -5640,7 +5632,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>601</v>
       </c>
@@ -5687,7 +5679,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>602</v>
       </c>
@@ -5734,7 +5726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>603</v>
       </c>
@@ -5781,7 +5773,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>604</v>
       </c>
@@ -5828,7 +5820,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>605</v>
       </c>
@@ -5875,7 +5867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>606</v>
       </c>
@@ -5922,7 +5914,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>607</v>
       </c>
@@ -5969,7 +5961,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>608</v>
       </c>
@@ -6016,7 +6008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>609</v>
       </c>
@@ -6063,7 +6055,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>610</v>
       </c>
@@ -6110,7 +6102,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>611</v>
       </c>
@@ -6157,7 +6149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>612</v>
       </c>
@@ -6204,7 +6196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>613</v>
       </c>
@@ -6251,7 +6243,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>614</v>
       </c>
@@ -6298,7 +6290,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>615</v>
       </c>
@@ -6345,7 +6337,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>616</v>
       </c>
@@ -6392,7 +6384,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>617</v>
       </c>
@@ -6439,7 +6431,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>618</v>
       </c>
@@ -6486,7 +6478,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>619</v>
       </c>
@@ -6533,7 +6525,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>620</v>
       </c>
@@ -6580,7 +6572,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>621</v>
       </c>
@@ -6627,7 +6619,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>622</v>
       </c>
@@ -6674,7 +6666,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>623</v>
       </c>
@@ -6721,7 +6713,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>624</v>
       </c>
@@ -6768,7 +6760,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>625</v>
       </c>
@@ -6815,7 +6807,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>626</v>
       </c>
@@ -6862,7 +6854,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>627</v>
       </c>
@@ -6909,7 +6901,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>628</v>
       </c>
@@ -6956,7 +6948,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>629</v>
       </c>
@@ -7003,7 +6995,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>630</v>
       </c>
@@ -7050,7 +7042,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>631</v>
       </c>
@@ -7097,7 +7089,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>632</v>
       </c>
@@ -7144,7 +7136,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>633</v>
       </c>
@@ -7191,7 +7183,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>634</v>
       </c>
@@ -7238,7 +7230,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>635</v>
       </c>
@@ -7285,7 +7277,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>636</v>
       </c>
@@ -7332,7 +7324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>637</v>
       </c>
@@ -7379,7 +7371,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>638</v>
       </c>
@@ -7426,7 +7418,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>639</v>
       </c>
@@ -7473,7 +7465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>640</v>
       </c>
@@ -7520,7 +7512,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>641</v>
       </c>
@@ -7567,7 +7559,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>642</v>
       </c>
@@ -7614,7 +7606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>643</v>
       </c>
@@ -7661,7 +7653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>644</v>
       </c>
@@ -7708,7 +7700,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>645</v>
       </c>
@@ -7755,7 +7747,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>646</v>
       </c>
@@ -7802,7 +7794,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>647</v>
       </c>
@@ -7849,7 +7841,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>648</v>
       </c>
@@ -7896,7 +7888,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>649</v>
       </c>
@@ -7943,7 +7935,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>650</v>
       </c>
@@ -7990,7 +7982,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>651</v>
       </c>
@@ -8037,7 +8029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>652</v>
       </c>
@@ -8084,7 +8076,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>653</v>
       </c>
@@ -8131,7 +8123,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>654</v>
       </c>
@@ -8178,7 +8170,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>655</v>
       </c>
@@ -8225,7 +8217,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>656</v>
       </c>
@@ -8272,7 +8264,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>657</v>
       </c>
@@ -8319,7 +8311,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>658</v>
       </c>
@@ -8366,7 +8358,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>659</v>
       </c>
@@ -8413,7 +8405,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>660</v>
       </c>
@@ -8460,7 +8452,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>661</v>
       </c>
@@ -8507,7 +8499,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>662</v>
       </c>
@@ -8554,7 +8546,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>663</v>
       </c>
@@ -8601,7 +8593,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>664</v>
       </c>
@@ -8648,7 +8640,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>665</v>
       </c>
@@ -8695,7 +8687,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>666</v>
       </c>
@@ -8742,7 +8734,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>667</v>
       </c>
@@ -8789,7 +8781,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>668</v>
       </c>
@@ -8836,7 +8828,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>669</v>
       </c>
@@ -8883,7 +8875,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>670</v>
       </c>
@@ -8930,7 +8922,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>671</v>
       </c>
@@ -8977,7 +8969,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>672</v>
       </c>
@@ -9024,7 +9016,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>673</v>
       </c>
@@ -9071,7 +9063,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>674</v>
       </c>
@@ -9118,7 +9110,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>675</v>
       </c>
@@ -9165,7 +9157,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>676</v>
       </c>
@@ -9212,7 +9204,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>677</v>
       </c>
@@ -9259,7 +9251,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>678</v>
       </c>
@@ -9306,7 +9298,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>679</v>
       </c>
@@ -9353,7 +9345,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>680</v>
       </c>
@@ -9400,7 +9392,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>681</v>
       </c>
@@ -9447,7 +9439,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>682</v>
       </c>
@@ -9494,7 +9486,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>683</v>
       </c>
@@ -9541,7 +9533,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>684</v>
       </c>
@@ -9588,7 +9580,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>685</v>
       </c>
@@ -9635,7 +9627,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>686</v>
       </c>
@@ -9682,7 +9674,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>687</v>
       </c>
@@ -9729,7 +9721,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>688</v>
       </c>
@@ -9776,7 +9768,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>689</v>
       </c>
@@ -9823,7 +9815,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>690</v>
       </c>
@@ -9870,7 +9862,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>691</v>
       </c>
@@ -9917,7 +9909,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>692</v>
       </c>
@@ -9964,7 +9956,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>693</v>
       </c>
@@ -10011,7 +10003,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>694</v>
       </c>
@@ -10058,7 +10050,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>695</v>
       </c>
@@ -10105,7 +10097,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>696</v>
       </c>
@@ -10152,7 +10144,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>697</v>
       </c>
@@ -10199,7 +10191,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>698</v>
       </c>
@@ -10246,7 +10238,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>699</v>
       </c>
@@ -10293,7 +10285,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>700</v>
       </c>
@@ -10340,7 +10332,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>701</v>
       </c>
@@ -10387,7 +10379,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>702</v>
       </c>
@@ -10434,7 +10426,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>703</v>
       </c>
@@ -10481,7 +10473,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>704</v>
       </c>
@@ -10528,7 +10520,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>705</v>
       </c>
@@ -10575,7 +10567,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>706</v>
       </c>
@@ -10622,7 +10614,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>707</v>
       </c>
@@ -10669,7 +10661,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>708</v>
       </c>
@@ -10716,7 +10708,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>709</v>
       </c>
@@ -10763,7 +10755,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>710</v>
       </c>
@@ -10810,7 +10802,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>711</v>
       </c>
@@ -10857,7 +10849,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>712</v>
       </c>
@@ -10951,7 +10943,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>714</v>
       </c>
@@ -10998,7 +10990,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>715</v>
       </c>
@@ -11045,7 +11037,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>716</v>
       </c>
@@ -11092,7 +11084,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>717</v>
       </c>
@@ -11139,7 +11131,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>718</v>
       </c>
@@ -11186,7 +11178,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>719</v>
       </c>
@@ -11233,7 +11225,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>720</v>
       </c>
@@ -11280,7 +11272,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>721</v>
       </c>
@@ -11327,7 +11319,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>722</v>
       </c>
@@ -11374,7 +11366,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>723</v>
       </c>
@@ -11421,7 +11413,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>724</v>
       </c>
@@ -11468,7 +11460,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>725</v>
       </c>
@@ -11515,7 +11507,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>726</v>
       </c>
@@ -11562,7 +11554,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>727</v>
       </c>
@@ -11609,7 +11601,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>728</v>
       </c>
@@ -11656,7 +11648,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>729</v>
       </c>
@@ -11703,7 +11695,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>730</v>
       </c>
@@ -11750,7 +11742,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>731</v>
       </c>
@@ -11797,7 +11789,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>732</v>
       </c>
@@ -11844,7 +11836,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>733</v>
       </c>
@@ -11891,7 +11883,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>734</v>
       </c>
@@ -11938,7 +11930,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>735</v>
       </c>
@@ -11985,7 +11977,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>736</v>
       </c>
@@ -12032,7 +12024,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>737</v>
       </c>
@@ -12079,7 +12071,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>738</v>
       </c>
@@ -12126,7 +12118,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>739</v>
       </c>
@@ -12173,7 +12165,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>740</v>
       </c>
@@ -12220,7 +12212,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>741</v>
       </c>
@@ -12267,7 +12259,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>742</v>
       </c>
@@ -12314,7 +12306,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>743</v>
       </c>
@@ -12361,7 +12353,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>744</v>
       </c>
@@ -12408,7 +12400,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>745</v>
       </c>
@@ -12455,7 +12447,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>746</v>
       </c>
@@ -12502,7 +12494,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>747</v>
       </c>
@@ -12549,7 +12541,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>748</v>
       </c>
@@ -12596,7 +12588,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>749</v>
       </c>
@@ -12643,7 +12635,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>750</v>
       </c>
@@ -12690,7 +12682,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>751</v>
       </c>
@@ -12737,7 +12729,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>752</v>
       </c>
@@ -12784,7 +12776,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>753</v>
       </c>
@@ -12831,7 +12823,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>754</v>
       </c>
@@ -12878,7 +12870,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>755</v>
       </c>
@@ -12925,7 +12917,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>756</v>
       </c>
@@ -12972,7 +12964,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>757</v>
       </c>
@@ -13019,7 +13011,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>758</v>
       </c>
@@ -13066,7 +13058,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>759</v>
       </c>
@@ -13113,7 +13105,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>760</v>
       </c>
@@ -13160,7 +13152,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>761</v>
       </c>
@@ -13207,7 +13199,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>762</v>
       </c>
@@ -13254,7 +13246,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>763</v>
       </c>
@@ -13301,7 +13293,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>764</v>
       </c>
@@ -13351,7 +13343,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>765</v>
       </c>
@@ -13401,7 +13393,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>766</v>
       </c>
@@ -13451,7 +13443,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>767</v>
       </c>
@@ -13501,7 +13493,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>768</v>
       </c>
@@ -13551,7 +13543,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>769</v>
       </c>
@@ -13601,7 +13593,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>770</v>
       </c>
@@ -13651,7 +13643,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>771</v>
       </c>
@@ -13701,7 +13693,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>772</v>
       </c>
@@ -13751,7 +13743,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>773</v>
       </c>
@@ -13801,7 +13793,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>774</v>
       </c>
@@ -13851,7 +13843,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>775</v>
       </c>
@@ -13901,7 +13893,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>776</v>
       </c>
@@ -13951,7 +13943,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>777</v>
       </c>
@@ -14001,7 +13993,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>778</v>
       </c>
@@ -14051,7 +14043,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>779</v>
       </c>
@@ -14101,7 +14093,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>780</v>
       </c>
@@ -14151,7 +14143,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>781</v>
       </c>
@@ -14201,7 +14193,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>782</v>
       </c>
@@ -14301,7 +14293,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>784</v>
       </c>
@@ -14351,7 +14343,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>785</v>
       </c>
@@ -14401,7 +14393,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>786</v>
       </c>
@@ -14451,7 +14443,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>787</v>
       </c>
@@ -14501,7 +14493,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>788</v>
       </c>
@@ -14551,7 +14543,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>789</v>
       </c>
@@ -14601,7 +14593,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>790</v>
       </c>
@@ -14651,7 +14643,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>791</v>
       </c>
@@ -14701,7 +14693,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>792</v>
       </c>
@@ -14751,7 +14743,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>793</v>
       </c>
@@ -14801,7 +14793,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>794</v>
       </c>
@@ -14851,7 +14843,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>795</v>
       </c>
@@ -14901,7 +14893,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>796</v>
       </c>
@@ -14951,7 +14943,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>797</v>
       </c>
@@ -15001,7 +14993,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>798</v>
       </c>
@@ -15051,7 +15043,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>799</v>
       </c>
@@ -15101,7 +15093,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>800</v>
       </c>
@@ -15151,7 +15143,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>801</v>
       </c>
@@ -15201,7 +15193,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>802</v>
       </c>
@@ -15251,7 +15243,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>803</v>
       </c>
@@ -15301,7 +15293,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>804</v>
       </c>
@@ -15351,7 +15343,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>805</v>
       </c>
@@ -15401,7 +15393,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>806</v>
       </c>
@@ -15451,7 +15443,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>807</v>
       </c>
@@ -15501,7 +15493,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>808</v>
       </c>
@@ -15551,7 +15543,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>809</v>
       </c>
@@ -15601,7 +15593,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>810</v>
       </c>
@@ -15651,7 +15643,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>811</v>
       </c>
@@ -15701,7 +15693,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>812</v>
       </c>
@@ -15751,7 +15743,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>813</v>
       </c>
@@ -15801,7 +15793,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>814</v>
       </c>
@@ -15851,7 +15843,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>815</v>
       </c>
@@ -15901,7 +15893,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>816</v>
       </c>
@@ -15951,7 +15943,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>817</v>
       </c>
@@ -16001,7 +15993,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>836</v>
       </c>
@@ -16051,7 +16043,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>837</v>
       </c>
@@ -16101,7 +16093,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>838</v>
       </c>
@@ -16151,7 +16143,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>839</v>
       </c>
@@ -16198,7 +16190,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>840</v>
       </c>
@@ -16245,7 +16237,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>841</v>
       </c>
@@ -16292,7 +16284,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>842</v>
       </c>
@@ -16339,7 +16331,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>843</v>
       </c>
@@ -16386,7 +16378,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>844</v>
       </c>
@@ -16433,7 +16425,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>845</v>
       </c>
@@ -16480,7 +16472,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>846</v>
       </c>
@@ -16527,7 +16519,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>847</v>
       </c>
@@ -16574,7 +16566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>848</v>
       </c>
@@ -16621,7 +16613,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>849</v>
       </c>
@@ -16668,7 +16660,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>850</v>
       </c>
@@ -16715,7 +16707,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>851</v>
       </c>
@@ -16762,7 +16754,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>852</v>
       </c>
@@ -16809,7 +16801,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>880</v>
       </c>
@@ -16856,7 +16848,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>881</v>
       </c>
@@ -16903,7 +16895,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>882</v>
       </c>
@@ -16950,7 +16942,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>883</v>
       </c>
@@ -16997,7 +16989,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>884</v>
       </c>
@@ -17044,7 +17036,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>885</v>
       </c>
@@ -17091,7 +17083,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>886</v>
       </c>
@@ -17138,7 +17130,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>887</v>
       </c>
@@ -17185,7 +17177,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>888</v>
       </c>
@@ -17232,7 +17224,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>889</v>
       </c>
@@ -17279,7 +17271,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>890</v>
       </c>
@@ -17326,7 +17318,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>891</v>
       </c>
@@ -17373,7 +17365,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>892</v>
       </c>
@@ -17420,7 +17412,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>893</v>
       </c>
@@ -17467,7 +17459,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>894</v>
       </c>
@@ -17514,7 +17506,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>895</v>
       </c>
@@ -17564,7 +17556,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>896</v>
       </c>
@@ -17614,7 +17606,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>897</v>
       </c>
@@ -17664,7 +17656,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>898</v>
       </c>
@@ -17714,7 +17706,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>899</v>
       </c>
@@ -17764,7 +17756,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>900</v>
       </c>
@@ -17814,7 +17806,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>901</v>
       </c>
@@ -17864,7 +17856,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>902</v>
       </c>
@@ -18011,7 +18003,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>905</v>
       </c>
@@ -18061,7 +18053,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>906</v>
       </c>
@@ -18111,7 +18103,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>907</v>
       </c>
@@ -18161,7 +18153,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>908</v>
       </c>
@@ -18211,7 +18203,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>909</v>
       </c>
@@ -18261,7 +18253,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>910</v>
       </c>
@@ -18311,7 +18303,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>911</v>
       </c>
@@ -18361,7 +18353,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>912</v>
       </c>
@@ -18411,7 +18403,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>913</v>
       </c>
@@ -18461,7 +18453,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="274" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>914</v>
       </c>
@@ -18511,7 +18503,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>915</v>
       </c>
@@ -18561,7 +18553,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>916</v>
       </c>
@@ -18611,7 +18603,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>917</v>
       </c>
@@ -18661,7 +18653,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>918</v>
       </c>
@@ -18711,7 +18703,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>919</v>
       </c>
@@ -18761,7 +18753,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>920</v>
       </c>
@@ -18811,7 +18803,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>921</v>
       </c>
@@ -18861,7 +18853,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>922</v>
       </c>
@@ -18911,7 +18903,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>923</v>
       </c>
@@ -18961,7 +18953,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>924</v>
       </c>
@@ -19011,7 +19003,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>925</v>
       </c>
@@ -19061,7 +19053,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>926</v>
       </c>
@@ -19111,7 +19103,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>927</v>
       </c>
@@ -19161,7 +19153,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>928</v>
       </c>
@@ -19211,7 +19203,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>929</v>
       </c>
@@ -19261,7 +19253,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>930</v>
       </c>
@@ -19311,7 +19303,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>931</v>
       </c>
@@ -19361,7 +19353,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>932</v>
       </c>
@@ -19411,7 +19403,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>959</v>
       </c>
@@ -19461,7 +19453,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>960</v>
       </c>
@@ -19511,7 +19503,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>961</v>
       </c>
@@ -19561,7 +19553,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>962</v>
       </c>
@@ -19611,7 +19603,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>963</v>
       </c>
@@ -19661,7 +19653,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>964</v>
       </c>
@@ -19708,7 +19700,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>965</v>
       </c>
@@ -19755,7 +19747,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>966</v>
       </c>
@@ -19802,7 +19794,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>967</v>
       </c>
@@ -19849,7 +19841,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>968</v>
       </c>
@@ -19896,7 +19888,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>969</v>
       </c>
@@ -19943,7 +19935,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>1003</v>
       </c>
@@ -19990,7 +19982,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>1004</v>
       </c>
@@ -20037,7 +20029,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>1005</v>
       </c>
@@ -20084,7 +20076,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>1006</v>
       </c>
@@ -20131,7 +20123,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>1007</v>
       </c>
@@ -20181,7 +20173,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>1008</v>
       </c>
@@ -20231,7 +20223,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="310" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>1009</v>
       </c>
@@ -20281,7 +20273,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>1010</v>
       </c>
@@ -20331,7 +20323,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>1011</v>
       </c>
@@ -20381,7 +20373,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1012</v>
       </c>
@@ -20431,7 +20423,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1013</v>
       </c>
@@ -20481,7 +20473,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="315" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>1014</v>
       </c>
@@ -20531,7 +20523,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>1015</v>
       </c>
@@ -20581,7 +20573,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1016</v>
       </c>
@@ -20631,7 +20623,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>1017</v>
       </c>
@@ -20681,7 +20673,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>1018</v>
       </c>
@@ -20731,7 +20723,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>1019</v>
       </c>
@@ -20781,7 +20773,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>1020</v>
       </c>
@@ -20831,7 +20823,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>1021</v>
       </c>
@@ -20881,7 +20873,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>1022</v>
       </c>
@@ -20931,7 +20923,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>1023</v>
       </c>
@@ -20981,7 +20973,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>1024</v>
       </c>
@@ -21031,7 +21023,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1025</v>
       </c>
@@ -21081,7 +21073,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>1026</v>
       </c>
@@ -21131,7 +21123,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>1027</v>
       </c>
@@ -21181,7 +21173,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>1028</v>
       </c>
@@ -21231,7 +21223,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>1029</v>
       </c>
@@ -21281,7 +21273,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>1030</v>
       </c>
@@ -21331,7 +21323,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>1031</v>
       </c>
@@ -21381,7 +21373,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>1032</v>
       </c>
@@ -21431,7 +21423,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>1033</v>
       </c>
@@ -21481,7 +21473,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>1034</v>
       </c>
@@ -21531,7 +21523,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>1035</v>
       </c>
@@ -21581,7 +21573,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>1036</v>
       </c>
@@ -21631,7 +21623,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>1037</v>
       </c>
@@ -21681,7 +21673,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>1038</v>
       </c>
@@ -21731,7 +21723,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>1039</v>
       </c>
@@ -21781,7 +21773,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>1040</v>
       </c>
@@ -21831,7 +21823,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>1041</v>
       </c>
@@ -21881,7 +21873,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1042</v>
       </c>
@@ -21931,7 +21923,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1043</v>
       </c>
@@ -21981,7 +21973,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>1044</v>
       </c>
@@ -22031,7 +22023,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>1045</v>
       </c>
@@ -22081,7 +22073,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1046</v>
       </c>
@@ -22131,7 +22123,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>1047</v>
       </c>
@@ -22181,7 +22173,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>1048</v>
       </c>
@@ -22231,7 +22223,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>1049</v>
       </c>
@@ -22281,7 +22273,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>1050</v>
       </c>
@@ -22331,7 +22323,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>1051</v>
       </c>
@@ -22381,7 +22373,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>1052</v>
       </c>
@@ -22431,7 +22423,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>1053</v>
       </c>
@@ -22481,7 +22473,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>1054</v>
       </c>
@@ -22531,7 +22523,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>1055</v>
       </c>
@@ -22581,7 +22573,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>1056</v>
       </c>
@@ -22631,7 +22623,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>1057</v>
       </c>
@@ -22681,7 +22673,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>1058</v>
       </c>
@@ -22731,7 +22723,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>1059</v>
       </c>
@@ -22781,7 +22773,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>1060</v>
       </c>
@@ -22831,7 +22823,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1061</v>
       </c>
@@ -22881,7 +22873,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1062</v>
       </c>
@@ -22931,7 +22923,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>1063</v>
       </c>
@@ -23031,7 +23023,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1065</v>
       </c>
@@ -23081,7 +23073,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1066</v>
       </c>
@@ -23131,7 +23123,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>1067</v>
       </c>
@@ -23181,7 +23173,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1068</v>
       </c>
@@ -23231,7 +23223,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1069</v>
       </c>
@@ -23281,7 +23273,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>1070</v>
       </c>
@@ -23331,7 +23323,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1071</v>
       </c>
@@ -23381,7 +23373,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1072</v>
       </c>
@@ -23431,7 +23423,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1073</v>
       </c>
@@ -23481,7 +23473,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>1074</v>
       </c>
@@ -23531,7 +23523,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>1075</v>
       </c>
@@ -23581,7 +23573,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1076</v>
       </c>
@@ -23631,7 +23623,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>1077</v>
       </c>
@@ -23681,7 +23673,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>1078</v>
       </c>
@@ -23731,7 +23723,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1079</v>
       </c>
@@ -23781,7 +23773,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1080</v>
       </c>
@@ -23831,7 +23823,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1081</v>
       </c>
@@ -23881,7 +23873,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1082</v>
       </c>
@@ -23931,7 +23923,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1083</v>
       </c>
@@ -23981,7 +23973,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>1084</v>
       </c>
@@ -24031,7 +24023,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1085</v>
       </c>
@@ -24081,7 +24073,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1115</v>
       </c>
@@ -24131,7 +24123,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1129</v>
       </c>
@@ -24181,7 +24173,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1130</v>
       </c>
@@ -24231,7 +24223,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1131</v>
       </c>
@@ -24281,7 +24273,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1132</v>
       </c>
@@ -24331,7 +24323,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1116</v>
       </c>
@@ -24381,7 +24373,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1117</v>
       </c>
@@ -24431,7 +24423,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1118</v>
       </c>
@@ -24481,7 +24473,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1119</v>
       </c>
@@ -24531,7 +24523,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1120</v>
       </c>
@@ -24581,7 +24573,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1121</v>
       </c>
@@ -24631,7 +24623,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1123</v>
       </c>
@@ -24681,7 +24673,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1124</v>
       </c>
@@ -24731,7 +24723,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1125</v>
       </c>
@@ -24781,7 +24773,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1133</v>
       </c>
@@ -24831,7 +24823,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1134</v>
       </c>
@@ -24881,7 +24873,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1135</v>
       </c>
@@ -24931,7 +24923,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1136</v>
       </c>
@@ -24981,7 +24973,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1137</v>
       </c>
@@ -25031,7 +25023,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1138</v>
       </c>
@@ -25081,7 +25073,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1139</v>
       </c>
@@ -25131,7 +25123,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1140</v>
       </c>
@@ -25181,7 +25173,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>1141</v>
       </c>
@@ -25231,7 +25223,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1142</v>
       </c>
@@ -25281,7 +25273,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1143</v>
       </c>
@@ -25331,7 +25323,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1144</v>
       </c>
@@ -25381,7 +25373,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1145</v>
       </c>
@@ -25431,7 +25423,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1146</v>
       </c>
@@ -25481,7 +25473,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1147</v>
       </c>
@@ -25531,7 +25523,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1148</v>
       </c>
@@ -25581,7 +25573,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1149</v>
       </c>
@@ -25631,7 +25623,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1150</v>
       </c>
@@ -25681,7 +25673,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1151</v>
       </c>
@@ -25731,7 +25723,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1152</v>
       </c>
@@ -25781,7 +25773,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1153</v>
       </c>
@@ -25831,7 +25823,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1154</v>
       </c>
@@ -25881,7 +25873,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1155</v>
       </c>
@@ -25931,7 +25923,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1156</v>
       </c>
@@ -25981,7 +25973,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1157</v>
       </c>
@@ -26031,7 +26023,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>1158</v>
       </c>
@@ -26081,7 +26073,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1159</v>
       </c>
@@ -26131,7 +26123,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1160</v>
       </c>
@@ -26181,7 +26173,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1161</v>
       </c>
@@ -26231,7 +26223,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1162</v>
       </c>
@@ -26281,7 +26273,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>1163</v>
       </c>
@@ -26331,7 +26323,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>1164</v>
       </c>
@@ -26431,7 +26423,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>1166</v>
       </c>
@@ -26481,7 +26473,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>1167</v>
       </c>
@@ -26581,7 +26573,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>1169</v>
       </c>
@@ -26631,7 +26623,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>1170</v>
       </c>
@@ -26681,7 +26673,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>1171</v>
       </c>
@@ -26731,7 +26723,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>1172</v>
       </c>
@@ -26781,7 +26773,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>1173</v>
       </c>
@@ -26831,7 +26823,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>1174</v>
       </c>
@@ -26881,7 +26873,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>1175</v>
       </c>
@@ -26931,7 +26923,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>1176</v>
       </c>
@@ -26981,7 +26973,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>1177</v>
       </c>
@@ -27031,7 +27023,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="446" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>1178</v>
       </c>
@@ -27081,7 +27073,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="447" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>1179</v>
       </c>
@@ -27128,7 +27120,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="448" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>1180</v>
       </c>
@@ -27175,7 +27167,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="449" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>1181</v>
       </c>
@@ -27222,7 +27214,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="450" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>1182</v>
       </c>
@@ -27269,7 +27261,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="451" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>1183</v>
       </c>
@@ -27316,7 +27308,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="452" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>1184</v>
       </c>
@@ -27363,7 +27355,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="453" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>1185</v>
       </c>
@@ -27410,7 +27402,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="454" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>1186</v>
       </c>
@@ -27457,7 +27449,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="455" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>1187</v>
       </c>
@@ -27504,7 +27496,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="456" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>1188</v>
       </c>
@@ -27551,7 +27543,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="457" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>1189</v>
       </c>
@@ -27645,7 +27637,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="459" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>1191</v>
       </c>
@@ -27692,7 +27684,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="460" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>1192</v>
       </c>
@@ -27739,7 +27731,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="461" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>1193</v>
       </c>
@@ -27786,7 +27778,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="462" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>1194</v>
       </c>
@@ -27833,7 +27825,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="463" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>1195</v>
       </c>
@@ -27880,7 +27872,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="464" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>1196</v>
       </c>
@@ -27927,7 +27919,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>1197</v>
       </c>
@@ -27974,7 +27966,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="466" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>1198</v>
       </c>
@@ -28021,7 +28013,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="467" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>1199</v>
       </c>
@@ -28068,7 +28060,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>1200</v>
       </c>
@@ -28115,7 +28107,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="469" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>1201</v>
       </c>
@@ -28162,7 +28154,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>1202</v>
       </c>
@@ -28209,7 +28201,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>1203</v>
       </c>
@@ -28256,7 +28248,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="472" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>1204</v>
       </c>
@@ -28303,7 +28295,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="473" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>1205</v>
       </c>
@@ -28350,7 +28342,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>1206</v>
       </c>
@@ -28397,7 +28389,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="475" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>1207</v>
       </c>
@@ -28444,7 +28436,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="476" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>1208</v>
       </c>
@@ -28491,7 +28483,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>1209</v>
       </c>
@@ -28538,7 +28530,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>1210</v>
       </c>
@@ -28585,7 +28577,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="479" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>1211</v>
       </c>
@@ -28632,7 +28624,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="480" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>1212</v>
       </c>
@@ -28679,7 +28671,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="481" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>1213</v>
       </c>
@@ -28726,7 +28718,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="482" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>1214</v>
       </c>
@@ -28773,7 +28765,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="483" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>1215</v>
       </c>
@@ -28820,7 +28812,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="484" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>1216</v>
       </c>
@@ -28867,7 +28859,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="485" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>1217</v>
       </c>
@@ -28914,7 +28906,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="486" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>1218</v>
       </c>
@@ -28961,7 +28953,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="487" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>1219</v>
       </c>
@@ -29008,7 +29000,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="488" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>1220</v>
       </c>
@@ -29055,7 +29047,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="489" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>1221</v>
       </c>
@@ -29102,7 +29094,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>1222</v>
       </c>
@@ -29149,7 +29141,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="491" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>1223</v>
       </c>
@@ -29196,7 +29188,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="492" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>1224</v>
       </c>
@@ -29243,7 +29235,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="493" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>1225</v>
       </c>
@@ -29290,7 +29282,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="494" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>1226</v>
       </c>
@@ -29337,7 +29329,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="495" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>1227</v>
       </c>
@@ -29384,7 +29376,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="496" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>1228</v>
       </c>
@@ -29431,7 +29423,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="497" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>1229</v>
       </c>
@@ -29478,7 +29470,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="498" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>1230</v>
       </c>
@@ -29525,7 +29517,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>1231</v>
       </c>
@@ -29572,7 +29564,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>1232</v>
       </c>
@@ -29619,7 +29611,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>1233</v>
       </c>
@@ -29666,7 +29658,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="502" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>1234</v>
       </c>
@@ -29713,7 +29705,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="503" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>1235</v>
       </c>
@@ -29760,7 +29752,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>1236</v>
       </c>
@@ -29807,7 +29799,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="505" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>1237</v>
       </c>
@@ -29854,7 +29846,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="506" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>1238</v>
       </c>
@@ -29901,7 +29893,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="507" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>1239</v>
       </c>
@@ -29948,7 +29940,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="508" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>1240</v>
       </c>
@@ -29995,7 +29987,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="509" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>1241</v>
       </c>
@@ -30042,7 +30034,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="510" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>1242</v>
       </c>
@@ -30089,7 +30081,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="511" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>1243</v>
       </c>
@@ -30136,7 +30128,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="512" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>1244</v>
       </c>
@@ -30183,7 +30175,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="513" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>1245</v>
       </c>
@@ -30230,7 +30222,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="514" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>1246</v>
       </c>
@@ -30277,7 +30269,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="515" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>1247</v>
       </c>
@@ -30324,7 +30316,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="516" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>1248</v>
       </c>
@@ -30371,7 +30363,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="517" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>1249</v>
       </c>
@@ -30418,7 +30410,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="518" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>1250</v>
       </c>
@@ -30465,7 +30457,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="519" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>1251</v>
       </c>
@@ -30512,7 +30504,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="520" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>1252</v>
       </c>
@@ -30559,7 +30551,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="521" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>1253</v>
       </c>
@@ -30606,7 +30598,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="522" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>1254</v>
       </c>
@@ -30653,7 +30645,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="523" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>1255</v>
       </c>
@@ -30700,7 +30692,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="524" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>1256</v>
       </c>
@@ -30747,7 +30739,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="525" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>1257</v>
       </c>
@@ -30794,7 +30786,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="526" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>1258</v>
       </c>
@@ -30841,7 +30833,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="527" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>1259</v>
       </c>
@@ -30888,7 +30880,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="528" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>1260</v>
       </c>
@@ -30935,7 +30927,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="529" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>1261</v>
       </c>
@@ -30982,7 +30974,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="530" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>1262</v>
       </c>
@@ -31029,7 +31021,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="531" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>1263</v>
       </c>
@@ -31073,7 +31065,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="532" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>1264</v>
       </c>
@@ -31117,7 +31109,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="533" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>1265</v>
       </c>
@@ -31164,7 +31156,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="534" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>1266</v>
       </c>
@@ -31211,7 +31203,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="535" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>1267</v>
       </c>
@@ -31258,7 +31250,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="536" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>1268</v>
       </c>
@@ -31305,7 +31297,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="537" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>1269</v>
       </c>
@@ -31352,7 +31344,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="538" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>1270</v>
       </c>
@@ -31399,7 +31391,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="539" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>1271</v>
       </c>
@@ -31443,7 +31435,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="540" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>1272</v>
       </c>
@@ -31487,7 +31479,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="541" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>1273</v>
       </c>
@@ -31534,7 +31526,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="542" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>1274</v>
       </c>
@@ -31581,7 +31573,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="543" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>1275</v>
       </c>
@@ -31628,7 +31620,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="544" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>1276</v>
       </c>
@@ -31675,7 +31667,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>1277</v>
       </c>
@@ -31722,7 +31714,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>1278</v>
       </c>
@@ -31769,7 +31761,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>1279</v>
       </c>
@@ -31816,7 +31808,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>1280</v>
       </c>
@@ -31863,7 +31855,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>1281</v>
       </c>
@@ -31910,7 +31902,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>1282</v>
       </c>
@@ -31957,7 +31949,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>1283</v>
       </c>
@@ -32004,7 +31996,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>1284</v>
       </c>
@@ -32051,7 +32043,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>1285</v>
       </c>
@@ -32098,7 +32090,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>1286</v>
       </c>
@@ -32145,7 +32137,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>1287</v>
       </c>
@@ -32192,7 +32184,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>1288</v>
       </c>
@@ -32242,7 +32234,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>1289</v>
       </c>
@@ -32292,7 +32284,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>1290</v>
       </c>
@@ -32342,7 +32334,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>1291</v>
       </c>
@@ -32392,7 +32384,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>1292</v>
       </c>
@@ -32442,7 +32434,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>1293</v>
       </c>
@@ -32492,7 +32484,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>1294</v>
       </c>
@@ -32542,7 +32534,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>1295</v>
       </c>
@@ -32592,7 +32584,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>1296</v>
       </c>
@@ -32642,7 +32634,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>1297</v>
       </c>
@@ -32692,7 +32684,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>1298</v>
       </c>
@@ -32742,7 +32734,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>1299</v>
       </c>
@@ -32792,7 +32784,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>1300</v>
       </c>
@@ -32842,7 +32834,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>1301</v>
       </c>
@@ -32892,7 +32884,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>1302</v>
       </c>
@@ -32942,7 +32934,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>1303</v>
       </c>
@@ -32992,7 +32984,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>1304</v>
       </c>
@@ -33042,7 +33034,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>1305</v>
       </c>
@@ -33092,7 +33084,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>1306</v>
       </c>
@@ -33142,7 +33134,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>1307</v>
       </c>
@@ -33192,7 +33184,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>1308</v>
       </c>
@@ -33242,7 +33234,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>1309</v>
       </c>
@@ -33292,7 +33284,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>1310</v>
       </c>
@@ -33342,7 +33334,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>1311</v>
       </c>
@@ -33392,7 +33384,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>1312</v>
       </c>
@@ -33442,7 +33434,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>1313</v>
       </c>
@@ -33492,7 +33484,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>1314</v>
       </c>
@@ -33542,7 +33534,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>1315</v>
       </c>
@@ -33592,7 +33584,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>1316</v>
       </c>
@@ -33642,7 +33634,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>1317</v>
       </c>
@@ -33692,7 +33684,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>1318</v>
       </c>
@@ -33742,7 +33734,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>1319</v>
       </c>
@@ -33792,7 +33784,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>1320</v>
       </c>
@@ -33842,7 +33834,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>1321</v>
       </c>
@@ -33892,7 +33884,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>1322</v>
       </c>
@@ -33942,7 +33934,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>1323</v>
       </c>
@@ -33992,7 +33984,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>1324</v>
       </c>
@@ -34042,7 +34034,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>1325</v>
       </c>
@@ -34092,7 +34084,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>1326</v>
       </c>
@@ -34142,7 +34134,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>1327</v>
       </c>
@@ -34192,7 +34184,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>1328</v>
       </c>
@@ -34242,7 +34234,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>1329</v>
       </c>
@@ -34292,7 +34284,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>1330</v>
       </c>
@@ -34342,7 +34334,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>1331</v>
       </c>
@@ -34392,7 +34384,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>1332</v>
       </c>
@@ -34442,7 +34434,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>1333</v>
       </c>
@@ -34492,7 +34484,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>1334</v>
       </c>
@@ -34542,7 +34534,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>1335</v>
       </c>
@@ -34592,7 +34584,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>1336</v>
       </c>
@@ -34642,7 +34634,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>1337</v>
       </c>
@@ -34692,7 +34684,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>1338</v>
       </c>
@@ -34742,7 +34734,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>1339</v>
       </c>
@@ -34792,7 +34784,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>1340</v>
       </c>
@@ -34842,7 +34834,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="609" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>1341</v>
       </c>
@@ -34892,7 +34884,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>1342</v>
       </c>
@@ -34942,7 +34934,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>1343</v>
       </c>
@@ -34992,7 +34984,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>1344</v>
       </c>
@@ -35042,7 +35034,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="613" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>1345</v>
       </c>
@@ -35092,7 +35084,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>1346</v>
       </c>
@@ -35142,7 +35134,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>1347</v>
       </c>
@@ -35192,7 +35184,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="616" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>1348</v>
       </c>
@@ -35242,7 +35234,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="617" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>1349</v>
       </c>
@@ -35262,7 +35254,7 @@
         <v>594</v>
       </c>
       <c r="G617" s="1">
-        <v>10403471645</v>
+        <v>40347164</v>
       </c>
       <c r="H617" s="1" t="s">
         <v>40</v>
@@ -35292,7 +35284,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="618" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>1350</v>
       </c>
@@ -35342,7 +35334,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="619" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>1351</v>
       </c>
@@ -35392,7 +35384,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>1352</v>
       </c>
@@ -35442,7 +35434,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>1353</v>
       </c>
@@ -35492,7 +35484,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="622" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>1354</v>
       </c>
@@ -35542,7 +35534,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="623" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>1355</v>
       </c>
@@ -35592,7 +35584,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="624" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>1356</v>
       </c>
@@ -35642,7 +35634,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="625" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>1357</v>
       </c>
@@ -35689,7 +35681,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="626" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>1358</v>
       </c>
@@ -35736,7 +35728,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="627" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>1359</v>
       </c>
@@ -35783,7 +35775,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="628" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>1360</v>
       </c>
@@ -35830,7 +35822,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="629" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>1361</v>
       </c>
@@ -35877,7 +35869,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="630" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>1362</v>
       </c>
@@ -35924,7 +35916,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="631" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>1363</v>
       </c>
@@ -35971,7 +35963,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="632" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>1364</v>
       </c>
@@ -36018,7 +36010,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="633" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>1365</v>
       </c>
@@ -36065,7 +36057,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>1366</v>
       </c>
@@ -36112,7 +36104,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="635" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>1367</v>
       </c>
@@ -36159,7 +36151,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="636" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>1368</v>
       </c>
@@ -36206,7 +36198,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="637" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>1369</v>
       </c>
@@ -36253,7 +36245,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="638" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>1370</v>
       </c>
@@ -36300,7 +36292,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="639" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>1371</v>
       </c>
@@ -36347,7 +36339,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="640" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>1372</v>
       </c>
@@ -36394,7 +36386,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="641" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>1373</v>
       </c>
@@ -36441,7 +36433,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="642" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>1374</v>
       </c>
@@ -36488,7 +36480,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="643" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>1375</v>
       </c>
@@ -36535,7 +36527,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="644" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>1376</v>
       </c>
@@ -36582,7 +36574,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="645" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>1377</v>
       </c>
@@ -36629,7 +36621,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="646" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>1378</v>
       </c>
@@ -36676,7 +36668,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="647" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>1379</v>
       </c>
@@ -36723,7 +36715,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="648" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>1380</v>
       </c>
@@ -36770,7 +36762,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="649" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>1381</v>
       </c>
@@ -36817,7 +36809,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="650" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>1382</v>
       </c>
@@ -36864,7 +36856,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="651" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>1383</v>
       </c>
@@ -36911,7 +36903,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="652" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>1384</v>
       </c>
@@ -36958,7 +36950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="653" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
         <v>1385</v>
       </c>
@@ -37005,7 +36997,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="654" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
         <v>1386</v>
       </c>
@@ -37052,7 +37044,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="655" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
         <v>1387</v>
       </c>
@@ -37099,7 +37091,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="656" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
         <v>1388</v>
       </c>
@@ -37146,7 +37138,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="657" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
         <v>1389</v>
       </c>
@@ -37193,7 +37185,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="658" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
         <v>1390</v>
       </c>
@@ -37240,7 +37232,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="659" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
         <v>1391</v>
       </c>
@@ -37287,7 +37279,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="660" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
         <v>1392</v>
       </c>
@@ -37334,7 +37326,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="661" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
         <v>1393</v>
       </c>
@@ -37381,7 +37373,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="662" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
         <v>1394</v>
       </c>
@@ -37428,7 +37420,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="663" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
         <v>1395</v>
       </c>
@@ -37475,7 +37467,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="664" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
         <v>1396</v>
       </c>
@@ -37522,7 +37514,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="665" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
         <v>1397</v>
       </c>
@@ -37569,7 +37561,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="666" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
         <v>1398</v>
       </c>
@@ -37616,7 +37608,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="667" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
         <v>1399</v>
       </c>
@@ -37663,7 +37655,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="668" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
         <v>1400</v>
       </c>
@@ -37710,7 +37702,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="669" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
         <v>1401</v>
       </c>
@@ -37757,7 +37749,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="670" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
         <v>1402</v>
       </c>
@@ -37804,7 +37796,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="671" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
         <v>1403</v>
       </c>
@@ -37851,7 +37843,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="672" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
         <v>1404</v>
       </c>
@@ -37898,7 +37890,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="673" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
         <v>1405</v>
       </c>
@@ -37945,7 +37937,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="674" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
         <v>1406</v>
       </c>
@@ -37992,7 +37984,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="675" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
         <v>1407</v>
       </c>
@@ -38039,7 +38031,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="676" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
         <v>1408</v>
       </c>
@@ -38086,7 +38078,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="677" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
         <v>1409</v>
       </c>
@@ -38133,7 +38125,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="678" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
         <v>1410</v>
       </c>
@@ -38180,7 +38172,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="679" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
         <v>1411</v>
       </c>
@@ -38227,7 +38219,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="680" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
         <v>1412</v>
       </c>
@@ -38274,7 +38266,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="681" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
         <v>1413</v>
       </c>
@@ -38321,7 +38313,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="682" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
         <v>1414</v>
       </c>
@@ -38368,7 +38360,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="683" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
         <v>1415</v>
       </c>
@@ -38415,7 +38407,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="684" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
         <v>1416</v>
       </c>
@@ -38462,7 +38454,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="685" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
         <v>1417</v>
       </c>
@@ -38509,7 +38501,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="686" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
         <v>1418</v>
       </c>
@@ -38556,7 +38548,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="687" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
         <v>1419</v>
       </c>
@@ -38603,7 +38595,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="688" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
         <v>1420</v>
       </c>
@@ -38650,7 +38642,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="689" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
         <v>1421</v>
       </c>
@@ -38697,7 +38689,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="690" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
         <v>1422</v>
       </c>
@@ -38744,7 +38736,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="691" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
         <v>1423</v>
       </c>
@@ -38791,7 +38783,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="692" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
         <v>1424</v>
       </c>
@@ -38838,7 +38830,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="693" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
         <v>1425</v>
       </c>
@@ -38885,7 +38877,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="694" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
         <v>1426</v>
       </c>
@@ -38932,7 +38924,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="695" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
         <v>1427</v>
       </c>
@@ -38979,7 +38971,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="696" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
         <v>1428</v>
       </c>
@@ -39026,7 +39018,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="697" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
         <v>1429</v>
       </c>
@@ -39073,7 +39065,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="698" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
         <v>1430</v>
       </c>
@@ -39120,7 +39112,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="699" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
         <v>1431</v>
       </c>
@@ -39167,7 +39159,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="700" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
         <v>1432</v>
       </c>
@@ -39214,7 +39206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="701" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
         <v>1433</v>
       </c>
@@ -39261,7 +39253,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="702" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
         <v>1434</v>
       </c>
@@ -39308,7 +39300,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="703" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
         <v>1435</v>
       </c>
@@ -39355,7 +39347,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="704" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
         <v>1436</v>
       </c>
@@ -39402,7 +39394,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="705" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
         <v>1437</v>
       </c>
@@ -39449,7 +39441,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="706" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
         <v>1438</v>
       </c>
@@ -39496,7 +39488,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="707" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
         <v>1439</v>
       </c>
@@ -39543,7 +39535,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="708" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
         <v>1440</v>
       </c>
@@ -39590,7 +39582,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="709" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
         <v>1441</v>
       </c>
@@ -39637,7 +39629,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="710" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
         <v>1442</v>
       </c>
@@ -39684,7 +39676,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="711" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
         <v>1443</v>
       </c>
@@ -39731,7 +39723,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="712" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
         <v>1444</v>
       </c>
@@ -39778,7 +39770,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="713" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
         <v>1445</v>
       </c>
@@ -39825,7 +39817,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="714" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
         <v>1446</v>
       </c>
@@ -39872,7 +39864,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="715" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
         <v>1447</v>
       </c>
@@ -39919,7 +39911,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="716" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
         <v>1448</v>
       </c>
@@ -39966,7 +39958,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="717" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
         <v>1449</v>
       </c>
@@ -40013,7 +40005,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="718" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
         <v>1450</v>
       </c>
@@ -40060,7 +40052,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="719" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
         <v>1452</v>
       </c>
@@ -40107,7 +40099,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="720" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
         <v>1459</v>
       </c>
@@ -40154,7 +40146,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="721" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
         <v>1460</v>
       </c>
@@ -40198,7 +40190,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="722" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
         <v>1461</v>
       </c>
@@ -40242,7 +40234,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="723" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
         <v>1462</v>
       </c>
@@ -40286,7 +40278,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="724" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
         <v>1463</v>
       </c>
@@ -40333,7 +40325,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="725" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
         <v>1471</v>
       </c>
@@ -40377,7 +40369,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="726" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
         <v>1472</v>
       </c>
@@ -40421,7 +40413,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="727" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
         <v>1473</v>
       </c>
@@ -40465,7 +40457,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="728" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
         <v>1474</v>
       </c>
@@ -40509,7 +40501,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="729" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
         <v>1475</v>
       </c>
@@ -40553,7 +40545,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="730" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
         <v>1476</v>
       </c>
@@ -40597,7 +40589,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="731" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
         <v>1532</v>
       </c>
@@ -40641,7 +40633,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="732" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
         <v>1533</v>
       </c>
@@ -40685,7 +40677,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="733" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
         <v>1534</v>
       </c>
@@ -40729,7 +40721,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="734" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
         <v>1535</v>
       </c>
@@ -40773,7 +40765,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="735" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
         <v>1536</v>
       </c>
@@ -40817,7 +40809,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="736" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
         <v>1537</v>
       </c>
@@ -40861,7 +40853,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="737" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
         <v>1538</v>
       </c>
@@ -40905,7 +40897,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="738" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
         <v>1539</v>
       </c>
@@ -40949,7 +40941,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="739" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
         <v>1540</v>
       </c>
@@ -40993,7 +40985,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="740" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
         <v>1541</v>
       </c>
@@ -41037,7 +41029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="741" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
         <v>1542</v>
       </c>
@@ -41081,7 +41073,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="742" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
         <v>1543</v>
       </c>
@@ -41125,7 +41117,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="743" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
         <v>1544</v>
       </c>
@@ -41169,7 +41161,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="744" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
         <v>1545</v>
       </c>
@@ -41213,7 +41205,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="745" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
         <v>1546</v>
       </c>
@@ -41257,7 +41249,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="746" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
         <v>1547</v>
       </c>
@@ -41301,7 +41293,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="747" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
         <v>1548</v>
       </c>
@@ -41345,7 +41337,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="748" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
         <v>1549</v>
       </c>
@@ -41389,7 +41381,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="749" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
         <v>1550</v>
       </c>
@@ -41433,7 +41425,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="750" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
         <v>1551</v>
       </c>
@@ -41477,7 +41469,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="751" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
         <v>1552</v>
       </c>
@@ -41521,7 +41513,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="752" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
         <v>1553</v>
       </c>
@@ -41565,7 +41557,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="753" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
         <v>1554</v>
       </c>
@@ -41609,7 +41601,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="754" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
         <v>1555</v>
       </c>
@@ -41653,7 +41645,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="755" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
         <v>1556</v>
       </c>
@@ -41697,7 +41689,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="756" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
         <v>1557</v>
       </c>
@@ -41741,7 +41733,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="757" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
         <v>1558</v>
       </c>
@@ -41785,7 +41777,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="758" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
         <v>1559</v>
       </c>
@@ -41829,7 +41821,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="759" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
         <v>1560</v>
       </c>
@@ -41873,7 +41865,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="760" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
         <v>1561</v>
       </c>
@@ -41917,7 +41909,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="761" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
         <v>1562</v>
       </c>
@@ -41961,7 +41953,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="762" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
         <v>1563</v>
       </c>
@@ -42005,7 +41997,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="763" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
         <v>1564</v>
       </c>
@@ -42049,7 +42041,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="764" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
         <v>1565</v>
       </c>
@@ -42093,7 +42085,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="765" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
         <v>1566</v>
       </c>
@@ -42137,7 +42129,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="766" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
         <v>1567</v>
       </c>
@@ -42181,7 +42173,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="767" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
         <v>1568</v>
       </c>
@@ -42225,7 +42217,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="768" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
         <v>1569</v>
       </c>
@@ -42269,7 +42261,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="769" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
         <v>1570</v>
       </c>
@@ -42313,7 +42305,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="770" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
         <v>1571</v>
       </c>
@@ -42357,7 +42349,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="771" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
         <v>1572</v>
       </c>
@@ -42401,7 +42393,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="772" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
         <v>1573</v>
       </c>
@@ -42445,7 +42437,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="773" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
         <v>1574</v>
       </c>
@@ -42489,7 +42481,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="774" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
         <v>1575</v>
       </c>
@@ -42533,7 +42525,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="775" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
         <v>1576</v>
       </c>
@@ -42577,7 +42569,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="776" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
         <v>1577</v>
       </c>
@@ -42621,7 +42613,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="777" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
         <v>1578</v>
       </c>
@@ -42665,7 +42657,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="778" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
         <v>1579</v>
       </c>
@@ -42709,7 +42701,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="779" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
         <v>1580</v>
       </c>
@@ -42753,7 +42745,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="780" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
         <v>1581</v>
       </c>
@@ -42797,7 +42789,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="781" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
         <v>1582</v>
       </c>
@@ -42841,7 +42833,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="782" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
         <v>1583</v>
       </c>
@@ -42885,7 +42877,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="783" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
         <v>1584</v>
       </c>
@@ -42929,7 +42921,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="784" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
         <v>1585</v>
       </c>
@@ -42973,7 +42965,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="785" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
         <v>1586</v>
       </c>
@@ -43017,7 +43009,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="786" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
         <v>1587</v>
       </c>
@@ -43061,7 +43053,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="787" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
         <v>1588</v>
       </c>
@@ -43105,7 +43097,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="788" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
         <v>1589</v>
       </c>
@@ -43149,7 +43141,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="789" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A789" s="1" t="s">
         <v>1590</v>
       </c>
@@ -43193,7 +43185,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="790" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A790" s="1" t="s">
         <v>1591</v>
       </c>
@@ -43237,7 +43229,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="791" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A791" s="1" t="s">
         <v>1594</v>
       </c>
@@ -43256,7 +43248,7 @@
       <c r="F791" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="G791" s="10">
+      <c r="G791" s="1">
         <v>10430636931</v>
       </c>
       <c r="H791" s="1" t="s">
@@ -43287,7 +43279,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="792" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A792" s="1" t="s">
         <v>1595</v>
       </c>
@@ -43306,7 +43298,7 @@
       <c r="F792" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="G792" s="10">
+      <c r="G792" s="1">
         <v>10444412823</v>
       </c>
       <c r="H792" s="1" t="s">
@@ -43337,7 +43329,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="793" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
         <v>1596</v>
       </c>
@@ -43388,13 +43380,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P793" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="CUSILAYME APAZA MARILUZ"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P718">
     <sortCondition ref="D1:D718"/>
   </sortState>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{908D80F9-DFC1-49A7-A8A6-56311309B57A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8733406-6C2B-4CB4-BCEA-E089975C2641}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$793</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$904</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,6 +45,7 @@
     <author>tc={4E3C9A9E-14E5-43AA-8B1F-779CDCC8D0F5}</author>
     <author>tc={8D189750-CB69-4720-9438-68E8E26098F2}</author>
     <author>tc={1FED0FA3-1881-4474-876E-0AE471879AA2}</author>
+    <author>tc={36ACBF48-DE41-4995-A0BB-2901FF5E1206}</author>
   </authors>
   <commentList>
     <comment ref="B27" authorId="0" shapeId="0" xr:uid="{388AD7C4-BD45-408C-9C25-D76BA7C147BF}">
@@ -119,12 +120,21 @@
     No se refleja en el archivo de DESE</t>
       </text>
     </comment>
+    <comment ref="B868" authorId="9" shapeId="0" xr:uid="{36ACBF48-DE41-4995-A0BB-2901FF5E1206}">
+      <text>
+        <t xml:space="preserve">[Comentario encadenado]
+Su versión de Excel le permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
+Comentario:
+    Estaba en 22/09/2026
+</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9786" uniqueCount="1799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9785" uniqueCount="1798">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -5182,9 +5192,6 @@
   </si>
   <si>
     <t>08/08/2026</t>
-  </si>
-  <si>
-    <t>22/09/2026</t>
   </si>
   <si>
     <t>01/08/2026</t>
@@ -5527,7 +5534,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5600,6 +5607,25 @@
       <name val="Aptos Display"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="7"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -5625,7 +5651,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5660,6 +5686,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6001,6 +6036,10 @@
   <threadedComment ref="A719" dT="2026-08-25T17:21:34.22" personId="{4AFC30EF-3D5B-4D86-B079-7855968373AE}" id="{1FED0FA3-1881-4474-876E-0AE471879AA2}">
     <text>No se refleja en el archivo de DESE</text>
   </threadedComment>
+  <threadedComment ref="B868" dT="2026-09-10T13:41:20.83" personId="{4AFC30EF-3D5B-4D86-B079-7855968373AE}" id="{36ACBF48-DE41-4995-A0BB-2901FF5E1206}">
+    <text xml:space="preserve">Estaba en 22/09/2026
+</text>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -45564,7 +45603,7 @@
     </row>
     <row r="827" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A827" s="1" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="B827" s="7" t="s">
         <v>879</v>
@@ -45611,7 +45650,7 @@
     </row>
     <row r="828" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A828" s="1" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="B828" s="7" t="s">
         <v>1623</v>
@@ -45644,7 +45683,7 @@
         <v>245</v>
       </c>
       <c r="L828" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="N828" s="1">
         <v>1</v>
@@ -45658,7 +45697,7 @@
     </row>
     <row r="829" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A829" s="1" t="s">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="B829" s="7" t="s">
         <v>1679</v>
@@ -45691,7 +45730,7 @@
         <v>245</v>
       </c>
       <c r="L829" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="N829" s="1">
         <v>1</v>
@@ -45705,7 +45744,7 @@
     </row>
     <row r="830" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A830" s="1" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="B830" s="7" t="s">
         <v>1680</v>
@@ -45738,7 +45777,7 @@
         <v>245</v>
       </c>
       <c r="L830" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="N830" s="1">
         <v>1</v>
@@ -45752,7 +45791,7 @@
     </row>
     <row r="831" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A831" s="1" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="B831" s="7" t="s">
         <v>1681</v>
@@ -45785,7 +45824,7 @@
         <v>245</v>
       </c>
       <c r="L831" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="N831" s="1">
         <v>1</v>
@@ -45799,7 +45838,7 @@
     </row>
     <row r="832" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A832" s="1" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="B832" s="7" t="s">
         <v>1624</v>
@@ -45832,7 +45871,7 @@
         <v>245</v>
       </c>
       <c r="L832" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="N832" s="1">
         <v>1</v>
@@ -45846,7 +45885,7 @@
     </row>
     <row r="833" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A833" s="1" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="B833" s="7" t="s">
         <v>1682</v>
@@ -45879,7 +45918,7 @@
         <v>245</v>
       </c>
       <c r="L833" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="N833" s="1">
         <v>1</v>
@@ -45893,7 +45932,7 @@
     </row>
     <row r="834" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A834" s="1" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="B834" s="7" t="s">
         <v>1478</v>
@@ -45926,7 +45965,7 @@
         <v>245</v>
       </c>
       <c r="L834" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="N834" s="1">
         <v>1</v>
@@ -45940,7 +45979,7 @@
     </row>
     <row r="835" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A835" s="1" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="B835" s="7" t="s">
         <v>1683</v>
@@ -45973,7 +46012,7 @@
         <v>245</v>
       </c>
       <c r="L835" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="N835" s="1">
         <v>1</v>
@@ -45987,7 +46026,7 @@
     </row>
     <row r="836" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A836" s="1" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="B836" s="7" t="s">
         <v>1684</v>
@@ -46020,7 +46059,7 @@
         <v>245</v>
       </c>
       <c r="L836" s="1" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
       <c r="N836" s="1">
         <v>1</v>
@@ -46034,7 +46073,7 @@
     </row>
     <row r="837" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A837" s="1" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="B837" s="7" t="s">
         <v>1480</v>
@@ -46067,7 +46106,7 @@
         <v>248</v>
       </c>
       <c r="L837" s="1" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="N837" s="1">
         <v>1</v>
@@ -46081,7 +46120,7 @@
     </row>
     <row r="838" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A838" s="1" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="B838" s="7" t="s">
         <v>1592</v>
@@ -46114,7 +46153,7 @@
         <v>248</v>
       </c>
       <c r="L838" s="1" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="N838" s="1">
         <v>1</v>
@@ -46128,7 +46167,7 @@
     </row>
     <row r="839" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A839" s="1" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="B839" s="7" t="s">
         <v>1623</v>
@@ -46161,7 +46200,7 @@
         <v>248</v>
       </c>
       <c r="L839" s="1" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="N839" s="1">
         <v>1</v>
@@ -46175,7 +46214,7 @@
     </row>
     <row r="840" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A840" s="1" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B840" s="7" t="s">
         <v>1464</v>
@@ -46208,7 +46247,7 @@
         <v>245</v>
       </c>
       <c r="L840" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N840" s="1">
         <v>1</v>
@@ -46222,7 +46261,7 @@
     </row>
     <row r="841" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A841" s="1" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="B841" s="7" t="s">
         <v>1479</v>
@@ -46255,7 +46294,7 @@
         <v>245</v>
       </c>
       <c r="L841" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N841" s="1">
         <v>1</v>
@@ -46269,7 +46308,7 @@
     </row>
     <row r="842" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A842" s="1" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="B842" s="7" t="s">
         <v>1619</v>
@@ -46302,7 +46341,7 @@
         <v>245</v>
       </c>
       <c r="L842" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N842" s="1">
         <v>1</v>
@@ -46316,7 +46355,7 @@
     </row>
     <row r="843" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A843" s="1" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="B843" s="7" t="s">
         <v>1621</v>
@@ -46349,7 +46388,7 @@
         <v>245</v>
       </c>
       <c r="L843" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N843" s="1">
         <v>1</v>
@@ -46363,7 +46402,7 @@
     </row>
     <row r="844" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A844" s="1" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="B844" s="7" t="s">
         <v>1465</v>
@@ -46396,7 +46435,7 @@
         <v>245</v>
       </c>
       <c r="L844" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N844" s="1">
         <v>1</v>
@@ -46410,7 +46449,7 @@
     </row>
     <row r="845" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A845" s="1" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="B845" s="7" t="s">
         <v>1685</v>
@@ -46443,7 +46482,7 @@
         <v>245</v>
       </c>
       <c r="L845" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N845" s="1">
         <v>1</v>
@@ -46457,7 +46496,7 @@
     </row>
     <row r="846" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A846" s="1" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="B846" s="7" t="s">
         <v>1618</v>
@@ -46490,7 +46529,7 @@
         <v>245</v>
       </c>
       <c r="L846" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N846" s="1">
         <v>1</v>
@@ -46504,7 +46543,7 @@
     </row>
     <row r="847" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A847" s="1" t="s">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="B847" s="7" t="s">
         <v>1478</v>
@@ -46537,7 +46576,7 @@
         <v>245</v>
       </c>
       <c r="L847" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N847" s="1">
         <v>1</v>
@@ -46551,7 +46590,7 @@
     </row>
     <row r="848" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A848" s="1" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="B848" s="7" t="s">
         <v>1477</v>
@@ -46584,7 +46623,7 @@
         <v>245</v>
       </c>
       <c r="L848" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N848" s="1">
         <v>1</v>
@@ -46598,7 +46637,7 @@
     </row>
     <row r="849" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A849" s="1" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B849" s="7" t="s">
         <v>1616</v>
@@ -46631,7 +46670,7 @@
         <v>245</v>
       </c>
       <c r="L849" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N849" s="1">
         <v>1</v>
@@ -46645,7 +46684,7 @@
     </row>
     <row r="850" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A850" s="1" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B850" s="7" t="s">
         <v>1679</v>
@@ -46678,7 +46717,7 @@
         <v>245</v>
       </c>
       <c r="L850" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N850" s="1">
         <v>1</v>
@@ -46692,7 +46731,7 @@
     </row>
     <row r="851" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A851" s="1" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="B851" s="7" t="s">
         <v>1620</v>
@@ -46725,7 +46764,7 @@
         <v>245</v>
       </c>
       <c r="L851" s="1" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="N851" s="1">
         <v>1</v>
@@ -46739,7 +46778,7 @@
     </row>
     <row r="852" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A852" s="1" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="B852" s="7" t="s">
         <v>1683</v>
@@ -46772,7 +46811,7 @@
         <v>246</v>
       </c>
       <c r="L852" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="N852" s="1">
         <v>2</v>
@@ -46786,7 +46825,7 @@
     </row>
     <row r="853" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A853" s="1" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="B853" s="7" t="s">
         <v>1683</v>
@@ -46819,7 +46858,7 @@
         <v>246</v>
       </c>
       <c r="L853" s="1" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="N853" s="1">
         <v>2</v>
@@ -46833,7 +46872,7 @@
     </row>
     <row r="854" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A854" s="1" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B854" s="7" t="s">
         <v>1683</v>
@@ -46866,7 +46905,7 @@
         <v>246</v>
       </c>
       <c r="L854" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="N854" s="1">
         <v>2</v>
@@ -46880,7 +46919,7 @@
     </row>
     <row r="855" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A855" s="1" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="B855" s="7" t="s">
         <v>1593</v>
@@ -46913,7 +46952,7 @@
         <v>246</v>
       </c>
       <c r="L855" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="N855" s="1">
         <v>2</v>
@@ -46927,7 +46966,7 @@
     </row>
     <row r="856" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A856" s="1" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="B856" s="7" t="s">
         <v>1593</v>
@@ -46960,7 +46999,7 @@
         <v>246</v>
       </c>
       <c r="L856" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="N856" s="1">
         <v>2</v>
@@ -46974,7 +47013,7 @@
     </row>
     <row r="857" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A857" s="1" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="B857" s="7" t="s">
         <v>1593</v>
@@ -47007,7 +47046,7 @@
         <v>246</v>
       </c>
       <c r="L857" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="N857" s="1">
         <v>2</v>
@@ -47021,7 +47060,7 @@
     </row>
     <row r="858" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A858" s="1" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="B858" s="7" t="s">
         <v>1684</v>
@@ -47054,7 +47093,7 @@
         <v>246</v>
       </c>
       <c r="L858" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="N858" s="1">
         <v>2</v>
@@ -47068,7 +47107,7 @@
     </row>
     <row r="859" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A859" s="1" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="B859" s="7" t="s">
         <v>1684</v>
@@ -47101,7 +47140,7 @@
         <v>246</v>
       </c>
       <c r="L859" s="1" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="N859" s="1">
         <v>2</v>
@@ -47115,7 +47154,7 @@
     </row>
     <row r="860" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A860" s="1" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="B860" s="7" t="s">
         <v>1684</v>
@@ -47148,7 +47187,7 @@
         <v>246</v>
       </c>
       <c r="L860" s="1" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="N860" s="1">
         <v>2</v>
@@ -47162,7 +47201,7 @@
     </row>
     <row r="861" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A861" s="1" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="B861" s="7" t="s">
         <v>1615</v>
@@ -47195,7 +47234,7 @@
         <v>246</v>
       </c>
       <c r="L861" s="1" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="N861" s="1">
         <v>2</v>
@@ -47209,7 +47248,7 @@
     </row>
     <row r="862" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A862" s="1" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="B862" s="7" t="s">
         <v>1615</v>
@@ -47242,7 +47281,7 @@
         <v>246</v>
       </c>
       <c r="L862" s="1" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="N862" s="1">
         <v>2</v>
@@ -47256,7 +47295,7 @@
     </row>
     <row r="863" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A863" s="1" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="B863" s="7" t="s">
         <v>1615</v>
@@ -47289,7 +47328,7 @@
         <v>246</v>
       </c>
       <c r="L863" s="1" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="N863" s="1">
         <v>2</v>
@@ -47303,7 +47342,7 @@
     </row>
     <row r="864" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A864" s="1" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="B864" s="7" t="s">
         <v>1616</v>
@@ -47336,7 +47375,7 @@
         <v>245</v>
       </c>
       <c r="L864" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="N864" s="1">
         <v>1</v>
@@ -47350,7 +47389,7 @@
     </row>
     <row r="865" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A865" s="1" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="B865" s="7" t="s">
         <v>1619</v>
@@ -47383,7 +47422,7 @@
         <v>245</v>
       </c>
       <c r="L865" s="1" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="N865" s="1">
         <v>1</v>
@@ -47397,7 +47436,7 @@
     </row>
     <row r="866" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A866" s="1" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="B866" s="7" t="s">
         <v>1593</v>
@@ -47430,7 +47469,7 @@
         <v>245</v>
       </c>
       <c r="L866" s="1" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="N866" s="1">
         <v>1</v>
@@ -47444,7 +47483,7 @@
     </row>
     <row r="867" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A867" s="1" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="B867" s="7" t="s">
         <v>1615</v>
@@ -47477,7 +47516,7 @@
         <v>245</v>
       </c>
       <c r="L867" s="1" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="N867" s="1">
         <v>1</v>
@@ -47489,59 +47528,60 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="868" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A868" s="1" t="s">
-        <v>1762</v>
-      </c>
-      <c r="B868" s="7" t="s">
-        <v>1686</v>
-      </c>
-      <c r="C868" s="1">
-        <v>2026</v>
-      </c>
-      <c r="D868" s="1">
+    <row r="868" spans="1:16" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A868" s="16" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B868" s="17">
+        <v>46256</v>
+      </c>
+      <c r="C868" s="16">
+        <v>2026</v>
+      </c>
+      <c r="D868" s="16">
         <v>8</v>
       </c>
-      <c r="E868" s="1" t="s">
+      <c r="E868" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="F868" s="1" t="s">
+      <c r="F868" s="16" t="s">
         <v>532</v>
       </c>
-      <c r="G868" s="15">
+      <c r="G868" s="18">
         <v>10417044227</v>
       </c>
-      <c r="H868" s="1" t="s">
+      <c r="H868" s="16" t="s">
         <v>235</v>
       </c>
-      <c r="I868" s="1" t="s">
+      <c r="I868" s="16" t="s">
         <v>515</v>
       </c>
-      <c r="J868" s="1" t="s">
+      <c r="J868" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="K868" s="1" t="s">
+      <c r="K868" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="L868" s="1" t="s">
-        <v>1699</v>
-      </c>
-      <c r="N868" s="1">
-        <v>1</v>
-      </c>
-      <c r="O868" s="1" t="s">
+      <c r="L868" s="16" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M868" s="16"/>
+      <c r="N868" s="16">
+        <v>1</v>
+      </c>
+      <c r="O868" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="P868" s="14">
+      <c r="P868" s="19">
         <v>3.1</v>
       </c>
     </row>
     <row r="869" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A869" s="1" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="B869" s="7" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="C869" s="1">
         <v>2026</v>
@@ -47571,7 +47611,7 @@
         <v>247</v>
       </c>
       <c r="L869" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="N869" s="1">
         <v>2</v>
@@ -47585,7 +47625,7 @@
     </row>
     <row r="870" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A870" s="1" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="B870" s="7" t="s">
         <v>1464</v>
@@ -47618,7 +47658,7 @@
         <v>247</v>
       </c>
       <c r="L870" s="1" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="N870" s="1">
         <v>2</v>
@@ -47632,7 +47672,7 @@
     </row>
     <row r="871" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A871" s="1" t="s">
-        <v>1765</v>
+        <v>1764</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>1479</v>
@@ -47665,7 +47705,7 @@
         <v>247</v>
       </c>
       <c r="L871" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="N871" s="1">
         <v>2</v>
@@ -47679,7 +47719,7 @@
     </row>
     <row r="872" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A872" s="1" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B872" s="7" t="s">
         <v>1620</v>
@@ -47712,7 +47752,7 @@
         <v>247</v>
       </c>
       <c r="L872" s="1" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="N872" s="1">
         <v>2</v>
@@ -47726,7 +47766,7 @@
     </row>
     <row r="873" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A873" s="1" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B873" s="7" t="s">
         <v>1621</v>
@@ -47759,7 +47799,7 @@
         <v>247</v>
       </c>
       <c r="L873" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="N873" s="1">
         <v>2</v>
@@ -47773,7 +47813,7 @@
     </row>
     <row r="874" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A874" s="1" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="B874" s="7" t="s">
         <v>1465</v>
@@ -47806,7 +47846,7 @@
         <v>247</v>
       </c>
       <c r="L874" s="1" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="N874" s="1">
         <v>2</v>
@@ -47820,7 +47860,7 @@
     </row>
     <row r="875" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A875" s="1" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="B875" s="7" t="s">
         <v>1619</v>
@@ -47853,7 +47893,7 @@
         <v>247</v>
       </c>
       <c r="L875" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="N875" s="1">
         <v>2</v>
@@ -47867,7 +47907,7 @@
     </row>
     <row r="876" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A876" s="1" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="B876" s="7" t="s">
         <v>1683</v>
@@ -47900,7 +47940,7 @@
         <v>247</v>
       </c>
       <c r="L876" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="N876" s="1">
         <v>2</v>
@@ -47914,7 +47954,7 @@
     </row>
     <row r="877" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A877" s="1" t="s">
-        <v>1771</v>
+        <v>1770</v>
       </c>
       <c r="B877" s="7" t="s">
         <v>1593</v>
@@ -47947,7 +47987,7 @@
         <v>247</v>
       </c>
       <c r="L877" s="1" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="N877" s="1">
         <v>2</v>
@@ -47961,7 +48001,7 @@
     </row>
     <row r="878" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A878" s="1" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="B878" s="7" t="s">
         <v>1684</v>
@@ -47994,7 +48034,7 @@
         <v>247</v>
       </c>
       <c r="L878" s="1" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="N878" s="1">
         <v>2</v>
@@ -48008,7 +48048,7 @@
     </row>
     <row r="879" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A879" s="1" t="s">
-        <v>1773</v>
+        <v>1772</v>
       </c>
       <c r="B879" s="7" t="s">
         <v>1615</v>
@@ -48041,7 +48081,7 @@
         <v>247</v>
       </c>
       <c r="L879" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="N879" s="1">
         <v>2</v>
@@ -48055,10 +48095,10 @@
     </row>
     <row r="880" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A880" s="1" t="s">
-        <v>1774</v>
+        <v>1773</v>
       </c>
       <c r="B880" s="7" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="C880" s="1">
         <v>2026</v>
@@ -48088,7 +48128,7 @@
         <v>247</v>
       </c>
       <c r="L880" s="1" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="N880" s="1">
         <v>2</v>
@@ -48102,10 +48142,10 @@
     </row>
     <row r="881" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A881" s="1" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B881" s="7" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="C881" s="1">
         <v>2026</v>
@@ -48135,7 +48175,7 @@
         <v>245</v>
       </c>
       <c r="L881" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="N881" s="1">
         <v>1</v>
@@ -48149,7 +48189,7 @@
     </row>
     <row r="882" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A882" s="1" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>1464</v>
@@ -48182,7 +48222,7 @@
         <v>245</v>
       </c>
       <c r="L882" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="N882" s="1">
         <v>1</v>
@@ -48196,7 +48236,7 @@
     </row>
     <row r="883" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A883" s="1" t="s">
-        <v>1777</v>
+        <v>1776</v>
       </c>
       <c r="B883" s="7" t="s">
         <v>1479</v>
@@ -48229,7 +48269,7 @@
         <v>245</v>
       </c>
       <c r="L883" s="1" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="N883" s="1">
         <v>1</v>
@@ -48243,7 +48283,7 @@
     </row>
     <row r="884" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A884" s="1" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="B884" s="7" t="s">
         <v>1620</v>
@@ -48276,7 +48316,7 @@
         <v>245</v>
       </c>
       <c r="L884" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="N884" s="1">
         <v>1</v>
@@ -48290,7 +48330,7 @@
     </row>
     <row r="885" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A885" s="1" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="B885" s="7" t="s">
         <v>1621</v>
@@ -48323,7 +48363,7 @@
         <v>245</v>
       </c>
       <c r="L885" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="N885" s="1">
         <v>1</v>
@@ -48337,7 +48377,7 @@
     </row>
     <row r="886" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A886" s="1" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="B886" s="7" t="s">
         <v>1465</v>
@@ -48370,7 +48410,7 @@
         <v>245</v>
       </c>
       <c r="L886" s="1" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="N886" s="1">
         <v>1</v>
@@ -48384,7 +48424,7 @@
     </row>
     <row r="887" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A887" s="1" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="B887" s="7" t="s">
         <v>1624</v>
@@ -48417,7 +48457,7 @@
         <v>245</v>
       </c>
       <c r="L887" s="1" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="N887" s="1">
         <v>1</v>
@@ -48431,7 +48471,7 @@
     </row>
     <row r="888" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A888" s="1" t="s">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="B888" s="7" t="s">
         <v>1593</v>
@@ -48464,7 +48504,7 @@
         <v>245</v>
       </c>
       <c r="L888" s="1" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="N888" s="1">
         <v>1</v>
@@ -48478,7 +48518,7 @@
     </row>
     <row r="889" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A889" s="1" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="B889" s="7" t="s">
         <v>1623</v>
@@ -48511,7 +48551,7 @@
         <v>245</v>
       </c>
       <c r="L889" s="1" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="N889" s="1">
         <v>1</v>
@@ -48525,7 +48565,7 @@
     </row>
     <row r="890" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A890" s="1" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="B890" s="7" t="s">
         <v>1465</v>
@@ -48572,7 +48612,7 @@
     </row>
     <row r="891" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A891" s="1" t="s">
-        <v>1785</v>
+        <v>1784</v>
       </c>
       <c r="B891" s="7" t="s">
         <v>1679</v>
@@ -48619,10 +48659,10 @@
     </row>
     <row r="892" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A892" s="1" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="B892" s="7" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="C892" s="1">
         <v>2026</v>
@@ -48666,7 +48706,7 @@
     </row>
     <row r="893" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A893" s="1" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>1683</v>
@@ -48699,7 +48739,7 @@
         <v>245</v>
       </c>
       <c r="L893" s="1" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="N893" s="1">
         <v>1</v>
@@ -48713,7 +48753,7 @@
     </row>
     <row r="894" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A894" s="1" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B894" s="7" t="s">
         <v>1593</v>
@@ -48746,7 +48786,7 @@
         <v>245</v>
       </c>
       <c r="L894" s="1" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="N894" s="1">
         <v>1</v>
@@ -48760,7 +48800,7 @@
     </row>
     <row r="895" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A895" s="1" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B895" s="7" t="s">
         <v>1684</v>
@@ -48793,7 +48833,7 @@
         <v>245</v>
       </c>
       <c r="L895" s="1" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="N895" s="1">
         <v>1</v>
@@ -48807,7 +48847,7 @@
     </row>
     <row r="896" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A896" s="1" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="B896" s="7" t="s">
         <v>1615</v>
@@ -48840,7 +48880,7 @@
         <v>245</v>
       </c>
       <c r="L896" s="1" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="N896" s="1">
         <v>1</v>
@@ -48854,7 +48894,7 @@
     </row>
     <row r="897" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A897" s="1" t="s">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="B897" s="7" t="s">
         <v>1616</v>
@@ -48887,7 +48927,7 @@
         <v>245</v>
       </c>
       <c r="L897" s="1" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="N897" s="1">
         <v>1</v>
@@ -48901,7 +48941,7 @@
     </row>
     <row r="898" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A898" s="1" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="B898" s="7" t="s">
         <v>1592</v>
@@ -48934,7 +48974,7 @@
         <v>247</v>
       </c>
       <c r="L898" s="1" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="N898" s="1">
         <v>2</v>
@@ -48948,7 +48988,7 @@
     </row>
     <row r="899" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A899" s="1" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="B899" s="7" t="s">
         <v>1623</v>
@@ -48981,7 +49021,7 @@
         <v>247</v>
       </c>
       <c r="L899" s="1" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="N899" s="1">
         <v>2</v>
@@ -48995,7 +49035,7 @@
     </row>
     <row r="900" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A900" s="1" t="s">
-        <v>1794</v>
+        <v>1793</v>
       </c>
       <c r="B900" s="7" t="s">
         <v>1680</v>
@@ -49028,7 +49068,7 @@
         <v>247</v>
       </c>
       <c r="L900" s="1" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="N900" s="1">
         <v>2</v>
@@ -49042,7 +49082,7 @@
     </row>
     <row r="901" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A901" s="1" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="B901" s="7" t="s">
         <v>1622</v>
@@ -49075,7 +49115,7 @@
         <v>247</v>
       </c>
       <c r="L901" s="1" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="N901" s="1">
         <v>2</v>
@@ -49089,7 +49129,7 @@
     </row>
     <row r="902" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A902" s="1" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="B902" s="7" t="s">
         <v>412</v>
@@ -49122,7 +49162,7 @@
         <v>250</v>
       </c>
       <c r="L902" s="1" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="N902" s="1">
         <v>10</v>
@@ -49136,7 +49176,7 @@
     </row>
     <row r="903" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A903" s="1" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="B903" s="7" t="s">
         <v>1593</v>
@@ -49169,7 +49209,7 @@
         <v>245</v>
       </c>
       <c r="L903" s="1" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
       <c r="N903" s="1">
         <v>1</v>
@@ -49183,7 +49223,7 @@
     </row>
     <row r="904" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A904" s="1" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>1624</v>
@@ -49216,7 +49256,7 @@
         <v>250</v>
       </c>
       <c r="L904" s="1" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="N904" s="1">
         <v>14</v>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70526BCD-C5D9-455B-88C6-E6E29329414E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE83ECD1-6D3C-4FDB-8A92-5A9D89E96987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12292" uniqueCount="1988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12292" uniqueCount="1986">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -5564,12 +5564,6 @@
   </si>
   <si>
     <t>Desarrollo de prototipo y/o producto</t>
-  </si>
-  <si>
-    <t>SOPORTE PRODUCTIVO</t>
-  </si>
-  <si>
-    <t>Soporte en producción</t>
   </si>
   <si>
     <t>Teñido artesanal con tintes naturales de sustratos textiles Teñido de prenda</t>
@@ -48198,7 +48192,7 @@
     </row>
     <row r="870" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A870" s="1" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="B870" s="7" t="s">
         <v>1472</v>
@@ -48231,7 +48225,7 @@
         <v>245</v>
       </c>
       <c r="L870" s="1" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="M870" s="1" t="s">
         <v>528</v>
@@ -48245,7 +48239,7 @@
     </row>
     <row r="871" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A871" s="1" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="B871" s="7" t="s">
         <v>1609</v>
@@ -48292,7 +48286,7 @@
     </row>
     <row r="872" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A872" s="1" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="B872" s="7" t="s">
         <v>1610</v>
@@ -48339,7 +48333,7 @@
     </row>
     <row r="873" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A873" s="1" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="B873" s="7" t="s">
         <v>1465</v>
@@ -48386,7 +48380,7 @@
     </row>
     <row r="874" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A874" s="1" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="B874" s="7" t="s">
         <v>1611</v>
@@ -48433,7 +48427,7 @@
     </row>
     <row r="875" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A875" s="1" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="B875" s="7" t="s">
         <v>1612</v>
@@ -48480,7 +48474,7 @@
     </row>
     <row r="876" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A876" s="1" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="B876" s="7" t="s">
         <v>1625</v>
@@ -48513,7 +48507,7 @@
         <v>245</v>
       </c>
       <c r="L876" s="1" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="M876" s="1" t="s">
         <v>528</v>
@@ -48527,7 +48521,7 @@
     </row>
     <row r="877" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A877" s="1" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="B877" s="7" t="s">
         <v>1473</v>
@@ -48574,7 +48568,7 @@
     </row>
     <row r="878" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A878" s="1" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="B878" s="7" t="s">
         <v>1474</v>
@@ -48621,7 +48615,7 @@
     </row>
     <row r="879" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A879" s="1" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="B879" s="7" t="s">
         <v>1613</v>
@@ -48668,7 +48662,7 @@
     </row>
     <row r="880" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A880" s="1" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="B880" s="7" t="s">
         <v>1614</v>
@@ -48715,7 +48709,7 @@
     </row>
     <row r="881" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A881" s="1" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="B881" s="7" t="s">
         <v>1475</v>
@@ -48762,7 +48756,7 @@
     </row>
     <row r="882" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A882" s="1" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="B882" s="7" t="s">
         <v>1587</v>
@@ -48809,7 +48803,7 @@
     </row>
     <row r="883" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A883" s="1" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="B883" s="7" t="s">
         <v>1616</v>
@@ -48856,7 +48850,7 @@
     </row>
     <row r="884" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A884" s="1" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="B884" s="7" t="s">
         <v>1615</v>
@@ -48903,7 +48897,7 @@
     </row>
     <row r="885" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A885" s="1" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="B885" s="7" t="s">
         <v>1617</v>
@@ -48950,7 +48944,7 @@
     </row>
     <row r="886" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A886" s="1" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
       <c r="B886" s="7" t="s">
         <v>1608</v>
@@ -48983,7 +48977,7 @@
         <v>249</v>
       </c>
       <c r="L886" s="1" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="M886" s="1" t="s">
         <v>528</v>
@@ -48997,7 +48991,7 @@
     </row>
     <row r="887" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A887" s="1" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
       <c r="B887" s="7" t="s">
         <v>1608</v>
@@ -49030,7 +49024,7 @@
         <v>249</v>
       </c>
       <c r="L887" s="1" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="M887" s="1" t="s">
         <v>528</v>
@@ -49044,7 +49038,7 @@
     </row>
     <row r="888" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A888" s="1" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
       <c r="B888" s="7" t="s">
         <v>1628</v>
@@ -49077,7 +49071,7 @@
         <v>251</v>
       </c>
       <c r="L888" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M888" s="1" t="s">
         <v>528</v>
@@ -49091,7 +49085,7 @@
     </row>
     <row r="889" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A889" s="1" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="B889" s="7" t="s">
         <v>1628</v>
@@ -49124,7 +49118,7 @@
         <v>251</v>
       </c>
       <c r="L889" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M889" s="1" t="s">
         <v>528</v>
@@ -49138,7 +49132,7 @@
     </row>
     <row r="890" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A890" s="1" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="B890" s="7" t="s">
         <v>1628</v>
@@ -49171,7 +49165,7 @@
         <v>251</v>
       </c>
       <c r="L890" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M890" s="1" t="s">
         <v>528</v>
@@ -49185,7 +49179,7 @@
     </row>
     <row r="891" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A891" s="1" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="B891" s="7" t="s">
         <v>1628</v>
@@ -49218,7 +49212,7 @@
         <v>251</v>
       </c>
       <c r="L891" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M891" s="1" t="s">
         <v>528</v>
@@ -49232,7 +49226,7 @@
     </row>
     <row r="892" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A892" s="1" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="B892" s="7" t="s">
         <v>1628</v>
@@ -49265,7 +49259,7 @@
         <v>251</v>
       </c>
       <c r="L892" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M892" s="1" t="s">
         <v>528</v>
@@ -49279,7 +49273,7 @@
     </row>
     <row r="893" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A893" s="1" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="B893" s="7" t="s">
         <v>1628</v>
@@ -49312,7 +49306,7 @@
         <v>251</v>
       </c>
       <c r="L893" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M893" s="1" t="s">
         <v>528</v>
@@ -49326,7 +49320,7 @@
     </row>
     <row r="894" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A894" s="1" t="s">
-        <v>1850</v>
+        <v>1848</v>
       </c>
       <c r="B894" s="7" t="s">
         <v>1628</v>
@@ -49359,7 +49353,7 @@
         <v>251</v>
       </c>
       <c r="L894" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M894" s="1" t="s">
         <v>528</v>
@@ -49373,7 +49367,7 @@
     </row>
     <row r="895" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A895" s="1" t="s">
-        <v>1851</v>
+        <v>1849</v>
       </c>
       <c r="B895" s="7" t="s">
         <v>1628</v>
@@ -49406,7 +49400,7 @@
         <v>251</v>
       </c>
       <c r="L895" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M895" s="1" t="s">
         <v>528</v>
@@ -49420,7 +49414,7 @@
     </row>
     <row r="896" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A896" s="1" t="s">
-        <v>1852</v>
+        <v>1850</v>
       </c>
       <c r="B896" s="7" t="s">
         <v>1628</v>
@@ -49453,7 +49447,7 @@
         <v>251</v>
       </c>
       <c r="L896" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M896" s="1" t="s">
         <v>528</v>
@@ -49467,7 +49461,7 @@
     </row>
     <row r="897" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A897" s="1" t="s">
-        <v>1853</v>
+        <v>1851</v>
       </c>
       <c r="B897" s="7" t="s">
         <v>1628</v>
@@ -49500,7 +49494,7 @@
         <v>251</v>
       </c>
       <c r="L897" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M897" s="1" t="s">
         <v>528</v>
@@ -49514,7 +49508,7 @@
     </row>
     <row r="898" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A898" s="1" t="s">
-        <v>1854</v>
+        <v>1852</v>
       </c>
       <c r="B898" s="7" t="s">
         <v>1628</v>
@@ -49547,7 +49541,7 @@
         <v>251</v>
       </c>
       <c r="L898" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M898" s="1" t="s">
         <v>528</v>
@@ -49561,7 +49555,7 @@
     </row>
     <row r="899" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A899" s="1" t="s">
-        <v>1855</v>
+        <v>1853</v>
       </c>
       <c r="B899" s="7" t="s">
         <v>1628</v>
@@ -49594,7 +49588,7 @@
         <v>251</v>
       </c>
       <c r="L899" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M899" s="1" t="s">
         <v>528</v>
@@ -49608,7 +49602,7 @@
     </row>
     <row r="900" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A900" s="1" t="s">
-        <v>1856</v>
+        <v>1854</v>
       </c>
       <c r="B900" s="7" t="s">
         <v>1628</v>
@@ -49641,7 +49635,7 @@
         <v>251</v>
       </c>
       <c r="L900" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M900" s="1" t="s">
         <v>528</v>
@@ -49655,7 +49649,7 @@
     </row>
     <row r="901" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A901" s="1" t="s">
-        <v>1857</v>
+        <v>1855</v>
       </c>
       <c r="B901" s="7" t="s">
         <v>1628</v>
@@ -49688,7 +49682,7 @@
         <v>251</v>
       </c>
       <c r="L901" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M901" s="1" t="s">
         <v>528</v>
@@ -49702,7 +49696,7 @@
     </row>
     <row r="902" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A902" s="1" t="s">
-        <v>1858</v>
+        <v>1856</v>
       </c>
       <c r="B902" s="7" t="s">
         <v>1628</v>
@@ -49735,7 +49729,7 @@
         <v>251</v>
       </c>
       <c r="L902" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M902" s="1" t="s">
         <v>528</v>
@@ -49749,7 +49743,7 @@
     </row>
     <row r="903" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A903" s="1" t="s">
-        <v>1859</v>
+        <v>1857</v>
       </c>
       <c r="B903" s="7" t="s">
         <v>1628</v>
@@ -49782,7 +49776,7 @@
         <v>251</v>
       </c>
       <c r="L903" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M903" s="1" t="s">
         <v>528</v>
@@ -49796,7 +49790,7 @@
     </row>
     <row r="904" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A904" s="1" t="s">
-        <v>1860</v>
+        <v>1858</v>
       </c>
       <c r="B904" s="7" t="s">
         <v>1628</v>
@@ -49829,7 +49823,7 @@
         <v>251</v>
       </c>
       <c r="L904" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M904" s="1" t="s">
         <v>528</v>
@@ -49843,7 +49837,7 @@
     </row>
     <row r="905" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A905" s="1" t="s">
-        <v>1861</v>
+        <v>1859</v>
       </c>
       <c r="B905" s="7" t="s">
         <v>1628</v>
@@ -49876,7 +49870,7 @@
         <v>251</v>
       </c>
       <c r="L905" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M905" s="1" t="s">
         <v>528</v>
@@ -49890,7 +49884,7 @@
     </row>
     <row r="906" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A906" s="1" t="s">
-        <v>1862</v>
+        <v>1860</v>
       </c>
       <c r="B906" s="7" t="s">
         <v>1628</v>
@@ -49923,7 +49917,7 @@
         <v>251</v>
       </c>
       <c r="L906" s="1" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M906" s="1" t="s">
         <v>528</v>
@@ -49937,7 +49931,7 @@
     </row>
     <row r="907" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A907" s="1" t="s">
-        <v>1863</v>
+        <v>1861</v>
       </c>
       <c r="B907" s="7" t="s">
         <v>1588</v>
@@ -49967,7 +49961,7 @@
         <v>251</v>
       </c>
       <c r="L907" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M907" s="1" t="s">
         <v>528</v>
@@ -49981,7 +49975,7 @@
     </row>
     <row r="908" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A908" s="1" t="s">
-        <v>1864</v>
+        <v>1862</v>
       </c>
       <c r="B908" s="7" t="s">
         <v>1588</v>
@@ -50011,7 +50005,7 @@
         <v>251</v>
       </c>
       <c r="L908" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M908" s="1" t="s">
         <v>528</v>
@@ -50025,7 +50019,7 @@
     </row>
     <row r="909" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A909" s="1" t="s">
-        <v>1865</v>
+        <v>1863</v>
       </c>
       <c r="B909" s="7" t="s">
         <v>1588</v>
@@ -50055,7 +50049,7 @@
         <v>251</v>
       </c>
       <c r="L909" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M909" s="1" t="s">
         <v>528</v>
@@ -50069,7 +50063,7 @@
     </row>
     <row r="910" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A910" s="1" t="s">
-        <v>1866</v>
+        <v>1864</v>
       </c>
       <c r="B910" s="7" t="s">
         <v>1588</v>
@@ -50099,7 +50093,7 @@
         <v>251</v>
       </c>
       <c r="L910" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M910" s="1" t="s">
         <v>528</v>
@@ -50113,7 +50107,7 @@
     </row>
     <row r="911" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A911" s="1" t="s">
-        <v>1867</v>
+        <v>1865</v>
       </c>
       <c r="B911" s="7" t="s">
         <v>1588</v>
@@ -50143,7 +50137,7 @@
         <v>251</v>
       </c>
       <c r="L911" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M911" s="1" t="s">
         <v>528</v>
@@ -50157,7 +50151,7 @@
     </row>
     <row r="912" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A912" s="1" t="s">
-        <v>1868</v>
+        <v>1866</v>
       </c>
       <c r="B912" s="7" t="s">
         <v>1588</v>
@@ -50187,7 +50181,7 @@
         <v>251</v>
       </c>
       <c r="L912" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M912" s="1" t="s">
         <v>528</v>
@@ -50201,7 +50195,7 @@
     </row>
     <row r="913" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A913" s="1" t="s">
-        <v>1869</v>
+        <v>1867</v>
       </c>
       <c r="B913" s="7" t="s">
         <v>1588</v>
@@ -50231,7 +50225,7 @@
         <v>251</v>
       </c>
       <c r="L913" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M913" s="1" t="s">
         <v>528</v>
@@ -50245,7 +50239,7 @@
     </row>
     <row r="914" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A914" s="1" t="s">
-        <v>1870</v>
+        <v>1868</v>
       </c>
       <c r="B914" s="7" t="s">
         <v>1588</v>
@@ -50275,7 +50269,7 @@
         <v>251</v>
       </c>
       <c r="L914" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M914" s="1" t="s">
         <v>528</v>
@@ -50289,7 +50283,7 @@
     </row>
     <row r="915" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A915" s="1" t="s">
-        <v>1871</v>
+        <v>1869</v>
       </c>
       <c r="B915" s="7" t="s">
         <v>1588</v>
@@ -50319,7 +50313,7 @@
         <v>251</v>
       </c>
       <c r="L915" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M915" s="1" t="s">
         <v>528</v>
@@ -50333,7 +50327,7 @@
     </row>
     <row r="916" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A916" s="1" t="s">
-        <v>1872</v>
+        <v>1870</v>
       </c>
       <c r="B916" s="7" t="s">
         <v>1588</v>
@@ -50366,7 +50360,7 @@
         <v>251</v>
       </c>
       <c r="L916" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M916" s="1" t="s">
         <v>528</v>
@@ -50380,7 +50374,7 @@
     </row>
     <row r="917" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A917" s="1" t="s">
-        <v>1873</v>
+        <v>1871</v>
       </c>
       <c r="B917" s="7" t="s">
         <v>1588</v>
@@ -50413,7 +50407,7 @@
         <v>251</v>
       </c>
       <c r="L917" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M917" s="1" t="s">
         <v>528</v>
@@ -50427,7 +50421,7 @@
     </row>
     <row r="918" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A918" s="1" t="s">
-        <v>1874</v>
+        <v>1872</v>
       </c>
       <c r="B918" s="7" t="s">
         <v>1588</v>
@@ -50460,7 +50454,7 @@
         <v>251</v>
       </c>
       <c r="L918" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M918" s="1" t="s">
         <v>528</v>
@@ -50474,7 +50468,7 @@
     </row>
     <row r="919" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A919" s="1" t="s">
-        <v>1875</v>
+        <v>1873</v>
       </c>
       <c r="B919" s="7" t="s">
         <v>1588</v>
@@ -50507,7 +50501,7 @@
         <v>251</v>
       </c>
       <c r="L919" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M919" s="1" t="s">
         <v>528</v>
@@ -50521,7 +50515,7 @@
     </row>
     <row r="920" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A920" s="1" t="s">
-        <v>1876</v>
+        <v>1874</v>
       </c>
       <c r="B920" s="7" t="s">
         <v>1588</v>
@@ -50554,7 +50548,7 @@
         <v>251</v>
       </c>
       <c r="L920" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M920" s="1" t="s">
         <v>528</v>
@@ -50568,7 +50562,7 @@
     </row>
     <row r="921" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A921" s="1" t="s">
-        <v>1877</v>
+        <v>1875</v>
       </c>
       <c r="B921" s="7" t="s">
         <v>1588</v>
@@ -50601,7 +50595,7 @@
         <v>251</v>
       </c>
       <c r="L921" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M921" s="1" t="s">
         <v>528</v>
@@ -50615,7 +50609,7 @@
     </row>
     <row r="922" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A922" s="1" t="s">
-        <v>1878</v>
+        <v>1876</v>
       </c>
       <c r="B922" s="7" t="s">
         <v>1588</v>
@@ -50648,7 +50642,7 @@
         <v>251</v>
       </c>
       <c r="L922" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M922" s="1" t="s">
         <v>528</v>
@@ -50662,7 +50656,7 @@
     </row>
     <row r="923" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A923" s="1" t="s">
-        <v>1879</v>
+        <v>1877</v>
       </c>
       <c r="B923" s="7" t="s">
         <v>1588</v>
@@ -50695,7 +50689,7 @@
         <v>251</v>
       </c>
       <c r="L923" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M923" s="1" t="s">
         <v>528</v>
@@ -50709,7 +50703,7 @@
     </row>
     <row r="924" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A924" s="1" t="s">
-        <v>1880</v>
+        <v>1878</v>
       </c>
       <c r="B924" s="7" t="s">
         <v>1588</v>
@@ -50742,7 +50736,7 @@
         <v>251</v>
       </c>
       <c r="L924" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M924" s="1" t="s">
         <v>528</v>
@@ -50756,7 +50750,7 @@
     </row>
     <row r="925" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A925" s="1" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="B925" s="7" t="s">
         <v>1588</v>
@@ -50786,7 +50780,7 @@
         <v>251</v>
       </c>
       <c r="L925" s="1" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M925" s="1" t="s">
         <v>528</v>
@@ -50800,7 +50794,7 @@
     </row>
     <row r="926" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A926" s="1" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="B926" s="7" t="s">
         <v>1608</v>
@@ -50830,7 +50824,7 @@
         <v>251</v>
       </c>
       <c r="L926" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M926" s="1" t="s">
         <v>528</v>
@@ -50844,7 +50838,7 @@
     </row>
     <row r="927" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A927" s="1" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="B927" s="7" t="s">
         <v>1608</v>
@@ -50874,7 +50868,7 @@
         <v>251</v>
       </c>
       <c r="L927" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M927" s="1" t="s">
         <v>528</v>
@@ -50888,7 +50882,7 @@
     </row>
     <row r="928" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A928" s="1" t="s">
-        <v>1884</v>
+        <v>1882</v>
       </c>
       <c r="B928" s="7" t="s">
         <v>1608</v>
@@ -50918,7 +50912,7 @@
         <v>251</v>
       </c>
       <c r="L928" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M928" s="1" t="s">
         <v>528</v>
@@ -50932,7 +50926,7 @@
     </row>
     <row r="929" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A929" s="1" t="s">
-        <v>1885</v>
+        <v>1883</v>
       </c>
       <c r="B929" s="7" t="s">
         <v>1608</v>
@@ -50962,7 +50956,7 @@
         <v>251</v>
       </c>
       <c r="L929" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M929" s="1" t="s">
         <v>528</v>
@@ -50976,7 +50970,7 @@
     </row>
     <row r="930" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A930" s="1" t="s">
-        <v>1886</v>
+        <v>1884</v>
       </c>
       <c r="B930" s="7" t="s">
         <v>1608</v>
@@ -51006,7 +51000,7 @@
         <v>251</v>
       </c>
       <c r="L930" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M930" s="1" t="s">
         <v>528</v>
@@ -51020,7 +51014,7 @@
     </row>
     <row r="931" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A931" s="1" t="s">
-        <v>1887</v>
+        <v>1885</v>
       </c>
       <c r="B931" s="7" t="s">
         <v>1608</v>
@@ -51050,7 +51044,7 @@
         <v>251</v>
       </c>
       <c r="L931" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M931" s="1" t="s">
         <v>528</v>
@@ -51064,7 +51058,7 @@
     </row>
     <row r="932" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A932" s="1" t="s">
-        <v>1888</v>
+        <v>1886</v>
       </c>
       <c r="B932" s="7" t="s">
         <v>1608</v>
@@ -51094,7 +51088,7 @@
         <v>251</v>
       </c>
       <c r="L932" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M932" s="1" t="s">
         <v>528</v>
@@ -51108,7 +51102,7 @@
     </row>
     <row r="933" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A933" s="1" t="s">
-        <v>1889</v>
+        <v>1887</v>
       </c>
       <c r="B933" s="7" t="s">
         <v>1608</v>
@@ -51138,7 +51132,7 @@
         <v>251</v>
       </c>
       <c r="L933" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M933" s="1" t="s">
         <v>528</v>
@@ -51152,7 +51146,7 @@
     </row>
     <row r="934" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A934" s="1" t="s">
-        <v>1890</v>
+        <v>1888</v>
       </c>
       <c r="B934" s="7" t="s">
         <v>1608</v>
@@ -51185,7 +51179,7 @@
         <v>251</v>
       </c>
       <c r="L934" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M934" s="1" t="s">
         <v>528</v>
@@ -51199,7 +51193,7 @@
     </row>
     <row r="935" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A935" s="1" t="s">
-        <v>1891</v>
+        <v>1889</v>
       </c>
       <c r="B935" s="7" t="s">
         <v>1608</v>
@@ -51232,7 +51226,7 @@
         <v>251</v>
       </c>
       <c r="L935" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M935" s="1" t="s">
         <v>528</v>
@@ -51246,7 +51240,7 @@
     </row>
     <row r="936" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A936" s="1" t="s">
-        <v>1892</v>
+        <v>1890</v>
       </c>
       <c r="B936" s="7" t="s">
         <v>1608</v>
@@ -51279,7 +51273,7 @@
         <v>251</v>
       </c>
       <c r="L936" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M936" s="1" t="s">
         <v>528</v>
@@ -51293,7 +51287,7 @@
     </row>
     <row r="937" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A937" s="1" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="B937" s="7" t="s">
         <v>1608</v>
@@ -51326,7 +51320,7 @@
         <v>251</v>
       </c>
       <c r="L937" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M937" s="1" t="s">
         <v>528</v>
@@ -51340,7 +51334,7 @@
     </row>
     <row r="938" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A938" s="1" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="B938" s="7" t="s">
         <v>1608</v>
@@ -51373,7 +51367,7 @@
         <v>251</v>
       </c>
       <c r="L938" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M938" s="1" t="s">
         <v>528</v>
@@ -51387,7 +51381,7 @@
     </row>
     <row r="939" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A939" s="1" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="B939" s="7" t="s">
         <v>1608</v>
@@ -51420,7 +51414,7 @@
         <v>251</v>
       </c>
       <c r="L939" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M939" s="1" t="s">
         <v>528</v>
@@ -51434,7 +51428,7 @@
     </row>
     <row r="940" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A940" s="1" t="s">
-        <v>1896</v>
+        <v>1894</v>
       </c>
       <c r="B940" s="7" t="s">
         <v>1608</v>
@@ -51467,7 +51461,7 @@
         <v>251</v>
       </c>
       <c r="L940" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M940" s="1" t="s">
         <v>528</v>
@@ -51481,7 +51475,7 @@
     </row>
     <row r="941" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A941" s="1" t="s">
-        <v>1897</v>
+        <v>1895</v>
       </c>
       <c r="B941" s="7" t="s">
         <v>1608</v>
@@ -51514,7 +51508,7 @@
         <v>251</v>
       </c>
       <c r="L941" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M941" s="1" t="s">
         <v>528</v>
@@ -51528,7 +51522,7 @@
     </row>
     <row r="942" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A942" s="1" t="s">
-        <v>1898</v>
+        <v>1896</v>
       </c>
       <c r="B942" s="7" t="s">
         <v>1608</v>
@@ -51561,7 +51555,7 @@
         <v>251</v>
       </c>
       <c r="L942" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M942" s="1" t="s">
         <v>528</v>
@@ -51575,7 +51569,7 @@
     </row>
     <row r="943" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A943" s="1" t="s">
-        <v>1899</v>
+        <v>1897</v>
       </c>
       <c r="B943" s="7" t="s">
         <v>1608</v>
@@ -51608,7 +51602,7 @@
         <v>251</v>
       </c>
       <c r="L943" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M943" s="1" t="s">
         <v>528</v>
@@ -51622,7 +51616,7 @@
     </row>
     <row r="944" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A944" s="1" t="s">
-        <v>1900</v>
+        <v>1898</v>
       </c>
       <c r="B944" s="7" t="s">
         <v>1608</v>
@@ -51652,7 +51646,7 @@
         <v>251</v>
       </c>
       <c r="L944" s="1" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M944" s="1" t="s">
         <v>528</v>
@@ -51666,7 +51660,7 @@
     </row>
     <row r="945" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A945" s="1" t="s">
-        <v>1901</v>
+        <v>1899</v>
       </c>
       <c r="B945" s="7" t="s">
         <v>1615</v>
@@ -51713,7 +51707,7 @@
     </row>
     <row r="946" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A946" s="1" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="B946" s="7" t="s">
         <v>1615</v>
@@ -51757,7 +51751,7 @@
     </row>
     <row r="947" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A947" s="1" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="B947" s="7" t="s">
         <v>1615</v>
@@ -51804,7 +51798,7 @@
     </row>
     <row r="948" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A948" s="1" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="B948" s="7" t="s">
         <v>1615</v>
@@ -51848,7 +51842,7 @@
     </row>
     <row r="949" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A949" s="1" t="s">
-        <v>1905</v>
+        <v>1903</v>
       </c>
       <c r="B949" s="7" t="s">
         <v>1615</v>
@@ -51892,7 +51886,7 @@
     </row>
     <row r="950" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A950" s="1" t="s">
-        <v>1906</v>
+        <v>1904</v>
       </c>
       <c r="B950" s="7" t="s">
         <v>1615</v>
@@ -51936,7 +51930,7 @@
     </row>
     <row r="951" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A951" s="1" t="s">
-        <v>1907</v>
+        <v>1905</v>
       </c>
       <c r="B951" s="7" t="s">
         <v>1615</v>
@@ -51980,7 +51974,7 @@
     </row>
     <row r="952" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A952" s="1" t="s">
-        <v>1908</v>
+        <v>1906</v>
       </c>
       <c r="B952" s="7" t="s">
         <v>1615</v>
@@ -52027,7 +52021,7 @@
     </row>
     <row r="953" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A953" s="1" t="s">
-        <v>1909</v>
+        <v>1907</v>
       </c>
       <c r="B953" s="7" t="s">
         <v>1615</v>
@@ -52074,7 +52068,7 @@
     </row>
     <row r="954" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A954" s="1" t="s">
-        <v>1910</v>
+        <v>1908</v>
       </c>
       <c r="B954" s="7" t="s">
         <v>1615</v>
@@ -52121,7 +52115,7 @@
     </row>
     <row r="955" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A955" s="1" t="s">
-        <v>1911</v>
+        <v>1909</v>
       </c>
       <c r="B955" s="7" t="s">
         <v>1615</v>
@@ -52165,7 +52159,7 @@
     </row>
     <row r="956" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A956" s="1" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="B956" s="7" t="s">
         <v>1615</v>
@@ -52209,7 +52203,7 @@
     </row>
     <row r="957" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A957" s="1" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="B957" s="7" t="s">
         <v>1615</v>
@@ -52253,7 +52247,7 @@
     </row>
     <row r="958" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A958" s="1" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="B958" s="7" t="s">
         <v>1615</v>
@@ -52297,7 +52291,7 @@
     </row>
     <row r="959" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A959" s="1" t="s">
-        <v>1915</v>
+        <v>1913</v>
       </c>
       <c r="B959" s="7" t="s">
         <v>1609</v>
@@ -52327,7 +52321,7 @@
         <v>251</v>
       </c>
       <c r="L959" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M959" s="1" t="s">
         <v>528</v>
@@ -52341,7 +52335,7 @@
     </row>
     <row r="960" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A960" s="1" t="s">
-        <v>1916</v>
+        <v>1914</v>
       </c>
       <c r="B960" s="7" t="s">
         <v>1609</v>
@@ -52371,7 +52365,7 @@
         <v>251</v>
       </c>
       <c r="L960" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M960" s="1" t="s">
         <v>528</v>
@@ -52385,7 +52379,7 @@
     </row>
     <row r="961" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A961" s="1" t="s">
-        <v>1917</v>
+        <v>1915</v>
       </c>
       <c r="B961" s="7" t="s">
         <v>1609</v>
@@ -52415,7 +52409,7 @@
         <v>251</v>
       </c>
       <c r="L961" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M961" s="1" t="s">
         <v>528</v>
@@ -52429,7 +52423,7 @@
     </row>
     <row r="962" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A962" s="1" t="s">
-        <v>1918</v>
+        <v>1916</v>
       </c>
       <c r="B962" s="7" t="s">
         <v>1609</v>
@@ -52459,7 +52453,7 @@
         <v>251</v>
       </c>
       <c r="L962" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M962" s="1" t="s">
         <v>528</v>
@@ -52473,7 +52467,7 @@
     </row>
     <row r="963" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A963" s="1" t="s">
-        <v>1919</v>
+        <v>1917</v>
       </c>
       <c r="B963" s="7" t="s">
         <v>1609</v>
@@ -52503,7 +52497,7 @@
         <v>251</v>
       </c>
       <c r="L963" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M963" s="1" t="s">
         <v>528</v>
@@ -52517,7 +52511,7 @@
     </row>
     <row r="964" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A964" s="1" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="B964" s="7" t="s">
         <v>1609</v>
@@ -52547,7 +52541,7 @@
         <v>251</v>
       </c>
       <c r="L964" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M964" s="1" t="s">
         <v>528</v>
@@ -52561,7 +52555,7 @@
     </row>
     <row r="965" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A965" s="1" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="B965" s="7" t="s">
         <v>1609</v>
@@ -52591,7 +52585,7 @@
         <v>251</v>
       </c>
       <c r="L965" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M965" s="1" t="s">
         <v>528</v>
@@ -52605,7 +52599,7 @@
     </row>
     <row r="966" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A966" s="1" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="B966" s="7" t="s">
         <v>1609</v>
@@ -52635,7 +52629,7 @@
         <v>251</v>
       </c>
       <c r="L966" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M966" s="1" t="s">
         <v>528</v>
@@ -52649,7 +52643,7 @@
     </row>
     <row r="967" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A967" s="1" t="s">
-        <v>1923</v>
+        <v>1921</v>
       </c>
       <c r="B967" s="7" t="s">
         <v>1609</v>
@@ -52679,7 +52673,7 @@
         <v>251</v>
       </c>
       <c r="L967" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M967" s="1" t="s">
         <v>528</v>
@@ -52693,7 +52687,7 @@
     </row>
     <row r="968" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A968" s="1" t="s">
-        <v>1924</v>
+        <v>1922</v>
       </c>
       <c r="B968" s="7" t="s">
         <v>1609</v>
@@ -52723,7 +52717,7 @@
         <v>251</v>
       </c>
       <c r="L968" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M968" s="1" t="s">
         <v>528</v>
@@ -52737,7 +52731,7 @@
     </row>
     <row r="969" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A969" s="1" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="B969" s="7" t="s">
         <v>1609</v>
@@ -52767,7 +52761,7 @@
         <v>251</v>
       </c>
       <c r="L969" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M969" s="1" t="s">
         <v>528</v>
@@ -52781,7 +52775,7 @@
     </row>
     <row r="970" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A970" s="1" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="B970" s="7" t="s">
         <v>1609</v>
@@ -52811,7 +52805,7 @@
         <v>251</v>
       </c>
       <c r="L970" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M970" s="1" t="s">
         <v>528</v>
@@ -52825,7 +52819,7 @@
     </row>
     <row r="971" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A971" s="1" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="B971" s="7" t="s">
         <v>1609</v>
@@ -52855,7 +52849,7 @@
         <v>251</v>
       </c>
       <c r="L971" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M971" s="1" t="s">
         <v>528</v>
@@ -52869,7 +52863,7 @@
     </row>
     <row r="972" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A972" s="1" t="s">
-        <v>1928</v>
+        <v>1926</v>
       </c>
       <c r="B972" s="7" t="s">
         <v>1609</v>
@@ -52899,7 +52893,7 @@
         <v>251</v>
       </c>
       <c r="L972" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M972" s="1" t="s">
         <v>528</v>
@@ -52913,7 +52907,7 @@
     </row>
     <row r="973" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A973" s="1" t="s">
-        <v>1929</v>
+        <v>1927</v>
       </c>
       <c r="B973" s="7" t="s">
         <v>1609</v>
@@ -52943,7 +52937,7 @@
         <v>251</v>
       </c>
       <c r="L973" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M973" s="1" t="s">
         <v>528</v>
@@ -52957,7 +52951,7 @@
     </row>
     <row r="974" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A974" s="1" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="B974" s="7" t="s">
         <v>1609</v>
@@ -52987,7 +52981,7 @@
         <v>251</v>
       </c>
       <c r="L974" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M974" s="1" t="s">
         <v>528</v>
@@ -53001,7 +52995,7 @@
     </row>
     <row r="975" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A975" s="1" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="B975" s="7" t="s">
         <v>1609</v>
@@ -53031,7 +53025,7 @@
         <v>251</v>
       </c>
       <c r="L975" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M975" s="1" t="s">
         <v>528</v>
@@ -53045,7 +53039,7 @@
     </row>
     <row r="976" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A976" s="1" t="s">
-        <v>1932</v>
+        <v>1930</v>
       </c>
       <c r="B976" s="7" t="s">
         <v>1609</v>
@@ -53078,7 +53072,7 @@
         <v>251</v>
       </c>
       <c r="L976" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M976" s="1" t="s">
         <v>528</v>
@@ -53092,7 +53086,7 @@
     </row>
     <row r="977" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A977" s="1" t="s">
-        <v>1933</v>
+        <v>1931</v>
       </c>
       <c r="B977" s="7" t="s">
         <v>1609</v>
@@ -53125,7 +53119,7 @@
         <v>251</v>
       </c>
       <c r="L977" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M977" s="1" t="s">
         <v>528</v>
@@ -53139,7 +53133,7 @@
     </row>
     <row r="978" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A978" s="1" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="B978" s="7" t="s">
         <v>1609</v>
@@ -53172,7 +53166,7 @@
         <v>251</v>
       </c>
       <c r="L978" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M978" s="1" t="s">
         <v>528</v>
@@ -53186,7 +53180,7 @@
     </row>
     <row r="979" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A979" s="1" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="B979" s="7" t="s">
         <v>1609</v>
@@ -53219,7 +53213,7 @@
         <v>251</v>
       </c>
       <c r="L979" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M979" s="1" t="s">
         <v>528</v>
@@ -53233,7 +53227,7 @@
     </row>
     <row r="980" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A980" s="1" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="B980" s="7" t="s">
         <v>1609</v>
@@ -53266,7 +53260,7 @@
         <v>251</v>
       </c>
       <c r="L980" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M980" s="1" t="s">
         <v>528</v>
@@ -53280,7 +53274,7 @@
     </row>
     <row r="981" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A981" s="1" t="s">
-        <v>1937</v>
+        <v>1935</v>
       </c>
       <c r="B981" s="7" t="s">
         <v>1609</v>
@@ -53313,7 +53307,7 @@
         <v>251</v>
       </c>
       <c r="L981" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M981" s="1" t="s">
         <v>528</v>
@@ -53327,7 +53321,7 @@
     </row>
     <row r="982" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A982" s="1" t="s">
-        <v>1938</v>
+        <v>1936</v>
       </c>
       <c r="B982" s="7" t="s">
         <v>1609</v>
@@ -53360,7 +53354,7 @@
         <v>251</v>
       </c>
       <c r="L982" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M982" s="1" t="s">
         <v>528</v>
@@ -53374,7 +53368,7 @@
     </row>
     <row r="983" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A983" s="1" t="s">
-        <v>1939</v>
+        <v>1937</v>
       </c>
       <c r="B983" s="7" t="s">
         <v>1609</v>
@@ -53407,7 +53401,7 @@
         <v>251</v>
       </c>
       <c r="L983" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M983" s="1" t="s">
         <v>528</v>
@@ -53421,7 +53415,7 @@
     </row>
     <row r="984" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A984" s="1" t="s">
-        <v>1940</v>
+        <v>1938</v>
       </c>
       <c r="B984" s="7" t="s">
         <v>1609</v>
@@ -53454,7 +53448,7 @@
         <v>251</v>
       </c>
       <c r="L984" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M984" s="1" t="s">
         <v>528</v>
@@ -53468,7 +53462,7 @@
     </row>
     <row r="985" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A985" s="1" t="s">
-        <v>1941</v>
+        <v>1939</v>
       </c>
       <c r="B985" s="7" t="s">
         <v>1609</v>
@@ -53501,7 +53495,7 @@
         <v>251</v>
       </c>
       <c r="L985" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M985" s="1" t="s">
         <v>528</v>
@@ -53515,7 +53509,7 @@
     </row>
     <row r="986" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A986" s="1" t="s">
-        <v>1942</v>
+        <v>1940</v>
       </c>
       <c r="B986" s="7" t="s">
         <v>1609</v>
@@ -53548,7 +53542,7 @@
         <v>251</v>
       </c>
       <c r="L986" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M986" s="1" t="s">
         <v>528</v>
@@ -53562,7 +53556,7 @@
     </row>
     <row r="987" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A987" s="1" t="s">
-        <v>1943</v>
+        <v>1941</v>
       </c>
       <c r="B987" s="7" t="s">
         <v>1609</v>
@@ -53595,7 +53589,7 @@
         <v>251</v>
       </c>
       <c r="L987" s="1" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M987" s="1" t="s">
         <v>528</v>
@@ -53609,7 +53603,7 @@
     </row>
     <row r="988" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A988" s="1" t="s">
-        <v>1944</v>
+        <v>1942</v>
       </c>
       <c r="B988" s="19" t="s">
         <v>826</v>
@@ -53656,7 +53650,7 @@
     </row>
     <row r="989" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A989" s="1" t="s">
-        <v>1945</v>
+        <v>1943</v>
       </c>
       <c r="B989" s="19" t="s">
         <v>826</v>
@@ -53703,7 +53697,7 @@
     </row>
     <row r="990" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A990" s="1" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="B990" s="19" t="s">
         <v>826</v>
@@ -53750,7 +53744,7 @@
     </row>
     <row r="991" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A991" s="1" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="B991" s="19" t="s">
         <v>826</v>
@@ -53797,7 +53791,7 @@
     </row>
     <row r="992" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A992" s="1" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="B992" s="19" t="s">
         <v>826</v>
@@ -53844,7 +53838,7 @@
     </row>
     <row r="993" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A993" s="1" t="s">
-        <v>1949</v>
+        <v>1947</v>
       </c>
       <c r="B993" s="19" t="s">
         <v>826</v>
@@ -53891,7 +53885,7 @@
     </row>
     <row r="994" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A994" s="1" t="s">
-        <v>1950</v>
+        <v>1948</v>
       </c>
       <c r="B994" s="19" t="s">
         <v>826</v>
@@ -53938,7 +53932,7 @@
     </row>
     <row r="995" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A995" s="1" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="B995" s="19" t="s">
         <v>826</v>
@@ -53985,7 +53979,7 @@
     </row>
     <row r="996" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A996" s="1" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B996" s="19" t="s">
         <v>826</v>
@@ -54032,7 +54026,7 @@
     </row>
     <row r="997" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A997" s="1" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="B997" s="19" t="s">
         <v>826</v>
@@ -54079,7 +54073,7 @@
     </row>
     <row r="998" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A998" s="1" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="B998" s="19" t="s">
         <v>826</v>
@@ -54126,7 +54120,7 @@
     </row>
     <row r="999" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A999" s="1" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="B999" s="19" t="s">
         <v>826</v>
@@ -54173,10 +54167,10 @@
     </row>
     <row r="1000" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1000" s="1" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="B1000" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1000" s="1">
         <v>2026</v>
@@ -54206,7 +54200,7 @@
         <v>251</v>
       </c>
       <c r="L1000" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1000" s="1" t="s">
         <v>528</v>
@@ -54220,10 +54214,10 @@
     </row>
     <row r="1001" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1001" s="1" t="s">
-        <v>1957</v>
+        <v>1955</v>
       </c>
       <c r="B1001" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1001" s="1">
         <v>2026</v>
@@ -54253,7 +54247,7 @@
         <v>251</v>
       </c>
       <c r="L1001" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1001" s="1" t="s">
         <v>528</v>
@@ -54267,10 +54261,10 @@
     </row>
     <row r="1002" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1002" s="1" t="s">
-        <v>1958</v>
+        <v>1956</v>
       </c>
       <c r="B1002" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1002" s="1">
         <v>2026</v>
@@ -54300,7 +54294,7 @@
         <v>251</v>
       </c>
       <c r="L1002" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1002" s="1" t="s">
         <v>528</v>
@@ -54314,10 +54308,10 @@
     </row>
     <row r="1003" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1003" s="1" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="B1003" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1003" s="1">
         <v>2026</v>
@@ -54347,7 +54341,7 @@
         <v>251</v>
       </c>
       <c r="L1003" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1003" s="1" t="s">
         <v>528</v>
@@ -54361,10 +54355,10 @@
     </row>
     <row r="1004" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1004" s="1" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="B1004" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1004" s="1">
         <v>2026</v>
@@ -54394,7 +54388,7 @@
         <v>251</v>
       </c>
       <c r="L1004" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1004" s="1" t="s">
         <v>528</v>
@@ -54408,10 +54402,10 @@
     </row>
     <row r="1005" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1005" s="1" t="s">
-        <v>1961</v>
+        <v>1959</v>
       </c>
       <c r="B1005" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1005" s="1">
         <v>2026</v>
@@ -54441,7 +54435,7 @@
         <v>251</v>
       </c>
       <c r="L1005" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1005" s="1" t="s">
         <v>528</v>
@@ -54455,10 +54449,10 @@
     </row>
     <row r="1006" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1006" s="1" t="s">
-        <v>1962</v>
+        <v>1960</v>
       </c>
       <c r="B1006" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1006" s="1">
         <v>2026</v>
@@ -54488,7 +54482,7 @@
         <v>251</v>
       </c>
       <c r="L1006" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1006" s="1" t="s">
         <v>528</v>
@@ -54502,10 +54496,10 @@
     </row>
     <row r="1007" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1007" s="1" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="B1007" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1007" s="1">
         <v>2026</v>
@@ -54535,7 +54529,7 @@
         <v>251</v>
       </c>
       <c r="L1007" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1007" s="1" t="s">
         <v>528</v>
@@ -54549,10 +54543,10 @@
     </row>
     <row r="1008" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1008" s="1" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="B1008" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1008" s="1">
         <v>2026</v>
@@ -54582,7 +54576,7 @@
         <v>251</v>
       </c>
       <c r="L1008" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1008" s="1" t="s">
         <v>528</v>
@@ -54596,10 +54590,10 @@
     </row>
     <row r="1009" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1009" s="1" t="s">
-        <v>1965</v>
+        <v>1963</v>
       </c>
       <c r="B1009" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1009" s="1">
         <v>2026</v>
@@ -54629,7 +54623,7 @@
         <v>251</v>
       </c>
       <c r="L1009" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1009" s="1" t="s">
         <v>528</v>
@@ -54643,10 +54637,10 @@
     </row>
     <row r="1010" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1010" s="1" t="s">
-        <v>1966</v>
+        <v>1964</v>
       </c>
       <c r="B1010" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1010" s="1">
         <v>2026</v>
@@ -54676,7 +54670,7 @@
         <v>251</v>
       </c>
       <c r="L1010" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1010" s="1" t="s">
         <v>528</v>
@@ -54690,10 +54684,10 @@
     </row>
     <row r="1011" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1011" s="1" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="B1011" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1011" s="1">
         <v>2026</v>
@@ -54723,7 +54717,7 @@
         <v>251</v>
       </c>
       <c r="L1011" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1011" s="1" t="s">
         <v>528</v>
@@ -54737,10 +54731,10 @@
     </row>
     <row r="1012" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1012" s="1" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="B1012" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1012" s="1">
         <v>2026</v>
@@ -54770,7 +54764,7 @@
         <v>251</v>
       </c>
       <c r="L1012" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1012" s="1" t="s">
         <v>528</v>
@@ -54784,10 +54778,10 @@
     </row>
     <row r="1013" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1013" s="1" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="B1013" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1013" s="1">
         <v>2026</v>
@@ -54817,7 +54811,7 @@
         <v>251</v>
       </c>
       <c r="L1013" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1013" s="1" t="s">
         <v>528</v>
@@ -54831,10 +54825,10 @@
     </row>
     <row r="1014" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1014" s="1" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="B1014" s="19" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C1014" s="1">
         <v>2026</v>
@@ -54864,7 +54858,7 @@
         <v>251</v>
       </c>
       <c r="L1014" s="1" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M1014" s="1" t="s">
         <v>528</v>
@@ -54878,7 +54872,7 @@
     </row>
     <row r="1015" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1015" s="1" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="B1015" s="19" t="s">
         <v>879</v>
@@ -54911,7 +54905,7 @@
         <v>252</v>
       </c>
       <c r="L1015" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1015" s="1" t="s">
         <v>546</v>
@@ -54925,7 +54919,7 @@
     </row>
     <row r="1016" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1016" s="1" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="B1016" s="19" t="s">
         <v>879</v>
@@ -54958,7 +54952,7 @@
         <v>252</v>
       </c>
       <c r="L1016" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1016" s="1" t="s">
         <v>546</v>
@@ -54972,7 +54966,7 @@
     </row>
     <row r="1017" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1017" s="1" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="B1017" s="19" t="s">
         <v>879</v>
@@ -55005,7 +54999,7 @@
         <v>252</v>
       </c>
       <c r="L1017" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1017" s="1" t="s">
         <v>546</v>
@@ -55019,7 +55013,7 @@
     </row>
     <row r="1018" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1018" s="1" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="B1018" s="19" t="s">
         <v>879</v>
@@ -55052,7 +55046,7 @@
         <v>252</v>
       </c>
       <c r="L1018" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1018" s="1" t="s">
         <v>546</v>
@@ -55066,7 +55060,7 @@
     </row>
     <row r="1019" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1019" s="1" t="s">
-        <v>1975</v>
+        <v>1973</v>
       </c>
       <c r="B1019" s="19" t="s">
         <v>879</v>
@@ -55099,7 +55093,7 @@
         <v>252</v>
       </c>
       <c r="L1019" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1019" s="1" t="s">
         <v>546</v>
@@ -55113,7 +55107,7 @@
     </row>
     <row r="1020" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1020" s="1" t="s">
-        <v>1976</v>
+        <v>1974</v>
       </c>
       <c r="B1020" s="19" t="s">
         <v>879</v>
@@ -55146,7 +55140,7 @@
         <v>252</v>
       </c>
       <c r="L1020" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1020" s="1" t="s">
         <v>546</v>
@@ -55160,7 +55154,7 @@
     </row>
     <row r="1021" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1021" s="1" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="B1021" s="19" t="s">
         <v>879</v>
@@ -55193,7 +55187,7 @@
         <v>252</v>
       </c>
       <c r="L1021" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1021" s="1" t="s">
         <v>546</v>
@@ -55207,7 +55201,7 @@
     </row>
     <row r="1022" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1022" s="1" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="B1022" s="19" t="s">
         <v>879</v>
@@ -55240,7 +55234,7 @@
         <v>252</v>
       </c>
       <c r="L1022" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1022" s="1" t="s">
         <v>546</v>
@@ -55254,7 +55248,7 @@
     </row>
     <row r="1023" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1023" s="1" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="B1023" s="19" t="s">
         <v>879</v>
@@ -55287,7 +55281,7 @@
         <v>252</v>
       </c>
       <c r="L1023" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1023" s="1" t="s">
         <v>546</v>
@@ -55301,7 +55295,7 @@
     </row>
     <row r="1024" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1024" s="1" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="B1024" s="19" t="s">
         <v>879</v>
@@ -55334,7 +55328,7 @@
         <v>252</v>
       </c>
       <c r="L1024" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1024" s="1" t="s">
         <v>546</v>
@@ -55348,7 +55342,7 @@
     </row>
     <row r="1025" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1025" s="1" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="B1025" s="19" t="s">
         <v>879</v>
@@ -55381,7 +55375,7 @@
         <v>252</v>
       </c>
       <c r="L1025" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1025" s="1" t="s">
         <v>546</v>
@@ -55395,7 +55389,7 @@
     </row>
     <row r="1026" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1026" s="1" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="B1026" s="19" t="s">
         <v>879</v>
@@ -55428,7 +55422,7 @@
         <v>252</v>
       </c>
       <c r="L1026" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1026" s="1" t="s">
         <v>546</v>
@@ -55442,7 +55436,7 @@
     </row>
     <row r="1027" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1027" s="1" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="B1027" s="19" t="s">
         <v>879</v>
@@ -55475,7 +55469,7 @@
         <v>252</v>
       </c>
       <c r="L1027" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1027" s="1" t="s">
         <v>546</v>
@@ -55489,7 +55483,7 @@
     </row>
     <row r="1028" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1028" s="1" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="B1028" s="19" t="s">
         <v>879</v>
@@ -55522,7 +55516,7 @@
         <v>252</v>
       </c>
       <c r="L1028" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1028" s="1" t="s">
         <v>546</v>
@@ -55536,7 +55530,7 @@
     </row>
     <row r="1029" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1029" s="1" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="B1029" s="19" t="s">
         <v>879</v>
@@ -55569,7 +55563,7 @@
         <v>252</v>
       </c>
       <c r="L1029" s="1" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M1029" s="1" t="s">
         <v>546</v>
@@ -55583,7 +55577,7 @@
     </row>
     <row r="1030" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1030" s="1" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="B1030" s="7" t="s">
         <v>1608</v>
@@ -55610,13 +55604,13 @@
         <v>1620</v>
       </c>
       <c r="J1030" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1030" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1030" s="1" t="s">
         <v>1809</v>
-      </c>
-      <c r="K1030" s="1" t="s">
-        <v>1810</v>
-      </c>
-      <c r="L1030" s="1" t="s">
-        <v>1811</v>
       </c>
       <c r="M1030" s="1" t="s">
         <v>528</v>
@@ -55630,7 +55624,7 @@
     </row>
     <row r="1031" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1031" s="1" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="B1031" s="7" t="s">
         <v>1608</v>
@@ -55657,13 +55651,13 @@
         <v>1620</v>
       </c>
       <c r="J1031" s="1" t="s">
-        <v>1809</v>
+        <v>194</v>
       </c>
       <c r="K1031" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1031" s="1" t="s">
         <v>1810</v>
-      </c>
-      <c r="L1031" s="1" t="s">
-        <v>1812</v>
       </c>
       <c r="M1031" s="1" t="s">
         <v>528</v>
@@ -55824,7 +55818,7 @@
         <v>249</v>
       </c>
       <c r="L3" s="18" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="M3" s="18" t="s">
         <v>528</v>
@@ -55859,7 +55853,7 @@
         <v>249</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="M4" s="18" t="s">
         <v>528</v>
@@ -55894,7 +55888,7 @@
         <v>245</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="M5" s="18" t="s">
         <v>528</v>
@@ -56104,7 +56098,7 @@
         <v>245</v>
       </c>
       <c r="L11" s="18" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="M11" s="18" t="s">
         <v>528</v>
@@ -56276,7 +56270,7 @@
         <v>1807</v>
       </c>
       <c r="K16" s="18" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="L16" s="18" t="s">
         <v>1455</v>
@@ -56311,7 +56305,7 @@
         <v>1807</v>
       </c>
       <c r="K17" s="18" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="L17" s="18" t="s">
         <v>1456</v>
@@ -56346,7 +56340,7 @@
         <v>1807</v>
       </c>
       <c r="K18" s="18" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="L18" s="18" t="s">
         <v>1457</v>
@@ -56381,10 +56375,10 @@
         <v>1807</v>
       </c>
       <c r="K19" s="18" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="L19" s="18" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="M19" s="18" t="s">
         <v>528</v>
@@ -56699,7 +56693,7 @@
         <v>251</v>
       </c>
       <c r="L28" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M28" s="18" t="s">
         <v>528</v>
@@ -56734,7 +56728,7 @@
         <v>251</v>
       </c>
       <c r="L29" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M29" s="18" t="s">
         <v>528</v>
@@ -56769,7 +56763,7 @@
         <v>251</v>
       </c>
       <c r="L30" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M30" s="18" t="s">
         <v>528</v>
@@ -56804,7 +56798,7 @@
         <v>251</v>
       </c>
       <c r="L31" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M31" s="18" t="s">
         <v>528</v>
@@ -56839,7 +56833,7 @@
         <v>251</v>
       </c>
       <c r="L32" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M32" s="18" t="s">
         <v>528</v>
@@ -56874,7 +56868,7 @@
         <v>251</v>
       </c>
       <c r="L33" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M33" s="18" t="s">
         <v>528</v>
@@ -56909,7 +56903,7 @@
         <v>251</v>
       </c>
       <c r="L34" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M34" s="18" t="s">
         <v>528</v>
@@ -56944,7 +56938,7 @@
         <v>251</v>
       </c>
       <c r="L35" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M35" s="18" t="s">
         <v>528</v>
@@ -56979,7 +56973,7 @@
         <v>251</v>
       </c>
       <c r="L36" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M36" s="18" t="s">
         <v>528</v>
@@ -57014,7 +57008,7 @@
         <v>251</v>
       </c>
       <c r="L37" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M37" s="18" t="s">
         <v>528</v>
@@ -57049,7 +57043,7 @@
         <v>251</v>
       </c>
       <c r="L38" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M38" s="18" t="s">
         <v>528</v>
@@ -57084,7 +57078,7 @@
         <v>251</v>
       </c>
       <c r="L39" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M39" s="18" t="s">
         <v>528</v>
@@ -57119,7 +57113,7 @@
         <v>251</v>
       </c>
       <c r="L40" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M40" s="18" t="s">
         <v>528</v>
@@ -57154,7 +57148,7 @@
         <v>251</v>
       </c>
       <c r="L41" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M41" s="18" t="s">
         <v>528</v>
@@ -57189,7 +57183,7 @@
         <v>251</v>
       </c>
       <c r="L42" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M42" s="18" t="s">
         <v>528</v>
@@ -57224,7 +57218,7 @@
         <v>251</v>
       </c>
       <c r="L43" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M43" s="18" t="s">
         <v>528</v>
@@ -57259,7 +57253,7 @@
         <v>251</v>
       </c>
       <c r="L44" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M44" s="18" t="s">
         <v>528</v>
@@ -57294,7 +57288,7 @@
         <v>251</v>
       </c>
       <c r="L45" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M45" s="18" t="s">
         <v>528</v>
@@ -57329,7 +57323,7 @@
         <v>251</v>
       </c>
       <c r="L46" s="18" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="M46" s="18" t="s">
         <v>528</v>
@@ -57355,10 +57349,10 @@
         <v>1748</v>
       </c>
       <c r="J47" s="18" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="K47" s="18" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="L47" s="18" t="s">
         <v>1601</v>
@@ -57393,7 +57387,7 @@
         <v>251</v>
       </c>
       <c r="L48" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M48" s="18" t="s">
         <v>528</v>
@@ -57425,7 +57419,7 @@
         <v>251</v>
       </c>
       <c r="L49" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M49" s="18" t="s">
         <v>528</v>
@@ -57457,7 +57451,7 @@
         <v>251</v>
       </c>
       <c r="L50" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M50" s="18" t="s">
         <v>528</v>
@@ -57489,7 +57483,7 @@
         <v>251</v>
       </c>
       <c r="L51" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M51" s="18" t="s">
         <v>528</v>
@@ -57521,7 +57515,7 @@
         <v>251</v>
       </c>
       <c r="L52" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M52" s="18" t="s">
         <v>528</v>
@@ -57553,7 +57547,7 @@
         <v>251</v>
       </c>
       <c r="L53" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M53" s="18" t="s">
         <v>528</v>
@@ -57585,7 +57579,7 @@
         <v>251</v>
       </c>
       <c r="L54" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M54" s="18" t="s">
         <v>528</v>
@@ -57617,7 +57611,7 @@
         <v>251</v>
       </c>
       <c r="L55" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M55" s="18" t="s">
         <v>528</v>
@@ -57652,7 +57646,7 @@
         <v>251</v>
       </c>
       <c r="L56" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M56" s="18" t="s">
         <v>528</v>
@@ -57687,7 +57681,7 @@
         <v>251</v>
       </c>
       <c r="L57" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M57" s="18" t="s">
         <v>528</v>
@@ -57722,7 +57716,7 @@
         <v>251</v>
       </c>
       <c r="L58" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M58" s="18" t="s">
         <v>528</v>
@@ -57757,7 +57751,7 @@
         <v>251</v>
       </c>
       <c r="L59" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M59" s="18" t="s">
         <v>528</v>
@@ -57792,7 +57786,7 @@
         <v>251</v>
       </c>
       <c r="L60" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M60" s="18" t="s">
         <v>528</v>
@@ -57827,7 +57821,7 @@
         <v>251</v>
       </c>
       <c r="L61" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M61" s="18" t="s">
         <v>528</v>
@@ -57862,7 +57856,7 @@
         <v>251</v>
       </c>
       <c r="L62" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M62" s="18" t="s">
         <v>528</v>
@@ -57897,7 +57891,7 @@
         <v>251</v>
       </c>
       <c r="L63" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M63" s="18" t="s">
         <v>528</v>
@@ -57932,7 +57926,7 @@
         <v>251</v>
       </c>
       <c r="L64" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M64" s="18" t="s">
         <v>528</v>
@@ -57964,7 +57958,7 @@
         <v>251</v>
       </c>
       <c r="L65" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M65" s="18" t="s">
         <v>528</v>
@@ -57996,7 +57990,7 @@
         <v>251</v>
       </c>
       <c r="L66" s="18" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="M66" s="18" t="s">
         <v>528</v>
@@ -58028,7 +58022,7 @@
         <v>251</v>
       </c>
       <c r="L67" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M67" s="18" t="s">
         <v>528</v>
@@ -58060,7 +58054,7 @@
         <v>251</v>
       </c>
       <c r="L68" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M68" s="18" t="s">
         <v>528</v>
@@ -58092,7 +58086,7 @@
         <v>251</v>
       </c>
       <c r="L69" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M69" s="18" t="s">
         <v>528</v>
@@ -58124,7 +58118,7 @@
         <v>251</v>
       </c>
       <c r="L70" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M70" s="18" t="s">
         <v>528</v>
@@ -58156,7 +58150,7 @@
         <v>251</v>
       </c>
       <c r="L71" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M71" s="18" t="s">
         <v>528</v>
@@ -58188,7 +58182,7 @@
         <v>251</v>
       </c>
       <c r="L72" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M72" s="18" t="s">
         <v>528</v>
@@ -58220,7 +58214,7 @@
         <v>251</v>
       </c>
       <c r="L73" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M73" s="18" t="s">
         <v>528</v>
@@ -58255,7 +58249,7 @@
         <v>251</v>
       </c>
       <c r="L74" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M74" s="18" t="s">
         <v>528</v>
@@ -58290,7 +58284,7 @@
         <v>251</v>
       </c>
       <c r="L75" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M75" s="18" t="s">
         <v>528</v>
@@ -58325,7 +58319,7 @@
         <v>251</v>
       </c>
       <c r="L76" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M76" s="18" t="s">
         <v>528</v>
@@ -58360,7 +58354,7 @@
         <v>251</v>
       </c>
       <c r="L77" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M77" s="18" t="s">
         <v>528</v>
@@ -58395,7 +58389,7 @@
         <v>251</v>
       </c>
       <c r="L78" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M78" s="18" t="s">
         <v>528</v>
@@ -58430,7 +58424,7 @@
         <v>251</v>
       </c>
       <c r="L79" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M79" s="18" t="s">
         <v>528</v>
@@ -58465,7 +58459,7 @@
         <v>251</v>
       </c>
       <c r="L80" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M80" s="18" t="s">
         <v>528</v>
@@ -58500,7 +58494,7 @@
         <v>251</v>
       </c>
       <c r="L81" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M81" s="18" t="s">
         <v>528</v>
@@ -58535,7 +58529,7 @@
         <v>251</v>
       </c>
       <c r="L82" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M82" s="18" t="s">
         <v>528</v>
@@ -58570,7 +58564,7 @@
         <v>251</v>
       </c>
       <c r="L83" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M83" s="18" t="s">
         <v>528</v>
@@ -58602,7 +58596,7 @@
         <v>251</v>
       </c>
       <c r="L84" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M84" s="18" t="s">
         <v>528</v>
@@ -58637,7 +58631,7 @@
         <v>251</v>
       </c>
       <c r="L85" s="18" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="M85" s="18" t="s">
         <v>528</v>
@@ -59129,7 +59123,7 @@
         <v>251</v>
       </c>
       <c r="L100" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M100" s="18" t="s">
         <v>528</v>
@@ -59161,7 +59155,7 @@
         <v>251</v>
       </c>
       <c r="L101" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M101" s="18" t="s">
         <v>528</v>
@@ -59193,7 +59187,7 @@
         <v>251</v>
       </c>
       <c r="L102" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M102" s="18" t="s">
         <v>528</v>
@@ -59225,7 +59219,7 @@
         <v>251</v>
       </c>
       <c r="L103" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M103" s="18" t="s">
         <v>528</v>
@@ -59257,7 +59251,7 @@
         <v>251</v>
       </c>
       <c r="L104" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M104" s="18" t="s">
         <v>528</v>
@@ -59289,7 +59283,7 @@
         <v>251</v>
       </c>
       <c r="L105" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M105" s="18" t="s">
         <v>528</v>
@@ -59321,7 +59315,7 @@
         <v>251</v>
       </c>
       <c r="L106" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M106" s="18" t="s">
         <v>528</v>
@@ -59353,7 +59347,7 @@
         <v>251</v>
       </c>
       <c r="L107" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M107" s="18" t="s">
         <v>528</v>
@@ -59385,7 +59379,7 @@
         <v>251</v>
       </c>
       <c r="L108" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M108" s="18" t="s">
         <v>528</v>
@@ -59417,7 +59411,7 @@
         <v>251</v>
       </c>
       <c r="L109" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M109" s="18" t="s">
         <v>528</v>
@@ -59449,7 +59443,7 @@
         <v>251</v>
       </c>
       <c r="L110" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M110" s="18" t="s">
         <v>528</v>
@@ -59481,7 +59475,7 @@
         <v>251</v>
       </c>
       <c r="L111" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M111" s="18" t="s">
         <v>528</v>
@@ -59513,7 +59507,7 @@
         <v>251</v>
       </c>
       <c r="L112" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M112" s="18" t="s">
         <v>528</v>
@@ -59545,7 +59539,7 @@
         <v>251</v>
       </c>
       <c r="L113" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M113" s="18" t="s">
         <v>528</v>
@@ -59577,7 +59571,7 @@
         <v>251</v>
       </c>
       <c r="L114" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M114" s="18" t="s">
         <v>528</v>
@@ -59609,7 +59603,7 @@
         <v>251</v>
       </c>
       <c r="L115" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M115" s="18" t="s">
         <v>528</v>
@@ -59644,7 +59638,7 @@
         <v>251</v>
       </c>
       <c r="L116" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M116" s="18" t="s">
         <v>528</v>
@@ -59679,7 +59673,7 @@
         <v>251</v>
       </c>
       <c r="L117" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M117" s="18" t="s">
         <v>528</v>
@@ -59714,7 +59708,7 @@
         <v>251</v>
       </c>
       <c r="L118" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M118" s="18" t="s">
         <v>528</v>
@@ -59749,7 +59743,7 @@
         <v>251</v>
       </c>
       <c r="L119" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M119" s="18" t="s">
         <v>528</v>
@@ -59784,7 +59778,7 @@
         <v>251</v>
       </c>
       <c r="L120" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M120" s="18" t="s">
         <v>528</v>
@@ -59819,7 +59813,7 @@
         <v>251</v>
       </c>
       <c r="L121" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M121" s="18" t="s">
         <v>528</v>
@@ -59854,7 +59848,7 @@
         <v>251</v>
       </c>
       <c r="L122" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M122" s="18" t="s">
         <v>528</v>
@@ -59889,7 +59883,7 @@
         <v>251</v>
       </c>
       <c r="L123" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M123" s="18" t="s">
         <v>528</v>
@@ -59924,7 +59918,7 @@
         <v>251</v>
       </c>
       <c r="L124" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M124" s="18" t="s">
         <v>528</v>
@@ -59959,7 +59953,7 @@
         <v>251</v>
       </c>
       <c r="L125" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M125" s="18" t="s">
         <v>528</v>
@@ -59994,7 +59988,7 @@
         <v>251</v>
       </c>
       <c r="L126" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M126" s="18" t="s">
         <v>528</v>
@@ -60029,7 +60023,7 @@
         <v>251</v>
       </c>
       <c r="L127" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M127" s="18" t="s">
         <v>528</v>
@@ -60064,7 +60058,7 @@
         <v>251</v>
       </c>
       <c r="L128" s="18" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="M128" s="18" t="s">
         <v>528</v>
@@ -60495,7 +60489,7 @@
     </row>
     <row r="141" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B141" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C141" s="18">
         <v>2026</v>
@@ -60519,7 +60513,7 @@
         <v>251</v>
       </c>
       <c r="L141" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M141" s="18" t="s">
         <v>528</v>
@@ -60530,7 +60524,7 @@
     </row>
     <row r="142" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B142" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C142" s="18">
         <v>2026</v>
@@ -60554,7 +60548,7 @@
         <v>251</v>
       </c>
       <c r="L142" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M142" s="18" t="s">
         <v>528</v>
@@ -60565,7 +60559,7 @@
     </row>
     <row r="143" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B143" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C143" s="18">
         <v>2026</v>
@@ -60589,7 +60583,7 @@
         <v>251</v>
       </c>
       <c r="L143" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M143" s="18" t="s">
         <v>528</v>
@@ -60600,7 +60594,7 @@
     </row>
     <row r="144" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B144" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C144" s="18">
         <v>2026</v>
@@ -60624,7 +60618,7 @@
         <v>251</v>
       </c>
       <c r="L144" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M144" s="18" t="s">
         <v>528</v>
@@ -60635,7 +60629,7 @@
     </row>
     <row r="145" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B145" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C145" s="18">
         <v>2026</v>
@@ -60659,7 +60653,7 @@
         <v>251</v>
       </c>
       <c r="L145" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M145" s="18" t="s">
         <v>528</v>
@@ -60670,7 +60664,7 @@
     </row>
     <row r="146" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B146" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C146" s="18">
         <v>2026</v>
@@ -60694,7 +60688,7 @@
         <v>251</v>
       </c>
       <c r="L146" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M146" s="18" t="s">
         <v>528</v>
@@ -60705,7 +60699,7 @@
     </row>
     <row r="147" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B147" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C147" s="18">
         <v>2026</v>
@@ -60729,7 +60723,7 @@
         <v>251</v>
       </c>
       <c r="L147" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M147" s="18" t="s">
         <v>528</v>
@@ -60740,7 +60734,7 @@
     </row>
     <row r="148" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B148" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C148" s="18">
         <v>2026</v>
@@ -60764,7 +60758,7 @@
         <v>251</v>
       </c>
       <c r="L148" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M148" s="18" t="s">
         <v>528</v>
@@ -60775,7 +60769,7 @@
     </row>
     <row r="149" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B149" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C149" s="18">
         <v>2026</v>
@@ -60799,7 +60793,7 @@
         <v>251</v>
       </c>
       <c r="L149" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M149" s="18" t="s">
         <v>528</v>
@@ -60810,7 +60804,7 @@
     </row>
     <row r="150" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B150" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C150" s="18">
         <v>2026</v>
@@ -60834,7 +60828,7 @@
         <v>251</v>
       </c>
       <c r="L150" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M150" s="18" t="s">
         <v>528</v>
@@ -60845,7 +60839,7 @@
     </row>
     <row r="151" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B151" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C151" s="18">
         <v>2026</v>
@@ -60869,7 +60863,7 @@
         <v>251</v>
       </c>
       <c r="L151" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M151" s="18" t="s">
         <v>528</v>
@@ -60880,7 +60874,7 @@
     </row>
     <row r="152" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B152" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C152" s="18">
         <v>2026</v>
@@ -60904,7 +60898,7 @@
         <v>251</v>
       </c>
       <c r="L152" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M152" s="18" t="s">
         <v>528</v>
@@ -60915,7 +60909,7 @@
     </row>
     <row r="153" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B153" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C153" s="18">
         <v>2026</v>
@@ -60939,7 +60933,7 @@
         <v>251</v>
       </c>
       <c r="L153" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M153" s="18" t="s">
         <v>528</v>
@@ -60950,7 +60944,7 @@
     </row>
     <row r="154" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B154" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C154" s="18">
         <v>2026</v>
@@ -60974,7 +60968,7 @@
         <v>251</v>
       </c>
       <c r="L154" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M154" s="18" t="s">
         <v>528</v>
@@ -60985,7 +60979,7 @@
     </row>
     <row r="155" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B155" s="18" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="C155" s="18">
         <v>2026</v>
@@ -61009,7 +61003,7 @@
         <v>251</v>
       </c>
       <c r="L155" s="18" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="M155" s="18" t="s">
         <v>528</v>
@@ -61044,7 +61038,7 @@
         <v>252</v>
       </c>
       <c r="L156" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M156" s="18" t="s">
         <v>546</v>
@@ -61079,7 +61073,7 @@
         <v>252</v>
       </c>
       <c r="L157" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M157" s="18" t="s">
         <v>546</v>
@@ -61114,7 +61108,7 @@
         <v>252</v>
       </c>
       <c r="L158" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M158" s="18" t="s">
         <v>546</v>
@@ -61149,7 +61143,7 @@
         <v>252</v>
       </c>
       <c r="L159" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M159" s="18" t="s">
         <v>546</v>
@@ -61184,7 +61178,7 @@
         <v>252</v>
       </c>
       <c r="L160" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M160" s="18" t="s">
         <v>546</v>
@@ -61219,7 +61213,7 @@
         <v>252</v>
       </c>
       <c r="L161" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M161" s="18" t="s">
         <v>546</v>
@@ -61254,7 +61248,7 @@
         <v>252</v>
       </c>
       <c r="L162" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M162" s="18" t="s">
         <v>546</v>
@@ -61289,7 +61283,7 @@
         <v>252</v>
       </c>
       <c r="L163" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M163" s="18" t="s">
         <v>546</v>
@@ -61324,7 +61318,7 @@
         <v>252</v>
       </c>
       <c r="L164" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M164" s="18" t="s">
         <v>546</v>
@@ -61359,7 +61353,7 @@
         <v>252</v>
       </c>
       <c r="L165" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M165" s="18" t="s">
         <v>546</v>
@@ -61394,7 +61388,7 @@
         <v>252</v>
       </c>
       <c r="L166" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M166" s="18" t="s">
         <v>546</v>
@@ -61429,7 +61423,7 @@
         <v>252</v>
       </c>
       <c r="L167" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M167" s="18" t="s">
         <v>546</v>
@@ -61464,7 +61458,7 @@
         <v>252</v>
       </c>
       <c r="L168" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M168" s="18" t="s">
         <v>546</v>
@@ -61499,7 +61493,7 @@
         <v>252</v>
       </c>
       <c r="L169" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M169" s="18" t="s">
         <v>546</v>
@@ -61525,7 +61519,7 @@
         <v>252</v>
       </c>
       <c r="L170" s="18" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="M170" s="18" t="s">
         <v>546</v>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DB0A00B-D573-497E-B88D-92516852FA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA3EDEC8-C7BD-4F8C-B398-9F7C0E2E2E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Hoja1!$A$1:$P$170</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$805</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$1032</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12444" uniqueCount="1987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12444" uniqueCount="1990">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -6098,6 +6098,15 @@
   </si>
   <si>
     <t>9.2. Participación en mesas, comités y otros grupos de trabajo técnicos de caracter público y/o privado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistencia técnica en teñido industrial verde y rosa: hacia procesos textiles más eficientes y responsables </t>
+  </si>
+  <si>
+    <t>Asistencia técnica en teñido textil en gamas de rojo: aprovechamiento responsable de recursos tintóreo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistencia técnica en teñido natural con eucalipto: revalorización de residuos vegetales en la cadena textil </t>
   </si>
 </sst>
 </file>
@@ -6590,6 +6599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P1032"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6661,7 +6671,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>596</v>
       </c>
@@ -6708,7 +6718,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>598</v>
       </c>
@@ -6755,7 +6765,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>599</v>
       </c>
@@ -6802,7 +6812,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>600</v>
       </c>
@@ -6869,13 +6879,13 @@
         <v>533</v>
       </c>
       <c r="G6" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>14</v>
@@ -6896,7 +6906,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>602</v>
       </c>
@@ -6943,7 +6953,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>603</v>
       </c>
@@ -6990,7 +7000,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>604</v>
       </c>
@@ -7037,7 +7047,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>605</v>
       </c>
@@ -7084,7 +7094,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>606</v>
       </c>
@@ -7131,7 +7141,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>607</v>
       </c>
@@ -7178,7 +7188,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>608</v>
       </c>
@@ -7245,13 +7255,13 @@
         <v>533</v>
       </c>
       <c r="G14" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="J14" s="1" t="s">
         <v>14</v>
@@ -7272,7 +7282,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>610</v>
       </c>
@@ -7319,7 +7329,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>611</v>
       </c>
@@ -7366,7 +7376,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>612</v>
       </c>
@@ -7413,7 +7423,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>613</v>
       </c>
@@ -7460,7 +7470,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>614</v>
       </c>
@@ -7507,7 +7517,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>615</v>
       </c>
@@ -7554,7 +7564,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>616</v>
       </c>
@@ -7601,7 +7611,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>617</v>
       </c>
@@ -7648,7 +7658,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>618</v>
       </c>
@@ -7695,7 +7705,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>619</v>
       </c>
@@ -7742,7 +7752,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>620</v>
       </c>
@@ -7789,7 +7799,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>621</v>
       </c>
@@ -7836,7 +7846,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>622</v>
       </c>
@@ -7883,7 +7893,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>623</v>
       </c>
@@ -7930,7 +7940,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>624</v>
       </c>
@@ -7977,7 +7987,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>625</v>
       </c>
@@ -8024,7 +8034,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>626</v>
       </c>
@@ -8071,7 +8081,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>627</v>
       </c>
@@ -8118,7 +8128,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>628</v>
       </c>
@@ -8165,7 +8175,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>629</v>
       </c>
@@ -8212,7 +8222,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>630</v>
       </c>
@@ -8259,7 +8269,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>631</v>
       </c>
@@ -8306,7 +8316,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>632</v>
       </c>
@@ -8353,7 +8363,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>633</v>
       </c>
@@ -8400,7 +8410,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>634</v>
       </c>
@@ -8447,7 +8457,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>635</v>
       </c>
@@ -8494,7 +8504,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>636</v>
       </c>
@@ -8541,7 +8551,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>637</v>
       </c>
@@ -8588,7 +8598,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>638</v>
       </c>
@@ -8635,7 +8645,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>639</v>
       </c>
@@ -8682,7 +8692,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>640</v>
       </c>
@@ -8729,7 +8739,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>641</v>
       </c>
@@ -8776,7 +8786,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>642</v>
       </c>
@@ -8823,7 +8833,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>643</v>
       </c>
@@ -8870,7 +8880,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>644</v>
       </c>
@@ -8917,7 +8927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>645</v>
       </c>
@@ -8964,7 +8974,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>646</v>
       </c>
@@ -9011,7 +9021,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>647</v>
       </c>
@@ -9058,7 +9068,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>648</v>
       </c>
@@ -9105,7 +9115,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>649</v>
       </c>
@@ -9152,7 +9162,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>650</v>
       </c>
@@ -9199,7 +9209,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>651</v>
       </c>
@@ -9246,7 +9256,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>652</v>
       </c>
@@ -9293,7 +9303,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>653</v>
       </c>
@@ -9340,7 +9350,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>654</v>
       </c>
@@ -9387,7 +9397,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>655</v>
       </c>
@@ -9434,7 +9444,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>656</v>
       </c>
@@ -9481,7 +9491,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>657</v>
       </c>
@@ -9528,7 +9538,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>658</v>
       </c>
@@ -9575,7 +9585,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>659</v>
       </c>
@@ -9622,7 +9632,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>660</v>
       </c>
@@ -9669,7 +9679,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>661</v>
       </c>
@@ -9716,7 +9726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>662</v>
       </c>
@@ -9763,7 +9773,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>663</v>
       </c>
@@ -9810,7 +9820,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>664</v>
       </c>
@@ -9857,7 +9867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>665</v>
       </c>
@@ -9904,7 +9914,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>666</v>
       </c>
@@ -9951,7 +9961,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>667</v>
       </c>
@@ -9998,7 +10008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>668</v>
       </c>
@@ -10045,7 +10055,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>669</v>
       </c>
@@ -10092,7 +10102,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>670</v>
       </c>
@@ -10139,7 +10149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>671</v>
       </c>
@@ -10186,7 +10196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>672</v>
       </c>
@@ -10233,7 +10243,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>673</v>
       </c>
@@ -10280,7 +10290,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>674</v>
       </c>
@@ -10327,7 +10337,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>675</v>
       </c>
@@ -10374,7 +10384,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>676</v>
       </c>
@@ -10421,7 +10431,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>677</v>
       </c>
@@ -10468,7 +10478,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>678</v>
       </c>
@@ -10515,7 +10525,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>679</v>
       </c>
@@ -10562,7 +10572,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>680</v>
       </c>
@@ -10609,7 +10619,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>681</v>
       </c>
@@ -10656,7 +10666,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>682</v>
       </c>
@@ -10703,7 +10713,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>683</v>
       </c>
@@ -10750,7 +10760,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>684</v>
       </c>
@@ -10797,7 +10807,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>685</v>
       </c>
@@ -10844,7 +10854,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>686</v>
       </c>
@@ -10891,7 +10901,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>687</v>
       </c>
@@ -10938,7 +10948,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>688</v>
       </c>
@@ -10985,7 +10995,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>689</v>
       </c>
@@ -11032,7 +11042,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>690</v>
       </c>
@@ -11079,7 +11089,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>691</v>
       </c>
@@ -11126,7 +11136,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>692</v>
       </c>
@@ -11173,7 +11183,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>693</v>
       </c>
@@ -11220,7 +11230,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>694</v>
       </c>
@@ -11267,7 +11277,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>695</v>
       </c>
@@ -11314,7 +11324,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>696</v>
       </c>
@@ -11361,7 +11371,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>697</v>
       </c>
@@ -11408,7 +11418,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>698</v>
       </c>
@@ -11455,7 +11465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>699</v>
       </c>
@@ -11502,7 +11512,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>700</v>
       </c>
@@ -11549,7 +11559,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>701</v>
       </c>
@@ -11596,7 +11606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>702</v>
       </c>
@@ -11643,7 +11653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>703</v>
       </c>
@@ -11690,7 +11700,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>704</v>
       </c>
@@ -11737,7 +11747,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>705</v>
       </c>
@@ -11784,7 +11794,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>706</v>
       </c>
@@ -11831,7 +11841,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>707</v>
       </c>
@@ -11878,7 +11888,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>708</v>
       </c>
@@ -11925,7 +11935,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>709</v>
       </c>
@@ -11972,7 +11982,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>710</v>
       </c>
@@ -12019,7 +12029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>711</v>
       </c>
@@ -12066,7 +12076,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>712</v>
       </c>
@@ -12113,7 +12123,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>713</v>
       </c>
@@ -12160,7 +12170,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>714</v>
       </c>
@@ -12207,7 +12217,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>715</v>
       </c>
@@ -12254,7 +12264,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>716</v>
       </c>
@@ -12301,7 +12311,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>717</v>
       </c>
@@ -12348,7 +12358,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>718</v>
       </c>
@@ -12395,7 +12405,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>719</v>
       </c>
@@ -12442,7 +12452,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>720</v>
       </c>
@@ -12489,7 +12499,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>721</v>
       </c>
@@ -12536,7 +12546,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>722</v>
       </c>
@@ -12583,7 +12593,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>723</v>
       </c>
@@ -12630,7 +12640,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>724</v>
       </c>
@@ -12677,7 +12687,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>725</v>
       </c>
@@ -12724,7 +12734,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>726</v>
       </c>
@@ -12771,7 +12781,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>727</v>
       </c>
@@ -12818,7 +12828,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>728</v>
       </c>
@@ -12865,7 +12875,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>729</v>
       </c>
@@ -12912,7 +12922,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>730</v>
       </c>
@@ -12959,7 +12969,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>731</v>
       </c>
@@ -13006,7 +13016,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>732</v>
       </c>
@@ -13053,7 +13063,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>733</v>
       </c>
@@ -13100,7 +13110,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>734</v>
       </c>
@@ -13147,7 +13157,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>735</v>
       </c>
@@ -13194,7 +13204,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>736</v>
       </c>
@@ -13241,7 +13251,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>737</v>
       </c>
@@ -13288,7 +13298,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>738</v>
       </c>
@@ -13335,7 +13345,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>739</v>
       </c>
@@ -13382,7 +13392,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>740</v>
       </c>
@@ -13429,7 +13439,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>741</v>
       </c>
@@ -13476,7 +13486,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>742</v>
       </c>
@@ -13523,7 +13533,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>743</v>
       </c>
@@ -13570,7 +13580,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>744</v>
       </c>
@@ -13617,7 +13627,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>745</v>
       </c>
@@ -13664,7 +13674,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>746</v>
       </c>
@@ -13711,7 +13721,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>747</v>
       </c>
@@ -13758,7 +13768,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>748</v>
       </c>
@@ -13805,7 +13815,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>749</v>
       </c>
@@ -13852,7 +13862,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>750</v>
       </c>
@@ -13899,7 +13909,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>751</v>
       </c>
@@ -13946,7 +13956,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>752</v>
       </c>
@@ -13993,7 +14003,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>753</v>
       </c>
@@ -14040,7 +14050,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>754</v>
       </c>
@@ -14087,7 +14097,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>755</v>
       </c>
@@ -14134,7 +14144,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>756</v>
       </c>
@@ -14181,7 +14191,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>757</v>
       </c>
@@ -14228,7 +14238,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>758</v>
       </c>
@@ -14275,7 +14285,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>759</v>
       </c>
@@ -14322,7 +14332,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>760</v>
       </c>
@@ -14369,7 +14379,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>761</v>
       </c>
@@ -14416,7 +14426,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>762</v>
       </c>
@@ -14463,7 +14473,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>763</v>
       </c>
@@ -14510,7 +14520,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>764</v>
       </c>
@@ -14560,7 +14570,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>765</v>
       </c>
@@ -14610,7 +14620,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>766</v>
       </c>
@@ -14660,7 +14670,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>767</v>
       </c>
@@ -14710,7 +14720,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>768</v>
       </c>
@@ -14760,7 +14770,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>769</v>
       </c>
@@ -14810,7 +14820,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>770</v>
       </c>
@@ -14860,7 +14870,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>771</v>
       </c>
@@ -14910,7 +14920,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>772</v>
       </c>
@@ -14960,7 +14970,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>773</v>
       </c>
@@ -15010,7 +15020,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>774</v>
       </c>
@@ -15060,7 +15070,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>775</v>
       </c>
@@ -15110,7 +15120,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>776</v>
       </c>
@@ -15160,7 +15170,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>777</v>
       </c>
@@ -15210,7 +15220,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>778</v>
       </c>
@@ -15260,7 +15270,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>779</v>
       </c>
@@ -15310,7 +15320,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>780</v>
       </c>
@@ -15360,7 +15370,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>781</v>
       </c>
@@ -15410,7 +15420,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>782</v>
       </c>
@@ -15460,7 +15470,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>783</v>
       </c>
@@ -15510,7 +15520,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>784</v>
       </c>
@@ -15560,7 +15570,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>785</v>
       </c>
@@ -15610,7 +15620,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>786</v>
       </c>
@@ -15660,7 +15670,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>787</v>
       </c>
@@ -15710,7 +15720,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>788</v>
       </c>
@@ -15760,7 +15770,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>789</v>
       </c>
@@ -15810,7 +15820,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>790</v>
       </c>
@@ -15860,7 +15870,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>791</v>
       </c>
@@ -15910,7 +15920,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>792</v>
       </c>
@@ -15960,7 +15970,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>793</v>
       </c>
@@ -16010,7 +16020,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>794</v>
       </c>
@@ -16060,7 +16070,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>795</v>
       </c>
@@ -16110,7 +16120,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>796</v>
       </c>
@@ -16160,7 +16170,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>797</v>
       </c>
@@ -16210,7 +16220,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>798</v>
       </c>
@@ -16260,7 +16270,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>799</v>
       </c>
@@ -16310,7 +16320,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>800</v>
       </c>
@@ -16360,7 +16370,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>801</v>
       </c>
@@ -16410,7 +16420,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>802</v>
       </c>
@@ -16460,7 +16470,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>803</v>
       </c>
@@ -16510,7 +16520,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>804</v>
       </c>
@@ -16560,7 +16570,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>805</v>
       </c>
@@ -16610,7 +16620,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>806</v>
       </c>
@@ -16660,7 +16670,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>807</v>
       </c>
@@ -16710,7 +16720,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>808</v>
       </c>
@@ -16760,7 +16770,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>809</v>
       </c>
@@ -16810,7 +16820,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>810</v>
       </c>
@@ -16860,7 +16870,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>811</v>
       </c>
@@ -16910,7 +16920,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>812</v>
       </c>
@@ -16960,7 +16970,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>813</v>
       </c>
@@ -17010,7 +17020,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>814</v>
       </c>
@@ -17060,7 +17070,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>815</v>
       </c>
@@ -17110,7 +17120,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>816</v>
       </c>
@@ -17160,7 +17170,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>817</v>
       </c>
@@ -17210,7 +17220,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>836</v>
       </c>
@@ -17260,7 +17270,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>837</v>
       </c>
@@ -17310,7 +17320,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>838</v>
       </c>
@@ -17360,7 +17370,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>839</v>
       </c>
@@ -17407,7 +17417,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>840</v>
       </c>
@@ -17454,7 +17464,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>841</v>
       </c>
@@ -17501,7 +17511,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>842</v>
       </c>
@@ -17548,7 +17558,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>843</v>
       </c>
@@ -17595,7 +17605,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>844</v>
       </c>
@@ -17642,7 +17652,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>845</v>
       </c>
@@ -17689,7 +17699,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>846</v>
       </c>
@@ -17736,7 +17746,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>847</v>
       </c>
@@ -17783,7 +17793,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>848</v>
       </c>
@@ -17830,7 +17840,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>849</v>
       </c>
@@ -17877,7 +17887,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>850</v>
       </c>
@@ -17924,7 +17934,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>851</v>
       </c>
@@ -17971,7 +17981,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>852</v>
       </c>
@@ -18018,7 +18028,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>880</v>
       </c>
@@ -18065,7 +18075,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>881</v>
       </c>
@@ -18112,7 +18122,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>882</v>
       </c>
@@ -18159,7 +18169,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>883</v>
       </c>
@@ -18206,7 +18216,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>884</v>
       </c>
@@ -18253,7 +18263,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>885</v>
       </c>
@@ -18300,7 +18310,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>886</v>
       </c>
@@ -18347,7 +18357,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>887</v>
       </c>
@@ -18394,7 +18404,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>888</v>
       </c>
@@ -18441,7 +18451,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>889</v>
       </c>
@@ -18488,7 +18498,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>890</v>
       </c>
@@ -18535,7 +18545,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>891</v>
       </c>
@@ -18582,7 +18592,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>892</v>
       </c>
@@ -18629,7 +18639,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>893</v>
       </c>
@@ -18676,7 +18686,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>894</v>
       </c>
@@ -18723,7 +18733,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>895</v>
       </c>
@@ -18773,7 +18783,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>896</v>
       </c>
@@ -18823,7 +18833,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>897</v>
       </c>
@@ -18873,7 +18883,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>898</v>
       </c>
@@ -18923,7 +18933,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>899</v>
       </c>
@@ -18973,7 +18983,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>900</v>
       </c>
@@ -19023,7 +19033,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>901</v>
       </c>
@@ -19073,7 +19083,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>902</v>
       </c>
@@ -19123,7 +19133,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>903</v>
       </c>
@@ -19170,7 +19180,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>904</v>
       </c>
@@ -19220,7 +19230,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>905</v>
       </c>
@@ -19270,7 +19280,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>906</v>
       </c>
@@ -19320,7 +19330,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>907</v>
       </c>
@@ -19370,7 +19380,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>908</v>
       </c>
@@ -19420,7 +19430,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>909</v>
       </c>
@@ -19470,7 +19480,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>910</v>
       </c>
@@ -19520,7 +19530,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>911</v>
       </c>
@@ -19570,7 +19580,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>912</v>
       </c>
@@ -19620,7 +19630,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>913</v>
       </c>
@@ -19690,13 +19700,13 @@
         <v>575</v>
       </c>
       <c r="G274" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H274" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>242</v>
@@ -19720,7 +19730,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>915</v>
       </c>
@@ -19770,7 +19780,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>916</v>
       </c>
@@ -19820,7 +19830,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>917</v>
       </c>
@@ -19870,7 +19880,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>918</v>
       </c>
@@ -19920,7 +19930,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>919</v>
       </c>
@@ -19970,7 +19980,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>920</v>
       </c>
@@ -20020,7 +20030,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>921</v>
       </c>
@@ -20070,7 +20080,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>922</v>
       </c>
@@ -20120,7 +20130,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>923</v>
       </c>
@@ -20170,7 +20180,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>924</v>
       </c>
@@ -20220,7 +20230,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>925</v>
       </c>
@@ -20270,7 +20280,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>926</v>
       </c>
@@ -20320,7 +20330,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>927</v>
       </c>
@@ -20370,7 +20380,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>928</v>
       </c>
@@ -20420,7 +20430,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>929</v>
       </c>
@@ -20470,7 +20480,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>930</v>
       </c>
@@ -20520,7 +20530,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>931</v>
       </c>
@@ -20570,7 +20580,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>932</v>
       </c>
@@ -20620,7 +20630,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>959</v>
       </c>
@@ -20670,7 +20680,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>960</v>
       </c>
@@ -20720,7 +20730,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>961</v>
       </c>
@@ -20770,7 +20780,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>962</v>
       </c>
@@ -20820,7 +20830,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>963</v>
       </c>
@@ -20870,7 +20880,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>964</v>
       </c>
@@ -20917,7 +20927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>965</v>
       </c>
@@ -20964,7 +20974,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>966</v>
       </c>
@@ -21011,7 +21021,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>967</v>
       </c>
@@ -21058,7 +21068,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>968</v>
       </c>
@@ -21105,7 +21115,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>969</v>
       </c>
@@ -21152,7 +21162,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>1003</v>
       </c>
@@ -21199,7 +21209,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>1004</v>
       </c>
@@ -21246,7 +21256,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>1005</v>
       </c>
@@ -21293,7 +21303,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>1006</v>
       </c>
@@ -21340,7 +21350,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>1007</v>
       </c>
@@ -21390,7 +21400,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>1008</v>
       </c>
@@ -21460,13 +21470,13 @@
         <v>532</v>
       </c>
       <c r="G310" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H310" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I310" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J310" s="1" t="s">
         <v>242</v>
@@ -21490,7 +21500,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>1010</v>
       </c>
@@ -21540,7 +21550,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>1011</v>
       </c>
@@ -21590,7 +21600,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1012</v>
       </c>
@@ -21640,7 +21650,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1013</v>
       </c>
@@ -21710,13 +21720,13 @@
         <v>532</v>
       </c>
       <c r="G315" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H315" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I315" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J315" s="1" t="s">
         <v>14</v>
@@ -21740,7 +21750,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>1015</v>
       </c>
@@ -21790,7 +21800,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1016</v>
       </c>
@@ -21840,7 +21850,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>1017</v>
       </c>
@@ -21890,7 +21900,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>1018</v>
       </c>
@@ -21940,7 +21950,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>1019</v>
       </c>
@@ -21990,7 +22000,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>1020</v>
       </c>
@@ -22040,7 +22050,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>1021</v>
       </c>
@@ -22090,7 +22100,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>1022</v>
       </c>
@@ -22140,7 +22150,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>1023</v>
       </c>
@@ -22190,7 +22200,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>1024</v>
       </c>
@@ -22240,7 +22250,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1025</v>
       </c>
@@ -22290,7 +22300,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>1026</v>
       </c>
@@ -22340,7 +22350,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>1027</v>
       </c>
@@ -22390,7 +22400,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>1028</v>
       </c>
@@ -22440,7 +22450,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>1029</v>
       </c>
@@ -22510,13 +22520,13 @@
         <v>533</v>
       </c>
       <c r="G331" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H331" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I331" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J331" s="1" t="s">
         <v>242</v>
@@ -22540,7 +22550,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>1031</v>
       </c>
@@ -22590,7 +22600,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>1032</v>
       </c>
@@ -22640,7 +22650,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>1033</v>
       </c>
@@ -22690,7 +22700,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>1034</v>
       </c>
@@ -22740,7 +22750,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>1035</v>
       </c>
@@ -22790,7 +22800,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>1036</v>
       </c>
@@ -22840,7 +22850,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>1037</v>
       </c>
@@ -22890,7 +22900,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>1038</v>
       </c>
@@ -22940,7 +22950,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>1039</v>
       </c>
@@ -22990,7 +23000,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>1040</v>
       </c>
@@ -23040,7 +23050,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>1041</v>
       </c>
@@ -23090,7 +23100,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1042</v>
       </c>
@@ -23140,7 +23150,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1043</v>
       </c>
@@ -23190,7 +23200,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>1044</v>
       </c>
@@ -23240,7 +23250,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>1045</v>
       </c>
@@ -23290,7 +23300,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1046</v>
       </c>
@@ -23340,7 +23350,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>1047</v>
       </c>
@@ -23390,7 +23400,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>1048</v>
       </c>
@@ -23440,7 +23450,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>1049</v>
       </c>
@@ -23490,7 +23500,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>1050</v>
       </c>
@@ -23540,7 +23550,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>1051</v>
       </c>
@@ -23590,7 +23600,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>1052</v>
       </c>
@@ -23640,7 +23650,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>1053</v>
       </c>
@@ -23690,7 +23700,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>1054</v>
       </c>
@@ -23740,7 +23750,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>1055</v>
       </c>
@@ -23790,7 +23800,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>1056</v>
       </c>
@@ -23840,7 +23850,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>1057</v>
       </c>
@@ -23890,7 +23900,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>1058</v>
       </c>
@@ -23940,7 +23950,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>1059</v>
       </c>
@@ -23990,7 +24000,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>1060</v>
       </c>
@@ -24040,7 +24050,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1061</v>
       </c>
@@ -24090,7 +24100,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1062</v>
       </c>
@@ -24140,7 +24150,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>1063</v>
       </c>
@@ -24190,7 +24200,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>1064</v>
       </c>
@@ -24240,7 +24250,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1065</v>
       </c>
@@ -24290,7 +24300,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1066</v>
       </c>
@@ -24340,7 +24350,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>1067</v>
       </c>
@@ -24390,7 +24400,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1068</v>
       </c>
@@ -24440,7 +24450,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1069</v>
       </c>
@@ -24490,7 +24500,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>1070</v>
       </c>
@@ -24540,7 +24550,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1071</v>
       </c>
@@ -24590,7 +24600,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1072</v>
       </c>
@@ -24640,7 +24650,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1073</v>
       </c>
@@ -24690,7 +24700,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>1074</v>
       </c>
@@ -24740,7 +24750,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>1075</v>
       </c>
@@ -24790,7 +24800,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1076</v>
       </c>
@@ -24840,7 +24850,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>1077</v>
       </c>
@@ -24890,7 +24900,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>1078</v>
       </c>
@@ -24940,7 +24950,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1079</v>
       </c>
@@ -24990,7 +25000,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1080</v>
       </c>
@@ -25040,7 +25050,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1081</v>
       </c>
@@ -25090,7 +25100,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1082</v>
       </c>
@@ -25140,7 +25150,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1083</v>
       </c>
@@ -25190,7 +25200,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>1084</v>
       </c>
@@ -25240,7 +25250,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1085</v>
       </c>
@@ -25290,7 +25300,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1115</v>
       </c>
@@ -25340,7 +25350,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1129</v>
       </c>
@@ -25390,7 +25400,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1130</v>
       </c>
@@ -25440,7 +25450,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1131</v>
       </c>
@@ -25490,7 +25500,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1132</v>
       </c>
@@ -25540,7 +25550,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1116</v>
       </c>
@@ -25590,7 +25600,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1117</v>
       </c>
@@ -25640,7 +25650,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1118</v>
       </c>
@@ -25690,7 +25700,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1119</v>
       </c>
@@ -25740,7 +25750,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1120</v>
       </c>
@@ -25790,7 +25800,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1121</v>
       </c>
@@ -25860,13 +25870,13 @@
         <v>533</v>
       </c>
       <c r="G398" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H398" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I398" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J398" s="1" t="s">
         <v>14</v>
@@ -25910,13 +25920,13 @@
         <v>533</v>
       </c>
       <c r="G399" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H399" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I399" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J399" s="1" t="s">
         <v>14</v>
@@ -25940,7 +25950,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1125</v>
       </c>
@@ -25990,7 +26000,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1133</v>
       </c>
@@ -26040,7 +26050,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1134</v>
       </c>
@@ -26090,7 +26100,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1135</v>
       </c>
@@ -26140,7 +26150,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1136</v>
       </c>
@@ -26190,7 +26200,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1137</v>
       </c>
@@ -26240,7 +26250,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1138</v>
       </c>
@@ -26290,7 +26300,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1139</v>
       </c>
@@ -26340,7 +26350,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1140</v>
       </c>
@@ -26390,7 +26400,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>1141</v>
       </c>
@@ -26440,7 +26450,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1142</v>
       </c>
@@ -26490,7 +26500,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1143</v>
       </c>
@@ -26540,7 +26550,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1144</v>
       </c>
@@ -26590,7 +26600,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1145</v>
       </c>
@@ -26640,7 +26650,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1146</v>
       </c>
@@ -26690,7 +26700,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1147</v>
       </c>
@@ -26740,7 +26750,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1148</v>
       </c>
@@ -26790,7 +26800,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1149</v>
       </c>
@@ -26840,7 +26850,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1150</v>
       </c>
@@ -26890,7 +26900,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1151</v>
       </c>
@@ -26940,7 +26950,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1152</v>
       </c>
@@ -26990,7 +27000,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1153</v>
       </c>
@@ -27040,7 +27050,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1154</v>
       </c>
@@ -27090,7 +27100,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1155</v>
       </c>
@@ -27140,7 +27150,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1156</v>
       </c>
@@ -27190,7 +27200,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1157</v>
       </c>
@@ -27240,7 +27250,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>1158</v>
       </c>
@@ -27290,7 +27300,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1159</v>
       </c>
@@ -27340,7 +27350,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1160</v>
       </c>
@@ -27390,7 +27400,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1161</v>
       </c>
@@ -27440,7 +27450,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1162</v>
       </c>
@@ -27510,13 +27520,13 @@
         <v>547</v>
       </c>
       <c r="G431" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H431" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I431" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J431" s="1" t="s">
         <v>242</v>
@@ -27540,7 +27550,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>1164</v>
       </c>
@@ -27590,7 +27600,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>1165</v>
       </c>
@@ -27640,7 +27650,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>1166</v>
       </c>
@@ -27690,7 +27700,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>1167</v>
       </c>
@@ -27740,7 +27750,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>1168</v>
       </c>
@@ -27790,7 +27800,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>1169</v>
       </c>
@@ -27840,7 +27850,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="438" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>1170</v>
       </c>
@@ -27890,7 +27900,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>1171</v>
       </c>
@@ -27940,7 +27950,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="440" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>1172</v>
       </c>
@@ -27990,7 +28000,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>1173</v>
       </c>
@@ -28040,7 +28050,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>1174</v>
       </c>
@@ -28090,7 +28100,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>1175</v>
       </c>
@@ -28140,7 +28150,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>1176</v>
       </c>
@@ -28190,7 +28200,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>1177</v>
       </c>
@@ -28240,7 +28250,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="446" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>1178</v>
       </c>
@@ -28290,7 +28300,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="447" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>1179</v>
       </c>
@@ -28337,7 +28347,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="448" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>1180</v>
       </c>
@@ -28384,7 +28394,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>1181</v>
       </c>
@@ -28431,7 +28441,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>1182</v>
       </c>
@@ -28478,7 +28488,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>1183</v>
       </c>
@@ -28525,7 +28535,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>1184</v>
       </c>
@@ -28572,7 +28582,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>1185</v>
       </c>
@@ -28619,7 +28629,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>1186</v>
       </c>
@@ -28666,7 +28676,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>1187</v>
       </c>
@@ -28713,7 +28723,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>1188</v>
       </c>
@@ -28760,7 +28770,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>1189</v>
       </c>
@@ -28807,7 +28817,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>1190</v>
       </c>
@@ -28854,7 +28864,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>1191</v>
       </c>
@@ -28901,7 +28911,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>1192</v>
       </c>
@@ -28948,7 +28958,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>1193</v>
       </c>
@@ -28995,7 +29005,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>1194</v>
       </c>
@@ -29042,7 +29052,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>1195</v>
       </c>
@@ -29089,7 +29099,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>1196</v>
       </c>
@@ -29136,7 +29146,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>1197</v>
       </c>
@@ -29183,7 +29193,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>1198</v>
       </c>
@@ -29230,7 +29240,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>1199</v>
       </c>
@@ -29277,7 +29287,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>1200</v>
       </c>
@@ -29324,7 +29334,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>1201</v>
       </c>
@@ -29371,7 +29381,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>1202</v>
       </c>
@@ -29418,7 +29428,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>1203</v>
       </c>
@@ -29465,7 +29475,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>1204</v>
       </c>
@@ -29512,7 +29522,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>1205</v>
       </c>
@@ -29559,7 +29569,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>1206</v>
       </c>
@@ -29606,7 +29616,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>1207</v>
       </c>
@@ -29653,7 +29663,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>1208</v>
       </c>
@@ -29700,7 +29710,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>1209</v>
       </c>
@@ -29747,7 +29757,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>1210</v>
       </c>
@@ -29794,7 +29804,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>1211</v>
       </c>
@@ -29841,7 +29851,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>1212</v>
       </c>
@@ -29888,7 +29898,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>1213</v>
       </c>
@@ -29935,7 +29945,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>1214</v>
       </c>
@@ -29982,7 +29992,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>1215</v>
       </c>
@@ -30029,7 +30039,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>1216</v>
       </c>
@@ -30076,7 +30086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>1217</v>
       </c>
@@ -30123,7 +30133,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>1218</v>
       </c>
@@ -30170,7 +30180,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>1219</v>
       </c>
@@ -30217,7 +30227,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>1220</v>
       </c>
@@ -30264,7 +30274,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>1221</v>
       </c>
@@ -30311,7 +30321,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>1222</v>
       </c>
@@ -30358,7 +30368,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>1223</v>
       </c>
@@ -30405,7 +30415,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>1224</v>
       </c>
@@ -30452,7 +30462,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>1225</v>
       </c>
@@ -30499,7 +30509,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>1226</v>
       </c>
@@ -30546,7 +30556,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>1227</v>
       </c>
@@ -30593,7 +30603,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>1228</v>
       </c>
@@ -30640,7 +30650,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>1229</v>
       </c>
@@ -30687,7 +30697,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>1230</v>
       </c>
@@ -30734,7 +30744,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>1231</v>
       </c>
@@ -30781,7 +30791,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>1232</v>
       </c>
@@ -30828,7 +30838,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>1233</v>
       </c>
@@ -30875,7 +30885,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>1234</v>
       </c>
@@ -30922,7 +30932,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>1235</v>
       </c>
@@ -30969,7 +30979,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>1236</v>
       </c>
@@ -31016,7 +31026,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>1237</v>
       </c>
@@ -31063,7 +31073,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>1238</v>
       </c>
@@ -31110,7 +31120,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>1239</v>
       </c>
@@ -31157,7 +31167,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>1240</v>
       </c>
@@ -31204,7 +31214,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>1241</v>
       </c>
@@ -31251,7 +31261,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>1242</v>
       </c>
@@ -31298,7 +31308,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>1243</v>
       </c>
@@ -31345,7 +31355,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>1244</v>
       </c>
@@ -31392,7 +31402,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>1245</v>
       </c>
@@ -31439,7 +31449,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>1246</v>
       </c>
@@ -31486,7 +31496,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>1247</v>
       </c>
@@ -31533,7 +31543,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>1248</v>
       </c>
@@ -31580,7 +31590,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>1249</v>
       </c>
@@ -31627,7 +31637,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>1250</v>
       </c>
@@ -31674,7 +31684,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>1251</v>
       </c>
@@ -31721,7 +31731,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>1252</v>
       </c>
@@ -31768,7 +31778,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>1253</v>
       </c>
@@ -31815,7 +31825,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>1254</v>
       </c>
@@ -31862,7 +31872,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>1255</v>
       </c>
@@ -31909,7 +31919,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>1256</v>
       </c>
@@ -31956,7 +31966,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>1257</v>
       </c>
@@ -32003,7 +32013,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>1258</v>
       </c>
@@ -32050,7 +32060,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>1259</v>
       </c>
@@ -32097,7 +32107,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>1260</v>
       </c>
@@ -32144,7 +32154,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="529" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>1261</v>
       </c>
@@ -32191,7 +32201,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="530" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>1262</v>
       </c>
@@ -32238,7 +32248,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="531" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>1263</v>
       </c>
@@ -32282,7 +32292,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="532" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>1264</v>
       </c>
@@ -32326,7 +32336,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="533" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>1265</v>
       </c>
@@ -32373,7 +32383,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="534" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>1266</v>
       </c>
@@ -32420,7 +32430,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="535" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>1267</v>
       </c>
@@ -32467,7 +32477,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="536" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>1268</v>
       </c>
@@ -32514,7 +32524,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="537" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>1269</v>
       </c>
@@ -32561,7 +32571,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="538" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>1270</v>
       </c>
@@ -32608,7 +32618,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="539" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>1271</v>
       </c>
@@ -32652,7 +32662,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="540" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>1272</v>
       </c>
@@ -32696,7 +32706,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="541" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>1273</v>
       </c>
@@ -32743,7 +32753,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="542" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>1274</v>
       </c>
@@ -32790,7 +32800,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="543" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>1275</v>
       </c>
@@ -32837,7 +32847,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="544" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>1276</v>
       </c>
@@ -32884,7 +32894,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>1277</v>
       </c>
@@ -32931,7 +32941,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>1278</v>
       </c>
@@ -32978,7 +32988,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>1279</v>
       </c>
@@ -33025,7 +33035,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>1280</v>
       </c>
@@ -33072,7 +33082,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>1281</v>
       </c>
@@ -33119,7 +33129,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="550" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>1282</v>
       </c>
@@ -33166,7 +33176,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="551" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>1283</v>
       </c>
@@ -33213,7 +33223,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="552" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>1284</v>
       </c>
@@ -33260,7 +33270,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="553" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>1285</v>
       </c>
@@ -33307,7 +33317,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="554" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>1286</v>
       </c>
@@ -33354,7 +33364,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>1287</v>
       </c>
@@ -33401,7 +33411,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>1288</v>
       </c>
@@ -33451,7 +33461,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="557" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>1289</v>
       </c>
@@ -33501,7 +33511,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>1290</v>
       </c>
@@ -33551,7 +33561,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="559" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>1291</v>
       </c>
@@ -33601,7 +33611,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="560" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>1292</v>
       </c>
@@ -33651,7 +33661,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>1293</v>
       </c>
@@ -33701,7 +33711,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>1294</v>
       </c>
@@ -33751,7 +33761,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>1295</v>
       </c>
@@ -33801,7 +33811,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>1296</v>
       </c>
@@ -33851,7 +33861,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>1297</v>
       </c>
@@ -33901,7 +33911,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>1298</v>
       </c>
@@ -33951,7 +33961,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>1299</v>
       </c>
@@ -34001,7 +34011,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>1300</v>
       </c>
@@ -34051,7 +34061,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>1301</v>
       </c>
@@ -34101,7 +34111,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>1302</v>
       </c>
@@ -34151,7 +34161,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>1303</v>
       </c>
@@ -34201,7 +34211,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>1304</v>
       </c>
@@ -34251,7 +34261,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>1305</v>
       </c>
@@ -34301,7 +34311,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>1306</v>
       </c>
@@ -34351,7 +34361,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>1307</v>
       </c>
@@ -34401,7 +34411,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>1308</v>
       </c>
@@ -34451,7 +34461,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>1309</v>
       </c>
@@ -34501,7 +34511,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>1310</v>
       </c>
@@ -34551,7 +34561,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>1311</v>
       </c>
@@ -34601,7 +34611,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>1312</v>
       </c>
@@ -34651,7 +34661,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="581" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>1313</v>
       </c>
@@ -34701,7 +34711,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>1314</v>
       </c>
@@ -34751,7 +34761,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="583" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>1315</v>
       </c>
@@ -34801,7 +34811,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>1316</v>
       </c>
@@ -34851,7 +34861,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>1317</v>
       </c>
@@ -34901,7 +34911,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>1318</v>
       </c>
@@ -34951,7 +34961,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>1319</v>
       </c>
@@ -35001,7 +35011,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>1320</v>
       </c>
@@ -35051,7 +35061,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>1321</v>
       </c>
@@ -35101,7 +35111,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>1322</v>
       </c>
@@ -35151,7 +35161,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="591" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>1323</v>
       </c>
@@ -35201,7 +35211,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>1324</v>
       </c>
@@ -35251,7 +35261,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>1325</v>
       </c>
@@ -35301,7 +35311,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="594" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>1326</v>
       </c>
@@ -35351,7 +35361,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="595" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>1327</v>
       </c>
@@ -35401,7 +35411,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="596" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>1328</v>
       </c>
@@ -35451,7 +35461,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="597" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>1329</v>
       </c>
@@ -35501,7 +35511,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="598" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>1330</v>
       </c>
@@ -35551,7 +35561,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="599" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>1331</v>
       </c>
@@ -35601,7 +35611,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="600" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>1332</v>
       </c>
@@ -35651,7 +35661,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="601" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>1333</v>
       </c>
@@ -35701,7 +35711,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="602" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>1334</v>
       </c>
@@ -35751,7 +35761,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="603" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>1335</v>
       </c>
@@ -35801,7 +35811,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="604" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>1336</v>
       </c>
@@ -35851,7 +35861,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="605" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>1337</v>
       </c>
@@ -35901,7 +35911,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="606" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>1338</v>
       </c>
@@ -35951,7 +35961,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="607" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>1339</v>
       </c>
@@ -36021,13 +36031,13 @@
         <v>824</v>
       </c>
       <c r="G608" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H608" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I608" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="J608" s="1" t="s">
         <v>242</v>
@@ -36051,7 +36061,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="609" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>1341</v>
       </c>
@@ -36101,7 +36111,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="610" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>1342</v>
       </c>
@@ -36151,7 +36161,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="611" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>1343</v>
       </c>
@@ -36201,7 +36211,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="612" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>1344</v>
       </c>
@@ -36251,7 +36261,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="613" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>1345</v>
       </c>
@@ -36301,7 +36311,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="614" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>1346</v>
       </c>
@@ -36351,7 +36361,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="615" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>1347</v>
       </c>
@@ -36401,7 +36411,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="616" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>1348</v>
       </c>
@@ -36471,7 +36481,7 @@
         <v>594</v>
       </c>
       <c r="G617" s="1">
-        <v>40347164</v>
+        <v>10403471645</v>
       </c>
       <c r="H617" s="1" t="s">
         <v>40</v>
@@ -36501,7 +36511,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="618" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>1350</v>
       </c>
@@ -36551,7 +36561,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="619" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>1351</v>
       </c>
@@ -36601,7 +36611,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="620" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>1352</v>
       </c>
@@ -36651,7 +36661,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="621" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>1353</v>
       </c>
@@ -36701,7 +36711,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="622" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>1354</v>
       </c>
@@ -36751,7 +36761,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="623" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>1355</v>
       </c>
@@ -36801,7 +36811,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="624" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>1356</v>
       </c>
@@ -36851,7 +36861,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>1357</v>
       </c>
@@ -36898,7 +36908,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>1358</v>
       </c>
@@ -36945,7 +36955,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>1359</v>
       </c>
@@ -36992,7 +37002,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>1360</v>
       </c>
@@ -37039,7 +37049,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>1361</v>
       </c>
@@ -37086,7 +37096,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>1362</v>
       </c>
@@ -37133,7 +37143,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>1363</v>
       </c>
@@ -37180,7 +37190,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>1364</v>
       </c>
@@ -37227,7 +37237,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>1365</v>
       </c>
@@ -37274,7 +37284,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>1366</v>
       </c>
@@ -37321,7 +37331,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>1367</v>
       </c>
@@ -37368,7 +37378,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>1368</v>
       </c>
@@ -37415,7 +37425,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>1369</v>
       </c>
@@ -37462,7 +37472,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>1370</v>
       </c>
@@ -37509,7 +37519,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>1371</v>
       </c>
@@ -37556,7 +37566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>1372</v>
       </c>
@@ -37603,7 +37613,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>1373</v>
       </c>
@@ -37650,7 +37660,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>1374</v>
       </c>
@@ -37697,7 +37707,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>1375</v>
       </c>
@@ -37744,7 +37754,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>1376</v>
       </c>
@@ -37791,7 +37801,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>1377</v>
       </c>
@@ -37838,7 +37848,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>1378</v>
       </c>
@@ -37885,7 +37895,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>1379</v>
       </c>
@@ -37932,7 +37942,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>1380</v>
       </c>
@@ -37979,7 +37989,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>1381</v>
       </c>
@@ -38026,7 +38036,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>1382</v>
       </c>
@@ -38073,7 +38083,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>1383</v>
       </c>
@@ -38120,7 +38130,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>1384</v>
       </c>
@@ -38167,7 +38177,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="653" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
         <v>1385</v>
       </c>
@@ -38214,7 +38224,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="654" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
         <v>1386</v>
       </c>
@@ -38261,7 +38271,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
         <v>1387</v>
       </c>
@@ -38308,7 +38318,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
         <v>1388</v>
       </c>
@@ -38355,7 +38365,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
         <v>1389</v>
       </c>
@@ -38402,7 +38412,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
         <v>1390</v>
       </c>
@@ -38449,7 +38459,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
         <v>1391</v>
       </c>
@@ -38496,7 +38506,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
         <v>1392</v>
       </c>
@@ -38543,7 +38553,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
         <v>1393</v>
       </c>
@@ -38590,7 +38600,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
         <v>1394</v>
       </c>
@@ -38637,7 +38647,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="663" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
         <v>1395</v>
       </c>
@@ -38684,7 +38694,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="664" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
         <v>1396</v>
       </c>
@@ -38731,7 +38741,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
         <v>1397</v>
       </c>
@@ -38778,7 +38788,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="666" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
         <v>1398</v>
       </c>
@@ -38825,7 +38835,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="667" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
         <v>1399</v>
       </c>
@@ -38872,7 +38882,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="668" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
         <v>1400</v>
       </c>
@@ -38919,7 +38929,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="669" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
         <v>1401</v>
       </c>
@@ -38966,7 +38976,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="670" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
         <v>1402</v>
       </c>
@@ -39013,7 +39023,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="671" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
         <v>1403</v>
       </c>
@@ -39060,7 +39070,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="672" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
         <v>1404</v>
       </c>
@@ -39107,7 +39117,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="673" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
         <v>1405</v>
       </c>
@@ -39154,7 +39164,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="674" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
         <v>1406</v>
       </c>
@@ -39201,7 +39211,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="675" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
         <v>1407</v>
       </c>
@@ -39248,7 +39258,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="676" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
         <v>1408</v>
       </c>
@@ -39295,7 +39305,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="677" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
         <v>1409</v>
       </c>
@@ -39342,7 +39352,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="678" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
         <v>1410</v>
       </c>
@@ -39389,7 +39399,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="679" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
         <v>1411</v>
       </c>
@@ -39436,7 +39446,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="680" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
         <v>1412</v>
       </c>
@@ -39483,7 +39493,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="681" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
         <v>1413</v>
       </c>
@@ -39530,7 +39540,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="682" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
         <v>1414</v>
       </c>
@@ -39577,7 +39587,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="683" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
         <v>1415</v>
       </c>
@@ -39624,7 +39634,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
         <v>1416</v>
       </c>
@@ -39671,7 +39681,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
         <v>1417</v>
       </c>
@@ -39718,7 +39728,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
         <v>1418</v>
       </c>
@@ -39765,7 +39775,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
         <v>1419</v>
       </c>
@@ -39812,7 +39822,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="688" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
         <v>1420</v>
       </c>
@@ -39859,7 +39869,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="689" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
         <v>1421</v>
       </c>
@@ -39906,7 +39916,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="690" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
         <v>1422</v>
       </c>
@@ -39953,7 +39963,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
         <v>1423</v>
       </c>
@@ -40000,7 +40010,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
         <v>1424</v>
       </c>
@@ -40047,7 +40057,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
         <v>1425</v>
       </c>
@@ -40094,7 +40104,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
         <v>1426</v>
       </c>
@@ -40141,7 +40151,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
         <v>1427</v>
       </c>
@@ -40188,7 +40198,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="696" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
         <v>1428</v>
       </c>
@@ -40235,7 +40245,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="697" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
         <v>1429</v>
       </c>
@@ -40282,7 +40292,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
         <v>1430</v>
       </c>
@@ -40329,7 +40339,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
         <v>1431</v>
       </c>
@@ -40376,7 +40386,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
         <v>1432</v>
       </c>
@@ -40423,7 +40433,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
         <v>1433</v>
       </c>
@@ -40470,7 +40480,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
         <v>1434</v>
       </c>
@@ -40517,7 +40527,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="703" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
         <v>1435</v>
       </c>
@@ -40564,7 +40574,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="704" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
         <v>1436</v>
       </c>
@@ -40611,7 +40621,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="705" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
         <v>1437</v>
       </c>
@@ -40658,7 +40668,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="706" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
         <v>1438</v>
       </c>
@@ -40705,7 +40715,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="707" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
         <v>1439</v>
       </c>
@@ -40752,7 +40762,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="708" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
         <v>1440</v>
       </c>
@@ -40799,7 +40809,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="709" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
         <v>1441</v>
       </c>
@@ -40846,7 +40856,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="710" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
         <v>1442</v>
       </c>
@@ -40893,7 +40903,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="711" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
         <v>1443</v>
       </c>
@@ -40940,7 +40950,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="712" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
         <v>1444</v>
       </c>
@@ -40987,7 +40997,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="713" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
         <v>1445</v>
       </c>
@@ -41034,7 +41044,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="714" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
         <v>1446</v>
       </c>
@@ -41081,7 +41091,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="715" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
         <v>1447</v>
       </c>
@@ -41128,7 +41138,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="716" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
         <v>1448</v>
       </c>
@@ -41175,7 +41185,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="717" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
         <v>1449</v>
       </c>
@@ -41222,7 +41232,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="718" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
         <v>1450</v>
       </c>
@@ -41269,7 +41279,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="719" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
         <v>1452</v>
       </c>
@@ -41316,7 +41326,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="720" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
         <v>1459</v>
       </c>
@@ -41366,7 +41376,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="721" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
         <v>1460</v>
       </c>
@@ -41416,7 +41426,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="722" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
         <v>1461</v>
       </c>
@@ -41466,7 +41476,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="723" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
         <v>1462</v>
       </c>
@@ -41513,7 +41523,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="724" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
         <v>1463</v>
       </c>
@@ -41557,7 +41567,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="725" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
         <v>1469</v>
       </c>
@@ -41601,7 +41611,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="726" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
         <v>1470</v>
       </c>
@@ -41645,7 +41655,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="727" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
         <v>1471</v>
       </c>
@@ -41692,7 +41702,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="728" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
         <v>1600</v>
       </c>
@@ -41742,7 +41752,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="729" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
         <v>1601</v>
       </c>
@@ -41792,7 +41802,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="730" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
         <v>1602</v>
       </c>
@@ -41842,7 +41852,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="731" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
         <v>1603</v>
       </c>
@@ -41892,7 +41902,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="732" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
         <v>1604</v>
       </c>
@@ -41942,7 +41952,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="733" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
         <v>1605</v>
       </c>
@@ -41992,7 +42002,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="734" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
         <v>1606</v>
       </c>
@@ -42042,7 +42052,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="735" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
         <v>1607</v>
       </c>
@@ -42092,7 +42102,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="736" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
         <v>1608</v>
       </c>
@@ -42142,7 +42152,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="737" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
         <v>1609</v>
       </c>
@@ -42192,7 +42202,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="738" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
         <v>1610</v>
       </c>
@@ -42292,7 +42302,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="740" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
         <v>1612</v>
       </c>
@@ -42342,7 +42352,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="741" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
         <v>1613</v>
       </c>
@@ -42392,7 +42402,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="742" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
         <v>1614</v>
       </c>
@@ -42442,7 +42452,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="743" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
         <v>1615</v>
       </c>
@@ -42492,7 +42502,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="744" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
         <v>1616</v>
       </c>
@@ -42542,7 +42552,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="745" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
         <v>1617</v>
       </c>
@@ -42592,7 +42602,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="746" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
         <v>1618</v>
       </c>
@@ -42642,7 +42652,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="747" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
         <v>1619</v>
       </c>
@@ -42692,7 +42702,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="748" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
         <v>1620</v>
       </c>
@@ -42742,7 +42752,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="749" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
         <v>1621</v>
       </c>
@@ -42792,7 +42802,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="750" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
         <v>1622</v>
       </c>
@@ -42842,7 +42852,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="751" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
         <v>1623</v>
       </c>
@@ -42892,7 +42902,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="752" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
         <v>1624</v>
       </c>
@@ -42942,7 +42952,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="753" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
         <v>1625</v>
       </c>
@@ -42992,7 +43002,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="754" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
         <v>1626</v>
       </c>
@@ -43042,7 +43052,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="755" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
         <v>1627</v>
       </c>
@@ -43092,7 +43102,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="756" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
         <v>1628</v>
       </c>
@@ -43142,7 +43152,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="757" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
         <v>1629</v>
       </c>
@@ -43192,7 +43202,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="758" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
         <v>1630</v>
       </c>
@@ -43242,7 +43252,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="759" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
         <v>1631</v>
       </c>
@@ -43292,7 +43302,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="760" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
         <v>1632</v>
       </c>
@@ -43342,7 +43352,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="761" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
         <v>1633</v>
       </c>
@@ -43392,7 +43402,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="762" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
         <v>1634</v>
       </c>
@@ -43442,7 +43452,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="763" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
         <v>1635</v>
       </c>
@@ -43492,7 +43502,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="764" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
         <v>1636</v>
       </c>
@@ -43542,7 +43552,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="765" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
         <v>1637</v>
       </c>
@@ -43592,7 +43602,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="766" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
         <v>1638</v>
       </c>
@@ -43642,7 +43652,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="767" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
         <v>1639</v>
       </c>
@@ -43692,7 +43702,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="768" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
         <v>1640</v>
       </c>
@@ -43742,7 +43752,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="769" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:16" s="13" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" s="10" t="s">
         <v>1641</v>
       </c>
@@ -43792,7 +43802,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="770" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
         <v>1642</v>
       </c>
@@ -43842,7 +43852,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="771" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
         <v>1643</v>
       </c>
@@ -43892,7 +43902,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="772" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
         <v>1644</v>
       </c>
@@ -43942,7 +43952,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="773" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
         <v>1645</v>
       </c>
@@ -43992,7 +44002,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="774" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
         <v>1646</v>
       </c>
@@ -44042,7 +44052,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="775" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
         <v>1647</v>
       </c>
@@ -44092,7 +44102,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="776" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
         <v>1648</v>
       </c>
@@ -44142,7 +44152,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="777" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
         <v>1649</v>
       </c>
@@ -44192,7 +44202,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="778" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
         <v>1650</v>
       </c>
@@ -44242,7 +44252,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="779" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
         <v>1651</v>
       </c>
@@ -44292,7 +44302,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="780" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
         <v>1652</v>
       </c>
@@ -44342,7 +44352,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="781" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
         <v>1653</v>
       </c>
@@ -44392,7 +44402,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="782" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
         <v>1654</v>
       </c>
@@ -44442,7 +44452,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="783" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
         <v>1655</v>
       </c>
@@ -44492,7 +44502,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="784" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
         <v>1656</v>
       </c>
@@ -44542,7 +44552,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="785" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" s="1" t="s">
         <v>1657</v>
       </c>
@@ -44592,7 +44602,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="786" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" s="1" t="s">
         <v>1658</v>
       </c>
@@ -44642,7 +44652,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="787" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" s="1" t="s">
         <v>1659</v>
       </c>
@@ -44692,7 +44702,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="788" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" s="1" t="s">
         <v>1660</v>
       </c>
@@ -44742,7 +44752,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="789" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" s="1" t="s">
         <v>1661</v>
       </c>
@@ -44792,7 +44802,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="790" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" s="1" t="s">
         <v>1662</v>
       </c>
@@ -44842,7 +44852,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="791" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" s="1" t="s">
         <v>1663</v>
       </c>
@@ -44892,7 +44902,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="792" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" s="1" t="s">
         <v>1664</v>
       </c>
@@ -44942,7 +44952,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="793" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" s="1" t="s">
         <v>1665</v>
       </c>
@@ -44992,7 +45002,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="794" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" s="1" t="s">
         <v>1666</v>
       </c>
@@ -45042,7 +45052,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="795" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" s="1" t="s">
         <v>1667</v>
       </c>
@@ -45092,7 +45102,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="796" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" s="1" t="s">
         <v>1668</v>
       </c>
@@ -45142,7 +45152,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="797" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" s="1" t="s">
         <v>1669</v>
       </c>
@@ -45242,7 +45252,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="799" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" s="1" t="s">
         <v>1671</v>
       </c>
@@ -45292,7 +45302,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="800" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" s="1" t="s">
         <v>1672</v>
       </c>
@@ -45392,7 +45402,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="802" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" s="1" t="s">
         <v>1674</v>
       </c>
@@ -45442,7 +45452,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="803" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" s="1" t="s">
         <v>1675</v>
       </c>
@@ -45542,7 +45552,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="805" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" s="1" t="s">
         <v>1677</v>
       </c>
@@ -45592,7 +45602,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="806" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" s="1" t="s">
         <v>1758</v>
       </c>
@@ -45639,7 +45649,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="807" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" s="1" t="s">
         <v>1759</v>
       </c>
@@ -45686,7 +45696,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="808" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" s="1" t="s">
         <v>1760</v>
       </c>
@@ -45733,7 +45743,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="809" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" s="1" t="s">
         <v>1761</v>
       </c>
@@ -45780,7 +45790,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="810" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" s="1" t="s">
         <v>1762</v>
       </c>
@@ -45827,7 +45837,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="811" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" s="1" t="s">
         <v>1763</v>
       </c>
@@ -45874,7 +45884,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="812" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" s="1" t="s">
         <v>1764</v>
       </c>
@@ -45921,7 +45931,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="813" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" s="1" t="s">
         <v>1765</v>
       </c>
@@ -45956,7 +45966,7 @@
         <v>245</v>
       </c>
       <c r="L813" s="1" t="s">
-        <v>1745</v>
+        <v>1988</v>
       </c>
       <c r="M813" s="1" t="s">
         <v>528</v>
@@ -45968,7 +45978,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="814" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" s="1" t="s">
         <v>1766</v>
       </c>
@@ -46003,7 +46013,7 @@
         <v>245</v>
       </c>
       <c r="L814" s="1" t="s">
-        <v>1534</v>
+        <v>1987</v>
       </c>
       <c r="M814" s="1" t="s">
         <v>528</v>
@@ -46015,7 +46025,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="815" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" s="1" t="s">
         <v>1767</v>
       </c>
@@ -46062,7 +46072,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="816" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" s="1" t="s">
         <v>1768</v>
       </c>
@@ -46097,7 +46107,7 @@
         <v>245</v>
       </c>
       <c r="L816" s="1" t="s">
-        <v>1536</v>
+        <v>1989</v>
       </c>
       <c r="M816" s="1" t="s">
         <v>528</v>
@@ -46109,7 +46119,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="817" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" s="1" t="s">
         <v>1769</v>
       </c>
@@ -46156,7 +46166,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="818" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" s="1" t="s">
         <v>1770</v>
       </c>
@@ -46203,7 +46213,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="819" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" s="1" t="s">
         <v>1771</v>
       </c>
@@ -46297,7 +46307,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="821" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" s="1" t="s">
         <v>1773</v>
       </c>
@@ -46344,7 +46354,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="822" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" s="1" t="s">
         <v>1774</v>
       </c>
@@ -46391,7 +46401,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="823" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" s="1" t="s">
         <v>1775</v>
       </c>
@@ -46438,7 +46448,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="824" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" s="1" t="s">
         <v>1776</v>
       </c>
@@ -46485,7 +46495,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="825" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" s="1" t="s">
         <v>1777</v>
       </c>
@@ -46532,7 +46542,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="826" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" s="1" t="s">
         <v>1778</v>
       </c>
@@ -46579,7 +46589,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="827" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" s="1" t="s">
         <v>1779</v>
       </c>
@@ -46626,7 +46636,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="828" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" s="1" t="s">
         <v>1780</v>
       </c>
@@ -46673,7 +46683,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="829" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" s="1" t="s">
         <v>1781</v>
       </c>
@@ -46720,7 +46730,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="830" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" s="1" t="s">
         <v>1782</v>
       </c>
@@ -46767,7 +46777,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="831" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" s="1" t="s">
         <v>1783</v>
       </c>
@@ -46814,7 +46824,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="832" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" s="1" t="s">
         <v>1784</v>
       </c>
@@ -46861,7 +46871,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="833" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" s="1" t="s">
         <v>1785</v>
       </c>
@@ -46908,7 +46918,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="834" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" s="1" t="s">
         <v>1786</v>
       </c>
@@ -46955,7 +46965,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="835" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" s="1" t="s">
         <v>1787</v>
       </c>
@@ -47002,7 +47012,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="836" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" s="1" t="s">
         <v>1788</v>
       </c>
@@ -47049,7 +47059,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="837" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" s="1" t="s">
         <v>1789</v>
       </c>
@@ -47096,7 +47106,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="838" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" s="1" t="s">
         <v>1790</v>
       </c>
@@ -47143,7 +47153,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="839" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" s="1" t="s">
         <v>1791</v>
       </c>
@@ -47190,7 +47200,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="840" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" s="1" t="s">
         <v>1792</v>
       </c>
@@ -47237,7 +47247,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="841" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" s="1" t="s">
         <v>1793</v>
       </c>
@@ -47284,7 +47294,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="842" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" s="1" t="s">
         <v>1794</v>
       </c>
@@ -47331,7 +47341,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="843" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" s="1" t="s">
         <v>1795</v>
       </c>
@@ -47378,7 +47388,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="844" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" s="1" t="s">
         <v>1796</v>
       </c>
@@ -47425,7 +47435,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="845" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" s="1" t="s">
         <v>1797</v>
       </c>
@@ -47472,7 +47482,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="846" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" s="1" t="s">
         <v>1798</v>
       </c>
@@ -47519,7 +47529,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="847" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" s="1" t="s">
         <v>1799</v>
       </c>
@@ -47566,7 +47576,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="848" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" s="1" t="s">
         <v>1800</v>
       </c>
@@ -47613,7 +47623,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="849" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" s="1" t="s">
         <v>1801</v>
       </c>
@@ -47660,7 +47670,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="850" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" s="1" t="s">
         <v>1802</v>
       </c>
@@ -47707,7 +47717,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="851" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" s="1" t="s">
         <v>1803</v>
       </c>
@@ -47754,7 +47764,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="852" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" s="1" t="s">
         <v>1804</v>
       </c>
@@ -47801,7 +47811,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="853" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" s="1" t="s">
         <v>1805</v>
       </c>
@@ -47848,7 +47858,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="854" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" s="1" t="s">
         <v>1806</v>
       </c>
@@ -47895,7 +47905,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="855" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" s="1" t="s">
         <v>1807</v>
       </c>
@@ -47942,7 +47952,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="856" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" s="1" t="s">
         <v>1808</v>
       </c>
@@ -47989,7 +47999,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="857" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" s="1" t="s">
         <v>1809</v>
       </c>
@@ -48036,7 +48046,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="858" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" s="1" t="s">
         <v>1810</v>
       </c>
@@ -48083,7 +48093,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="859" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" s="1" t="s">
         <v>1811</v>
       </c>
@@ -48130,7 +48140,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="860" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" s="1" t="s">
         <v>1812</v>
       </c>
@@ -48177,7 +48187,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="861" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" s="1" t="s">
         <v>1813</v>
       </c>
@@ -48224,7 +48234,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="862" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" s="1" t="s">
         <v>1814</v>
       </c>
@@ -48271,7 +48281,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="863" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" s="1" t="s">
         <v>1815</v>
       </c>
@@ -48318,7 +48328,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="864" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" s="1" t="s">
         <v>1816</v>
       </c>
@@ -48365,7 +48375,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="865" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" s="1" t="s">
         <v>1817</v>
       </c>
@@ -48412,7 +48422,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="866" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" s="1" t="s">
         <v>1818</v>
       </c>
@@ -48459,7 +48469,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="867" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" s="1" t="s">
         <v>1819</v>
       </c>
@@ -48506,7 +48516,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="868" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" s="1" t="s">
         <v>1820</v>
       </c>
@@ -48553,7 +48563,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="869" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" s="1" t="s">
         <v>1821</v>
       </c>
@@ -48600,7 +48610,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="870" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" s="1" t="s">
         <v>1822</v>
       </c>
@@ -48647,7 +48657,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="871" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" s="1" t="s">
         <v>1823</v>
       </c>
@@ -48694,7 +48704,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="872" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" s="1" t="s">
         <v>1824</v>
       </c>
@@ -48741,7 +48751,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="873" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" s="1" t="s">
         <v>1825</v>
       </c>
@@ -48788,7 +48798,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="874" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" s="1" t="s">
         <v>1826</v>
       </c>
@@ -48835,7 +48845,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="875" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" s="1" t="s">
         <v>1827</v>
       </c>
@@ -48882,7 +48892,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="876" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" s="1" t="s">
         <v>1828</v>
       </c>
@@ -48929,7 +48939,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="877" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" s="1" t="s">
         <v>1829</v>
       </c>
@@ -48976,7 +48986,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="878" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" s="1" t="s">
         <v>1830</v>
       </c>
@@ -49023,7 +49033,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="879" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" s="1" t="s">
         <v>1831</v>
       </c>
@@ -49070,7 +49080,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="880" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" s="1" t="s">
         <v>1832</v>
       </c>
@@ -49117,7 +49127,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="881" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" s="1" t="s">
         <v>1833</v>
       </c>
@@ -49164,7 +49174,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="882" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" s="1" t="s">
         <v>1834</v>
       </c>
@@ -49211,7 +49221,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="883" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" s="1" t="s">
         <v>1835</v>
       </c>
@@ -49258,7 +49268,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="884" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" s="1" t="s">
         <v>1836</v>
       </c>
@@ -49305,7 +49315,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="885" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" s="1" t="s">
         <v>1837</v>
       </c>
@@ -49352,7 +49362,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="886" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" s="1" t="s">
         <v>1838</v>
       </c>
@@ -49399,7 +49409,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="887" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" s="1" t="s">
         <v>1839</v>
       </c>
@@ -49446,7 +49456,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="888" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" s="1" t="s">
         <v>1840</v>
       </c>
@@ -49493,7 +49503,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="889" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" s="1" t="s">
         <v>1841</v>
       </c>
@@ -49540,7 +49550,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="890" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" s="1" t="s">
         <v>1842</v>
       </c>
@@ -49587,7 +49597,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="891" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" s="1" t="s">
         <v>1843</v>
       </c>
@@ -49634,7 +49644,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="892" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" s="1" t="s">
         <v>1844</v>
       </c>
@@ -49681,7 +49691,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="893" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" s="1" t="s">
         <v>1845</v>
       </c>
@@ -49728,7 +49738,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="894" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" s="1" t="s">
         <v>1846</v>
       </c>
@@ -49775,7 +49785,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="895" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" s="1" t="s">
         <v>1847</v>
       </c>
@@ -49822,7 +49832,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="896" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" s="1" t="s">
         <v>1848</v>
       </c>
@@ -49869,7 +49879,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="897" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" s="1" t="s">
         <v>1849</v>
       </c>
@@ -49916,7 +49926,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="898" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" s="1" t="s">
         <v>1850</v>
       </c>
@@ -49963,7 +49973,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="899" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" s="1" t="s">
         <v>1851</v>
       </c>
@@ -50010,7 +50020,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="900" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" s="1" t="s">
         <v>1852</v>
       </c>
@@ -50057,7 +50067,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="901" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" s="1" t="s">
         <v>1853</v>
       </c>
@@ -50104,7 +50114,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="902" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" s="1" t="s">
         <v>1854</v>
       </c>
@@ -50151,7 +50161,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="903" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" s="1" t="s">
         <v>1855</v>
       </c>
@@ -50198,7 +50208,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="904" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" s="1" t="s">
         <v>1856</v>
       </c>
@@ -50245,7 +50255,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="905" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" s="1" t="s">
         <v>1857</v>
       </c>
@@ -50292,7 +50302,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="906" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" s="1" t="s">
         <v>1858</v>
       </c>
@@ -50339,7 +50349,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="907" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" s="1" t="s">
         <v>1859</v>
       </c>
@@ -50386,7 +50396,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="908" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" s="1" t="s">
         <v>1860</v>
       </c>
@@ -50430,7 +50440,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="909" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" s="1" t="s">
         <v>1861</v>
       </c>
@@ -50474,7 +50484,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="910" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" s="1" t="s">
         <v>1862</v>
       </c>
@@ -50518,7 +50528,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="911" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" s="1" t="s">
         <v>1863</v>
       </c>
@@ -50562,7 +50572,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="912" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" s="1" t="s">
         <v>1864</v>
       </c>
@@ -50606,7 +50616,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="913" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" s="1" t="s">
         <v>1865</v>
       </c>
@@ -50650,7 +50660,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="914" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" s="1" t="s">
         <v>1866</v>
       </c>
@@ -50694,7 +50704,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="915" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" s="1" t="s">
         <v>1867</v>
       </c>
@@ -50738,7 +50748,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="916" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" s="1" t="s">
         <v>1868</v>
       </c>
@@ -50782,7 +50792,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="917" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" s="1" t="s">
         <v>1869</v>
       </c>
@@ -50829,7 +50839,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="918" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" s="1" t="s">
         <v>1870</v>
       </c>
@@ -50876,7 +50886,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="919" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" s="1" t="s">
         <v>1871</v>
       </c>
@@ -50923,7 +50933,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="920" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" s="1" t="s">
         <v>1872</v>
       </c>
@@ -50970,7 +50980,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="921" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" s="1" t="s">
         <v>1873</v>
       </c>
@@ -51017,7 +51027,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="922" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" s="1" t="s">
         <v>1874</v>
       </c>
@@ -51064,7 +51074,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="923" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" s="1" t="s">
         <v>1875</v>
       </c>
@@ -51111,7 +51121,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="924" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" s="1" t="s">
         <v>1876</v>
       </c>
@@ -51158,7 +51168,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="925" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" s="1" t="s">
         <v>1877</v>
       </c>
@@ -51205,7 +51215,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="926" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" s="1" t="s">
         <v>1878</v>
       </c>
@@ -51249,7 +51259,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="927" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" s="1" t="s">
         <v>1879</v>
       </c>
@@ -51293,7 +51303,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="928" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" s="1" t="s">
         <v>1880</v>
       </c>
@@ -51337,7 +51347,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="929" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" s="1" t="s">
         <v>1881</v>
       </c>
@@ -51381,7 +51391,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="930" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" s="1" t="s">
         <v>1882</v>
       </c>
@@ -51425,7 +51435,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="931" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" s="1" t="s">
         <v>1883</v>
       </c>
@@ -51469,7 +51479,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="932" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" s="1" t="s">
         <v>1884</v>
       </c>
@@ -51513,7 +51523,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="933" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" s="1" t="s">
         <v>1885</v>
       </c>
@@ -51557,7 +51567,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="934" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" s="1" t="s">
         <v>1886</v>
       </c>
@@ -51601,7 +51611,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="935" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" s="1" t="s">
         <v>1887</v>
       </c>
@@ -51648,7 +51658,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="936" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" s="1" t="s">
         <v>1888</v>
       </c>
@@ -51695,7 +51705,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="937" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" s="1" t="s">
         <v>1889</v>
       </c>
@@ -51742,7 +51752,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="938" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A938" s="1" t="s">
         <v>1890</v>
       </c>
@@ -51789,7 +51799,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="939" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939" s="1" t="s">
         <v>1891</v>
       </c>
@@ -51836,7 +51846,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="940" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" s="1" t="s">
         <v>1892</v>
       </c>
@@ -51883,7 +51893,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="941" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941" s="1" t="s">
         <v>1893</v>
       </c>
@@ -51930,7 +51940,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="942" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" s="1" t="s">
         <v>1894</v>
       </c>
@@ -51977,7 +51987,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="943" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" s="1" t="s">
         <v>1895</v>
       </c>
@@ -52024,7 +52034,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="944" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" s="1" t="s">
         <v>1896</v>
       </c>
@@ -52071,7 +52081,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="945" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" s="1" t="s">
         <v>1897</v>
       </c>
@@ -52115,7 +52125,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="946" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" s="1" t="s">
         <v>1898</v>
       </c>
@@ -52162,7 +52172,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="947" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" s="1" t="s">
         <v>1899</v>
       </c>
@@ -52206,7 +52216,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="948" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" s="1" t="s">
         <v>1900</v>
       </c>
@@ -52253,7 +52263,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="949" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949" s="1" t="s">
         <v>1901</v>
       </c>
@@ -52297,7 +52307,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="950" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" s="1" t="s">
         <v>1902</v>
       </c>
@@ -52341,7 +52351,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="951" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" s="1" t="s">
         <v>1903</v>
       </c>
@@ -52385,7 +52395,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="952" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" s="1" t="s">
         <v>1904</v>
       </c>
@@ -52429,7 +52439,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="953" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" s="1" t="s">
         <v>1905</v>
       </c>
@@ -52476,7 +52486,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="954" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" s="1" t="s">
         <v>1906</v>
       </c>
@@ -52523,7 +52533,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="955" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A955" s="1" t="s">
         <v>1907</v>
       </c>
@@ -52570,7 +52580,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="956" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A956" s="1" t="s">
         <v>1908</v>
       </c>
@@ -52614,7 +52624,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="957" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" s="1" t="s">
         <v>1909</v>
       </c>
@@ -52658,7 +52668,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="958" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" s="1" t="s">
         <v>1910</v>
       </c>
@@ -52702,7 +52712,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="959" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A959" s="1" t="s">
         <v>1911</v>
       </c>
@@ -52746,7 +52756,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="960" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A960" s="1" t="s">
         <v>1912</v>
       </c>
@@ -52790,7 +52800,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="961" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961" s="1" t="s">
         <v>1913</v>
       </c>
@@ -52834,7 +52844,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="962" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" s="1" t="s">
         <v>1914</v>
       </c>
@@ -52878,7 +52888,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="963" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" s="1" t="s">
         <v>1915</v>
       </c>
@@ -52922,7 +52932,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="964" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" s="1" t="s">
         <v>1916</v>
       </c>
@@ -52966,7 +52976,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="965" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" s="1" t="s">
         <v>1917</v>
       </c>
@@ -53010,7 +53020,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="966" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" s="1" t="s">
         <v>1918</v>
       </c>
@@ -53054,7 +53064,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="967" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967" s="1" t="s">
         <v>1919</v>
       </c>
@@ -53098,7 +53108,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="968" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" s="1" t="s">
         <v>1920</v>
       </c>
@@ -53142,7 +53152,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="969" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" s="1" t="s">
         <v>1921</v>
       </c>
@@ -53186,7 +53196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="970" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" s="1" t="s">
         <v>1922</v>
       </c>
@@ -53230,7 +53240,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="971" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971" s="1" t="s">
         <v>1923</v>
       </c>
@@ -53274,7 +53284,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="972" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" s="1" t="s">
         <v>1924</v>
       </c>
@@ -53318,7 +53328,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="973" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973" s="1" t="s">
         <v>1925</v>
       </c>
@@ -53362,7 +53372,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="974" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" s="1" t="s">
         <v>1926</v>
       </c>
@@ -53406,7 +53416,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="975" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975" s="1" t="s">
         <v>1927</v>
       </c>
@@ -53450,7 +53460,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="976" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" s="1" t="s">
         <v>1928</v>
       </c>
@@ -53494,7 +53504,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="977" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977" s="1" t="s">
         <v>1929</v>
       </c>
@@ -53541,7 +53551,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="978" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" s="1" t="s">
         <v>1930</v>
       </c>
@@ -53588,7 +53598,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="979" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979" s="1" t="s">
         <v>1931</v>
       </c>
@@ -53635,7 +53645,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="980" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A980" s="1" t="s">
         <v>1932</v>
       </c>
@@ -53682,7 +53692,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="981" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981" s="1" t="s">
         <v>1933</v>
       </c>
@@ -53729,7 +53739,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="982" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A982" s="1" t="s">
         <v>1934</v>
       </c>
@@ -53776,7 +53786,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="983" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A983" s="1" t="s">
         <v>1935</v>
       </c>
@@ -53823,7 +53833,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="984" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A984" s="1" t="s">
         <v>1936</v>
       </c>
@@ -53870,7 +53880,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="985" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985" s="1" t="s">
         <v>1937</v>
       </c>
@@ -53917,7 +53927,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="986" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A986" s="1" t="s">
         <v>1938</v>
       </c>
@@ -53964,7 +53974,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="987" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A987" s="1" t="s">
         <v>1939</v>
       </c>
@@ -54011,7 +54021,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="988" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A988" s="1" t="s">
         <v>1940</v>
       </c>
@@ -54058,7 +54068,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="989" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A989" s="1" t="s">
         <v>1941</v>
       </c>
@@ -54105,7 +54115,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="990" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A990" s="1" t="s">
         <v>1942</v>
       </c>
@@ -54152,7 +54162,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="991" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991" s="1" t="s">
         <v>1943</v>
       </c>
@@ -54199,7 +54209,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="992" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A992" s="1" t="s">
         <v>1944</v>
       </c>
@@ -54246,7 +54256,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="993" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A993" s="1" t="s">
         <v>1945</v>
       </c>
@@ -54293,7 +54303,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="994" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A994" s="1" t="s">
         <v>1946</v>
       </c>
@@ -54340,7 +54350,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="995" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A995" s="1" t="s">
         <v>1947</v>
       </c>
@@ -54387,7 +54397,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="996" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A996" s="1" t="s">
         <v>1948</v>
       </c>
@@ -54434,7 +54444,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="997" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A997" s="1" t="s">
         <v>1949</v>
       </c>
@@ -54481,7 +54491,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="998" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A998" s="1" t="s">
         <v>1950</v>
       </c>
@@ -54528,7 +54538,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="999" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A999" s="1" t="s">
         <v>1951</v>
       </c>
@@ -54575,7 +54585,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1000" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="1" t="s">
         <v>1952</v>
       </c>
@@ -54622,7 +54632,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1001" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="1" t="s">
         <v>1953</v>
       </c>
@@ -54669,7 +54679,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1002" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="1" t="s">
         <v>1954</v>
       </c>
@@ -54716,7 +54726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1003" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="1" t="s">
         <v>1955</v>
       </c>
@@ -54763,7 +54773,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1004" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="1" t="s">
         <v>1956</v>
       </c>
@@ -54810,7 +54820,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1005" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="1" t="s">
         <v>1957</v>
       </c>
@@ -54857,7 +54867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1006" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="1" t="s">
         <v>1958</v>
       </c>
@@ -54904,7 +54914,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1007" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="1" t="s">
         <v>1959</v>
       </c>
@@ -54951,7 +54961,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1008" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="1" t="s">
         <v>1960</v>
       </c>
@@ -54998,7 +55008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1009" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="1" t="s">
         <v>1961</v>
       </c>
@@ -55045,7 +55055,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1010" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="1" t="s">
         <v>1962</v>
       </c>
@@ -55092,7 +55102,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1011" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="1" t="s">
         <v>1963</v>
       </c>
@@ -55139,7 +55149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1012" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="1" t="s">
         <v>1964</v>
       </c>
@@ -55186,7 +55196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1013" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="1" t="s">
         <v>1965</v>
       </c>
@@ -55233,7 +55243,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1014" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="1" t="s">
         <v>1966</v>
       </c>
@@ -55280,7 +55290,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1015" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="1" t="s">
         <v>1967</v>
       </c>
@@ -55327,7 +55337,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1016" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="1" t="s">
         <v>1968</v>
       </c>
@@ -55374,7 +55384,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1017" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="1" t="s">
         <v>1969</v>
       </c>
@@ -55421,7 +55431,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1018" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="1" t="s">
         <v>1970</v>
       </c>
@@ -55468,7 +55478,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1019" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="1" t="s">
         <v>1971</v>
       </c>
@@ -55515,7 +55525,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1020" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="1" t="s">
         <v>1972</v>
       </c>
@@ -55562,7 +55572,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1021" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="1" t="s">
         <v>1973</v>
       </c>
@@ -55609,7 +55619,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1022" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="1" t="s">
         <v>1974</v>
       </c>
@@ -55656,7 +55666,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1023" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="1" t="s">
         <v>1975</v>
       </c>
@@ -55703,7 +55713,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1024" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="1" t="s">
         <v>1976</v>
       </c>
@@ -55750,7 +55760,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1025" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="1" t="s">
         <v>1977</v>
       </c>
@@ -55797,7 +55807,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1026" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="1" t="s">
         <v>1978</v>
       </c>
@@ -55844,7 +55854,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1027" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027" s="1" t="s">
         <v>1979</v>
       </c>
@@ -55891,7 +55901,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1028" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="1" t="s">
         <v>1980</v>
       </c>
@@ -55938,7 +55948,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1029" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="1" t="s">
         <v>1981</v>
       </c>
@@ -55985,7 +55995,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1030" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="1" t="s">
         <v>1982</v>
       </c>
@@ -56032,7 +56042,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1031" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031" s="1" t="s">
         <v>1983</v>
       </c>
@@ -56079,7 +56089,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="1032" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1032" s="1" t="s">
         <v>1984</v>
       </c>
@@ -56127,7 +56137,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P805" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}"/>
+  <autoFilter ref="A1:P1032" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="OQUENDO MASIAS HILDA"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P727">
     <sortCondition ref="D709:D727"/>
   </sortState>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC77B950-3AEF-46BE-B41A-B36FA9BF661D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76DEA5F3-0BBE-4400-AD1B-3B09E1F04981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13167" uniqueCount="2166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13250" uniqueCount="2169">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -6635,6 +6635,15 @@
   </si>
   <si>
     <t>12/09/2026</t>
+  </si>
+  <si>
+    <t>WORLDVISION</t>
+  </si>
+  <si>
+    <t>FINANCIADO</t>
+  </si>
+  <si>
+    <t>FECHA_I</t>
   </si>
 </sst>
 </file>
@@ -6752,7 +6761,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6790,15 +6799,16 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -7150,7 +7160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
-  <dimension ref="A1:P1098"/>
+  <dimension ref="A1:R1098"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -7168,10 +7178,12 @@
     <col min="13" max="13" width="13.42578125" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.42578125" style="1" customWidth="1"/>
     <col min="15" max="15" width="8.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.7109375" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -7220,8 +7232,14 @@
       <c r="P1" s="4" t="s">
         <v>463</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" s="4" t="s">
+        <v>2167</v>
+      </c>
+      <c r="R1" s="6" t="s">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>596</v>
       </c>
@@ -7268,7 +7286,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>598</v>
       </c>
@@ -7315,7 +7333,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>599</v>
       </c>
@@ -7362,7 +7380,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>600</v>
       </c>
@@ -7409,7 +7427,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>601</v>
       </c>
@@ -7456,7 +7474,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>602</v>
       </c>
@@ -7503,7 +7521,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>603</v>
       </c>
@@ -7550,7 +7568,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>604</v>
       </c>
@@ -7597,7 +7615,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>605</v>
       </c>
@@ -7644,7 +7662,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>606</v>
       </c>
@@ -7691,7 +7709,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>607</v>
       </c>
@@ -7738,7 +7756,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>608</v>
       </c>
@@ -7785,7 +7803,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>609</v>
       </c>
@@ -7832,7 +7850,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>610</v>
       </c>
@@ -7879,7 +7897,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>611</v>
       </c>
@@ -7926,7 +7944,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>612</v>
       </c>
@@ -7973,7 +7991,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>613</v>
       </c>
@@ -8020,7 +8038,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>614</v>
       </c>
@@ -8067,7 +8085,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>615</v>
       </c>
@@ -8114,7 +8132,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>616</v>
       </c>
@@ -8161,7 +8179,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>617</v>
       </c>
@@ -8208,7 +8226,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>618</v>
       </c>
@@ -8255,7 +8273,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>619</v>
       </c>
@@ -8302,7 +8320,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>620</v>
       </c>
@@ -8349,7 +8367,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>621</v>
       </c>
@@ -8396,7 +8414,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>622</v>
       </c>
@@ -8442,8 +8460,9 @@
       <c r="O27" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R27" s="9"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>623</v>
       </c>
@@ -8490,7 +8509,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>624</v>
       </c>
@@ -8537,7 +8556,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>625</v>
       </c>
@@ -8584,7 +8603,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>626</v>
       </c>
@@ -8631,7 +8650,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>627</v>
       </c>
@@ -14694,7 +14713,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>756</v>
       </c>
@@ -14741,7 +14760,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>757</v>
       </c>
@@ -14788,7 +14807,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>758</v>
       </c>
@@ -14835,7 +14854,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>759</v>
       </c>
@@ -14882,7 +14901,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>760</v>
       </c>
@@ -14929,7 +14948,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>761</v>
       </c>
@@ -14976,7 +14995,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>762</v>
       </c>
@@ -15023,7 +15042,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>763</v>
       </c>
@@ -15069,8 +15088,9 @@
       <c r="O168" s="1" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R168" s="8"/>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>764</v>
       </c>
@@ -15119,8 +15139,9 @@
       <c r="P169" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R169" s="8"/>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>765</v>
       </c>
@@ -15169,8 +15190,9 @@
       <c r="P170" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R170" s="8"/>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>766</v>
       </c>
@@ -15219,8 +15241,9 @@
       <c r="P171" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R171" s="8"/>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>767</v>
       </c>
@@ -15269,8 +15292,9 @@
       <c r="P172" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R172" s="8"/>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>768</v>
       </c>
@@ -15319,8 +15343,9 @@
       <c r="P173" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R173" s="8"/>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>769</v>
       </c>
@@ -15369,8 +15394,9 @@
       <c r="P174" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R174" s="8"/>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>770</v>
       </c>
@@ -15419,8 +15445,9 @@
       <c r="P175" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R175" s="8"/>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>771</v>
       </c>
@@ -15469,8 +15496,9 @@
       <c r="P176" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R176" s="8"/>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>772</v>
       </c>
@@ -15519,8 +15547,9 @@
       <c r="P177" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R177" s="8"/>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>773</v>
       </c>
@@ -15569,8 +15598,9 @@
       <c r="P178" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R178" s="8"/>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>774</v>
       </c>
@@ -15619,8 +15649,9 @@
       <c r="P179" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R179" s="8"/>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>775</v>
       </c>
@@ -15669,8 +15700,9 @@
       <c r="P180" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R180" s="8"/>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>776</v>
       </c>
@@ -15719,8 +15751,9 @@
       <c r="P181" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R181" s="8"/>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>777</v>
       </c>
@@ -15769,8 +15802,9 @@
       <c r="P182" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R182" s="8"/>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>778</v>
       </c>
@@ -15819,8 +15853,9 @@
       <c r="P183" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R183" s="8"/>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>779</v>
       </c>
@@ -15869,8 +15904,9 @@
       <c r="P184" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R184" s="8"/>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>780</v>
       </c>
@@ -15919,8 +15955,9 @@
       <c r="P185" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R185" s="8"/>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>781</v>
       </c>
@@ -15969,8 +16006,9 @@
       <c r="P186" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R186" s="8"/>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>782</v>
       </c>
@@ -16019,8 +16057,9 @@
       <c r="P187" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R187" s="8"/>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>783</v>
       </c>
@@ -16069,8 +16108,9 @@
       <c r="P188" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R188" s="8"/>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>784</v>
       </c>
@@ -16119,8 +16159,9 @@
       <c r="P189" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R189" s="8"/>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>785</v>
       </c>
@@ -16169,8 +16210,9 @@
       <c r="P190" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R190" s="8"/>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>786</v>
       </c>
@@ -16219,8 +16261,9 @@
       <c r="P191" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R191" s="8"/>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>787</v>
       </c>
@@ -16269,8 +16312,9 @@
       <c r="P192" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R192" s="8"/>
+    </row>
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>788</v>
       </c>
@@ -16319,8 +16363,9 @@
       <c r="P193" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R193" s="8"/>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>789</v>
       </c>
@@ -16369,8 +16414,9 @@
       <c r="P194" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R194" s="8"/>
+    </row>
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>790</v>
       </c>
@@ -16419,8 +16465,9 @@
       <c r="P195" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R195" s="8"/>
+    </row>
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>791</v>
       </c>
@@ -16469,8 +16516,9 @@
       <c r="P196" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R196" s="8"/>
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>792</v>
       </c>
@@ -16519,8 +16567,9 @@
       <c r="P197" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R197" s="8"/>
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>793</v>
       </c>
@@ -16569,8 +16618,9 @@
       <c r="P198" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R198" s="8"/>
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>794</v>
       </c>
@@ -16619,8 +16669,9 @@
       <c r="P199" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R199" s="8"/>
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>795</v>
       </c>
@@ -16669,8 +16720,9 @@
       <c r="P200" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R200" s="8"/>
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>796</v>
       </c>
@@ -16719,8 +16771,9 @@
       <c r="P201" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R201" s="8"/>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>797</v>
       </c>
@@ -16769,8 +16822,9 @@
       <c r="P202" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R202" s="8"/>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>798</v>
       </c>
@@ -16819,8 +16873,9 @@
       <c r="P203" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R203" s="8"/>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>799</v>
       </c>
@@ -16869,8 +16924,9 @@
       <c r="P204" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R204" s="8"/>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>800</v>
       </c>
@@ -16919,8 +16975,9 @@
       <c r="P205" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R205" s="8"/>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>801</v>
       </c>
@@ -16969,8 +17026,9 @@
       <c r="P206" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R206" s="8"/>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>802</v>
       </c>
@@ -17019,8 +17077,9 @@
       <c r="P207" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R207" s="8"/>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>803</v>
       </c>
@@ -17069,8 +17128,9 @@
       <c r="P208" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R208" s="8"/>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>804</v>
       </c>
@@ -17119,8 +17179,9 @@
       <c r="P209" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R209" s="8"/>
+    </row>
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>805</v>
       </c>
@@ -17169,8 +17230,9 @@
       <c r="P210" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R210" s="8"/>
+    </row>
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>806</v>
       </c>
@@ -17219,8 +17281,9 @@
       <c r="P211" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R211" s="8"/>
+    </row>
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>807</v>
       </c>
@@ -17269,8 +17332,9 @@
       <c r="P212" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R212" s="8"/>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>808</v>
       </c>
@@ -17319,8 +17383,9 @@
       <c r="P213" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R213" s="8"/>
+    </row>
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>809</v>
       </c>
@@ -17369,8 +17434,9 @@
       <c r="P214" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R214" s="8"/>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>810</v>
       </c>
@@ -17419,8 +17485,9 @@
       <c r="P215" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R215" s="8"/>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>811</v>
       </c>
@@ -17469,8 +17536,9 @@
       <c r="P216" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R216" s="8"/>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>812</v>
       </c>
@@ -17519,8 +17587,9 @@
       <c r="P217" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R217" s="8"/>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>813</v>
       </c>
@@ -17569,8 +17638,9 @@
       <c r="P218" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R218" s="8"/>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>814</v>
       </c>
@@ -17619,8 +17689,9 @@
       <c r="P219" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R219" s="8"/>
+    </row>
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>815</v>
       </c>
@@ -17669,8 +17740,9 @@
       <c r="P220" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R220" s="8"/>
+    </row>
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>816</v>
       </c>
@@ -17719,8 +17791,9 @@
       <c r="P221" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R221" s="8"/>
+    </row>
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>817</v>
       </c>
@@ -17769,8 +17842,9 @@
       <c r="P222" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R222" s="8"/>
+    </row>
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>836</v>
       </c>
@@ -17819,8 +17893,9 @@
       <c r="P223" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R223" s="8"/>
+    </row>
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>837</v>
       </c>
@@ -17869,8 +17944,9 @@
       <c r="P224" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R224" s="8"/>
+    </row>
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>838</v>
       </c>
@@ -17919,8 +17995,9 @@
       <c r="P225" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R225" s="8"/>
+    </row>
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>839</v>
       </c>
@@ -17967,7 +18044,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>840</v>
       </c>
@@ -18014,7 +18091,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>841</v>
       </c>
@@ -18061,7 +18138,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>842</v>
       </c>
@@ -18108,7 +18185,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>843</v>
       </c>
@@ -18155,7 +18232,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>844</v>
       </c>
@@ -18202,7 +18279,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>845</v>
       </c>
@@ -18249,7 +18326,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>846</v>
       </c>
@@ -18296,7 +18373,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>847</v>
       </c>
@@ -18343,7 +18420,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>848</v>
       </c>
@@ -18390,7 +18467,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>849</v>
       </c>
@@ -18437,7 +18514,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>850</v>
       </c>
@@ -18484,7 +18561,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>851</v>
       </c>
@@ -18531,7 +18608,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>852</v>
       </c>
@@ -18578,7 +18655,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>880</v>
       </c>
@@ -18625,7 +18702,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>881</v>
       </c>
@@ -18672,7 +18749,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>882</v>
       </c>
@@ -18719,7 +18796,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>883</v>
       </c>
@@ -18766,7 +18843,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>884</v>
       </c>
@@ -18813,7 +18890,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>885</v>
       </c>
@@ -18860,7 +18937,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>886</v>
       </c>
@@ -18907,7 +18984,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>887</v>
       </c>
@@ -18954,7 +19031,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>888</v>
       </c>
@@ -19001,7 +19078,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>889</v>
       </c>
@@ -19048,7 +19125,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>890</v>
       </c>
@@ -19095,7 +19172,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>891</v>
       </c>
@@ -19142,7 +19219,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>892</v>
       </c>
@@ -19189,7 +19266,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>893</v>
       </c>
@@ -19235,8 +19312,9 @@
       <c r="O253" s="1" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R253" s="8"/>
+    </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>894</v>
       </c>
@@ -19282,8 +19360,9 @@
       <c r="O254" s="1" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R254" s="8"/>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>895</v>
       </c>
@@ -19332,8 +19411,9 @@
       <c r="P255" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R255" s="8"/>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>896</v>
       </c>
@@ -19382,8 +19462,9 @@
       <c r="P256" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R256" s="8"/>
+    </row>
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>897</v>
       </c>
@@ -19432,8 +19513,9 @@
       <c r="P257" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R257" s="8"/>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>898</v>
       </c>
@@ -19482,8 +19564,9 @@
       <c r="P258" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R258" s="8"/>
+    </row>
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>899</v>
       </c>
@@ -19532,8 +19615,9 @@
       <c r="P259" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R259" s="8"/>
+    </row>
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>900</v>
       </c>
@@ -19582,8 +19666,9 @@
       <c r="P260" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R260" s="8"/>
+    </row>
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>901</v>
       </c>
@@ -19632,8 +19717,9 @@
       <c r="P261" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R261" s="8"/>
+    </row>
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>902</v>
       </c>
@@ -19682,8 +19768,9 @@
       <c r="P262" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R262" s="8"/>
+    </row>
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>903</v>
       </c>
@@ -19729,8 +19816,9 @@
       <c r="P263" s="2">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R263" s="8"/>
+    </row>
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>904</v>
       </c>
@@ -19779,8 +19867,9 @@
       <c r="P264" s="2">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R264" s="8"/>
+    </row>
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>905</v>
       </c>
@@ -19829,8 +19918,9 @@
       <c r="P265" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R265" s="8"/>
+    </row>
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>906</v>
       </c>
@@ -19879,8 +19969,9 @@
       <c r="P266" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R266" s="8"/>
+    </row>
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>907</v>
       </c>
@@ -19929,8 +20020,9 @@
       <c r="P267" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R267" s="8"/>
+    </row>
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>908</v>
       </c>
@@ -19979,8 +20071,9 @@
       <c r="P268" s="2">
         <v>3.7</v>
       </c>
-    </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R268" s="8"/>
+    </row>
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>909</v>
       </c>
@@ -20029,8 +20122,9 @@
       <c r="P269" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R269" s="8"/>
+    </row>
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>910</v>
       </c>
@@ -20079,8 +20173,9 @@
       <c r="P270" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R270" s="8"/>
+    </row>
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>911</v>
       </c>
@@ -20129,8 +20224,9 @@
       <c r="P271" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R271" s="8"/>
+    </row>
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>912</v>
       </c>
@@ -20179,8 +20275,9 @@
       <c r="P272" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R272" s="8"/>
+    </row>
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>913</v>
       </c>
@@ -20229,8 +20326,9 @@
       <c r="P273" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R273" s="8"/>
+    </row>
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>914</v>
       </c>
@@ -20279,8 +20377,9 @@
       <c r="P274" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R274" s="8"/>
+    </row>
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>915</v>
       </c>
@@ -20329,8 +20428,9 @@
       <c r="P275" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R275" s="8"/>
+    </row>
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>916</v>
       </c>
@@ -20379,8 +20479,9 @@
       <c r="P276" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R276" s="8"/>
+    </row>
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>917</v>
       </c>
@@ -20429,8 +20530,9 @@
       <c r="P277" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R277" s="8"/>
+    </row>
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>918</v>
       </c>
@@ -20479,8 +20581,9 @@
       <c r="P278" s="2">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R278" s="8"/>
+    </row>
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>919</v>
       </c>
@@ -20529,8 +20632,9 @@
       <c r="P279" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R279" s="8"/>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>920</v>
       </c>
@@ -20579,8 +20683,9 @@
       <c r="P280" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R280" s="8"/>
+    </row>
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>921</v>
       </c>
@@ -20629,8 +20734,9 @@
       <c r="P281" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R281" s="8"/>
+    </row>
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>922</v>
       </c>
@@ -20679,8 +20785,9 @@
       <c r="P282" s="2">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R282" s="8"/>
+    </row>
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>923</v>
       </c>
@@ -20729,8 +20836,9 @@
       <c r="P283" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R283" s="8"/>
+    </row>
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>924</v>
       </c>
@@ -20779,8 +20887,9 @@
       <c r="P284" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R284" s="8"/>
+    </row>
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>925</v>
       </c>
@@ -20829,8 +20938,9 @@
       <c r="P285" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R285" s="8"/>
+    </row>
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>926</v>
       </c>
@@ -20879,8 +20989,9 @@
       <c r="P286" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R286" s="8"/>
+    </row>
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>927</v>
       </c>
@@ -20929,8 +21040,9 @@
       <c r="P287" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R287" s="8"/>
+    </row>
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>928</v>
       </c>
@@ -20979,8 +21091,9 @@
       <c r="P288" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R288" s="8"/>
+    </row>
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>929</v>
       </c>
@@ -21029,8 +21142,9 @@
       <c r="P289" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R289" s="8"/>
+    </row>
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>930</v>
       </c>
@@ -21079,8 +21193,9 @@
       <c r="P290" s="2">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R290" s="8"/>
+    </row>
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>931</v>
       </c>
@@ -21129,8 +21244,9 @@
       <c r="P291" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R291" s="8"/>
+    </row>
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>932</v>
       </c>
@@ -21179,8 +21295,9 @@
       <c r="P292" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R292" s="8"/>
+    </row>
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>959</v>
       </c>
@@ -21229,8 +21346,9 @@
       <c r="P293" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R293" s="8"/>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>960</v>
       </c>
@@ -21279,8 +21397,9 @@
       <c r="P294" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R294" s="8"/>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>961</v>
       </c>
@@ -21329,8 +21448,9 @@
       <c r="P295" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R295" s="8"/>
+    </row>
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>962</v>
       </c>
@@ -21379,8 +21499,9 @@
       <c r="P296" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R296" s="8"/>
+    </row>
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>963</v>
       </c>
@@ -21429,8 +21550,9 @@
       <c r="P297" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R297" s="8"/>
+    </row>
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>964</v>
       </c>
@@ -21477,7 +21599,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>965</v>
       </c>
@@ -21524,7 +21646,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>966</v>
       </c>
@@ -21571,7 +21693,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>967</v>
       </c>
@@ -21618,7 +21740,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>968</v>
       </c>
@@ -21665,7 +21787,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>969</v>
       </c>
@@ -21712,7 +21834,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>1003</v>
       </c>
@@ -21759,7 +21881,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>1004</v>
       </c>
@@ -21806,7 +21928,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>1005</v>
       </c>
@@ -21853,7 +21975,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>1006</v>
       </c>
@@ -21900,7 +22022,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>1007</v>
       </c>
@@ -21949,8 +22071,9 @@
       <c r="P308" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R308" s="8"/>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>1008</v>
       </c>
@@ -21999,8 +22122,9 @@
       <c r="P309" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R309" s="8"/>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>1009</v>
       </c>
@@ -22049,8 +22173,9 @@
       <c r="P310" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R310" s="8"/>
+    </row>
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>1010</v>
       </c>
@@ -22099,8 +22224,9 @@
       <c r="P311" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R311" s="8"/>
+    </row>
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>1011</v>
       </c>
@@ -22149,8 +22275,9 @@
       <c r="P312" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R312" s="8"/>
+    </row>
+    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1012</v>
       </c>
@@ -22199,8 +22326,9 @@
       <c r="P313" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R313" s="8"/>
+    </row>
+    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1013</v>
       </c>
@@ -22249,8 +22377,9 @@
       <c r="P314" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R314" s="8"/>
+    </row>
+    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>1014</v>
       </c>
@@ -22299,8 +22428,9 @@
       <c r="P315" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R315" s="8"/>
+    </row>
+    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>1015</v>
       </c>
@@ -22349,8 +22479,9 @@
       <c r="P316" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R316" s="8"/>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1016</v>
       </c>
@@ -22399,8 +22530,9 @@
       <c r="P317" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R317" s="8"/>
+    </row>
+    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>1017</v>
       </c>
@@ -22449,8 +22581,9 @@
       <c r="P318" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R318" s="8"/>
+    </row>
+    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>1018</v>
       </c>
@@ -22499,8 +22632,9 @@
       <c r="P319" s="2">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R319" s="8"/>
+    </row>
+    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>1019</v>
       </c>
@@ -22549,8 +22683,9 @@
       <c r="P320" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R320" s="8"/>
+    </row>
+    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>1020</v>
       </c>
@@ -22599,8 +22734,9 @@
       <c r="P321" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R321" s="8"/>
+    </row>
+    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>1021</v>
       </c>
@@ -22649,8 +22785,9 @@
       <c r="P322" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R322" s="8"/>
+    </row>
+    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>1022</v>
       </c>
@@ -22699,8 +22836,9 @@
       <c r="P323" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R323" s="8"/>
+    </row>
+    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>1023</v>
       </c>
@@ -22749,8 +22887,9 @@
       <c r="P324" s="2">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R324" s="8"/>
+    </row>
+    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>1024</v>
       </c>
@@ -22799,8 +22938,9 @@
       <c r="P325" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R325" s="8"/>
+    </row>
+    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>1025</v>
       </c>
@@ -22849,8 +22989,9 @@
       <c r="P326" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R326" s="8"/>
+    </row>
+    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>1026</v>
       </c>
@@ -22899,8 +23040,9 @@
       <c r="P327" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R327" s="8"/>
+    </row>
+    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>1027</v>
       </c>
@@ -22949,8 +23091,9 @@
       <c r="P328" s="2">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R328" s="8"/>
+    </row>
+    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>1028</v>
       </c>
@@ -22999,8 +23142,9 @@
       <c r="P329" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R329" s="8"/>
+    </row>
+    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>1029</v>
       </c>
@@ -23049,8 +23193,9 @@
       <c r="P330" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R330" s="8"/>
+    </row>
+    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>1030</v>
       </c>
@@ -23099,8 +23244,9 @@
       <c r="P331" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R331" s="8"/>
+    </row>
+    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>1031</v>
       </c>
@@ -23149,8 +23295,9 @@
       <c r="P332" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R332" s="8"/>
+    </row>
+    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>1032</v>
       </c>
@@ -23199,8 +23346,9 @@
       <c r="P333" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R333" s="8"/>
+    </row>
+    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>1033</v>
       </c>
@@ -23249,8 +23397,9 @@
       <c r="P334" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R334" s="8"/>
+    </row>
+    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>1034</v>
       </c>
@@ -23299,8 +23448,9 @@
       <c r="P335" s="2">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R335" s="8"/>
+    </row>
+    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>1035</v>
       </c>
@@ -23349,8 +23499,9 @@
       <c r="P336" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R336" s="8"/>
+    </row>
+    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>1036</v>
       </c>
@@ -23399,8 +23550,9 @@
       <c r="P337" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R337" s="8"/>
+    </row>
+    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>1037</v>
       </c>
@@ -23449,8 +23601,9 @@
       <c r="P338" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R338" s="8"/>
+    </row>
+    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>1038</v>
       </c>
@@ -23499,8 +23652,9 @@
       <c r="P339" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R339" s="8"/>
+    </row>
+    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>1039</v>
       </c>
@@ -23549,8 +23703,9 @@
       <c r="P340" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R340" s="8"/>
+    </row>
+    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>1040</v>
       </c>
@@ -23599,8 +23754,9 @@
       <c r="P341" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R341" s="8"/>
+    </row>
+    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>1041</v>
       </c>
@@ -23649,8 +23805,9 @@
       <c r="P342" s="2">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R342" s="8"/>
+    </row>
+    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1042</v>
       </c>
@@ -23699,8 +23856,9 @@
       <c r="P343" s="2">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R343" s="8"/>
+    </row>
+    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1043</v>
       </c>
@@ -23749,8 +23907,9 @@
       <c r="P344" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R344" s="8"/>
+    </row>
+    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>1044</v>
       </c>
@@ -23799,8 +23958,9 @@
       <c r="P345" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R345" s="8"/>
+    </row>
+    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>1045</v>
       </c>
@@ -23849,8 +24009,9 @@
       <c r="P346" s="2">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R346" s="8"/>
+    </row>
+    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1046</v>
       </c>
@@ -23899,8 +24060,9 @@
       <c r="P347" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R347" s="8"/>
+    </row>
+    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>1047</v>
       </c>
@@ -23949,8 +24111,9 @@
       <c r="P348" s="2">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R348" s="8"/>
+    </row>
+    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>1048</v>
       </c>
@@ -23999,8 +24162,9 @@
       <c r="P349" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R349" s="8"/>
+    </row>
+    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>1049</v>
       </c>
@@ -24049,8 +24213,9 @@
       <c r="P350" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R350" s="8"/>
+    </row>
+    <row r="351" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>1050</v>
       </c>
@@ -24099,8 +24264,9 @@
       <c r="P351" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R351" s="8"/>
+    </row>
+    <row r="352" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>1051</v>
       </c>
@@ -24149,8 +24315,9 @@
       <c r="P352" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R352" s="8"/>
+    </row>
+    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>1052</v>
       </c>
@@ -24199,8 +24366,9 @@
       <c r="P353" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R353" s="8"/>
+    </row>
+    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>1053</v>
       </c>
@@ -24249,8 +24417,9 @@
       <c r="P354" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R354" s="8"/>
+    </row>
+    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>1054</v>
       </c>
@@ -24299,8 +24468,9 @@
       <c r="P355" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R355" s="8"/>
+    </row>
+    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>1055</v>
       </c>
@@ -24349,8 +24519,9 @@
       <c r="P356" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R356" s="8"/>
+    </row>
+    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>1056</v>
       </c>
@@ -24399,8 +24570,9 @@
       <c r="P357" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R357" s="8"/>
+    </row>
+    <row r="358" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>1057</v>
       </c>
@@ -24449,8 +24621,9 @@
       <c r="P358" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R358" s="8"/>
+    </row>
+    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>1058</v>
       </c>
@@ -24499,8 +24672,9 @@
       <c r="P359" s="2">
         <v>2.1</v>
       </c>
-    </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R359" s="8"/>
+    </row>
+    <row r="360" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>1059</v>
       </c>
@@ -24549,8 +24723,9 @@
       <c r="P360" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R360" s="8"/>
+    </row>
+    <row r="361" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>1060</v>
       </c>
@@ -24599,8 +24774,9 @@
       <c r="P361" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R361" s="8"/>
+    </row>
+    <row r="362" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>1061</v>
       </c>
@@ -24649,8 +24825,9 @@
       <c r="P362" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R362" s="8"/>
+    </row>
+    <row r="363" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>1062</v>
       </c>
@@ -24699,8 +24876,9 @@
       <c r="P363" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R363" s="8"/>
+    </row>
+    <row r="364" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>1063</v>
       </c>
@@ -24749,8 +24927,9 @@
       <c r="P364" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R364" s="8"/>
+    </row>
+    <row r="365" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>1064</v>
       </c>
@@ -24799,8 +24978,9 @@
       <c r="P365" s="2">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R365" s="8"/>
+    </row>
+    <row r="366" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>1065</v>
       </c>
@@ -24849,8 +25029,9 @@
       <c r="P366" s="2">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R366" s="8"/>
+    </row>
+    <row r="367" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>1066</v>
       </c>
@@ -24899,8 +25080,9 @@
       <c r="P367" s="2">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R367" s="8"/>
+    </row>
+    <row r="368" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>1067</v>
       </c>
@@ -24949,8 +25131,9 @@
       <c r="P368" s="2">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R368" s="8"/>
+    </row>
+    <row r="369" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>1068</v>
       </c>
@@ -24999,8 +25182,9 @@
       <c r="P369" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R369" s="8"/>
+    </row>
+    <row r="370" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>1069</v>
       </c>
@@ -25049,8 +25233,9 @@
       <c r="P370" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R370" s="8"/>
+    </row>
+    <row r="371" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>1070</v>
       </c>
@@ -25099,8 +25284,9 @@
       <c r="P371" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R371" s="8"/>
+    </row>
+    <row r="372" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>1071</v>
       </c>
@@ -25149,8 +25335,9 @@
       <c r="P372" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R372" s="8"/>
+    </row>
+    <row r="373" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>1072</v>
       </c>
@@ -25199,8 +25386,9 @@
       <c r="P373" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R373" s="8"/>
+    </row>
+    <row r="374" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>1073</v>
       </c>
@@ -25249,8 +25437,9 @@
       <c r="P374" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R374" s="8"/>
+    </row>
+    <row r="375" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>1074</v>
       </c>
@@ -25299,8 +25488,9 @@
       <c r="P375" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R375" s="8"/>
+    </row>
+    <row r="376" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>1075</v>
       </c>
@@ -25349,8 +25539,9 @@
       <c r="P376" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R376" s="8"/>
+    </row>
+    <row r="377" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1076</v>
       </c>
@@ -25399,8 +25590,9 @@
       <c r="P377" s="2">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R377" s="8"/>
+    </row>
+    <row r="378" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>1077</v>
       </c>
@@ -25449,8 +25641,9 @@
       <c r="P378" s="2">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R378" s="8"/>
+    </row>
+    <row r="379" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>1078</v>
       </c>
@@ -25499,8 +25692,9 @@
       <c r="P379" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R379" s="8"/>
+    </row>
+    <row r="380" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>1079</v>
       </c>
@@ -25549,8 +25743,9 @@
       <c r="P380" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R380" s="8"/>
+    </row>
+    <row r="381" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1080</v>
       </c>
@@ -25599,8 +25794,9 @@
       <c r="P381" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R381" s="8"/>
+    </row>
+    <row r="382" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1081</v>
       </c>
@@ -25649,8 +25845,9 @@
       <c r="P382" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R382" s="8"/>
+    </row>
+    <row r="383" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>1082</v>
       </c>
@@ -25699,8 +25896,9 @@
       <c r="P383" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R383" s="8"/>
+    </row>
+    <row r="384" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>1083</v>
       </c>
@@ -25749,8 +25947,9 @@
       <c r="P384" s="2">
         <v>3.3</v>
       </c>
-    </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R384" s="8"/>
+    </row>
+    <row r="385" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>1084</v>
       </c>
@@ -25799,8 +25998,9 @@
       <c r="P385" s="2">
         <v>4.3</v>
       </c>
-    </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R385" s="8"/>
+    </row>
+    <row r="386" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>1085</v>
       </c>
@@ -25849,8 +26049,9 @@
       <c r="P386" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R386" s="8"/>
+    </row>
+    <row r="387" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1115</v>
       </c>
@@ -25899,8 +26100,9 @@
       <c r="P387" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R387" s="8"/>
+    </row>
+    <row r="388" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>1129</v>
       </c>
@@ -25949,8 +26151,9 @@
       <c r="P388" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R388" s="8"/>
+    </row>
+    <row r="389" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>1130</v>
       </c>
@@ -25999,8 +26202,9 @@
       <c r="P389" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R389" s="8"/>
+    </row>
+    <row r="390" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>1131</v>
       </c>
@@ -26049,8 +26253,9 @@
       <c r="P390" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R390" s="8"/>
+    </row>
+    <row r="391" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1132</v>
       </c>
@@ -26099,8 +26304,9 @@
       <c r="P391" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R391" s="8"/>
+    </row>
+    <row r="392" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>1116</v>
       </c>
@@ -26149,8 +26355,9 @@
       <c r="P392" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R392" s="8"/>
+    </row>
+    <row r="393" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>1117</v>
       </c>
@@ -26199,8 +26406,9 @@
       <c r="P393" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R393" s="8"/>
+    </row>
+    <row r="394" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>1118</v>
       </c>
@@ -26249,8 +26457,9 @@
       <c r="P394" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R394" s="8"/>
+    </row>
+    <row r="395" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>1119</v>
       </c>
@@ -26299,8 +26508,9 @@
       <c r="P395" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R395" s="8"/>
+    </row>
+    <row r="396" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>1120</v>
       </c>
@@ -26349,8 +26559,9 @@
       <c r="P396" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R396" s="8"/>
+    </row>
+    <row r="397" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1121</v>
       </c>
@@ -26399,8 +26610,9 @@
       <c r="P397" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R397" s="8"/>
+    </row>
+    <row r="398" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>1123</v>
       </c>
@@ -26449,8 +26661,9 @@
       <c r="P398" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R398" s="8"/>
+    </row>
+    <row r="399" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1124</v>
       </c>
@@ -26499,8 +26712,9 @@
       <c r="P399" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R399" s="8"/>
+    </row>
+    <row r="400" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>1125</v>
       </c>
@@ -26549,8 +26763,9 @@
       <c r="P400" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R400" s="8"/>
+    </row>
+    <row r="401" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>1133</v>
       </c>
@@ -26599,8 +26814,9 @@
       <c r="P401" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R401" s="8"/>
+    </row>
+    <row r="402" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1134</v>
       </c>
@@ -26649,8 +26865,9 @@
       <c r="P402" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R402" s="8"/>
+    </row>
+    <row r="403" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>1135</v>
       </c>
@@ -26699,8 +26916,9 @@
       <c r="P403" s="2">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R403" s="8"/>
+    </row>
+    <row r="404" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>1136</v>
       </c>
@@ -26749,8 +26967,9 @@
       <c r="P404" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R404" s="8"/>
+    </row>
+    <row r="405" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>1137</v>
       </c>
@@ -26799,8 +27018,9 @@
       <c r="P405" s="2">
         <v>3.2</v>
       </c>
-    </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R405" s="8"/>
+    </row>
+    <row r="406" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>1138</v>
       </c>
@@ -26849,8 +27069,9 @@
       <c r="P406" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R406" s="8"/>
+    </row>
+    <row r="407" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>1139</v>
       </c>
@@ -26899,8 +27120,9 @@
       <c r="P407" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R407" s="8"/>
+    </row>
+    <row r="408" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>1140</v>
       </c>
@@ -26949,8 +27171,9 @@
       <c r="P408" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R408" s="8"/>
+    </row>
+    <row r="409" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>1141</v>
       </c>
@@ -26999,8 +27222,9 @@
       <c r="P409" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R409" s="8"/>
+    </row>
+    <row r="410" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>1142</v>
       </c>
@@ -27049,8 +27273,9 @@
       <c r="P410" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R410" s="8"/>
+    </row>
+    <row r="411" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>1143</v>
       </c>
@@ -27099,8 +27324,9 @@
       <c r="P411" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R411" s="8"/>
+    </row>
+    <row r="412" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>1144</v>
       </c>
@@ -27149,8 +27375,9 @@
       <c r="P412" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R412" s="8"/>
+    </row>
+    <row r="413" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>1145</v>
       </c>
@@ -27199,8 +27426,9 @@
       <c r="P413" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R413" s="8"/>
+    </row>
+    <row r="414" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>1146</v>
       </c>
@@ -27249,8 +27477,9 @@
       <c r="P414" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R414" s="8"/>
+    </row>
+    <row r="415" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>1147</v>
       </c>
@@ -27299,8 +27528,9 @@
       <c r="P415" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R415" s="8"/>
+    </row>
+    <row r="416" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>1148</v>
       </c>
@@ -27349,8 +27579,9 @@
       <c r="P416" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R416" s="8"/>
+    </row>
+    <row r="417" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>1149</v>
       </c>
@@ -27399,8 +27630,9 @@
       <c r="P417" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R417" s="8"/>
+    </row>
+    <row r="418" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>1150</v>
       </c>
@@ -27449,8 +27681,9 @@
       <c r="P418" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R418" s="8"/>
+    </row>
+    <row r="419" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>1151</v>
       </c>
@@ -27499,8 +27732,9 @@
       <c r="P419" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R419" s="8"/>
+    </row>
+    <row r="420" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>1152</v>
       </c>
@@ -27549,8 +27783,9 @@
       <c r="P420" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R420" s="8"/>
+    </row>
+    <row r="421" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>1153</v>
       </c>
@@ -27599,8 +27834,9 @@
       <c r="P421" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R421" s="8"/>
+    </row>
+    <row r="422" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>1154</v>
       </c>
@@ -27649,8 +27885,9 @@
       <c r="P422" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R422" s="8"/>
+    </row>
+    <row r="423" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>1155</v>
       </c>
@@ -27699,8 +27936,9 @@
       <c r="P423" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R423" s="8"/>
+    </row>
+    <row r="424" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>1156</v>
       </c>
@@ -27749,8 +27987,9 @@
       <c r="P424" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R424" s="8"/>
+    </row>
+    <row r="425" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>1157</v>
       </c>
@@ -27799,8 +28038,9 @@
       <c r="P425" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R425" s="8"/>
+    </row>
+    <row r="426" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>1158</v>
       </c>
@@ -27849,8 +28089,9 @@
       <c r="P426" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R426" s="8"/>
+    </row>
+    <row r="427" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>1159</v>
       </c>
@@ -27899,8 +28140,9 @@
       <c r="P427" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R427" s="8"/>
+    </row>
+    <row r="428" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>1160</v>
       </c>
@@ -27949,8 +28191,9 @@
       <c r="P428" s="2">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R428" s="8"/>
+    </row>
+    <row r="429" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>1161</v>
       </c>
@@ -28000,7 +28243,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>1162</v>
       </c>
@@ -28050,7 +28293,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>1163</v>
       </c>
@@ -28100,7 +28343,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>1164</v>
       </c>
@@ -31952,7 +32195,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>1245</v>
       </c>
@@ -31999,7 +32242,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>1246</v>
       </c>
@@ -32046,7 +32289,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>1247</v>
       </c>
@@ -32093,7 +32336,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>1248</v>
       </c>
@@ -32140,7 +32383,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>1249</v>
       </c>
@@ -32187,7 +32430,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>1250</v>
       </c>
@@ -32234,7 +32477,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>1251</v>
       </c>
@@ -32281,7 +32524,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>1252</v>
       </c>
@@ -32328,7 +32571,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>1253</v>
       </c>
@@ -32374,8 +32617,9 @@
       <c r="O521" s="1" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="R521" s="8"/>
+    </row>
+    <row r="522" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>1254</v>
       </c>
@@ -32422,7 +32666,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>1255</v>
       </c>
@@ -32469,7 +32713,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>1256</v>
       </c>
@@ -32516,7 +32760,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>1257</v>
       </c>
@@ -32563,7 +32807,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>1258</v>
       </c>
@@ -32610,7 +32854,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>1259</v>
       </c>
@@ -32657,7 +32901,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>1260</v>
       </c>
@@ -34211,7 +34455,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>1293</v>
       </c>
@@ -34261,7 +34505,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>1294</v>
       </c>
@@ -34311,7 +34555,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>1295</v>
       </c>
@@ -34361,7 +34605,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>1296</v>
       </c>
@@ -34410,8 +34654,9 @@
       <c r="P564" s="2">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R564" s="8"/>
+    </row>
+    <row r="565" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>1297</v>
       </c>
@@ -34461,7 +34706,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>1298</v>
       </c>
@@ -34511,7 +34756,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>1299</v>
       </c>
@@ -34561,7 +34806,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>1300</v>
       </c>
@@ -34611,7 +34856,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>1301</v>
       </c>
@@ -34661,7 +34906,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>1302</v>
       </c>
@@ -34711,7 +34956,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>1303</v>
       </c>
@@ -34761,7 +35006,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>1304</v>
       </c>
@@ -34811,7 +35056,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>1305</v>
       </c>
@@ -34861,7 +35106,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>1306</v>
       </c>
@@ -34911,7 +35156,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>1307</v>
       </c>
@@ -34961,7 +35206,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>1308</v>
       </c>
@@ -36611,7 +36856,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="609" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>1341</v>
       </c>
@@ -36660,8 +36905,9 @@
       <c r="P609" s="2">
         <v>4.2</v>
       </c>
-    </row>
-    <row r="610" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R609" s="8"/>
+    </row>
+    <row r="610" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>1342</v>
       </c>
@@ -36711,7 +36957,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="611" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>1343</v>
       </c>
@@ -36761,7 +37007,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="612" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>1344</v>
       </c>
@@ -36811,7 +37057,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="613" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>1345</v>
       </c>
@@ -36861,7 +37107,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="614" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>1346</v>
       </c>
@@ -36911,7 +37157,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="615" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>1347</v>
       </c>
@@ -36961,7 +37207,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="616" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>1348</v>
       </c>
@@ -37011,7 +37257,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="617" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>1349</v>
       </c>
@@ -37061,7 +37307,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="618" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>1350</v>
       </c>
@@ -37110,8 +37356,9 @@
       <c r="P618" s="2">
         <v>5.0999999999999996</v>
       </c>
-    </row>
-    <row r="619" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R618" s="8"/>
+    </row>
+    <row r="619" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>1351</v>
       </c>
@@ -37161,7 +37408,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="620" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>1352</v>
       </c>
@@ -37211,7 +37458,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="621" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>1353</v>
       </c>
@@ -37261,7 +37508,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="622" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>1354</v>
       </c>
@@ -37311,7 +37558,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="623" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>1355</v>
       </c>
@@ -37361,7 +37608,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="624" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>1356</v>
       </c>
@@ -41171,7 +41418,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="705" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
         <v>1437</v>
       </c>
@@ -41218,7 +41465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="706" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
         <v>1438</v>
       </c>
@@ -41265,7 +41512,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="707" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
         <v>1439</v>
       </c>
@@ -41312,7 +41559,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="708" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
         <v>1440</v>
       </c>
@@ -41359,7 +41606,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="709" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
         <v>1441</v>
       </c>
@@ -41406,7 +41653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="710" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
         <v>1442</v>
       </c>
@@ -41453,7 +41700,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="711" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
         <v>1443</v>
       </c>
@@ -41500,7 +41747,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="712" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
         <v>1444</v>
       </c>
@@ -41547,7 +41794,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="713" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
         <v>1445</v>
       </c>
@@ -41594,7 +41841,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="714" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
         <v>1446</v>
       </c>
@@ -41641,7 +41888,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="715" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
         <v>1447</v>
       </c>
@@ -41688,7 +41935,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="716" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
         <v>1448</v>
       </c>
@@ -41735,7 +41982,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="717" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
         <v>1449</v>
       </c>
@@ -41782,7 +42029,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="718" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
         <v>1450</v>
       </c>
@@ -41829,7 +42076,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="719" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
         <v>1452</v>
       </c>
@@ -41875,8 +42122,9 @@
       <c r="O719" s="1" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="720" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R719" s="8"/>
+    </row>
+    <row r="720" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
         <v>1459</v>
       </c>
@@ -41926,7 +42174,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="721" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
         <v>1460</v>
       </c>
@@ -41976,7 +42224,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="722" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
         <v>1461</v>
       </c>
@@ -42025,8 +42273,9 @@
       <c r="P722" s="2">
         <v>4.0999999999999996</v>
       </c>
-    </row>
-    <row r="723" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R722" s="8"/>
+    </row>
+    <row r="723" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
         <v>1462</v>
       </c>
@@ -42073,7 +42322,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="724" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
         <v>1463</v>
       </c>
@@ -42117,7 +42366,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="725" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
         <v>1469</v>
       </c>
@@ -42161,7 +42410,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="726" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
         <v>1470</v>
       </c>
@@ -42205,7 +42454,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="727" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
         <v>1471</v>
       </c>
@@ -42252,7 +42501,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="728" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
         <v>1600</v>
       </c>
@@ -42302,7 +42551,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="729" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
         <v>1601</v>
       </c>
@@ -42352,7 +42601,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="730" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
         <v>1602</v>
       </c>
@@ -42402,7 +42651,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="731" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
         <v>1603</v>
       </c>
@@ -42452,7 +42701,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="732" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
         <v>1604</v>
       </c>
@@ -42502,7 +42751,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="733" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
         <v>1605</v>
       </c>
@@ -42552,7 +42801,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="734" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
         <v>1606</v>
       </c>
@@ -42602,7 +42851,7 @@
         <v>2.1</v>
       </c>
     </row>
-    <row r="735" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
         <v>1607</v>
       </c>
@@ -42652,7 +42901,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="736" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
         <v>1608</v>
       </c>
@@ -44302,7 +44551,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="769" spans="1:16" s="13" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:18" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A769" s="10" t="s">
         <v>1641</v>
       </c>
@@ -44351,8 +44600,9 @@
       <c r="P769" s="12">
         <v>3.1</v>
       </c>
-    </row>
-    <row r="770" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R769" s="11"/>
+    </row>
+    <row r="770" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
         <v>1642</v>
       </c>
@@ -44402,7 +44652,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="771" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
         <v>1643</v>
       </c>
@@ -44452,7 +44702,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="772" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
         <v>1644</v>
       </c>
@@ -44502,7 +44752,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="773" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
         <v>1645</v>
       </c>
@@ -44552,7 +44802,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="774" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
         <v>1646</v>
       </c>
@@ -44602,7 +44852,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="775" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
         <v>1647</v>
       </c>
@@ -44652,7 +44902,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="776" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
         <v>1648</v>
       </c>
@@ -44702,7 +44952,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="777" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A777" s="1" t="s">
         <v>1649</v>
       </c>
@@ -44752,7 +45002,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="778" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A778" s="1" t="s">
         <v>1650</v>
       </c>
@@ -44802,7 +45052,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="779" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A779" s="1" t="s">
         <v>1651</v>
       </c>
@@ -44852,7 +45102,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="780" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A780" s="1" t="s">
         <v>1652</v>
       </c>
@@ -44902,7 +45152,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="781" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A781" s="1" t="s">
         <v>1653</v>
       </c>
@@ -44952,7 +45202,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="782" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A782" s="1" t="s">
         <v>1654</v>
       </c>
@@ -45002,7 +45252,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="783" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A783" s="1" t="s">
         <v>1655</v>
       </c>
@@ -45052,7 +45302,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="784" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A784" s="1" t="s">
         <v>1656</v>
       </c>
@@ -50429,7 +50679,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="897" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A897" s="1" t="s">
         <v>1849</v>
       </c>
@@ -50476,7 +50726,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="898" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A898" s="1" t="s">
         <v>1850</v>
       </c>
@@ -50523,7 +50773,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="899" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A899" s="1" t="s">
         <v>1851</v>
       </c>
@@ -50570,7 +50820,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="900" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A900" s="1" t="s">
         <v>1852</v>
       </c>
@@ -50617,7 +50867,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="901" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A901" s="1" t="s">
         <v>1853</v>
       </c>
@@ -50664,7 +50914,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="902" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A902" s="1" t="s">
         <v>1854</v>
       </c>
@@ -50711,7 +50961,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="903" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A903" s="1" t="s">
         <v>1855</v>
       </c>
@@ -50758,7 +51008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="904" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A904" s="1" t="s">
         <v>1856</v>
       </c>
@@ -50805,7 +51055,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="905" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A905" s="1" t="s">
         <v>1857</v>
       </c>
@@ -50852,7 +51102,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="906" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A906" s="1" t="s">
         <v>1858</v>
       </c>
@@ -50899,7 +51149,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="907" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A907" s="1" t="s">
         <v>1859</v>
       </c>
@@ -50946,7 +51196,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="908" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A908" s="1" t="s">
         <v>1860</v>
       </c>
@@ -50989,8 +51239,14 @@
       <c r="O908" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="909" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P908" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q908" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="909" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A909" s="1" t="s">
         <v>1861</v>
       </c>
@@ -51033,8 +51289,14 @@
       <c r="O909" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="910" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P909" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q909" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="910" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A910" s="1" t="s">
         <v>1862</v>
       </c>
@@ -51077,8 +51339,14 @@
       <c r="O910" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="911" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P910" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q910" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="911" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A911" s="1" t="s">
         <v>1863</v>
       </c>
@@ -51121,8 +51389,14 @@
       <c r="O911" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="912" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P911" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q911" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="912" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A912" s="1" t="s">
         <v>1864</v>
       </c>
@@ -51165,8 +51439,14 @@
       <c r="O912" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="913" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P912" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q912" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="913" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A913" s="1" t="s">
         <v>1865</v>
       </c>
@@ -51209,8 +51489,14 @@
       <c r="O913" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="914" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P913" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q913" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="914" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A914" s="1" t="s">
         <v>1866</v>
       </c>
@@ -51253,8 +51539,14 @@
       <c r="O914" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="915" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P914" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q914" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="915" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A915" s="1" t="s">
         <v>1867</v>
       </c>
@@ -51297,8 +51589,14 @@
       <c r="O915" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="916" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P915" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q915" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="916" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A916" s="1" t="s">
         <v>1868</v>
       </c>
@@ -51341,8 +51639,14 @@
       <c r="O916" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="917" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P916" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q916" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="917" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A917" s="1" t="s">
         <v>1869</v>
       </c>
@@ -51388,8 +51692,14 @@
       <c r="O917" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="918" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P917" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q917" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="918" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A918" s="1" t="s">
         <v>1870</v>
       </c>
@@ -51435,8 +51745,14 @@
       <c r="O918" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="919" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P918" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q918" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="919" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A919" s="1" t="s">
         <v>1871</v>
       </c>
@@ -51482,8 +51798,14 @@
       <c r="O919" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="920" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P919" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q919" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="920" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A920" s="1" t="s">
         <v>1872</v>
       </c>
@@ -51529,8 +51851,14 @@
       <c r="O920" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="921" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P920" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q920" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="921" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A921" s="1" t="s">
         <v>1873</v>
       </c>
@@ -51576,8 +51904,14 @@
       <c r="O921" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="922" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P921" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q921" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="922" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A922" s="1" t="s">
         <v>1874</v>
       </c>
@@ -51623,8 +51957,14 @@
       <c r="O922" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="923" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P922" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q922" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="923" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A923" s="1" t="s">
         <v>1875</v>
       </c>
@@ -51670,8 +52010,14 @@
       <c r="O923" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="924" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P923" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q923" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="924" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A924" s="1" t="s">
         <v>1876</v>
       </c>
@@ -51717,8 +52063,14 @@
       <c r="O924" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="925" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P924" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q924" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="925" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A925" s="1" t="s">
         <v>1877</v>
       </c>
@@ -51764,8 +52116,14 @@
       <c r="O925" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="926" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P925" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q925" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="926" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A926" s="1" t="s">
         <v>1878</v>
       </c>
@@ -51808,8 +52166,14 @@
       <c r="O926" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="927" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P926" s="21">
+        <v>46251</v>
+      </c>
+      <c r="Q926" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="927" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A927" s="1" t="s">
         <v>1879</v>
       </c>
@@ -51852,8 +52216,14 @@
       <c r="O927" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="928" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P927" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q927" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="928" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A928" s="1" t="s">
         <v>1880</v>
       </c>
@@ -51896,8 +52266,14 @@
       <c r="O928" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="929" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P928" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q928" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="929" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A929" s="1" t="s">
         <v>1881</v>
       </c>
@@ -51940,8 +52316,14 @@
       <c r="O929" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="930" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P929" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q929" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="930" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A930" s="1" t="s">
         <v>1882</v>
       </c>
@@ -51984,8 +52366,14 @@
       <c r="O930" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="931" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P930" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q930" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="931" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A931" s="1" t="s">
         <v>1883</v>
       </c>
@@ -52028,8 +52416,14 @@
       <c r="O931" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="932" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P931" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q931" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="932" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A932" s="1" t="s">
         <v>1884</v>
       </c>
@@ -52072,8 +52466,14 @@
       <c r="O932" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="933" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P932" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q932" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="933" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A933" s="1" t="s">
         <v>1885</v>
       </c>
@@ -52116,8 +52516,14 @@
       <c r="O933" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="934" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P933" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q933" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="934" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A934" s="1" t="s">
         <v>1886</v>
       </c>
@@ -52160,8 +52566,14 @@
       <c r="O934" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="935" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P934" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q934" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="935" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A935" s="1" t="s">
         <v>1887</v>
       </c>
@@ -52207,8 +52619,14 @@
       <c r="O935" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="936" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P935" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q935" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="936" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A936" s="1" t="s">
         <v>1888</v>
       </c>
@@ -52254,8 +52672,14 @@
       <c r="O936" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="937" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P936" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q936" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="937" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A937" s="1" t="s">
         <v>1889</v>
       </c>
@@ -52301,8 +52725,14 @@
       <c r="O937" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="938" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P937" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q937" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="938" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A938" s="1" t="s">
         <v>1890</v>
       </c>
@@ -52348,8 +52778,14 @@
       <c r="O938" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="939" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P938" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q938" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="939" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A939" s="1" t="s">
         <v>1891</v>
       </c>
@@ -52395,8 +52831,14 @@
       <c r="O939" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="940" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P939" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q939" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="940" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A940" s="1" t="s">
         <v>1892</v>
       </c>
@@ -52442,8 +52884,14 @@
       <c r="O940" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="941" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P940" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q940" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="941" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A941" s="1" t="s">
         <v>1893</v>
       </c>
@@ -52489,8 +52937,14 @@
       <c r="O941" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="942" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P941" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q941" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="942" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A942" s="1" t="s">
         <v>1894</v>
       </c>
@@ -52536,8 +52990,14 @@
       <c r="O942" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="943" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P942" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q942" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="943" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A943" s="1" t="s">
         <v>1895</v>
       </c>
@@ -52583,8 +53043,14 @@
       <c r="O943" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="944" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P943" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q943" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="944" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A944" s="1" t="s">
         <v>1896</v>
       </c>
@@ -52630,8 +53096,14 @@
       <c r="O944" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="945" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P944" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q944" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="945" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A945" s="1" t="s">
         <v>1897</v>
       </c>
@@ -52674,8 +53146,14 @@
       <c r="O945" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="946" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P945" s="21">
+        <v>46253</v>
+      </c>
+      <c r="Q945" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="946" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A946" s="1" t="s">
         <v>1898</v>
       </c>
@@ -52721,8 +53199,14 @@
       <c r="O946" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="947" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P946" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q946" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="947" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A947" s="1" t="s">
         <v>1899</v>
       </c>
@@ -52765,8 +53249,14 @@
       <c r="O947" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="948" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P947" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q947" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="948" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A948" s="1" t="s">
         <v>1900</v>
       </c>
@@ -52812,8 +53302,14 @@
       <c r="O948" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="949" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P948" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q948" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="949" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A949" s="1" t="s">
         <v>1901</v>
       </c>
@@ -52856,8 +53352,14 @@
       <c r="O949" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="950" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P949" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q949" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="950" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A950" s="1" t="s">
         <v>1902</v>
       </c>
@@ -52900,8 +53402,14 @@
       <c r="O950" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="951" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P950" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q950" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="951" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A951" s="1" t="s">
         <v>1903</v>
       </c>
@@ -52944,8 +53452,14 @@
       <c r="O951" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="952" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P951" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q951" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="952" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A952" s="1" t="s">
         <v>1904</v>
       </c>
@@ -52988,8 +53502,14 @@
       <c r="O952" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="953" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P952" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q952" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="953" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A953" s="1" t="s">
         <v>1905</v>
       </c>
@@ -53035,8 +53555,14 @@
       <c r="O953" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="954" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P953" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q953" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="954" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A954" s="1" t="s">
         <v>1906</v>
       </c>
@@ -53082,8 +53608,14 @@
       <c r="O954" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="955" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P954" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q954" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="955" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A955" s="1" t="s">
         <v>1907</v>
       </c>
@@ -53129,8 +53661,14 @@
       <c r="O955" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="956" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P955" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q955" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="956" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A956" s="1" t="s">
         <v>1908</v>
       </c>
@@ -53173,8 +53711,14 @@
       <c r="O956" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="957" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P956" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q956" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="957" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A957" s="1" t="s">
         <v>1909</v>
       </c>
@@ -53217,8 +53761,14 @@
       <c r="O957" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="958" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P957" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q957" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="958" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A958" s="1" t="s">
         <v>1910</v>
       </c>
@@ -53261,8 +53811,14 @@
       <c r="O958" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="959" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P958" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q958" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="959" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A959" s="1" t="s">
         <v>1911</v>
       </c>
@@ -53305,8 +53861,14 @@
       <c r="O959" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="960" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P959" s="21">
+        <v>46258</v>
+      </c>
+      <c r="Q959" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="960" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A960" s="1" t="s">
         <v>1912</v>
       </c>
@@ -53349,8 +53911,14 @@
       <c r="O960" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="961" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P960" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q960" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="961" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A961" s="1" t="s">
         <v>1913</v>
       </c>
@@ -53393,8 +53961,14 @@
       <c r="O961" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="962" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P961" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q961" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="962" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A962" s="1" t="s">
         <v>1914</v>
       </c>
@@ -53437,8 +54011,14 @@
       <c r="O962" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="963" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P962" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q962" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="963" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A963" s="1" t="s">
         <v>1915</v>
       </c>
@@ -53481,8 +54061,14 @@
       <c r="O963" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="964" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P963" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q963" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="964" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A964" s="1" t="s">
         <v>1916</v>
       </c>
@@ -53525,8 +54111,14 @@
       <c r="O964" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="965" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P964" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q964" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="965" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A965" s="1" t="s">
         <v>1917</v>
       </c>
@@ -53569,8 +54161,14 @@
       <c r="O965" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="966" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P965" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q965" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="966" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A966" s="1" t="s">
         <v>1918</v>
       </c>
@@ -53613,8 +54211,14 @@
       <c r="O966" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="967" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P966" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q966" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="967" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A967" s="1" t="s">
         <v>1919</v>
       </c>
@@ -53657,8 +54261,14 @@
       <c r="O967" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="968" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P967" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q967" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="968" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A968" s="1" t="s">
         <v>1920</v>
       </c>
@@ -53701,8 +54311,14 @@
       <c r="O968" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="969" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P968" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q968" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="969" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A969" s="1" t="s">
         <v>1921</v>
       </c>
@@ -53745,8 +54361,14 @@
       <c r="O969" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="970" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P969" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q969" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="970" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A970" s="1" t="s">
         <v>1922</v>
       </c>
@@ -53789,8 +54411,14 @@
       <c r="O970" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="971" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P970" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q970" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="971" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A971" s="1" t="s">
         <v>1923</v>
       </c>
@@ -53833,8 +54461,14 @@
       <c r="O971" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="972" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P971" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q971" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="972" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A972" s="1" t="s">
         <v>1924</v>
       </c>
@@ -53877,8 +54511,14 @@
       <c r="O972" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="973" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P972" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q972" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="973" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A973" s="1" t="s">
         <v>1925</v>
       </c>
@@ -53921,8 +54561,14 @@
       <c r="O973" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="974" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P973" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q973" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="974" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A974" s="1" t="s">
         <v>1926</v>
       </c>
@@ -53965,8 +54611,14 @@
       <c r="O974" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="975" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P974" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q974" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="975" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A975" s="1" t="s">
         <v>1927</v>
       </c>
@@ -54009,8 +54661,14 @@
       <c r="O975" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="976" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P975" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q975" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="976" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A976" s="1" t="s">
         <v>1928</v>
       </c>
@@ -54053,8 +54711,14 @@
       <c r="O976" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="977" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P976" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q976" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="977" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A977" s="1" t="s">
         <v>1929</v>
       </c>
@@ -54100,8 +54764,14 @@
       <c r="O977" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="978" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P977" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q977" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="978" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A978" s="1" t="s">
         <v>1930</v>
       </c>
@@ -54147,8 +54817,14 @@
       <c r="O978" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="979" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P978" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q978" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="979" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A979" s="1" t="s">
         <v>1931</v>
       </c>
@@ -54194,8 +54870,14 @@
       <c r="O979" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="980" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P979" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q979" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="980" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A980" s="1" t="s">
         <v>1932</v>
       </c>
@@ -54241,8 +54923,14 @@
       <c r="O980" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="981" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P980" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q980" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="981" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A981" s="1" t="s">
         <v>1933</v>
       </c>
@@ -54288,8 +54976,14 @@
       <c r="O981" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="982" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P981" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q981" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="982" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A982" s="1" t="s">
         <v>1934</v>
       </c>
@@ -54335,8 +55029,14 @@
       <c r="O982" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="983" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P982" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q982" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="983" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A983" s="1" t="s">
         <v>1935</v>
       </c>
@@ -54382,8 +55082,14 @@
       <c r="O983" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="984" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P983" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q983" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="984" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A984" s="1" t="s">
         <v>1936</v>
       </c>
@@ -54429,8 +55135,14 @@
       <c r="O984" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="985" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P984" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q984" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="985" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A985" s="1" t="s">
         <v>1937</v>
       </c>
@@ -54476,8 +55188,14 @@
       <c r="O985" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="986" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P985" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q985" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="986" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A986" s="1" t="s">
         <v>1938</v>
       </c>
@@ -54523,8 +55241,14 @@
       <c r="O986" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="987" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P986" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q986" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="987" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A987" s="1" t="s">
         <v>1939</v>
       </c>
@@ -54570,8 +55294,14 @@
       <c r="O987" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="988" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P987" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q987" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="988" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A988" s="1" t="s">
         <v>1940</v>
       </c>
@@ -54617,8 +55347,14 @@
       <c r="O988" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="989" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P988" s="21">
+        <v>46246</v>
+      </c>
+      <c r="Q988" s="1" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="989" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A989" s="1" t="s">
         <v>1941</v>
       </c>
@@ -54665,7 +55401,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="990" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A990" s="1" t="s">
         <v>1942</v>
       </c>
@@ -54712,7 +55448,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="991" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A991" s="1" t="s">
         <v>1943</v>
       </c>
@@ -54759,7 +55495,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="992" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A992" s="1" t="s">
         <v>1944</v>
       </c>
@@ -56705,7 +57441,7 @@
       <c r="F1033" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1033" s="17">
+      <c r="G1033" s="1">
         <v>10238123050</v>
       </c>
       <c r="H1033" s="1" t="s">
@@ -56755,7 +57491,7 @@
       <c r="F1034" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1034" s="17">
+      <c r="G1034" s="1">
         <v>43832608</v>
       </c>
       <c r="H1034" s="1" t="s">
@@ -56805,7 +57541,7 @@
       <c r="F1035" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1035" s="17">
+      <c r="G1035" s="1">
         <v>10487664958</v>
       </c>
       <c r="H1035" s="1" t="s">
@@ -56855,7 +57591,7 @@
       <c r="F1036" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1036" s="17">
+      <c r="G1036" s="1">
         <v>10239380714</v>
       </c>
       <c r="H1036" s="1" t="s">
@@ -56905,7 +57641,7 @@
       <c r="F1037" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1037" s="17">
+      <c r="G1037" s="1">
         <v>10239128519</v>
       </c>
       <c r="H1037" s="1" t="s">
@@ -56955,7 +57691,7 @@
       <c r="F1038" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1038" s="17">
+      <c r="G1038" s="1">
         <v>10444412823</v>
       </c>
       <c r="H1038" s="1" t="s">
@@ -57005,7 +57741,7 @@
       <c r="F1039" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1039" s="17">
+      <c r="G1039" s="1">
         <v>10404750432</v>
       </c>
       <c r="H1039" s="1" t="s">
@@ -57055,7 +57791,7 @@
       <c r="F1040" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1040" s="17">
+      <c r="G1040" s="1">
         <v>10243926217</v>
       </c>
       <c r="H1040" s="1" t="s">
@@ -57105,7 +57841,7 @@
       <c r="F1041" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1041" s="17">
+      <c r="G1041" s="1">
         <v>10238300903</v>
       </c>
       <c r="H1041" s="1" t="s">
@@ -57155,7 +57891,7 @@
       <c r="F1042" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1042" s="17">
+      <c r="G1042" s="1">
         <v>10090021945</v>
       </c>
       <c r="H1042" s="1" t="s">
@@ -57205,7 +57941,7 @@
       <c r="F1043" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1043" s="17">
+      <c r="G1043" s="1">
         <v>10239106876</v>
       </c>
       <c r="H1043" s="1" t="s">
@@ -57255,7 +57991,7 @@
       <c r="F1044" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1044" s="17">
+      <c r="G1044" s="1">
         <v>10238589458</v>
       </c>
       <c r="H1044" s="1" t="s">
@@ -57305,7 +58041,7 @@
       <c r="F1045" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1045" s="17">
+      <c r="G1045" s="1">
         <v>10404750432</v>
       </c>
       <c r="H1045" s="1" t="s">
@@ -57355,7 +58091,7 @@
       <c r="F1046" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1046" s="17">
+      <c r="G1046" s="1">
         <v>10243926217</v>
       </c>
       <c r="H1046" s="1" t="s">
@@ -57405,7 +58141,7 @@
       <c r="F1047" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1047" s="17">
+      <c r="G1047" s="1">
         <v>10238300903</v>
       </c>
       <c r="H1047" s="1" t="s">
@@ -57455,7 +58191,7 @@
       <c r="F1048" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1048" s="17">
+      <c r="G1048" s="1">
         <v>10090021945</v>
       </c>
       <c r="H1048" s="1" t="s">
@@ -57505,7 +58241,7 @@
       <c r="F1049" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1049" s="17">
+      <c r="G1049" s="1">
         <v>10239106876</v>
       </c>
       <c r="H1049" s="1" t="s">
@@ -57555,7 +58291,7 @@
       <c r="F1050" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1050" s="17">
+      <c r="G1050" s="1">
         <v>10238589458</v>
       </c>
       <c r="H1050" s="1" t="s">
@@ -57605,7 +58341,7 @@
       <c r="F1051" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1051" s="17">
+      <c r="G1051" s="1">
         <v>10310385765</v>
       </c>
       <c r="H1051" s="1" t="s">
@@ -57655,7 +58391,7 @@
       <c r="F1052" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1052" s="17">
+      <c r="G1052" s="1">
         <v>10434938126</v>
       </c>
       <c r="H1052" s="1" t="s">
@@ -57705,7 +58441,7 @@
       <c r="F1053" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1053" s="17">
+      <c r="G1053" s="1">
         <v>10404815739</v>
       </c>
       <c r="H1053" s="1" t="s">
@@ -57755,7 +58491,7 @@
       <c r="F1054" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1054" s="17">
+      <c r="G1054" s="1">
         <v>10239584115</v>
       </c>
       <c r="H1054" s="1" t="s">
@@ -57805,7 +58541,7 @@
       <c r="F1055" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1055" s="17">
+      <c r="G1055" s="1">
         <v>10424320647</v>
       </c>
       <c r="H1055" s="1" t="s">
@@ -57855,7 +58591,7 @@
       <c r="F1056" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1056" s="17">
+      <c r="G1056" s="1">
         <v>10238474651</v>
       </c>
       <c r="H1056" s="1" t="s">
@@ -57905,7 +58641,7 @@
       <c r="F1057" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1057" s="17">
+      <c r="G1057" s="1">
         <v>40829448</v>
       </c>
       <c r="H1057" s="1" t="s">
@@ -57955,7 +58691,7 @@
       <c r="F1058" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1058" s="17">
+      <c r="G1058" s="1">
         <v>10251243951</v>
       </c>
       <c r="H1058" s="1" t="s">
@@ -58005,7 +58741,7 @@
       <c r="F1059" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1059" s="17">
+      <c r="G1059" s="1">
         <v>10238202693</v>
       </c>
       <c r="H1059" s="1" t="s">
@@ -58055,7 +58791,7 @@
       <c r="F1060" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1060" s="17">
+      <c r="G1060" s="1">
         <v>10238089358</v>
       </c>
       <c r="H1060" s="1" t="s">
@@ -58105,7 +58841,7 @@
       <c r="F1061" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1061" s="17">
+      <c r="G1061" s="1">
         <v>10403478488</v>
       </c>
       <c r="H1061" s="1" t="s">
@@ -58155,7 +58891,7 @@
       <c r="F1062" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1062" s="17">
+      <c r="G1062" s="1">
         <v>10434938126</v>
       </c>
       <c r="H1062" s="1" t="s">
@@ -58205,7 +58941,7 @@
       <c r="F1063" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1063" s="17">
+      <c r="G1063" s="1">
         <v>10403478488</v>
       </c>
       <c r="H1063" s="1" t="s">
@@ -58255,7 +58991,7 @@
       <c r="F1064" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1064" s="17">
+      <c r="G1064" s="1">
         <v>10310385765</v>
       </c>
       <c r="H1064" s="1" t="s">
@@ -58305,7 +59041,7 @@
       <c r="F1065" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1065" s="17">
+      <c r="G1065" s="1">
         <v>10404815739</v>
       </c>
       <c r="H1065" s="1" t="s">
@@ -58355,7 +59091,7 @@
       <c r="F1066" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1066" s="17">
+      <c r="G1066" s="1">
         <v>10239584115</v>
       </c>
       <c r="H1066" s="1" t="s">
@@ -58405,7 +59141,7 @@
       <c r="F1067" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1067" s="17">
+      <c r="G1067" s="1">
         <v>10424320647</v>
       </c>
       <c r="H1067" s="1" t="s">
@@ -58455,7 +59191,7 @@
       <c r="F1068" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1068" s="17">
+      <c r="G1068" s="1">
         <v>10238474651</v>
       </c>
       <c r="H1068" s="1" t="s">
@@ -58505,7 +59241,7 @@
       <c r="F1069" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1069" s="17">
+      <c r="G1069" s="1">
         <v>40829448</v>
       </c>
       <c r="H1069" s="1" t="s">
@@ -58555,7 +59291,7 @@
       <c r="F1070" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1070" s="17">
+      <c r="G1070" s="1">
         <v>10251243951</v>
       </c>
       <c r="H1070" s="1" t="s">
@@ -58605,7 +59341,7 @@
       <c r="F1071" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1071" s="17">
+      <c r="G1071" s="1">
         <v>10238202693</v>
       </c>
       <c r="H1071" s="1" t="s">
@@ -58655,7 +59391,7 @@
       <c r="F1072" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1072" s="17">
+      <c r="G1072" s="1">
         <v>10238089358</v>
       </c>
       <c r="H1072" s="1" t="s">
@@ -58686,7 +59422,7 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="1073" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1073" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1073" s="1" t="s">
         <v>2123</v>
       </c>
@@ -58705,7 +59441,7 @@
       <c r="F1073" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G1073" s="17">
+      <c r="G1073" s="1">
         <v>10400802225</v>
       </c>
       <c r="H1073" s="1" t="s">
@@ -58736,7 +59472,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="1074" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1074" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1074" s="1" t="s">
         <v>2124</v>
       </c>
@@ -58755,7 +59491,7 @@
       <c r="F1074" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G1074" s="17">
+      <c r="G1074" s="1">
         <v>10238552589</v>
       </c>
       <c r="H1074" s="1" t="s">
@@ -58786,7 +59522,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="1075" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1075" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1075" s="1" t="s">
         <v>2125</v>
       </c>
@@ -58805,7 +59541,7 @@
       <c r="F1075" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G1075" s="17">
+      <c r="G1075" s="1">
         <v>10239546736</v>
       </c>
       <c r="H1075" s="1" t="s">
@@ -58836,7 +59572,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="1076" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1076" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1076" s="1" t="s">
         <v>2126</v>
       </c>
@@ -58855,7 +59591,7 @@
       <c r="F1076" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G1076" s="17">
+      <c r="G1076" s="1">
         <v>10243840738</v>
       </c>
       <c r="H1076" s="1" t="s">
@@ -58886,7 +59622,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="1077" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1077" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1077" s="1" t="s">
         <v>2127</v>
       </c>
@@ -58905,7 +59641,7 @@
       <c r="F1077" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G1077" s="17">
+      <c r="G1077" s="1">
         <v>10417044227</v>
       </c>
       <c r="H1077" s="1" t="s">
@@ -58936,7 +59672,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="1078" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1078" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1078" s="1" t="s">
         <v>2128</v>
       </c>
@@ -58955,7 +59691,7 @@
       <c r="F1078" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G1078" s="17">
+      <c r="G1078" s="1">
         <v>10239637642</v>
       </c>
       <c r="H1078" s="1" t="s">
@@ -58986,7 +59722,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="1079" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1079" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1079" s="1" t="s">
         <v>2129</v>
       </c>
@@ -59005,7 +59741,7 @@
       <c r="F1079" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G1079" s="17">
+      <c r="G1079" s="1">
         <v>10401531284</v>
       </c>
       <c r="H1079" s="1" t="s">
@@ -59036,7 +59772,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="1080" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1080" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1080" s="1" t="s">
         <v>2130</v>
       </c>
@@ -59055,7 +59791,7 @@
       <c r="F1080" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="G1080" s="17">
+      <c r="G1080" s="1">
         <v>10090021945</v>
       </c>
       <c r="H1080" s="1" t="s">
@@ -59086,7 +59822,7 @@
         <v>3.3</v>
       </c>
     </row>
-    <row r="1081" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1081" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1081" s="1" t="s">
         <v>2131</v>
       </c>
@@ -59105,7 +59841,7 @@
       <c r="F1081" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1081" s="17">
+      <c r="G1081" s="1">
         <v>45431690</v>
       </c>
       <c r="H1081" s="1" t="s">
@@ -59135,8 +59871,9 @@
       <c r="P1081" s="2">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="1082" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R1081" s="8"/>
+    </row>
+    <row r="1082" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1082" s="1" t="s">
         <v>2132</v>
       </c>
@@ -59155,7 +59892,7 @@
       <c r="F1082" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1082" s="17">
+      <c r="G1082" s="1">
         <v>10239486377</v>
       </c>
       <c r="H1082" s="1" t="s">
@@ -59186,57 +59923,58 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="1083" spans="1:16" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1083" s="18" t="s">
+    <row r="1083" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1083" s="17" t="s">
         <v>2133</v>
       </c>
-      <c r="B1083" s="22">
+      <c r="B1083" s="20">
         <v>46269</v>
       </c>
-      <c r="C1083" s="18">
-        <v>2026</v>
-      </c>
-      <c r="D1083" s="18">
+      <c r="C1083" s="17">
+        <v>2026</v>
+      </c>
+      <c r="D1083" s="17">
         <v>9</v>
       </c>
-      <c r="E1083" s="18" t="s">
+      <c r="E1083" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="F1083" s="18" t="s">
+      <c r="F1083" s="17" t="s">
         <v>822</v>
       </c>
-      <c r="G1083" s="19">
+      <c r="G1083" s="17">
         <v>10476142941</v>
       </c>
-      <c r="H1083" s="18" t="s">
+      <c r="H1083" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="I1083" s="18" t="s">
+      <c r="I1083" s="17" t="s">
         <v>514</v>
       </c>
-      <c r="J1083" s="18" t="s">
+      <c r="J1083" s="17" t="s">
         <v>242</v>
       </c>
-      <c r="K1083" s="18" t="s">
+      <c r="K1083" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="L1083" s="18" t="s">
+      <c r="L1083" s="17" t="s">
         <v>2008</v>
       </c>
-      <c r="M1083" s="18" t="s">
-        <v>528</v>
-      </c>
-      <c r="N1083" s="18">
-        <v>1</v>
-      </c>
-      <c r="O1083" s="18" t="s">
+      <c r="M1083" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1083" s="17">
+        <v>1</v>
+      </c>
+      <c r="O1083" s="17" t="s">
         <v>2067</v>
       </c>
-      <c r="P1083" s="20">
+      <c r="P1083" s="18">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="1084" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R1083" s="20"/>
+    </row>
+    <row r="1084" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1084" s="1" t="s">
         <v>2134</v>
       </c>
@@ -59255,7 +59993,7 @@
       <c r="F1084" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1084" s="17">
+      <c r="G1084" s="1">
         <v>10456258536</v>
       </c>
       <c r="H1084" s="1" t="s">
@@ -59285,8 +60023,9 @@
       <c r="P1084" s="2">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="1085" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="R1084" s="8"/>
+    </row>
+    <row r="1085" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1085" s="1" t="s">
         <v>2135</v>
       </c>
@@ -59305,7 +60044,7 @@
       <c r="F1085" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="G1085" s="17">
+      <c r="G1085" s="1">
         <v>10238589458</v>
       </c>
       <c r="H1085" s="1" t="s">
@@ -59336,7 +60075,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="1086" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1086" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1086" s="1" t="s">
         <v>2136</v>
       </c>
@@ -59355,7 +60094,7 @@
       <c r="F1086" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="G1086" s="17">
+      <c r="G1086" s="1">
         <v>10247107920</v>
       </c>
       <c r="H1086" s="1" t="s">
@@ -59386,7 +60125,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="1087" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1087" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1087" s="1" t="s">
         <v>2137</v>
       </c>
@@ -59405,7 +60144,7 @@
       <c r="F1087" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="G1087" s="17">
+      <c r="G1087" s="1">
         <v>10239802821</v>
       </c>
       <c r="H1087" s="1" t="s">
@@ -59436,7 +60175,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="1088" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1088" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1088" s="1" t="s">
         <v>2138</v>
       </c>
@@ -59455,7 +60194,7 @@
       <c r="F1088" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="G1088" s="17">
+      <c r="G1088" s="1">
         <v>10424320647</v>
       </c>
       <c r="H1088" s="1" t="s">
@@ -59505,7 +60244,7 @@
       <c r="F1089" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="G1089" s="17">
+      <c r="G1089" s="1">
         <v>10239223431</v>
       </c>
       <c r="H1089" s="1" t="s">
@@ -59555,7 +60294,7 @@
       <c r="F1090" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="G1090" s="17">
+      <c r="G1090" s="1">
         <v>10090021945</v>
       </c>
       <c r="H1090" s="1" t="s">
@@ -59605,7 +60344,7 @@
       <c r="F1091" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="G1091" s="17">
+      <c r="G1091" s="1">
         <v>10239791013</v>
       </c>
       <c r="H1091" s="1" t="s">
@@ -59655,7 +60394,7 @@
       <c r="F1092" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="G1092" s="17">
+      <c r="G1092" s="1">
         <v>10238089358</v>
       </c>
       <c r="H1092" s="1" t="s">
@@ -59705,7 +60444,7 @@
       <c r="F1093" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1093" s="17">
+      <c r="G1093" s="1">
         <v>10404750432</v>
       </c>
       <c r="H1093" s="1" t="s">
@@ -59755,7 +60494,7 @@
       <c r="F1094" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1094" s="17">
+      <c r="G1094" s="1">
         <v>10444412823</v>
       </c>
       <c r="H1094" s="1" t="s">
@@ -59805,7 +60544,7 @@
       <c r="F1095" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1095" s="17">
+      <c r="G1095" s="1">
         <v>10239802821</v>
       </c>
       <c r="H1095" s="1" t="s">
@@ -59855,7 +60594,7 @@
       <c r="F1096" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1096" s="17">
+      <c r="G1096" s="1">
         <v>10404750432</v>
       </c>
       <c r="H1096" s="1" t="s">
@@ -59905,7 +60644,7 @@
       <c r="F1097" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1097" s="17">
+      <c r="G1097" s="1">
         <v>10444412823</v>
       </c>
       <c r="H1097" s="1" t="s">
@@ -59955,7 +60694,7 @@
       <c r="F1098" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1098" s="17">
+      <c r="G1098" s="1">
         <v>10239802821</v>
       </c>
       <c r="H1098" s="1" t="s">

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F329A12-97D5-4A65-9681-ED3745BBFC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07164D06-BD72-43AF-A684-5914754521ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07164D06-BD72-43AF-A684-5914754521ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB504F50-CAB1-47DC-88BE-0181A00A70F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12098" uniqueCount="2159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12285" uniqueCount="2113">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -6076,9 +6076,6 @@
     <t xml:space="preserve">Asistencia técnica en teñido natural con eucalipto: revalorización de residuos vegetales en la cadena textil </t>
   </si>
   <si>
-    <t>YOLANDA MERMA SUCLLE</t>
-  </si>
-  <si>
     <t>ZENOVIA LAZO TAQQUERE</t>
   </si>
   <si>
@@ -6160,201 +6157,6 @@
     <t>DISEÑO DE EMPAQUE Y/O ENVASE ORIENTADA AL MANUAL DE MARCA  (Actividad 4.3)</t>
   </si>
   <si>
-    <t>ANEXO 3</t>
-  </si>
-  <si>
-    <t>ANEXO 4</t>
-  </si>
-  <si>
-    <t>ANEXO 5</t>
-  </si>
-  <si>
-    <t>ANEXO 6</t>
-  </si>
-  <si>
-    <t>ANEXO 7</t>
-  </si>
-  <si>
-    <t>ANEXO 8</t>
-  </si>
-  <si>
-    <t>ANEXO 9</t>
-  </si>
-  <si>
-    <t>ANEXO 10</t>
-  </si>
-  <si>
-    <t>ANEXO 11</t>
-  </si>
-  <si>
-    <t>ANEXO 12</t>
-  </si>
-  <si>
-    <t>ANEXO 13</t>
-  </si>
-  <si>
-    <t>ANEXO 14</t>
-  </si>
-  <si>
-    <t>ANEXO 15</t>
-  </si>
-  <si>
-    <t>ANEXO 16</t>
-  </si>
-  <si>
-    <t>ANEXO 17</t>
-  </si>
-  <si>
-    <t>ANEXO 18</t>
-  </si>
-  <si>
-    <t>ANEXO 19</t>
-  </si>
-  <si>
-    <t>ANEXO 20</t>
-  </si>
-  <si>
-    <t>ANEXO 21</t>
-  </si>
-  <si>
-    <t>ANEXO 22</t>
-  </si>
-  <si>
-    <t>ANEXO 23</t>
-  </si>
-  <si>
-    <t>ANEXO 24</t>
-  </si>
-  <si>
-    <t>ANEXO 25</t>
-  </si>
-  <si>
-    <t>ANEXO 26</t>
-  </si>
-  <si>
-    <t>ANEXO 27</t>
-  </si>
-  <si>
-    <t>ANEXO 28</t>
-  </si>
-  <si>
-    <t>ANEXO 29</t>
-  </si>
-  <si>
-    <t>ANEXO 30</t>
-  </si>
-  <si>
-    <t>ANEXO 31</t>
-  </si>
-  <si>
-    <t>ANEXO 32</t>
-  </si>
-  <si>
-    <t>ANEXO 33</t>
-  </si>
-  <si>
-    <t>ANEXO 34</t>
-  </si>
-  <si>
-    <t>ANEXO 35</t>
-  </si>
-  <si>
-    <t>ANEXO 36</t>
-  </si>
-  <si>
-    <t>ANEXO 37</t>
-  </si>
-  <si>
-    <t>ANEXO 38</t>
-  </si>
-  <si>
-    <t>ANEXO 39</t>
-  </si>
-  <si>
-    <t>ANEXO 40</t>
-  </si>
-  <si>
-    <t>ANEXO 41</t>
-  </si>
-  <si>
-    <t>ANEXO 42</t>
-  </si>
-  <si>
-    <t>ANEXO 43</t>
-  </si>
-  <si>
-    <t>ANEXO 44</t>
-  </si>
-  <si>
-    <t>ANEXO 45</t>
-  </si>
-  <si>
-    <t>ANEXO 46</t>
-  </si>
-  <si>
-    <t>ANEXO 47</t>
-  </si>
-  <si>
-    <t>ANEXO 48</t>
-  </si>
-  <si>
-    <t>ANEXO 49</t>
-  </si>
-  <si>
-    <t>ANEXO 50</t>
-  </si>
-  <si>
-    <t>ANEXO 52</t>
-  </si>
-  <si>
-    <t>ANEXO 53</t>
-  </si>
-  <si>
-    <t>ANEXO 54</t>
-  </si>
-  <si>
-    <t>ANEXO 55</t>
-  </si>
-  <si>
-    <t>ANEXO 56</t>
-  </si>
-  <si>
-    <t>ANEXO 57</t>
-  </si>
-  <si>
-    <t>ANEXO 58</t>
-  </si>
-  <si>
-    <t>ANEXO 59</t>
-  </si>
-  <si>
-    <t>ANEXO 60</t>
-  </si>
-  <si>
-    <t>ANEXO 61</t>
-  </si>
-  <si>
-    <t>ANEXO 62</t>
-  </si>
-  <si>
-    <t>ANEXO 63</t>
-  </si>
-  <si>
-    <t>ANEXO 64</t>
-  </si>
-  <si>
-    <t>ANEXO 65</t>
-  </si>
-  <si>
-    <t>ANEXO 66</t>
-  </si>
-  <si>
-    <t>ANEXO 67</t>
-  </si>
-  <si>
-    <t>ANEXO 68</t>
-  </si>
-  <si>
     <t>C001134</t>
   </si>
   <si>
@@ -6611,6 +6413,66 @@
   </si>
   <si>
     <t>FECHA_I</t>
+  </si>
+  <si>
+    <t>teñido</t>
+  </si>
+  <si>
+    <t>018-Teñido artesanal con tintes sintéticos con las técnicas de teñido en sustratos textiles</t>
+  </si>
+  <si>
+    <t>Teñido</t>
+  </si>
+  <si>
+    <t>C001201</t>
+  </si>
+  <si>
+    <t>C001202</t>
+  </si>
+  <si>
+    <t>C001203</t>
+  </si>
+  <si>
+    <t>C001204</t>
+  </si>
+  <si>
+    <t>C001205</t>
+  </si>
+  <si>
+    <t>C001206</t>
+  </si>
+  <si>
+    <t>C001207</t>
+  </si>
+  <si>
+    <t>C001208</t>
+  </si>
+  <si>
+    <t>C001209</t>
+  </si>
+  <si>
+    <t>C001210</t>
+  </si>
+  <si>
+    <t>C001211</t>
+  </si>
+  <si>
+    <t>C001212</t>
+  </si>
+  <si>
+    <t>C001213</t>
+  </si>
+  <si>
+    <t>C001214</t>
+  </si>
+  <si>
+    <t>C001215</t>
+  </si>
+  <si>
+    <t>C001216</t>
+  </si>
+  <si>
+    <t>C001217</t>
   </si>
 </sst>
 </file>
@@ -6691,17 +6553,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Display"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -6728,7 +6588,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -6760,17 +6620,18 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7121,7 +6982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
-  <dimension ref="A1:R1098"/>
+  <dimension ref="A1:R1115"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -7138,7 +6999,7 @@
     <col min="12" max="12" width="79.7109375" style="1" customWidth="1"/>
     <col min="13" max="13" width="13.42578125" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.42578125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="8.7109375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="17.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13.7109375" customWidth="1"/>
     <col min="18" max="18" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
@@ -7194,10 +7055,10 @@
         <v>463</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>2157</v>
+        <v>2091</v>
       </c>
       <c r="R1" s="6" t="s">
-        <v>2158</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -51200,11 +51061,11 @@
       <c r="O908" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P908" s="19">
+      <c r="P908" s="15">
         <v>46251</v>
       </c>
       <c r="Q908" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="909" spans="1:17" x14ac:dyDescent="0.25">
@@ -51250,11 +51111,11 @@
       <c r="O909" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P909" s="19">
+      <c r="P909" s="15">
         <v>46251</v>
       </c>
       <c r="Q909" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="910" spans="1:17" x14ac:dyDescent="0.25">
@@ -51300,11 +51161,11 @@
       <c r="O910" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P910" s="19">
+      <c r="P910" s="15">
         <v>46251</v>
       </c>
       <c r="Q910" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="911" spans="1:17" x14ac:dyDescent="0.25">
@@ -51350,11 +51211,11 @@
       <c r="O911" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P911" s="19">
+      <c r="P911" s="15">
         <v>46251</v>
       </c>
       <c r="Q911" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="912" spans="1:17" x14ac:dyDescent="0.25">
@@ -51400,11 +51261,11 @@
       <c r="O912" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P912" s="19">
+      <c r="P912" s="15">
         <v>46251</v>
       </c>
       <c r="Q912" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="913" spans="1:17" x14ac:dyDescent="0.25">
@@ -51450,11 +51311,11 @@
       <c r="O913" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P913" s="19">
+      <c r="P913" s="15">
         <v>46251</v>
       </c>
       <c r="Q913" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="914" spans="1:17" x14ac:dyDescent="0.25">
@@ -51500,11 +51361,11 @@
       <c r="O914" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P914" s="19">
+      <c r="P914" s="15">
         <v>46251</v>
       </c>
       <c r="Q914" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="915" spans="1:17" x14ac:dyDescent="0.25">
@@ -51550,11 +51411,11 @@
       <c r="O915" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P915" s="19">
+      <c r="P915" s="15">
         <v>46251</v>
       </c>
       <c r="Q915" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="916" spans="1:17" x14ac:dyDescent="0.25">
@@ -51600,11 +51461,11 @@
       <c r="O916" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P916" s="19">
+      <c r="P916" s="15">
         <v>46251</v>
       </c>
       <c r="Q916" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="917" spans="1:17" x14ac:dyDescent="0.25">
@@ -51653,11 +51514,11 @@
       <c r="O917" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P917" s="19">
+      <c r="P917" s="15">
         <v>46251</v>
       </c>
       <c r="Q917" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="918" spans="1:17" x14ac:dyDescent="0.25">
@@ -51706,11 +51567,11 @@
       <c r="O918" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P918" s="19">
+      <c r="P918" s="15">
         <v>46251</v>
       </c>
       <c r="Q918" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="919" spans="1:17" x14ac:dyDescent="0.25">
@@ -51759,11 +51620,11 @@
       <c r="O919" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P919" s="19">
+      <c r="P919" s="15">
         <v>46251</v>
       </c>
       <c r="Q919" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="920" spans="1:17" x14ac:dyDescent="0.25">
@@ -51812,11 +51673,11 @@
       <c r="O920" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P920" s="19">
+      <c r="P920" s="15">
         <v>46251</v>
       </c>
       <c r="Q920" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="921" spans="1:17" x14ac:dyDescent="0.25">
@@ -51865,11 +51726,11 @@
       <c r="O921" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P921" s="19">
+      <c r="P921" s="15">
         <v>46251</v>
       </c>
       <c r="Q921" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="922" spans="1:17" x14ac:dyDescent="0.25">
@@ -51918,11 +51779,11 @@
       <c r="O922" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P922" s="19">
+      <c r="P922" s="15">
         <v>46251</v>
       </c>
       <c r="Q922" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="923" spans="1:17" x14ac:dyDescent="0.25">
@@ -51971,11 +51832,11 @@
       <c r="O923" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P923" s="19">
+      <c r="P923" s="15">
         <v>46251</v>
       </c>
       <c r="Q923" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="924" spans="1:17" x14ac:dyDescent="0.25">
@@ -52024,11 +51885,11 @@
       <c r="O924" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P924" s="19">
+      <c r="P924" s="15">
         <v>46251</v>
       </c>
       <c r="Q924" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="925" spans="1:17" x14ac:dyDescent="0.25">
@@ -52077,11 +51938,11 @@
       <c r="O925" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P925" s="19">
+      <c r="P925" s="15">
         <v>46251</v>
       </c>
       <c r="Q925" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="926" spans="1:17" x14ac:dyDescent="0.25">
@@ -52127,11 +51988,11 @@
       <c r="O926" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P926" s="19">
+      <c r="P926" s="15">
         <v>46251</v>
       </c>
       <c r="Q926" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="927" spans="1:17" x14ac:dyDescent="0.25">
@@ -52177,11 +52038,11 @@
       <c r="O927" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P927" s="19">
+      <c r="P927" s="15">
         <v>46253</v>
       </c>
       <c r="Q927" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="928" spans="1:17" x14ac:dyDescent="0.25">
@@ -52227,11 +52088,11 @@
       <c r="O928" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P928" s="19">
+      <c r="P928" s="15">
         <v>46253</v>
       </c>
       <c r="Q928" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="929" spans="1:17" x14ac:dyDescent="0.25">
@@ -52277,11 +52138,11 @@
       <c r="O929" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P929" s="19">
+      <c r="P929" s="15">
         <v>46253</v>
       </c>
       <c r="Q929" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="930" spans="1:17" x14ac:dyDescent="0.25">
@@ -52327,11 +52188,11 @@
       <c r="O930" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P930" s="19">
+      <c r="P930" s="15">
         <v>46253</v>
       </c>
       <c r="Q930" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="931" spans="1:17" x14ac:dyDescent="0.25">
@@ -52377,11 +52238,11 @@
       <c r="O931" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P931" s="19">
+      <c r="P931" s="15">
         <v>46253</v>
       </c>
       <c r="Q931" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="932" spans="1:17" x14ac:dyDescent="0.25">
@@ -52427,11 +52288,11 @@
       <c r="O932" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P932" s="19">
+      <c r="P932" s="15">
         <v>46253</v>
       </c>
       <c r="Q932" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="933" spans="1:17" x14ac:dyDescent="0.25">
@@ -52477,11 +52338,11 @@
       <c r="O933" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P933" s="19">
+      <c r="P933" s="15">
         <v>46253</v>
       </c>
       <c r="Q933" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="934" spans="1:17" x14ac:dyDescent="0.25">
@@ -52527,11 +52388,11 @@
       <c r="O934" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P934" s="19">
+      <c r="P934" s="15">
         <v>46253</v>
       </c>
       <c r="Q934" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="935" spans="1:17" x14ac:dyDescent="0.25">
@@ -52580,11 +52441,11 @@
       <c r="O935" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P935" s="19">
+      <c r="P935" s="15">
         <v>46253</v>
       </c>
       <c r="Q935" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="936" spans="1:17" x14ac:dyDescent="0.25">
@@ -52633,11 +52494,11 @@
       <c r="O936" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P936" s="19">
+      <c r="P936" s="15">
         <v>46253</v>
       </c>
       <c r="Q936" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="937" spans="1:17" x14ac:dyDescent="0.25">
@@ -52686,11 +52547,11 @@
       <c r="O937" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P937" s="19">
+      <c r="P937" s="15">
         <v>46253</v>
       </c>
       <c r="Q937" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="938" spans="1:17" x14ac:dyDescent="0.25">
@@ -52739,11 +52600,11 @@
       <c r="O938" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P938" s="19">
+      <c r="P938" s="15">
         <v>46253</v>
       </c>
       <c r="Q938" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="939" spans="1:17" x14ac:dyDescent="0.25">
@@ -52792,11 +52653,11 @@
       <c r="O939" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P939" s="19">
+      <c r="P939" s="15">
         <v>46253</v>
       </c>
       <c r="Q939" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="940" spans="1:17" x14ac:dyDescent="0.25">
@@ -52845,11 +52706,11 @@
       <c r="O940" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P940" s="19">
+      <c r="P940" s="15">
         <v>46253</v>
       </c>
       <c r="Q940" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="941" spans="1:17" x14ac:dyDescent="0.25">
@@ -52898,11 +52759,11 @@
       <c r="O941" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P941" s="19">
+      <c r="P941" s="15">
         <v>46253</v>
       </c>
       <c r="Q941" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="942" spans="1:17" x14ac:dyDescent="0.25">
@@ -52951,11 +52812,11 @@
       <c r="O942" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P942" s="19">
+      <c r="P942" s="15">
         <v>46253</v>
       </c>
       <c r="Q942" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="943" spans="1:17" x14ac:dyDescent="0.25">
@@ -53004,11 +52865,11 @@
       <c r="O943" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P943" s="19">
+      <c r="P943" s="15">
         <v>46253</v>
       </c>
       <c r="Q943" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="944" spans="1:17" x14ac:dyDescent="0.25">
@@ -53057,11 +52918,11 @@
       <c r="O944" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P944" s="19">
+      <c r="P944" s="15">
         <v>46253</v>
       </c>
       <c r="Q944" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="945" spans="1:17" x14ac:dyDescent="0.25">
@@ -53107,11 +52968,11 @@
       <c r="O945" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P945" s="19">
+      <c r="P945" s="15">
         <v>46253</v>
       </c>
       <c r="Q945" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="946" spans="1:17" x14ac:dyDescent="0.25">
@@ -53160,11 +53021,11 @@
       <c r="O946" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P946" s="19">
+      <c r="P946" s="15">
         <v>46258</v>
       </c>
       <c r="Q946" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="947" spans="1:17" x14ac:dyDescent="0.25">
@@ -53210,11 +53071,11 @@
       <c r="O947" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P947" s="19">
+      <c r="P947" s="15">
         <v>46258</v>
       </c>
       <c r="Q947" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="948" spans="1:17" x14ac:dyDescent="0.25">
@@ -53263,11 +53124,11 @@
       <c r="O948" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P948" s="19">
+      <c r="P948" s="15">
         <v>46258</v>
       </c>
       <c r="Q948" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="949" spans="1:17" x14ac:dyDescent="0.25">
@@ -53313,11 +53174,11 @@
       <c r="O949" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P949" s="19">
+      <c r="P949" s="15">
         <v>46258</v>
       </c>
       <c r="Q949" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="950" spans="1:17" x14ac:dyDescent="0.25">
@@ -53363,11 +53224,11 @@
       <c r="O950" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P950" s="19">
+      <c r="P950" s="15">
         <v>46258</v>
       </c>
       <c r="Q950" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="951" spans="1:17" x14ac:dyDescent="0.25">
@@ -53413,11 +53274,11 @@
       <c r="O951" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P951" s="19">
+      <c r="P951" s="15">
         <v>46258</v>
       </c>
       <c r="Q951" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="952" spans="1:17" x14ac:dyDescent="0.25">
@@ -53463,11 +53324,11 @@
       <c r="O952" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P952" s="19">
+      <c r="P952" s="15">
         <v>46258</v>
       </c>
       <c r="Q952" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="953" spans="1:17" x14ac:dyDescent="0.25">
@@ -53516,11 +53377,11 @@
       <c r="O953" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P953" s="19">
+      <c r="P953" s="15">
         <v>46258</v>
       </c>
       <c r="Q953" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="954" spans="1:17" x14ac:dyDescent="0.25">
@@ -53569,11 +53430,11 @@
       <c r="O954" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P954" s="19">
+      <c r="P954" s="15">
         <v>46258</v>
       </c>
       <c r="Q954" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="955" spans="1:17" x14ac:dyDescent="0.25">
@@ -53622,11 +53483,11 @@
       <c r="O955" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P955" s="19">
+      <c r="P955" s="15">
         <v>46258</v>
       </c>
       <c r="Q955" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="956" spans="1:17" x14ac:dyDescent="0.25">
@@ -53672,11 +53533,11 @@
       <c r="O956" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P956" s="19">
+      <c r="P956" s="15">
         <v>46258</v>
       </c>
       <c r="Q956" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="957" spans="1:17" x14ac:dyDescent="0.25">
@@ -53722,11 +53583,11 @@
       <c r="O957" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P957" s="19">
+      <c r="P957" s="15">
         <v>46258</v>
       </c>
       <c r="Q957" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="958" spans="1:17" x14ac:dyDescent="0.25">
@@ -53772,11 +53633,11 @@
       <c r="O958" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P958" s="19">
+      <c r="P958" s="15">
         <v>46258</v>
       </c>
       <c r="Q958" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="959" spans="1:17" x14ac:dyDescent="0.25">
@@ -53822,11 +53683,11 @@
       <c r="O959" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P959" s="19">
+      <c r="P959" s="15">
         <v>46258</v>
       </c>
       <c r="Q959" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="960" spans="1:17" x14ac:dyDescent="0.25">
@@ -53872,11 +53733,11 @@
       <c r="O960" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P960" s="19">
+      <c r="P960" s="15">
         <v>46246</v>
       </c>
       <c r="Q960" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="961" spans="1:17" x14ac:dyDescent="0.25">
@@ -53922,11 +53783,11 @@
       <c r="O961" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P961" s="19">
+      <c r="P961" s="15">
         <v>46246</v>
       </c>
       <c r="Q961" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="962" spans="1:17" x14ac:dyDescent="0.25">
@@ -53972,11 +53833,11 @@
       <c r="O962" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P962" s="19">
+      <c r="P962" s="15">
         <v>46246</v>
       </c>
       <c r="Q962" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="963" spans="1:17" x14ac:dyDescent="0.25">
@@ -54022,11 +53883,11 @@
       <c r="O963" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P963" s="19">
+      <c r="P963" s="15">
         <v>46246</v>
       </c>
       <c r="Q963" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="964" spans="1:17" x14ac:dyDescent="0.25">
@@ -54072,11 +53933,11 @@
       <c r="O964" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P964" s="19">
+      <c r="P964" s="15">
         <v>46246</v>
       </c>
       <c r="Q964" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="965" spans="1:17" x14ac:dyDescent="0.25">
@@ -54122,11 +53983,11 @@
       <c r="O965" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P965" s="19">
+      <c r="P965" s="15">
         <v>46246</v>
       </c>
       <c r="Q965" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="966" spans="1:17" x14ac:dyDescent="0.25">
@@ -54172,11 +54033,11 @@
       <c r="O966" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P966" s="19">
+      <c r="P966" s="15">
         <v>46246</v>
       </c>
       <c r="Q966" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="967" spans="1:17" x14ac:dyDescent="0.25">
@@ -54222,11 +54083,11 @@
       <c r="O967" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P967" s="19">
+      <c r="P967" s="15">
         <v>46246</v>
       </c>
       <c r="Q967" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="968" spans="1:17" x14ac:dyDescent="0.25">
@@ -54272,11 +54133,11 @@
       <c r="O968" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P968" s="19">
+      <c r="P968" s="15">
         <v>46246</v>
       </c>
       <c r="Q968" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="969" spans="1:17" x14ac:dyDescent="0.25">
@@ -54322,11 +54183,11 @@
       <c r="O969" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P969" s="19">
+      <c r="P969" s="15">
         <v>46246</v>
       </c>
       <c r="Q969" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="970" spans="1:17" x14ac:dyDescent="0.25">
@@ -54372,11 +54233,11 @@
       <c r="O970" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P970" s="19">
+      <c r="P970" s="15">
         <v>46246</v>
       </c>
       <c r="Q970" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="971" spans="1:17" x14ac:dyDescent="0.25">
@@ -54422,11 +54283,11 @@
       <c r="O971" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P971" s="19">
+      <c r="P971" s="15">
         <v>46246</v>
       </c>
       <c r="Q971" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="972" spans="1:17" x14ac:dyDescent="0.25">
@@ -54472,11 +54333,11 @@
       <c r="O972" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P972" s="19">
+      <c r="P972" s="15">
         <v>46246</v>
       </c>
       <c r="Q972" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="973" spans="1:17" x14ac:dyDescent="0.25">
@@ -54522,11 +54383,11 @@
       <c r="O973" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P973" s="19">
+      <c r="P973" s="15">
         <v>46246</v>
       </c>
       <c r="Q973" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="974" spans="1:17" x14ac:dyDescent="0.25">
@@ -54572,11 +54433,11 @@
       <c r="O974" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P974" s="19">
+      <c r="P974" s="15">
         <v>46246</v>
       </c>
       <c r="Q974" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="975" spans="1:17" x14ac:dyDescent="0.25">
@@ -54622,11 +54483,11 @@
       <c r="O975" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P975" s="19">
+      <c r="P975" s="15">
         <v>46246</v>
       </c>
       <c r="Q975" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="976" spans="1:17" x14ac:dyDescent="0.25">
@@ -54672,11 +54533,11 @@
       <c r="O976" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P976" s="19">
+      <c r="P976" s="15">
         <v>46246</v>
       </c>
       <c r="Q976" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="977" spans="1:17" x14ac:dyDescent="0.25">
@@ -54725,11 +54586,11 @@
       <c r="O977" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P977" s="19">
+      <c r="P977" s="15">
         <v>46246</v>
       </c>
       <c r="Q977" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="978" spans="1:17" x14ac:dyDescent="0.25">
@@ -54778,11 +54639,11 @@
       <c r="O978" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P978" s="19">
+      <c r="P978" s="15">
         <v>46246</v>
       </c>
       <c r="Q978" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="979" spans="1:17" x14ac:dyDescent="0.25">
@@ -54831,11 +54692,11 @@
       <c r="O979" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P979" s="19">
+      <c r="P979" s="15">
         <v>46246</v>
       </c>
       <c r="Q979" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="980" spans="1:17" x14ac:dyDescent="0.25">
@@ -54884,11 +54745,11 @@
       <c r="O980" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P980" s="19">
+      <c r="P980" s="15">
         <v>46246</v>
       </c>
       <c r="Q980" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="981" spans="1:17" x14ac:dyDescent="0.25">
@@ -54937,11 +54798,11 @@
       <c r="O981" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P981" s="19">
+      <c r="P981" s="15">
         <v>46246</v>
       </c>
       <c r="Q981" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="982" spans="1:17" x14ac:dyDescent="0.25">
@@ -54990,11 +54851,11 @@
       <c r="O982" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P982" s="19">
+      <c r="P982" s="15">
         <v>46246</v>
       </c>
       <c r="Q982" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="983" spans="1:17" x14ac:dyDescent="0.25">
@@ -55043,11 +54904,11 @@
       <c r="O983" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P983" s="19">
+      <c r="P983" s="15">
         <v>46246</v>
       </c>
       <c r="Q983" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="984" spans="1:17" x14ac:dyDescent="0.25">
@@ -55096,11 +54957,11 @@
       <c r="O984" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P984" s="19">
+      <c r="P984" s="15">
         <v>46246</v>
       </c>
       <c r="Q984" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="985" spans="1:17" x14ac:dyDescent="0.25">
@@ -55149,11 +55010,11 @@
       <c r="O985" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P985" s="19">
+      <c r="P985" s="15">
         <v>46246</v>
       </c>
       <c r="Q985" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="986" spans="1:17" x14ac:dyDescent="0.25">
@@ -55202,11 +55063,11 @@
       <c r="O986" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P986" s="19">
+      <c r="P986" s="15">
         <v>46246</v>
       </c>
       <c r="Q986" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="987" spans="1:17" x14ac:dyDescent="0.25">
@@ -55255,11 +55116,11 @@
       <c r="O987" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P987" s="19">
+      <c r="P987" s="15">
         <v>46246</v>
       </c>
       <c r="Q987" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="988" spans="1:17" x14ac:dyDescent="0.25">
@@ -55308,11 +55169,11 @@
       <c r="O988" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P988" s="19">
+      <c r="P988" s="15">
         <v>46246</v>
       </c>
       <c r="Q988" s="1" t="s">
-        <v>2156</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="989" spans="1:17" x14ac:dyDescent="0.25">
@@ -57385,10 +57246,10 @@
     </row>
     <row r="1033" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1033" s="1" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1033" s="7" t="s">
         <v>2073</v>
-      </c>
-      <c r="B1033" s="7" t="s">
-        <v>2139</v>
       </c>
       <c r="C1033" s="1">
         <v>2026</v>
@@ -57418,7 +57279,7 @@
         <v>245</v>
       </c>
       <c r="L1033" s="1" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="M1033" s="1" t="s">
         <v>528</v>
@@ -57435,10 +57296,10 @@
     </row>
     <row r="1034" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1034" s="1" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B1034" s="7" t="s">
         <v>2074</v>
-      </c>
-      <c r="B1034" s="7" t="s">
-        <v>2140</v>
       </c>
       <c r="C1034" s="1">
         <v>2026</v>
@@ -57456,7 +57317,7 @@
         <v>43832608</v>
       </c>
       <c r="H1034" s="1" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="I1034" s="1" t="s">
         <v>510</v>
@@ -57468,7 +57329,7 @@
         <v>245</v>
       </c>
       <c r="L1034" s="1" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="M1034" s="1" t="s">
         <v>528</v>
@@ -57477,7 +57338,7 @@
         <v>1</v>
       </c>
       <c r="O1034" s="1" t="s">
-        <v>2008</v>
+        <v>529</v>
       </c>
       <c r="P1034" s="2">
         <v>2.1</v>
@@ -57485,10 +57346,10 @@
     </row>
     <row r="1035" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1035" s="1" t="s">
+        <v>2009</v>
+      </c>
+      <c r="B1035" s="7" t="s">
         <v>2075</v>
-      </c>
-      <c r="B1035" s="7" t="s">
-        <v>2141</v>
       </c>
       <c r="C1035" s="1">
         <v>2026</v>
@@ -57518,7 +57379,7 @@
         <v>245</v>
       </c>
       <c r="L1035" s="1" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="M1035" s="1" t="s">
         <v>528</v>
@@ -57527,7 +57388,7 @@
         <v>1</v>
       </c>
       <c r="O1035" s="1" t="s">
-        <v>2009</v>
+        <v>529</v>
       </c>
       <c r="P1035" s="2">
         <v>2.1</v>
@@ -57535,10 +57396,10 @@
     </row>
     <row r="1036" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1036" s="1" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B1036" s="7" t="s">
         <v>2076</v>
-      </c>
-      <c r="B1036" s="7" t="s">
-        <v>2142</v>
       </c>
       <c r="C1036" s="1">
         <v>2026</v>
@@ -57568,7 +57429,7 @@
         <v>245</v>
       </c>
       <c r="L1036" s="1" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="M1036" s="1" t="s">
         <v>528</v>
@@ -57577,7 +57438,7 @@
         <v>1</v>
       </c>
       <c r="O1036" s="1" t="s">
-        <v>2010</v>
+        <v>529</v>
       </c>
       <c r="P1036" s="2">
         <v>2.1</v>
@@ -57585,10 +57446,10 @@
     </row>
     <row r="1037" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1037" s="1" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B1037" s="7" t="s">
         <v>2077</v>
-      </c>
-      <c r="B1037" s="7" t="s">
-        <v>2143</v>
       </c>
       <c r="C1037" s="1">
         <v>2026</v>
@@ -57618,7 +57479,7 @@
         <v>245</v>
       </c>
       <c r="L1037" s="1" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="M1037" s="1" t="s">
         <v>528</v>
@@ -57627,7 +57488,7 @@
         <v>1</v>
       </c>
       <c r="O1037" s="1" t="s">
-        <v>2011</v>
+        <v>529</v>
       </c>
       <c r="P1037" s="2">
         <v>2.1</v>
@@ -57635,10 +57496,10 @@
     </row>
     <row r="1038" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1038" s="1" t="s">
+        <v>2012</v>
+      </c>
+      <c r="B1038" s="7" t="s">
         <v>2078</v>
-      </c>
-      <c r="B1038" s="7" t="s">
-        <v>2144</v>
       </c>
       <c r="C1038" s="1">
         <v>2026</v>
@@ -57668,7 +57529,7 @@
         <v>245</v>
       </c>
       <c r="L1038" s="1" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="M1038" s="1" t="s">
         <v>528</v>
@@ -57677,7 +57538,7 @@
         <v>1</v>
       </c>
       <c r="O1038" s="1" t="s">
-        <v>2012</v>
+        <v>529</v>
       </c>
       <c r="P1038" s="2">
         <v>2.1</v>
@@ -57685,10 +57546,10 @@
     </row>
     <row r="1039" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1039" s="1" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1039" s="7" t="s">
         <v>2079</v>
-      </c>
-      <c r="B1039" s="7" t="s">
-        <v>2145</v>
       </c>
       <c r="C1039" s="1">
         <v>2026</v>
@@ -57718,7 +57579,7 @@
         <v>245</v>
       </c>
       <c r="L1039" s="1" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="M1039" s="1" t="s">
         <v>528</v>
@@ -57727,7 +57588,7 @@
         <v>1</v>
       </c>
       <c r="O1039" s="1" t="s">
-        <v>2013</v>
+        <v>529</v>
       </c>
       <c r="P1039" s="2">
         <v>3.1</v>
@@ -57735,10 +57596,10 @@
     </row>
     <row r="1040" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1040" s="1" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1040" s="7" t="s">
         <v>2080</v>
-      </c>
-      <c r="B1040" s="7" t="s">
-        <v>2146</v>
       </c>
       <c r="C1040" s="1">
         <v>2026</v>
@@ -57768,7 +57629,7 @@
         <v>245</v>
       </c>
       <c r="L1040" s="1" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="M1040" s="1" t="s">
         <v>528</v>
@@ -57777,7 +57638,7 @@
         <v>1</v>
       </c>
       <c r="O1040" s="1" t="s">
-        <v>2014</v>
+        <v>529</v>
       </c>
       <c r="P1040" s="2">
         <v>3.1</v>
@@ -57785,10 +57646,10 @@
     </row>
     <row r="1041" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1041" s="1" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1041" s="7" t="s">
         <v>2081</v>
-      </c>
-      <c r="B1041" s="7" t="s">
-        <v>2147</v>
       </c>
       <c r="C1041" s="1">
         <v>2026</v>
@@ -57818,7 +57679,7 @@
         <v>245</v>
       </c>
       <c r="L1041" s="1" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="M1041" s="1" t="s">
         <v>528</v>
@@ -57827,7 +57688,7 @@
         <v>1</v>
       </c>
       <c r="O1041" s="1" t="s">
-        <v>2015</v>
+        <v>529</v>
       </c>
       <c r="P1041" s="2">
         <v>3.1</v>
@@ -57835,10 +57696,10 @@
     </row>
     <row r="1042" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1042" s="1" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B1042" s="7" t="s">
         <v>2082</v>
-      </c>
-      <c r="B1042" s="7" t="s">
-        <v>2148</v>
       </c>
       <c r="C1042" s="1">
         <v>2026</v>
@@ -57868,7 +57729,7 @@
         <v>245</v>
       </c>
       <c r="L1042" s="1" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="M1042" s="1" t="s">
         <v>528</v>
@@ -57877,7 +57738,7 @@
         <v>1</v>
       </c>
       <c r="O1042" s="1" t="s">
-        <v>2016</v>
+        <v>529</v>
       </c>
       <c r="P1042" s="2">
         <v>3.1</v>
@@ -57885,10 +57746,10 @@
     </row>
     <row r="1043" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1043" s="1" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B1043" s="7" t="s">
         <v>2083</v>
-      </c>
-      <c r="B1043" s="7" t="s">
-        <v>2149</v>
       </c>
       <c r="C1043" s="1">
         <v>2026</v>
@@ -57918,7 +57779,7 @@
         <v>245</v>
       </c>
       <c r="L1043" s="1" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="M1043" s="1" t="s">
         <v>528</v>
@@ -57927,7 +57788,7 @@
         <v>1</v>
       </c>
       <c r="O1043" s="1" t="s">
-        <v>2017</v>
+        <v>529</v>
       </c>
       <c r="P1043" s="2">
         <v>3.1</v>
@@ -57935,10 +57796,10 @@
     </row>
     <row r="1044" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1044" s="1" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B1044" s="7" t="s">
         <v>2084</v>
-      </c>
-      <c r="B1044" s="7" t="s">
-        <v>2150</v>
       </c>
       <c r="C1044" s="1">
         <v>2026</v>
@@ -57968,7 +57829,7 @@
         <v>245</v>
       </c>
       <c r="L1044" s="1" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="M1044" s="1" t="s">
         <v>528</v>
@@ -57977,7 +57838,7 @@
         <v>1</v>
       </c>
       <c r="O1044" s="1" t="s">
-        <v>2018</v>
+        <v>529</v>
       </c>
       <c r="P1044" s="2">
         <v>3.1</v>
@@ -57985,10 +57846,10 @@
     </row>
     <row r="1045" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1045" s="1" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B1045" s="7" t="s">
         <v>2085</v>
-      </c>
-      <c r="B1045" s="7" t="s">
-        <v>2151</v>
       </c>
       <c r="C1045" s="1">
         <v>2026</v>
@@ -58018,7 +57879,7 @@
         <v>247</v>
       </c>
       <c r="L1045" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="M1045" s="1" t="s">
         <v>528</v>
@@ -58027,7 +57888,7 @@
         <v>2</v>
       </c>
       <c r="O1045" s="1" t="s">
-        <v>2019</v>
+        <v>529</v>
       </c>
       <c r="P1045" s="2">
         <v>3.1</v>
@@ -58035,10 +57896,10 @@
     </row>
     <row r="1046" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1046" s="1" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B1046" s="7" t="s">
         <v>2086</v>
-      </c>
-      <c r="B1046" s="7" t="s">
-        <v>2152</v>
       </c>
       <c r="C1046" s="1">
         <v>2026</v>
@@ -58068,7 +57929,7 @@
         <v>247</v>
       </c>
       <c r="L1046" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="M1046" s="1" t="s">
         <v>528</v>
@@ -58077,7 +57938,7 @@
         <v>2</v>
       </c>
       <c r="O1046" s="1" t="s">
-        <v>2020</v>
+        <v>529</v>
       </c>
       <c r="P1046" s="2">
         <v>3.1</v>
@@ -58085,10 +57946,10 @@
     </row>
     <row r="1047" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1047" s="1" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B1047" s="7" t="s">
         <v>2087</v>
-      </c>
-      <c r="B1047" s="7" t="s">
-        <v>2153</v>
       </c>
       <c r="C1047" s="1">
         <v>2026</v>
@@ -58118,7 +57979,7 @@
         <v>247</v>
       </c>
       <c r="L1047" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="M1047" s="1" t="s">
         <v>528</v>
@@ -58127,7 +57988,7 @@
         <v>2</v>
       </c>
       <c r="O1047" s="1" t="s">
-        <v>2021</v>
+        <v>529</v>
       </c>
       <c r="P1047" s="2">
         <v>3.1</v>
@@ -58135,10 +57996,10 @@
     </row>
     <row r="1048" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1048" s="1" t="s">
-        <v>2088</v>
+        <v>2022</v>
       </c>
       <c r="B1048" s="7" t="s">
-        <v>2144</v>
+        <v>2078</v>
       </c>
       <c r="C1048" s="1">
         <v>2026</v>
@@ -58168,7 +58029,7 @@
         <v>247</v>
       </c>
       <c r="L1048" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="M1048" s="1" t="s">
         <v>528</v>
@@ -58177,7 +58038,7 @@
         <v>2</v>
       </c>
       <c r="O1048" s="1" t="s">
-        <v>2022</v>
+        <v>529</v>
       </c>
       <c r="P1048" s="2">
         <v>3.1</v>
@@ -58185,10 +58046,10 @@
     </row>
     <row r="1049" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1049" s="1" t="s">
-        <v>2089</v>
+        <v>2023</v>
       </c>
       <c r="B1049" s="7" t="s">
-        <v>2154</v>
+        <v>2088</v>
       </c>
       <c r="C1049" s="1">
         <v>2026</v>
@@ -58218,7 +58079,7 @@
         <v>247</v>
       </c>
       <c r="L1049" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="M1049" s="1" t="s">
         <v>528</v>
@@ -58227,7 +58088,7 @@
         <v>2</v>
       </c>
       <c r="O1049" s="1" t="s">
-        <v>2023</v>
+        <v>529</v>
       </c>
       <c r="P1049" s="2">
         <v>3.1</v>
@@ -58235,10 +58096,10 @@
     </row>
     <row r="1050" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1050" s="1" t="s">
-        <v>2090</v>
+        <v>2024</v>
       </c>
       <c r="B1050" s="7" t="s">
-        <v>2155</v>
+        <v>2089</v>
       </c>
       <c r="C1050" s="1">
         <v>2026</v>
@@ -58268,7 +58129,7 @@
         <v>247</v>
       </c>
       <c r="L1050" s="1" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="M1050" s="1" t="s">
         <v>528</v>
@@ -58277,7 +58138,7 @@
         <v>2</v>
       </c>
       <c r="O1050" s="1" t="s">
-        <v>2024</v>
+        <v>529</v>
       </c>
       <c r="P1050" s="2">
         <v>3.1</v>
@@ -58285,10 +58146,10 @@
     </row>
     <row r="1051" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1051" s="1" t="s">
-        <v>2091</v>
+        <v>2025</v>
       </c>
       <c r="B1051" s="7" t="s">
-        <v>2145</v>
+        <v>2079</v>
       </c>
       <c r="C1051" s="1">
         <v>2026</v>
@@ -58327,7 +58188,7 @@
         <v>1</v>
       </c>
       <c r="O1051" s="1" t="s">
-        <v>2025</v>
+        <v>529</v>
       </c>
       <c r="P1051" s="2">
         <v>3.2</v>
@@ -58335,10 +58196,10 @@
     </row>
     <row r="1052" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1052" s="1" t="s">
-        <v>2092</v>
+        <v>2026</v>
       </c>
       <c r="B1052" s="7" t="s">
-        <v>2146</v>
+        <v>2080</v>
       </c>
       <c r="C1052" s="1">
         <v>2026</v>
@@ -58377,7 +58238,7 @@
         <v>1</v>
       </c>
       <c r="O1052" s="1" t="s">
-        <v>2026</v>
+        <v>529</v>
       </c>
       <c r="P1052" s="2">
         <v>3.2</v>
@@ -58385,10 +58246,10 @@
     </row>
     <row r="1053" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1053" s="1" t="s">
-        <v>2093</v>
+        <v>2027</v>
       </c>
       <c r="B1053" s="7" t="s">
-        <v>2147</v>
+        <v>2081</v>
       </c>
       <c r="C1053" s="1">
         <v>2026</v>
@@ -58427,7 +58288,7 @@
         <v>1</v>
       </c>
       <c r="O1053" s="1" t="s">
-        <v>2027</v>
+        <v>529</v>
       </c>
       <c r="P1053" s="2">
         <v>3.2</v>
@@ -58435,10 +58296,10 @@
     </row>
     <row r="1054" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1054" s="1" t="s">
-        <v>2094</v>
+        <v>2028</v>
       </c>
       <c r="B1054" s="7" t="s">
-        <v>2148</v>
+        <v>2082</v>
       </c>
       <c r="C1054" s="1">
         <v>2026</v>
@@ -58477,7 +58338,7 @@
         <v>1</v>
       </c>
       <c r="O1054" s="1" t="s">
-        <v>2028</v>
+        <v>529</v>
       </c>
       <c r="P1054" s="2">
         <v>3.2</v>
@@ -58485,10 +58346,10 @@
     </row>
     <row r="1055" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1055" s="1" t="s">
-        <v>2095</v>
+        <v>2029</v>
       </c>
       <c r="B1055" s="7" t="s">
-        <v>2149</v>
+        <v>2083</v>
       </c>
       <c r="C1055" s="1">
         <v>2026</v>
@@ -58527,7 +58388,7 @@
         <v>1</v>
       </c>
       <c r="O1055" s="1" t="s">
-        <v>2029</v>
+        <v>529</v>
       </c>
       <c r="P1055" s="2">
         <v>3.2</v>
@@ -58535,10 +58396,10 @@
     </row>
     <row r="1056" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1056" s="1" t="s">
-        <v>2096</v>
+        <v>2030</v>
       </c>
       <c r="B1056" s="7" t="s">
-        <v>2151</v>
+        <v>2085</v>
       </c>
       <c r="C1056" s="1">
         <v>2026</v>
@@ -58577,7 +58438,7 @@
         <v>1</v>
       </c>
       <c r="O1056" s="1" t="s">
-        <v>2030</v>
+        <v>529</v>
       </c>
       <c r="P1056" s="2">
         <v>3.2</v>
@@ -58585,10 +58446,10 @@
     </row>
     <row r="1057" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1057" s="1" t="s">
-        <v>2097</v>
+        <v>2031</v>
       </c>
       <c r="B1057" s="7" t="s">
-        <v>2144</v>
+        <v>2078</v>
       </c>
       <c r="C1057" s="1">
         <v>2026</v>
@@ -58627,7 +58488,7 @@
         <v>1</v>
       </c>
       <c r="O1057" s="1" t="s">
-        <v>2031</v>
+        <v>529</v>
       </c>
       <c r="P1057" s="2">
         <v>3.2</v>
@@ -58635,10 +58496,10 @@
     </row>
     <row r="1058" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1058" s="1" t="s">
-        <v>2098</v>
+        <v>2032</v>
       </c>
       <c r="B1058" s="7" t="s">
-        <v>2154</v>
+        <v>2088</v>
       </c>
       <c r="C1058" s="1">
         <v>2026</v>
@@ -58677,7 +58538,7 @@
         <v>1</v>
       </c>
       <c r="O1058" s="1" t="s">
-        <v>2032</v>
+        <v>529</v>
       </c>
       <c r="P1058" s="2">
         <v>3.2</v>
@@ -58685,10 +58546,10 @@
     </row>
     <row r="1059" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1059" s="1" t="s">
-        <v>2099</v>
+        <v>2033</v>
       </c>
       <c r="B1059" s="7" t="s">
-        <v>2155</v>
+        <v>2089</v>
       </c>
       <c r="C1059" s="1">
         <v>2026</v>
@@ -58727,7 +58588,7 @@
         <v>1</v>
       </c>
       <c r="O1059" s="1" t="s">
-        <v>2033</v>
+        <v>529</v>
       </c>
       <c r="P1059" s="2">
         <v>3.2</v>
@@ -58735,10 +58596,10 @@
     </row>
     <row r="1060" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1060" s="1" t="s">
-        <v>2100</v>
+        <v>2034</v>
       </c>
       <c r="B1060" s="7" t="s">
-        <v>2139</v>
+        <v>2073</v>
       </c>
       <c r="C1060" s="1">
         <v>2026</v>
@@ -58777,7 +58638,7 @@
         <v>1</v>
       </c>
       <c r="O1060" s="1" t="s">
-        <v>2034</v>
+        <v>529</v>
       </c>
       <c r="P1060" s="2">
         <v>3.2</v>
@@ -58785,10 +58646,10 @@
     </row>
     <row r="1061" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1061" s="1" t="s">
-        <v>2101</v>
+        <v>2035</v>
       </c>
       <c r="B1061" s="7" t="s">
-        <v>2140</v>
+        <v>2074</v>
       </c>
       <c r="C1061" s="1">
         <v>2026</v>
@@ -58827,7 +58688,7 @@
         <v>1</v>
       </c>
       <c r="O1061" s="1" t="s">
-        <v>2035</v>
+        <v>529</v>
       </c>
       <c r="P1061" s="2">
         <v>3.2</v>
@@ -58835,10 +58696,10 @@
     </row>
     <row r="1062" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1062" s="1" t="s">
-        <v>2102</v>
+        <v>2036</v>
       </c>
       <c r="B1062" s="7" t="s">
-        <v>2152</v>
+        <v>2086</v>
       </c>
       <c r="C1062" s="1">
         <v>2026</v>
@@ -58868,7 +58729,7 @@
         <v>246</v>
       </c>
       <c r="L1062" s="1" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="M1062" s="1" t="s">
         <v>528</v>
@@ -58877,7 +58738,7 @@
         <v>2</v>
       </c>
       <c r="O1062" s="1" t="s">
-        <v>2036</v>
+        <v>529</v>
       </c>
       <c r="P1062" s="2">
         <v>3.2</v>
@@ -58885,10 +58746,10 @@
     </row>
     <row r="1063" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1063" s="1" t="s">
-        <v>2103</v>
+        <v>2037</v>
       </c>
       <c r="B1063" s="7" t="s">
-        <v>2142</v>
+        <v>2076</v>
       </c>
       <c r="C1063" s="1">
         <v>2026</v>
@@ -58918,7 +58779,7 @@
         <v>246</v>
       </c>
       <c r="L1063" s="1" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="M1063" s="1" t="s">
         <v>528</v>
@@ -58927,7 +58788,7 @@
         <v>2</v>
       </c>
       <c r="O1063" s="1" t="s">
-        <v>2037</v>
+        <v>529</v>
       </c>
       <c r="P1063" s="2">
         <v>3.2</v>
@@ -58935,10 +58796,10 @@
     </row>
     <row r="1064" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1064" s="1" t="s">
-        <v>2104</v>
+        <v>2038</v>
       </c>
       <c r="B1064" s="7" t="s">
-        <v>2152</v>
+        <v>2086</v>
       </c>
       <c r="C1064" s="1">
         <v>2026</v>
@@ -58968,7 +58829,7 @@
         <v>246</v>
       </c>
       <c r="L1064" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="M1064" s="1" t="s">
         <v>528</v>
@@ -58977,7 +58838,7 @@
         <v>2</v>
       </c>
       <c r="O1064" s="1" t="s">
-        <v>2038</v>
+        <v>529</v>
       </c>
       <c r="P1064" s="2">
         <v>3.2</v>
@@ -58985,10 +58846,10 @@
     </row>
     <row r="1065" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1065" s="1" t="s">
-        <v>2105</v>
+        <v>2039</v>
       </c>
       <c r="B1065" s="7" t="s">
-        <v>2152</v>
+        <v>2086</v>
       </c>
       <c r="C1065" s="1">
         <v>2026</v>
@@ -59018,7 +58879,7 @@
         <v>246</v>
       </c>
       <c r="L1065" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="M1065" s="1" t="s">
         <v>528</v>
@@ -59027,7 +58888,7 @@
         <v>2</v>
       </c>
       <c r="O1065" s="1" t="s">
-        <v>2039</v>
+        <v>529</v>
       </c>
       <c r="P1065" s="2">
         <v>3.2</v>
@@ -59035,10 +58896,10 @@
     </row>
     <row r="1066" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1066" s="1" t="s">
-        <v>2106</v>
+        <v>2040</v>
       </c>
       <c r="B1066" s="7" t="s">
-        <v>2153</v>
+        <v>2087</v>
       </c>
       <c r="C1066" s="1">
         <v>2026</v>
@@ -59068,7 +58929,7 @@
         <v>246</v>
       </c>
       <c r="L1066" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="M1066" s="1" t="s">
         <v>528</v>
@@ -59077,7 +58938,7 @@
         <v>2</v>
       </c>
       <c r="O1066" s="1" t="s">
-        <v>2040</v>
+        <v>529</v>
       </c>
       <c r="P1066" s="2">
         <v>3.2</v>
@@ -59085,10 +58946,10 @@
     </row>
     <row r="1067" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1067" s="1" t="s">
-        <v>2107</v>
+        <v>2041</v>
       </c>
       <c r="B1067" s="7" t="s">
-        <v>2153</v>
+        <v>2087</v>
       </c>
       <c r="C1067" s="1">
         <v>2026</v>
@@ -59118,7 +58979,7 @@
         <v>246</v>
       </c>
       <c r="L1067" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="M1067" s="1" t="s">
         <v>528</v>
@@ -59127,7 +58988,7 @@
         <v>2</v>
       </c>
       <c r="O1067" s="1" t="s">
-        <v>2041</v>
+        <v>529</v>
       </c>
       <c r="P1067" s="2">
         <v>3.2</v>
@@ -59135,10 +58996,10 @@
     </row>
     <row r="1068" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1068" s="1" t="s">
-        <v>2108</v>
+        <v>2042</v>
       </c>
       <c r="B1068" s="7" t="s">
-        <v>2153</v>
+        <v>2087</v>
       </c>
       <c r="C1068" s="1">
         <v>2026</v>
@@ -59168,7 +59029,7 @@
         <v>246</v>
       </c>
       <c r="L1068" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="M1068" s="1" t="s">
         <v>528</v>
@@ -59177,7 +59038,7 @@
         <v>2</v>
       </c>
       <c r="O1068" s="1" t="s">
-        <v>2042</v>
+        <v>529</v>
       </c>
       <c r="P1068" s="2">
         <v>3.2</v>
@@ -59185,10 +59046,10 @@
     </row>
     <row r="1069" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1069" s="1" t="s">
-        <v>2109</v>
+        <v>2043</v>
       </c>
       <c r="B1069" s="7" t="s">
-        <v>2141</v>
+        <v>2075</v>
       </c>
       <c r="C1069" s="1">
         <v>2026</v>
@@ -59218,7 +59079,7 @@
         <v>246</v>
       </c>
       <c r="L1069" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="M1069" s="1" t="s">
         <v>528</v>
@@ -59227,7 +59088,7 @@
         <v>2</v>
       </c>
       <c r="O1069" s="1" t="s">
-        <v>2043</v>
+        <v>529</v>
       </c>
       <c r="P1069" s="2">
         <v>3.2</v>
@@ -59235,10 +59096,10 @@
     </row>
     <row r="1070" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1070" s="1" t="s">
-        <v>2110</v>
+        <v>2044</v>
       </c>
       <c r="B1070" s="7" t="s">
-        <v>2141</v>
+        <v>2075</v>
       </c>
       <c r="C1070" s="1">
         <v>2026</v>
@@ -59268,7 +59129,7 @@
         <v>246</v>
       </c>
       <c r="L1070" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="M1070" s="1" t="s">
         <v>528</v>
@@ -59277,7 +59138,7 @@
         <v>2</v>
       </c>
       <c r="O1070" s="1" t="s">
-        <v>2044</v>
+        <v>529</v>
       </c>
       <c r="P1070" s="2">
         <v>3.2</v>
@@ -59285,10 +59146,10 @@
     </row>
     <row r="1071" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1071" s="1" t="s">
-        <v>2111</v>
+        <v>2045</v>
       </c>
       <c r="B1071" s="7" t="s">
-        <v>2141</v>
+        <v>2075</v>
       </c>
       <c r="C1071" s="1">
         <v>2026</v>
@@ -59318,7 +59179,7 @@
         <v>246</v>
       </c>
       <c r="L1071" s="1" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="M1071" s="1" t="s">
         <v>528</v>
@@ -59327,7 +59188,7 @@
         <v>2</v>
       </c>
       <c r="O1071" s="1" t="s">
-        <v>2045</v>
+        <v>529</v>
       </c>
       <c r="P1071" s="2">
         <v>3.2</v>
@@ -59335,10 +59196,10 @@
     </row>
     <row r="1072" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1072" s="1" t="s">
-        <v>2112</v>
+        <v>2046</v>
       </c>
       <c r="B1072" s="7" t="s">
-        <v>2142</v>
+        <v>2076</v>
       </c>
       <c r="C1072" s="1">
         <v>2026</v>
@@ -59368,7 +59229,7 @@
         <v>246</v>
       </c>
       <c r="L1072" s="1" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="M1072" s="1" t="s">
         <v>528</v>
@@ -59377,7 +59238,7 @@
         <v>2</v>
       </c>
       <c r="O1072" s="1" t="s">
-        <v>2046</v>
+        <v>529</v>
       </c>
       <c r="P1072" s="2">
         <v>3.2</v>
@@ -59385,10 +59246,10 @@
     </row>
     <row r="1073" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1073" s="1" t="s">
-        <v>2113</v>
+        <v>2047</v>
       </c>
       <c r="B1073" s="7" t="s">
-        <v>2154</v>
+        <v>2088</v>
       </c>
       <c r="C1073" s="1">
         <v>2026</v>
@@ -59406,7 +59267,7 @@
         <v>10400802225</v>
       </c>
       <c r="H1073" s="1" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="I1073" s="1" t="s">
         <v>514</v>
@@ -59418,7 +59279,7 @@
         <v>247</v>
       </c>
       <c r="L1073" s="1" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="M1073" s="1" t="s">
         <v>528</v>
@@ -59427,7 +59288,7 @@
         <v>2</v>
       </c>
       <c r="O1073" s="1" t="s">
-        <v>2047</v>
+        <v>529</v>
       </c>
       <c r="P1073" s="2">
         <v>3.3</v>
@@ -59435,10 +59296,10 @@
     </row>
     <row r="1074" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1074" s="1" t="s">
-        <v>2114</v>
+        <v>2048</v>
       </c>
       <c r="B1074" s="7" t="s">
-        <v>2141</v>
+        <v>2075</v>
       </c>
       <c r="C1074" s="1">
         <v>2026</v>
@@ -59468,7 +59329,7 @@
         <v>247</v>
       </c>
       <c r="L1074" s="1" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="M1074" s="1" t="s">
         <v>528</v>
@@ -59477,7 +59338,7 @@
         <v>2</v>
       </c>
       <c r="O1074" s="1" t="s">
-        <v>2048</v>
+        <v>529</v>
       </c>
       <c r="P1074" s="2">
         <v>3.3</v>
@@ -59485,10 +59346,10 @@
     </row>
     <row r="1075" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1075" s="1" t="s">
-        <v>2115</v>
+        <v>2049</v>
       </c>
       <c r="B1075" s="7" t="s">
-        <v>2144</v>
+        <v>2078</v>
       </c>
       <c r="C1075" s="1">
         <v>2026</v>
@@ -59518,7 +59379,7 @@
         <v>247</v>
       </c>
       <c r="L1075" s="1" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="M1075" s="1" t="s">
         <v>528</v>
@@ -59527,7 +59388,7 @@
         <v>2</v>
       </c>
       <c r="O1075" s="1" t="s">
-        <v>2049</v>
+        <v>529</v>
       </c>
       <c r="P1075" s="2">
         <v>3.3</v>
@@ -59535,10 +59396,10 @@
     </row>
     <row r="1076" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1076" s="1" t="s">
-        <v>2116</v>
+        <v>2050</v>
       </c>
       <c r="B1076" s="7" t="s">
-        <v>2140</v>
+        <v>2074</v>
       </c>
       <c r="C1076" s="1">
         <v>2026</v>
@@ -59568,7 +59429,7 @@
         <v>247</v>
       </c>
       <c r="L1076" s="1" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="M1076" s="1" t="s">
         <v>528</v>
@@ -59577,7 +59438,7 @@
         <v>2</v>
       </c>
       <c r="O1076" s="1" t="s">
-        <v>2050</v>
+        <v>529</v>
       </c>
       <c r="P1076" s="2">
         <v>3.3</v>
@@ -59585,10 +59446,10 @@
     </row>
     <row r="1077" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1077" s="1" t="s">
-        <v>2117</v>
+        <v>2051</v>
       </c>
       <c r="B1077" s="7" t="s">
-        <v>2146</v>
+        <v>2080</v>
       </c>
       <c r="C1077" s="1">
         <v>2026</v>
@@ -59618,7 +59479,7 @@
         <v>247</v>
       </c>
       <c r="L1077" s="1" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="M1077" s="1" t="s">
         <v>528</v>
@@ -59627,7 +59488,7 @@
         <v>2</v>
       </c>
       <c r="O1077" s="1" t="s">
-        <v>2051</v>
+        <v>529</v>
       </c>
       <c r="P1077" s="2">
         <v>3.3</v>
@@ -59635,10 +59496,10 @@
     </row>
     <row r="1078" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1078" s="1" t="s">
-        <v>2118</v>
+        <v>2052</v>
       </c>
       <c r="B1078" s="7" t="s">
-        <v>2151</v>
+        <v>2085</v>
       </c>
       <c r="C1078" s="1">
         <v>2026</v>
@@ -59668,7 +59529,7 @@
         <v>247</v>
       </c>
       <c r="L1078" s="1" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="M1078" s="1" t="s">
         <v>528</v>
@@ -59677,7 +59538,7 @@
         <v>2</v>
       </c>
       <c r="O1078" s="1" t="s">
-        <v>2052</v>
+        <v>529</v>
       </c>
       <c r="P1078" s="2">
         <v>3.3</v>
@@ -59685,10 +59546,10 @@
     </row>
     <row r="1079" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1079" s="1" t="s">
-        <v>2119</v>
+        <v>2053</v>
       </c>
       <c r="B1079" s="7" t="s">
-        <v>2152</v>
+        <v>2086</v>
       </c>
       <c r="C1079" s="1">
         <v>2026</v>
@@ -59718,7 +59579,7 @@
         <v>247</v>
       </c>
       <c r="L1079" s="1" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="M1079" s="1" t="s">
         <v>528</v>
@@ -59727,7 +59588,7 @@
         <v>2</v>
       </c>
       <c r="O1079" s="1" t="s">
-        <v>2053</v>
+        <v>529</v>
       </c>
       <c r="P1079" s="2">
         <v>3.3</v>
@@ -59735,10 +59596,10 @@
     </row>
     <row r="1080" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1080" s="1" t="s">
-        <v>2120</v>
+        <v>2054</v>
       </c>
       <c r="B1080" s="7" t="s">
-        <v>2147</v>
+        <v>2081</v>
       </c>
       <c r="C1080" s="1">
         <v>2026</v>
@@ -59768,7 +59629,7 @@
         <v>247</v>
       </c>
       <c r="L1080" s="1" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="M1080" s="1" t="s">
         <v>528</v>
@@ -59777,7 +59638,7 @@
         <v>2</v>
       </c>
       <c r="O1080" s="1" t="s">
-        <v>2054</v>
+        <v>529</v>
       </c>
       <c r="P1080" s="2">
         <v>3.3</v>
@@ -59785,7 +59646,7 @@
     </row>
     <row r="1081" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1081" s="1" t="s">
-        <v>2121</v>
+        <v>2055</v>
       </c>
       <c r="B1081" s="8">
         <v>46267</v>
@@ -59803,13 +59664,13 @@
         <v>822</v>
       </c>
       <c r="G1081" s="1">
-        <v>45431690</v>
+        <v>10454316903</v>
       </c>
       <c r="H1081" s="1" t="s">
-        <v>1980</v>
+        <v>383</v>
       </c>
       <c r="I1081" s="1" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="J1081" s="1" t="s">
         <v>242</v>
@@ -59818,7 +59679,7 @@
         <v>245</v>
       </c>
       <c r="L1081" s="1" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="M1081" s="1" t="s">
         <v>528</v>
@@ -59827,7 +59688,7 @@
         <v>1</v>
       </c>
       <c r="O1081" s="1" t="s">
-        <v>2055</v>
+        <v>529</v>
       </c>
       <c r="P1081" s="2">
         <v>3.4</v>
@@ -59836,10 +59697,10 @@
     </row>
     <row r="1082" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1082" s="1" t="s">
-        <v>2122</v>
+        <v>2056</v>
       </c>
       <c r="B1082" s="7" t="s">
-        <v>2147</v>
+        <v>2081</v>
       </c>
       <c r="C1082" s="1">
         <v>2026</v>
@@ -59869,7 +59730,7 @@
         <v>245</v>
       </c>
       <c r="L1082" s="1" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="M1082" s="1" t="s">
         <v>528</v>
@@ -59878,66 +59739,66 @@
         <v>1</v>
       </c>
       <c r="O1082" s="1" t="s">
-        <v>2056</v>
+        <v>529</v>
       </c>
       <c r="P1082" s="2">
         <v>3.4</v>
       </c>
     </row>
-    <row r="1083" spans="1:18" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1083" s="15" t="s">
-        <v>2123</v>
-      </c>
-      <c r="B1083" s="18">
+    <row r="1083" spans="1:18" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1083" s="16" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B1083" s="17">
         <v>46269</v>
       </c>
-      <c r="C1083" s="15">
-        <v>2026</v>
-      </c>
-      <c r="D1083" s="15">
+      <c r="C1083" s="16">
+        <v>2026</v>
+      </c>
+      <c r="D1083" s="16">
         <v>9</v>
       </c>
-      <c r="E1083" s="15" t="s">
+      <c r="E1083" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="F1083" s="15" t="s">
+      <c r="F1083" s="16" t="s">
         <v>822</v>
       </c>
-      <c r="G1083" s="15">
+      <c r="G1083" s="16">
         <v>10476142941</v>
       </c>
-      <c r="H1083" s="15" t="s">
+      <c r="H1083" s="16" t="s">
         <v>382</v>
       </c>
-      <c r="I1083" s="15" t="s">
+      <c r="I1083" s="16" t="s">
         <v>514</v>
       </c>
-      <c r="J1083" s="15" t="s">
+      <c r="J1083" s="16" t="s">
         <v>242</v>
       </c>
-      <c r="K1083" s="15" t="s">
+      <c r="K1083" s="16" t="s">
         <v>245</v>
       </c>
-      <c r="L1083" s="15" t="s">
-        <v>1998</v>
-      </c>
-      <c r="M1083" s="15" t="s">
-        <v>528</v>
-      </c>
-      <c r="N1083" s="15">
-        <v>1</v>
-      </c>
-      <c r="O1083" s="15" t="s">
-        <v>2057</v>
-      </c>
-      <c r="P1083" s="16">
+      <c r="L1083" s="16" t="s">
+        <v>1997</v>
+      </c>
+      <c r="M1083" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1083" s="16">
+        <v>1</v>
+      </c>
+      <c r="O1083" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="P1083" s="18">
         <v>3.4</v>
       </c>
-      <c r="R1083" s="18"/>
+      <c r="R1083" s="17"/>
     </row>
     <row r="1084" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1084" s="1" t="s">
-        <v>2124</v>
+        <v>2058</v>
       </c>
       <c r="B1084" s="8">
         <v>46272</v>
@@ -59970,7 +59831,7 @@
         <v>245</v>
       </c>
       <c r="L1084" s="1" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="M1084" s="1" t="s">
         <v>528</v>
@@ -59979,7 +59840,7 @@
         <v>1</v>
       </c>
       <c r="O1084" s="1" t="s">
-        <v>2058</v>
+        <v>529</v>
       </c>
       <c r="P1084" s="2">
         <v>3.4</v>
@@ -59988,10 +59849,10 @@
     </row>
     <row r="1085" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1085" s="1" t="s">
-        <v>2125</v>
+        <v>2059</v>
       </c>
       <c r="B1085" s="7" t="s">
-        <v>2151</v>
+        <v>2085</v>
       </c>
       <c r="C1085" s="1">
         <v>2026</v>
@@ -60021,7 +59882,7 @@
         <v>250</v>
       </c>
       <c r="L1085" s="1" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="M1085" s="1" t="s">
         <v>528</v>
@@ -60030,7 +59891,7 @@
         <v>12</v>
       </c>
       <c r="O1085" s="1" t="s">
-        <v>2059</v>
+        <v>529</v>
       </c>
       <c r="P1085" s="2">
         <v>3.7</v>
@@ -60038,10 +59899,10 @@
     </row>
     <row r="1086" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1086" s="1" t="s">
-        <v>2126</v>
+        <v>2060</v>
       </c>
       <c r="B1086" s="7" t="s">
-        <v>2151</v>
+        <v>2085</v>
       </c>
       <c r="C1086" s="1">
         <v>2026</v>
@@ -60071,7 +59932,7 @@
         <v>250</v>
       </c>
       <c r="L1086" s="1" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="M1086" s="1" t="s">
         <v>528</v>
@@ -60080,7 +59941,7 @@
         <v>25</v>
       </c>
       <c r="O1086" s="1" t="s">
-        <v>2060</v>
+        <v>529</v>
       </c>
       <c r="P1086" s="2">
         <v>3.7</v>
@@ -60088,10 +59949,10 @@
     </row>
     <row r="1087" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1087" s="1" t="s">
-        <v>2127</v>
+        <v>2061</v>
       </c>
       <c r="B1087" s="7" t="s">
-        <v>2147</v>
+        <v>2081</v>
       </c>
       <c r="C1087" s="1">
         <v>2026</v>
@@ -60121,7 +59982,7 @@
         <v>245</v>
       </c>
       <c r="L1087" s="1" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="M1087" s="1" t="s">
         <v>528</v>
@@ -60130,7 +59991,7 @@
         <v>1</v>
       </c>
       <c r="O1087" s="1" t="s">
-        <v>2061</v>
+        <v>529</v>
       </c>
       <c r="P1087" s="2">
         <v>4.0999999999999996</v>
@@ -60138,10 +59999,10 @@
     </row>
     <row r="1088" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1088" s="1" t="s">
-        <v>2128</v>
+        <v>2062</v>
       </c>
       <c r="B1088" s="7" t="s">
-        <v>2153</v>
+        <v>2087</v>
       </c>
       <c r="C1088" s="1">
         <v>2026</v>
@@ -60171,7 +60032,7 @@
         <v>245</v>
       </c>
       <c r="L1088" s="1" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="M1088" s="1" t="s">
         <v>528</v>
@@ -60180,7 +60041,7 @@
         <v>1</v>
       </c>
       <c r="O1088" s="1" t="s">
-        <v>2062</v>
+        <v>529</v>
       </c>
       <c r="P1088" s="2">
         <v>4.0999999999999996</v>
@@ -60188,10 +60049,10 @@
     </row>
     <row r="1089" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1089" s="1" t="s">
-        <v>2129</v>
+        <v>2063</v>
       </c>
       <c r="B1089" s="7" t="s">
-        <v>2139</v>
+        <v>2073</v>
       </c>
       <c r="C1089" s="1">
         <v>2026</v>
@@ -60221,7 +60082,7 @@
         <v>245</v>
       </c>
       <c r="L1089" s="1" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="M1089" s="1" t="s">
         <v>528</v>
@@ -60230,7 +60091,7 @@
         <v>1</v>
       </c>
       <c r="O1089" s="1" t="s">
-        <v>2063</v>
+        <v>529</v>
       </c>
       <c r="P1089" s="2">
         <v>4.0999999999999996</v>
@@ -60238,10 +60099,10 @@
     </row>
     <row r="1090" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1090" s="1" t="s">
-        <v>2130</v>
+        <v>2064</v>
       </c>
       <c r="B1090" s="7" t="s">
-        <v>2142</v>
+        <v>2076</v>
       </c>
       <c r="C1090" s="1">
         <v>2026</v>
@@ -60271,7 +60132,7 @@
         <v>245</v>
       </c>
       <c r="L1090" s="1" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="M1090" s="1" t="s">
         <v>528</v>
@@ -60280,7 +60141,7 @@
         <v>1</v>
       </c>
       <c r="O1090" s="1" t="s">
-        <v>2064</v>
+        <v>529</v>
       </c>
       <c r="P1090" s="2">
         <v>4.2</v>
@@ -60288,10 +60149,10 @@
     </row>
     <row r="1091" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1091" s="1" t="s">
-        <v>2131</v>
+        <v>2065</v>
       </c>
       <c r="B1091" s="7" t="s">
-        <v>2142</v>
+        <v>2076</v>
       </c>
       <c r="C1091" s="1">
         <v>2026</v>
@@ -60321,7 +60182,7 @@
         <v>245</v>
       </c>
       <c r="L1091" s="1" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="M1091" s="1" t="s">
         <v>528</v>
@@ -60330,7 +60191,7 @@
         <v>1</v>
       </c>
       <c r="O1091" s="1" t="s">
-        <v>2065</v>
+        <v>529</v>
       </c>
       <c r="P1091" s="2">
         <v>4.2</v>
@@ -60338,10 +60199,10 @@
     </row>
     <row r="1092" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1092" s="1" t="s">
-        <v>2132</v>
+        <v>2066</v>
       </c>
       <c r="B1092" s="7" t="s">
-        <v>2151</v>
+        <v>2085</v>
       </c>
       <c r="C1092" s="1">
         <v>2026</v>
@@ -60371,7 +60232,7 @@
         <v>245</v>
       </c>
       <c r="L1092" s="1" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="M1092" s="1" t="s">
         <v>528</v>
@@ -60380,7 +60241,7 @@
         <v>1</v>
       </c>
       <c r="O1092" s="1" t="s">
-        <v>2066</v>
+        <v>529</v>
       </c>
       <c r="P1092" s="2">
         <v>4.2</v>
@@ -60388,10 +60249,10 @@
     </row>
     <row r="1093" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1093" s="1" t="s">
-        <v>2133</v>
+        <v>2067</v>
       </c>
       <c r="B1093" s="7" t="s">
-        <v>2151</v>
+        <v>2085</v>
       </c>
       <c r="C1093" s="1">
         <v>2026</v>
@@ -60421,7 +60282,7 @@
         <v>245</v>
       </c>
       <c r="L1093" s="1" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="M1093" s="1" t="s">
         <v>528</v>
@@ -60430,7 +60291,7 @@
         <v>1</v>
       </c>
       <c r="O1093" s="1" t="s">
-        <v>2067</v>
+        <v>529</v>
       </c>
       <c r="P1093" s="2">
         <v>4.3</v>
@@ -60438,10 +60299,10 @@
     </row>
     <row r="1094" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1094" s="1" t="s">
-        <v>2134</v>
+        <v>2068</v>
       </c>
       <c r="B1094" s="7" t="s">
-        <v>2152</v>
+        <v>2086</v>
       </c>
       <c r="C1094" s="1">
         <v>2026</v>
@@ -60471,7 +60332,7 @@
         <v>245</v>
       </c>
       <c r="L1094" s="1" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="M1094" s="1" t="s">
         <v>528</v>
@@ -60480,7 +60341,7 @@
         <v>1</v>
       </c>
       <c r="O1094" s="1" t="s">
-        <v>2068</v>
+        <v>529</v>
       </c>
       <c r="P1094" s="2">
         <v>4.3</v>
@@ -60488,10 +60349,10 @@
     </row>
     <row r="1095" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1095" s="1" t="s">
-        <v>2135</v>
+        <v>2069</v>
       </c>
       <c r="B1095" s="7" t="s">
-        <v>2153</v>
+        <v>2087</v>
       </c>
       <c r="C1095" s="1">
         <v>2026</v>
@@ -60521,7 +60382,7 @@
         <v>245</v>
       </c>
       <c r="L1095" s="1" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="M1095" s="1" t="s">
         <v>528</v>
@@ -60530,7 +60391,7 @@
         <v>1</v>
       </c>
       <c r="O1095" s="1" t="s">
-        <v>2069</v>
+        <v>529</v>
       </c>
       <c r="P1095" s="2">
         <v>4.3</v>
@@ -60538,10 +60399,10 @@
     </row>
     <row r="1096" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1096" s="1" t="s">
-        <v>2136</v>
+        <v>2070</v>
       </c>
       <c r="B1096" s="7" t="s">
-        <v>2139</v>
+        <v>2073</v>
       </c>
       <c r="C1096" s="1">
         <v>2026</v>
@@ -60571,7 +60432,7 @@
         <v>248</v>
       </c>
       <c r="L1096" s="1" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="M1096" s="1" t="s">
         <v>528</v>
@@ -60580,7 +60441,7 @@
         <v>1</v>
       </c>
       <c r="O1096" s="1" t="s">
-        <v>2070</v>
+        <v>529</v>
       </c>
       <c r="P1096" s="2">
         <v>4.3</v>
@@ -60588,10 +60449,10 @@
     </row>
     <row r="1097" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1097" s="1" t="s">
-        <v>2137</v>
+        <v>2071</v>
       </c>
       <c r="B1097" s="7" t="s">
-        <v>2140</v>
+        <v>2074</v>
       </c>
       <c r="C1097" s="1">
         <v>2026</v>
@@ -60621,7 +60482,7 @@
         <v>248</v>
       </c>
       <c r="L1097" s="1" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="M1097" s="1" t="s">
         <v>528</v>
@@ -60630,7 +60491,7 @@
         <v>1</v>
       </c>
       <c r="O1097" s="1" t="s">
-        <v>2071</v>
+        <v>529</v>
       </c>
       <c r="P1097" s="2">
         <v>4.3</v>
@@ -60638,10 +60499,10 @@
     </row>
     <row r="1098" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1098" s="1" t="s">
-        <v>2138</v>
+        <v>2072</v>
       </c>
       <c r="B1098" s="7" t="s">
-        <v>2141</v>
+        <v>2075</v>
       </c>
       <c r="C1098" s="1">
         <v>2026</v>
@@ -60671,7 +60532,7 @@
         <v>248</v>
       </c>
       <c r="L1098" s="1" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="M1098" s="1" t="s">
         <v>528</v>
@@ -60680,10 +60541,809 @@
         <v>1</v>
       </c>
       <c r="O1098" s="1" t="s">
-        <v>2072</v>
+        <v>529</v>
       </c>
       <c r="P1098" s="2">
         <v>4.3</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1099" s="1" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B1099" s="7" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C1099" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1099" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1099" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1099" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1099" s="20">
+        <v>73321680</v>
+      </c>
+      <c r="H1099" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="I1099" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1099" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1099" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1099" s="1" t="s">
+        <v>2093</v>
+      </c>
+      <c r="M1099" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1099" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1099" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1100" s="1" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B1100" s="7" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C1100" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1100" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1100" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1100" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1100" s="20">
+        <v>72495328</v>
+      </c>
+      <c r="H1100" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="I1100" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1100" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1100" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1100" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1100" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1100" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1100" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1101" s="1" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B1101" s="7" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C1101" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1101" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1101" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1101" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1101" s="20">
+        <v>75237035</v>
+      </c>
+      <c r="H1101" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="I1101" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1101" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1101" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1101" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1101" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1101" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1101" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1102" s="1" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B1102" s="7" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1102" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1102" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1102" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1102" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1102" s="20">
+        <v>71727977</v>
+      </c>
+      <c r="H1102" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="I1102" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1102" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1102" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1102" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1102" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1102" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1102" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1103" s="1" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B1103" s="7" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1103" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1103" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1103" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1103" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1103" s="20">
+        <v>76403635</v>
+      </c>
+      <c r="H1103" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="I1103" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1103" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1103" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1103" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1103" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1103" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1103" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1104" s="1" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B1104" s="7" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1104" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1104" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1104" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1104" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1104" s="20">
+        <v>70117107</v>
+      </c>
+      <c r="H1104" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="I1104" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1104" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1104" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1104" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1104" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1104" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1104" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1105" s="1" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B1105" s="7" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1105" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1105" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1105" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1105" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1105" s="20">
+        <v>60171003</v>
+      </c>
+      <c r="H1105" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="I1105" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1105" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1105" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1105" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1105" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1105" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1105" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1106" s="1" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B1106" s="7" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1106" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1106" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1106" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1106" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1106" s="20">
+        <v>41005322</v>
+      </c>
+      <c r="H1106" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="I1106" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1106" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1106" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1106" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1106" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1106" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1106" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1107" s="1" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B1107" s="7" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1107" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1107" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1107" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1107" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1107" s="20">
+        <v>71505538</v>
+      </c>
+      <c r="H1107" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="I1107" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1107" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1107" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1107" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1107" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1107" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1107" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1108" s="1" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B1108" s="7" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C1108" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1108" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1108" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1108" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1108" s="20">
+        <v>61094381</v>
+      </c>
+      <c r="H1108" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="I1108" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1108" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1108" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1108" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1108" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1108" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1108" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1109" s="1" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B1109" s="7" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C1109" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1109" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1109" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1109" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1109" s="20">
+        <v>60566010</v>
+      </c>
+      <c r="H1109" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="I1109" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1109" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1109" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1109" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1109" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1109" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1109" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1110" s="1" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B1110" s="7" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C1110" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1110" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1110" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1110" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1110" s="20">
+        <v>72471575</v>
+      </c>
+      <c r="H1110" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="I1110" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1110" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1110" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1110" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1110" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1110" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1110" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1111" s="1" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B1111" s="7" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C1111" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1111" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1111" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1111" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1111" s="20">
+        <v>71873373</v>
+      </c>
+      <c r="H1111" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="I1111" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1111" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1111" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1111" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1111" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1111" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1111" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1112" s="1" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1112" s="7" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C1112" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1112" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1112" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1112" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1112" s="20">
+        <v>76747062</v>
+      </c>
+      <c r="H1112" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="I1112" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1112" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1112" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1112" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1112" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1112" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1112" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1113" s="1" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B1113" s="7" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C1113" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1113" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1113" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1113" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1113" s="20">
+        <v>72076653</v>
+      </c>
+      <c r="H1113" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="I1113" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1113" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1113" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1113" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1113" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1113" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1113" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1114" s="1" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B1114" s="7" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1114" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1114" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1114" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1114" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1114" s="20">
+        <v>70117125</v>
+      </c>
+      <c r="H1114" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="I1114" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1114" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1114" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1114" s="1" t="s">
+        <v>2095</v>
+      </c>
+      <c r="M1114" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1114" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1114" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1115" s="1" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B1115" s="7" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1115" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1115" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1115" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1115" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1115" s="20">
+        <v>71851516</v>
+      </c>
+      <c r="H1115" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="I1115" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J1115" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1115" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1115" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1115" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1115" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1115" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB504F50-CAB1-47DC-88BE-0181A00A70F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFCD4EA-63FE-4DEB-97B2-F7D2BBBA4115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12285" uniqueCount="2113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13485" uniqueCount="2287">
   <si>
     <t>ID_ACTIVIDAD</t>
   </si>
@@ -6473,6 +6473,528 @@
   </si>
   <si>
     <t>C001217</t>
+  </si>
+  <si>
+    <t>117P-Asistencia técnica específica de economía circular en la cadena textil camélidos</t>
+  </si>
+  <si>
+    <t>117P-Asistencia técnica específica de economía circular en la cadena textil camélidos - Teñido natural amarillo</t>
+  </si>
+  <si>
+    <t>117P-Asistencia técnica específica de economía circular en la cadena textil camélidos - Teñido natural tonalidad amarillo</t>
+  </si>
+  <si>
+    <t>117P-Asistencia técnica específica de economía circular en la cadena textil camélidos - Teñido natural tono amarillo</t>
+  </si>
+  <si>
+    <t>117P-Asistencia técnica específica de economía circular en la cadena textil camélidos - Teñido sintetico Azul</t>
+  </si>
+  <si>
+    <t>117P-Asistencia técnica específica de economía circular en la cadena textil camélidos - Teñido sintético azul</t>
+  </si>
+  <si>
+    <t>117P-Asistencia técnica específica de economía circular en la cadena textil camélidos - Teñido sintético tonalidad azul</t>
+  </si>
+  <si>
+    <t>117P-Asistencia técnica específica de economía circular en la cadena textil camélidos - Teñido sintético tono azul</t>
+  </si>
+  <si>
+    <t>C001218</t>
+  </si>
+  <si>
+    <t>C001219</t>
+  </si>
+  <si>
+    <t>C001220</t>
+  </si>
+  <si>
+    <t>C001221</t>
+  </si>
+  <si>
+    <t>C001222</t>
+  </si>
+  <si>
+    <t>C001223</t>
+  </si>
+  <si>
+    <t>C001224</t>
+  </si>
+  <si>
+    <t>C001225</t>
+  </si>
+  <si>
+    <t>C001226</t>
+  </si>
+  <si>
+    <t>C001227</t>
+  </si>
+  <si>
+    <t>C001228</t>
+  </si>
+  <si>
+    <t>C001229</t>
+  </si>
+  <si>
+    <t>C001230</t>
+  </si>
+  <si>
+    <t>C001231</t>
+  </si>
+  <si>
+    <t>C001232</t>
+  </si>
+  <si>
+    <t>C001233</t>
+  </si>
+  <si>
+    <t>30/09/2026</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>24/09/2026</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>CURSO DE CAPACITACIÓN ESPECIALIZADA EN ECONOMIA CIRCULAR EN TEÑIDO TEXTIL CON LA TECNICA MULTICOLOR</t>
+  </si>
+  <si>
+    <t>Teñido policromatico de fibras textiles mediante aplicación de vapor para la reducción del consumo de agua y la optimización de recursos</t>
+  </si>
+  <si>
+    <t>C001234</t>
+  </si>
+  <si>
+    <t>C001235</t>
+  </si>
+  <si>
+    <t>C001236</t>
+  </si>
+  <si>
+    <t>C001237</t>
+  </si>
+  <si>
+    <t>C001238</t>
+  </si>
+  <si>
+    <t>C001239</t>
+  </si>
+  <si>
+    <t>C001240</t>
+  </si>
+  <si>
+    <t>C001241</t>
+  </si>
+  <si>
+    <t>C001242</t>
+  </si>
+  <si>
+    <t>C001243</t>
+  </si>
+  <si>
+    <t>C001244</t>
+  </si>
+  <si>
+    <t>C001245</t>
+  </si>
+  <si>
+    <t>C001246</t>
+  </si>
+  <si>
+    <t>C001247</t>
+  </si>
+  <si>
+    <t>C001248</t>
+  </si>
+  <si>
+    <t>C001249</t>
+  </si>
+  <si>
+    <t>C001250</t>
+  </si>
+  <si>
+    <t>C001251</t>
+  </si>
+  <si>
+    <t>C001252</t>
+  </si>
+  <si>
+    <t>C001253</t>
+  </si>
+  <si>
+    <t>C001254</t>
+  </si>
+  <si>
+    <t>C001255</t>
+  </si>
+  <si>
+    <t>C001256</t>
+  </si>
+  <si>
+    <t>C001257</t>
+  </si>
+  <si>
+    <t>C001258</t>
+  </si>
+  <si>
+    <t>C001259</t>
+  </si>
+  <si>
+    <t>C001260</t>
+  </si>
+  <si>
+    <t>C001261</t>
+  </si>
+  <si>
+    <t>C001262</t>
+  </si>
+  <si>
+    <t>C001263</t>
+  </si>
+  <si>
+    <t>LEANDRO ANCCA DORA</t>
+  </si>
+  <si>
+    <t>VALLEJO MAINA FELIPA ELSA</t>
+  </si>
+  <si>
+    <t>CHILO OLLACHICA GLORIA ISABEL</t>
+  </si>
+  <si>
+    <t>MARCELINA OLLACHICA ALVAREZ</t>
+  </si>
+  <si>
+    <t>ITUCAYASI CARLOS LUZ MARINA</t>
+  </si>
+  <si>
+    <t>ITUCAYASI CARLOS MONICA SOLEDAD</t>
+  </si>
+  <si>
+    <t>OLLACHICA ALVAREZ MARCELINA</t>
+  </si>
+  <si>
+    <t>CAPACITACIÓN ESPECIALIZADA EN ECONOMÍA CIRCULAR EN PROCESOS DE TEÑIDO TEXTIL</t>
+  </si>
+  <si>
+    <t>C001264</t>
+  </si>
+  <si>
+    <t>C001265</t>
+  </si>
+  <si>
+    <t>C001266</t>
+  </si>
+  <si>
+    <t>C001267</t>
+  </si>
+  <si>
+    <t>C001268</t>
+  </si>
+  <si>
+    <t>C001269</t>
+  </si>
+  <si>
+    <t>C001270</t>
+  </si>
+  <si>
+    <t>C001271</t>
+  </si>
+  <si>
+    <t>C001272</t>
+  </si>
+  <si>
+    <t>C001273</t>
+  </si>
+  <si>
+    <t>C001274</t>
+  </si>
+  <si>
+    <t>C001275</t>
+  </si>
+  <si>
+    <t>C001276</t>
+  </si>
+  <si>
+    <t>C001277</t>
+  </si>
+  <si>
+    <t>C001278</t>
+  </si>
+  <si>
+    <t>C001279</t>
+  </si>
+  <si>
+    <t>C001280</t>
+  </si>
+  <si>
+    <t>C001281</t>
+  </si>
+  <si>
+    <t>C001282</t>
+  </si>
+  <si>
+    <t>CAPACITACION ESPECIALIZADA EN PRODUCCION SOSTENIBLE Y ECONOMIA CIRCULAR PARA LA EXPORTACION - SAN SEBASTIÁN</t>
+  </si>
+  <si>
+    <t>C001283</t>
+  </si>
+  <si>
+    <t>C001284</t>
+  </si>
+  <si>
+    <t>C001285</t>
+  </si>
+  <si>
+    <t>C001286</t>
+  </si>
+  <si>
+    <t>C001287</t>
+  </si>
+  <si>
+    <t>C001288</t>
+  </si>
+  <si>
+    <t>C001289</t>
+  </si>
+  <si>
+    <t>C001290</t>
+  </si>
+  <si>
+    <t>C001291</t>
+  </si>
+  <si>
+    <t>C001292</t>
+  </si>
+  <si>
+    <t>C001293</t>
+  </si>
+  <si>
+    <t>C001294</t>
+  </si>
+  <si>
+    <t>C001295</t>
+  </si>
+  <si>
+    <t>C001296</t>
+  </si>
+  <si>
+    <t>C001297</t>
+  </si>
+  <si>
+    <t>C001298</t>
+  </si>
+  <si>
+    <t>C001299</t>
+  </si>
+  <si>
+    <t>C001300</t>
+  </si>
+  <si>
+    <t>C001301</t>
+  </si>
+  <si>
+    <t>C001302</t>
+  </si>
+  <si>
+    <t>C001303</t>
+  </si>
+  <si>
+    <t>C001304</t>
+  </si>
+  <si>
+    <t>C001305</t>
+  </si>
+  <si>
+    <t>C001306</t>
+  </si>
+  <si>
+    <t>C001307</t>
+  </si>
+  <si>
+    <t>C001308</t>
+  </si>
+  <si>
+    <t>C001309</t>
+  </si>
+  <si>
+    <t>C001310</t>
+  </si>
+  <si>
+    <t>C001311</t>
+  </si>
+  <si>
+    <t>C001312</t>
+  </si>
+  <si>
+    <t>HUACHO COLQUE DANTE</t>
+  </si>
+  <si>
+    <t>HUAMAN CASTILLA MAXIMILIANA</t>
+  </si>
+  <si>
+    <t>SALGUERO HUARSAYA EUSEBIO MARCOS</t>
+  </si>
+  <si>
+    <t>QUISPE ACUÑA OSCAR</t>
+  </si>
+  <si>
+    <t>AGUILAR SUYO ZENAIDA</t>
+  </si>
+  <si>
+    <t>PAUCAR FLOREZ GREGORIA</t>
+  </si>
+  <si>
+    <t>VARGAS MONTESINOS JOAQUINA</t>
+  </si>
+  <si>
+    <t>MAMANI YANA RAUL</t>
+  </si>
+  <si>
+    <t>VELARDE BRUNA VDA. DE LAMPA VICTORIA RUPERTA</t>
+  </si>
+  <si>
+    <t>HUAMANTTUPA LOZANO GRISELDA</t>
+  </si>
+  <si>
+    <t>CAJCHAYA MAMANI SONIA VICTORIA</t>
+  </si>
+  <si>
+    <t>LEVITA CALLAÑAUPA DE LLANCAY HONORATA</t>
+  </si>
+  <si>
+    <t>CONDORI APAZA YANET</t>
+  </si>
+  <si>
+    <t>ALLER MOJONERO WILBERT</t>
+  </si>
+  <si>
+    <t>COILA YANA EDUARDO</t>
+  </si>
+  <si>
+    <t>TTITO QUISPE LUCIO</t>
+  </si>
+  <si>
+    <t>FLORES BACILIO ROSA MARGOTH</t>
+  </si>
+  <si>
+    <t>QUIROZ HERNANDEZ JULIA</t>
+  </si>
+  <si>
+    <t>ROMAN MOLERO CRISTOBAL</t>
+  </si>
+  <si>
+    <t>QUIÑONES JALISTO WILBERT</t>
+  </si>
+  <si>
+    <t>TUNQUE CHOQUE ZENAIDA</t>
+  </si>
+  <si>
+    <t>CCANA CCOLQUE RUTH ISABEL</t>
+  </si>
+  <si>
+    <t>PAUCAR VELARDE FELICITAS SILVIA</t>
+  </si>
+  <si>
+    <t>CONDORI HUAMAN ROSMERY</t>
+  </si>
+  <si>
+    <t>MEJIA MACHACA EPIFANIA</t>
+  </si>
+  <si>
+    <t>CONDORI ILAHUALA ANA ESTHER</t>
+  </si>
+  <si>
+    <t>CONDORI RAMOS CATALINA</t>
+  </si>
+  <si>
+    <t>HUAYLLA VILLEGAS MARGARITA</t>
+  </si>
+  <si>
+    <t>CAPACITACIÓN ESPECIALIZADA EN TECNOLOGÍAS DIGITALES APLICADAS A LA ECONOMÍA CIRCULAR PARA LA TRANSFORMACIÓN PRODUCTIVA</t>
+  </si>
+  <si>
+    <t>C001313</t>
+  </si>
+  <si>
+    <t>C001314</t>
+  </si>
+  <si>
+    <t>C001315</t>
+  </si>
+  <si>
+    <t>C001316</t>
+  </si>
+  <si>
+    <t>C001317</t>
+  </si>
+  <si>
+    <t>C001318</t>
+  </si>
+  <si>
+    <t>C001319</t>
+  </si>
+  <si>
+    <t>C001320</t>
+  </si>
+  <si>
+    <t>C001321</t>
+  </si>
+  <si>
+    <t>C001322</t>
+  </si>
+  <si>
+    <t>C001323</t>
+  </si>
+  <si>
+    <t>C001324</t>
+  </si>
+  <si>
+    <t>C001325</t>
+  </si>
+  <si>
+    <t>C001326</t>
+  </si>
+  <si>
+    <t>C001327</t>
+  </si>
+  <si>
+    <t>C001328</t>
+  </si>
+  <si>
+    <t>C001329</t>
+  </si>
+  <si>
+    <t>C001330</t>
+  </si>
+  <si>
+    <t>C001331</t>
+  </si>
+  <si>
+    <t>C001332</t>
+  </si>
+  <si>
+    <t>C001333</t>
+  </si>
+  <si>
+    <t>C001334</t>
+  </si>
+  <si>
+    <t>C001335</t>
+  </si>
+  <si>
+    <t>C001336</t>
+  </si>
+  <si>
+    <t>C001337</t>
+  </si>
+  <si>
+    <t>VARGAS MAMANI FLORILUZ DEL CARMEN</t>
   </si>
 </sst>
 </file>
@@ -6982,7 +7504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D04F3C6-8190-4D94-9613-CDA0600594BA}">
-  <dimension ref="A1:R1115"/>
+  <dimension ref="A1:R1235"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
@@ -61346,6 +61868,5286 @@
         <v>50</v>
       </c>
     </row>
+    <row r="1116" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1116" s="1" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B1116" s="7" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C1116" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1116" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1116" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1116" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1116" s="20">
+        <v>10462583996</v>
+      </c>
+      <c r="H1116" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="J1116" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1116" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="L1116" s="1" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M1116" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1116" s="1">
+        <v>15</v>
+      </c>
+      <c r="O1116" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1117" s="1" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B1117" s="7" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C1117" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1117" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1117" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1117" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1117" s="20">
+        <v>75771143</v>
+      </c>
+      <c r="H1117" s="1" t="s">
+        <v>1524</v>
+      </c>
+      <c r="J1117" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1117" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1117" s="1" t="s">
+        <v>2113</v>
+      </c>
+      <c r="M1117" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1117" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1117" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1118" s="1" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B1118" s="7" t="s">
+        <v>2082</v>
+      </c>
+      <c r="C1118" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1118" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1118" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1118" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1118" s="20">
+        <v>45146935</v>
+      </c>
+      <c r="H1118" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="J1118" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1118" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1118" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="M1118" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1118" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1118" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1119" s="1" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B1119" s="7" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1119" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1119" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1119" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1119" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1119" s="20">
+        <v>47188247</v>
+      </c>
+      <c r="H1119" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="J1119" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1119" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1119" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="M1119" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1119" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1119" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1120" s="1" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B1120" s="7" t="s">
+        <v>2078</v>
+      </c>
+      <c r="C1120" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1120" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1120" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1120" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1120" s="20">
+        <v>45652745</v>
+      </c>
+      <c r="H1120" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="J1120" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1120" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1120" s="1" t="s">
+        <v>2114</v>
+      </c>
+      <c r="M1120" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1120" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1120" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1121" s="1" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B1121" s="7" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C1121" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1121" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1121" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1121" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1121" s="20">
+        <v>46756737</v>
+      </c>
+      <c r="H1121" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="J1121" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1121" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1121" s="1" t="s">
+        <v>2115</v>
+      </c>
+      <c r="M1121" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1121" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1121" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1122" s="1" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B1122" s="7" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C1122" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1122" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1122" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1122" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1122" s="20">
+        <v>73570769</v>
+      </c>
+      <c r="H1122" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="J1122" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1122" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1122" s="1" t="s">
+        <v>2115</v>
+      </c>
+      <c r="M1122" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1122" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1122" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1123" s="1" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B1123" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1123" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1123" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1123" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1123" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1123" s="20">
+        <v>73200292</v>
+      </c>
+      <c r="H1123" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="J1123" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1123" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1123" s="1" t="s">
+        <v>2116</v>
+      </c>
+      <c r="M1123" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1123" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1123" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1124" s="1" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1124" s="7" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C1124" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1124" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1124" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1124" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1124" s="20">
+        <v>61401694</v>
+      </c>
+      <c r="H1124" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="J1124" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1124" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1124" s="1" t="s">
+        <v>2116</v>
+      </c>
+      <c r="M1124" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1124" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1124" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1125" s="1" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B1125" s="7" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1125" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1125" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1125" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1125" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1125" s="20">
+        <v>45146935</v>
+      </c>
+      <c r="H1125" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="J1125" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1125" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1125" s="1" t="s">
+        <v>2117</v>
+      </c>
+      <c r="M1125" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1125" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1125" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1126" s="1" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B1126" s="7" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C1126" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1126" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1126" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1126" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1126" s="20">
+        <v>47188247</v>
+      </c>
+      <c r="H1126" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="J1126" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1126" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1126" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="M1126" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1126" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1126" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1127" s="1" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1127" s="7" t="s">
+        <v>2087</v>
+      </c>
+      <c r="C1127" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1127" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1127" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1127" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1127" s="20">
+        <v>45652745</v>
+      </c>
+      <c r="H1127" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="J1127" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1127" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1127" s="1" t="s">
+        <v>2118</v>
+      </c>
+      <c r="M1127" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1127" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1127" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1128" s="1" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B1128" s="7" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C1128" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1128" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1128" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1128" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1128" s="20">
+        <v>46756737</v>
+      </c>
+      <c r="H1128" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="J1128" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1128" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1128" s="1" t="s">
+        <v>2119</v>
+      </c>
+      <c r="M1128" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1128" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1128" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1129" s="1" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B1129" s="7" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1129" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1129" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1129" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1129" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1129" s="20">
+        <v>73570769</v>
+      </c>
+      <c r="H1129" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="J1129" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1129" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1129" s="1" t="s">
+        <v>2119</v>
+      </c>
+      <c r="M1129" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1129" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1129" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1130" s="1" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B1130" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1130" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1130" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1130" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1130" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1130" s="20">
+        <v>73200292</v>
+      </c>
+      <c r="H1130" s="1" t="s">
+        <v>1526</v>
+      </c>
+      <c r="J1130" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="K1130" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="L1130" s="1" t="s">
+        <v>2120</v>
+      </c>
+      <c r="M1130" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1130" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1130" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1131" s="1" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B1131" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1131" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1131" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1131" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1131" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1131" s="20">
+        <v>61401694</v>
+      </c>
+      <c r="H1131" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="J1131" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1131" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1131" s="1" t="s">
+        <v>2120</v>
+      </c>
+      <c r="M1131" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1131" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1131" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1132" s="1" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B1132" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1132" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1132" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1132" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1132" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1132" s="20">
+        <v>40457168</v>
+      </c>
+      <c r="H1132" s="1" t="s">
+        <v>2175</v>
+      </c>
+      <c r="J1132" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1132" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1132" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1132" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1132" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1132" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1133" s="1" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B1133" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1133" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1133" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1133" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1133" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1133" s="20">
+        <v>70840385</v>
+      </c>
+      <c r="H1133" s="1" t="s">
+        <v>2179</v>
+      </c>
+      <c r="J1133" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1133" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1133" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1133" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1133" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1133" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1134" s="1" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B1134" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1134" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1134" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1134" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1134" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1134" s="20">
+        <v>10420494128</v>
+      </c>
+      <c r="H1134" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="J1134" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1134" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1134" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1134" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1134" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1134" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1135" s="1" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1135" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1135" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1135" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1135" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1135" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1135" s="20">
+        <v>10248888291</v>
+      </c>
+      <c r="H1135" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="J1135" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1135" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1135" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1135" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1135" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1135" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1136" s="1" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B1136" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1136" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1136" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1136" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1136" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1136" s="20">
+        <v>10248952542</v>
+      </c>
+      <c r="H1136" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="J1136" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1136" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1136" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1136" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1136" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1136" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1137" s="1" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B1137" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1137" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1137" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1137" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1137" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1137" s="20">
+        <v>10411675179</v>
+      </c>
+      <c r="H1137" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="J1137" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1137" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1137" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1137" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1137" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1137" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1138" s="1" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B1138" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1138" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1138" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1138" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1138" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1138" s="20">
+        <v>10446727180</v>
+      </c>
+      <c r="H1138" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="J1138" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1138" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1138" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1138" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1138" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1138" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1139" s="1" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1139" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1139" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1139" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1139" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1139" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1139" s="20">
+        <v>10408822641</v>
+      </c>
+      <c r="H1139" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="J1139" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1139" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1139" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1139" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1139" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1139" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1140" s="1" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B1140" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1140" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1140" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1140" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1140" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1140" s="20">
+        <v>10248841821</v>
+      </c>
+      <c r="H1140" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="J1140" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1140" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1140" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1140" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1140" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1140" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1141" s="1" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B1141" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1141" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1141" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1141" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1141" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1141" s="20">
+        <v>10248919740</v>
+      </c>
+      <c r="H1141" s="1" t="s">
+        <v>2174</v>
+      </c>
+      <c r="J1141" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1141" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1141" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1141" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1141" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1141" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1142" s="1" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B1142" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1142" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1142" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1142" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1142" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1142" s="20">
+        <v>10434752294</v>
+      </c>
+      <c r="H1142" s="1" t="s">
+        <v>2176</v>
+      </c>
+      <c r="J1142" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1142" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1142" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1142" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1142" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1142" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1143" s="1" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B1143" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1143" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1143" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1143" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1143" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1143" s="20">
+        <v>10443205573</v>
+      </c>
+      <c r="H1143" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="J1143" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1143" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1143" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1143" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1143" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1143" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1144" s="1" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B1144" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1144" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1144" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1144" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1144" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1144" s="20">
+        <v>10250171761</v>
+      </c>
+      <c r="H1144" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="J1144" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1144" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1144" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1144" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1144" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1144" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1145" s="1" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B1145" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1145" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1145" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1145" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1145" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1145" s="20">
+        <v>10248673007</v>
+      </c>
+      <c r="H1145" s="1" t="s">
+        <v>2180</v>
+      </c>
+      <c r="J1145" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1145" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1145" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1145" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1145" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1145" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1146" s="1" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B1146" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1146" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1146" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1146" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1146" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1146" s="20">
+        <v>10761912424</v>
+      </c>
+      <c r="H1146" s="1" t="s">
+        <v>2178</v>
+      </c>
+      <c r="J1146" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1146" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1146" s="1" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M1146" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1146" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1146" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1147" s="1" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B1147" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1147" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1147" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1147" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1147" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1147" s="20">
+        <v>10248952542</v>
+      </c>
+      <c r="H1147" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="J1147" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1147" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1147" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1147" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1147" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1147" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1148" s="1" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B1148" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1148" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1148" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1148" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1148" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1148" s="20">
+        <v>10411675179</v>
+      </c>
+      <c r="H1148" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="J1148" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1148" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1148" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1148" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1148" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1148" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1149" s="1" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B1149" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1149" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1149" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1149" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1149" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1149" s="20">
+        <v>10446727180</v>
+      </c>
+      <c r="H1149" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="J1149" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1149" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1149" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1149" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1149" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1149" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1150" s="1" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B1150" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1150" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1150" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1150" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1150" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1150" s="20">
+        <v>10408822641</v>
+      </c>
+      <c r="H1150" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="J1150" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1150" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1150" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1150" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1150" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1150" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1151" s="1" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B1151" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1151" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1151" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1151" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1151" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1151" s="20">
+        <v>10248841821</v>
+      </c>
+      <c r="H1151" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="J1151" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1151" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1151" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1151" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1151" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1151" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1152" s="1" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B1152" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1152" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1152" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1152" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1152" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1152" s="20">
+        <v>10248919740</v>
+      </c>
+      <c r="H1152" s="1" t="s">
+        <v>2174</v>
+      </c>
+      <c r="J1152" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1152" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1152" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1152" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1152" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1152" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1153" s="1" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B1153" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1153" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1153" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1153" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1153" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1153" s="20">
+        <v>40457168</v>
+      </c>
+      <c r="H1153" s="1" t="s">
+        <v>2175</v>
+      </c>
+      <c r="J1153" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1153" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1153" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1153" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1153" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1153" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1154" s="1" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B1154" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1154" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1154" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1154" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1154" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1154" s="20">
+        <v>10434752294</v>
+      </c>
+      <c r="H1154" s="1" t="s">
+        <v>2176</v>
+      </c>
+      <c r="J1154" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1154" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1154" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1154" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1154" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1154" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1155" s="1" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B1155" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1155" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1155" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1155" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1155" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1155" s="20">
+        <v>10443205573</v>
+      </c>
+      <c r="H1155" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="J1155" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1155" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1155" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1155" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1155" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1155" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1156" s="1" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B1156" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1156" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1156" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1156" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1156" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1156" s="20">
+        <v>10250171761</v>
+      </c>
+      <c r="H1156" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="J1156" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1156" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1156" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1156" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1156" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1156" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1157" s="1" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B1157" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1157" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1157" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1157" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1157" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1157" s="20">
+        <v>10248673007</v>
+      </c>
+      <c r="H1157" s="1" t="s">
+        <v>2177</v>
+      </c>
+      <c r="J1157" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1157" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1157" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1157" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1157" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1157" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1158" s="1" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B1158" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1158" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1158" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1158" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1158" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1158" s="20">
+        <v>10761912424</v>
+      </c>
+      <c r="H1158" s="1" t="s">
+        <v>2178</v>
+      </c>
+      <c r="J1158" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1158" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1158" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1158" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1158" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1158" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1159" s="1" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B1159" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1159" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1159" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1159" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1159" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1159" s="20">
+        <v>70840385</v>
+      </c>
+      <c r="H1159" s="1" t="s">
+        <v>2179</v>
+      </c>
+      <c r="J1159" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1159" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1159" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1159" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1159" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1159" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1160" s="1" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B1160" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1160" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1160" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1160" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1160" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1160" s="20">
+        <v>10420494128</v>
+      </c>
+      <c r="H1160" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="J1160" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1160" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1160" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1160" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1160" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1160" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1161" s="1" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B1161" s="7" t="s">
+        <v>2077</v>
+      </c>
+      <c r="C1161" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1161" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1161" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1161" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="G1161" s="20">
+        <v>10248888291</v>
+      </c>
+      <c r="H1161" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="J1161" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1161" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1161" s="1" t="s">
+        <v>2143</v>
+      </c>
+      <c r="M1161" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1161" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1161" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1162" s="1" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B1162" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1162" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1162" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1162" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1162" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1162" s="20">
+        <v>72495328</v>
+      </c>
+      <c r="H1162" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="J1162" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1162" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1162" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1162" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1162" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1162" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1163" s="1" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B1163" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1163" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1163" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1163" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1163" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1163" s="20">
+        <v>75237035</v>
+      </c>
+      <c r="H1163" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="J1163" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1163" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1163" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1163" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1163" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1163" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1164" s="1" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B1164" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1164" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1164" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1164" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1164" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1164" s="20">
+        <v>71727977</v>
+      </c>
+      <c r="H1164" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="J1164" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1164" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1164" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1164" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1164" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1164" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1165" s="1" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B1165" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1165" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1165" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1165" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1165" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1165" s="20">
+        <v>76403635</v>
+      </c>
+      <c r="H1165" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="J1165" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1165" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1165" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1165" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1165" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1165" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1166" s="1" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B1166" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1166" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1166" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1166" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1166" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1166" s="20">
+        <v>60171003</v>
+      </c>
+      <c r="H1166" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="J1166" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1166" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1166" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1166" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1166" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1166" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1167" s="1" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B1167" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1167" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1167" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1167" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1167" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1167" s="20">
+        <v>61094381</v>
+      </c>
+      <c r="H1167" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="J1167" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1167" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1167" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1167" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1167" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1167" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1168" s="1" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B1168" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1168" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1168" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1168" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1168" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1168" s="20">
+        <v>60566010</v>
+      </c>
+      <c r="H1168" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="J1168" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1168" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1168" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1168" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1168" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1168" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1169" s="1" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1169" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1169" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1169" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1169" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1169" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1169" s="20">
+        <v>71873373</v>
+      </c>
+      <c r="H1169" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="J1169" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1169" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1169" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1169" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1169" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1169" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1170" s="1" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1170" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1170" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1170" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1170" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1170" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1170" s="20">
+        <v>72076653</v>
+      </c>
+      <c r="H1170" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="J1170" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1170" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1170" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1170" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1170" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1170" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1171" s="1" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1171" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1171" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1171" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1171" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1171" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1171" s="20">
+        <v>10733216803</v>
+      </c>
+      <c r="H1171" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="J1171" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1171" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1171" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1171" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1171" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1171" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1172" s="1" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B1172" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1172" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1172" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1172" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1172" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1172" s="20">
+        <v>10743116904</v>
+      </c>
+      <c r="H1172" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="J1172" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1172" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1172" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1172" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1172" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1172" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1173" s="1" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B1173" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1173" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1173" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1173" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1173" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1173" s="20">
+        <v>10701171077</v>
+      </c>
+      <c r="H1173" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="J1173" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1173" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1173" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1173" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1173" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1173" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1174" s="1" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B1174" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1174" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1174" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1174" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1174" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1174" s="20">
+        <v>10410053221</v>
+      </c>
+      <c r="H1174" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="J1174" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1174" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1174" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1174" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1174" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1174" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1175" s="1" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B1175" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1175" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1175" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1175" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1175" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1175" s="20">
+        <v>10715055380</v>
+      </c>
+      <c r="H1175" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="J1175" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1175" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1175" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1175" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1175" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1175" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1176" s="1" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B1176" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1176" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1176" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1176" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1176" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1176" s="20">
+        <v>10724715759</v>
+      </c>
+      <c r="H1176" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="J1176" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1176" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1176" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1176" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1176" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1176" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1177" s="1" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B1177" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1177" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1177" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1177" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1177" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1177" s="20">
+        <v>10767470628</v>
+      </c>
+      <c r="H1177" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="J1177" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1177" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1177" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1177" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1177" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1177" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1178" s="1" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1178" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1178" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1178" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1178" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1178" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1178" s="20">
+        <v>10752826761</v>
+      </c>
+      <c r="H1178" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="J1178" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1178" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1178" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1178" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1178" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1178" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1179" s="1" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B1179" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1179" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1179" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1179" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1179" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1179" s="20">
+        <v>10701171255</v>
+      </c>
+      <c r="H1179" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="J1179" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1179" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1179" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1179" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1179" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1179" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1180" s="1" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B1180" s="7" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1180" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1180" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1180" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1180" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1180" s="20">
+        <v>10718515161</v>
+      </c>
+      <c r="H1180" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="J1180" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1180" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1180" s="1" t="s">
+        <v>2181</v>
+      </c>
+      <c r="M1180" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1180" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1180" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1181" s="1" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B1181" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1181" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1181" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1181" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1181" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1181" s="20">
+        <v>71218324</v>
+      </c>
+      <c r="H1181" s="1" t="s">
+        <v>2232</v>
+      </c>
+      <c r="J1181" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1181" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1181" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1181" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1181" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1181" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1182" s="1" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B1182" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1182" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1182" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1182" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1182" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1182" s="20">
+        <v>23915633</v>
+      </c>
+      <c r="H1182" s="1" t="s">
+        <v>2233</v>
+      </c>
+      <c r="J1182" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1182" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1182" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1182" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1182" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1182" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1183" s="1" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B1183" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1183" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1183" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1183" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1183" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1183" s="20">
+        <v>23911269</v>
+      </c>
+      <c r="H1183" s="1" t="s">
+        <v>2234</v>
+      </c>
+      <c r="J1183" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1183" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1183" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1183" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1183" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1183" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1184" s="1" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B1184" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1184" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1184" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1184" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1184" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1184" s="20">
+        <v>23982064</v>
+      </c>
+      <c r="H1184" s="1" t="s">
+        <v>2235</v>
+      </c>
+      <c r="J1184" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1184" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1184" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1184" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1184" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1184" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1185" s="1" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B1185" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1185" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1185" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1185" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1185" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1185" s="20">
+        <v>23960156</v>
+      </c>
+      <c r="H1185" s="1" t="s">
+        <v>2236</v>
+      </c>
+      <c r="J1185" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1185" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1185" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1185" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1185" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1185" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1186" s="1" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B1186" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1186" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1186" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1186" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1186" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1186" s="20">
+        <v>42047719</v>
+      </c>
+      <c r="H1186" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="J1186" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1186" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1186" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1186" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1186" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1186" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1187" s="1" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B1187" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1187" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1187" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1187" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1187" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1187" s="20">
+        <v>23840825</v>
+      </c>
+      <c r="H1187" s="1" t="s">
+        <v>2237</v>
+      </c>
+      <c r="J1187" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1187" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1187" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1187" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1187" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1187" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1188" s="1" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B1188" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1188" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1188" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1188" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1188" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1188" s="20">
+        <v>23811505</v>
+      </c>
+      <c r="H1188" s="1" t="s">
+        <v>2238</v>
+      </c>
+      <c r="J1188" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1188" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1188" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1188" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1188" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1188" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1189" s="1" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B1189" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1189" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1189" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1189" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1189" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1189" s="20">
+        <v>42071025</v>
+      </c>
+      <c r="H1189" s="1" t="s">
+        <v>2239</v>
+      </c>
+      <c r="J1189" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1189" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1189" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1189" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1189" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1189" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1190" s="1" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B1190" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1190" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1190" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1190" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1190" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1190" s="20">
+        <v>2403362</v>
+      </c>
+      <c r="H1190" s="1" t="s">
+        <v>2240</v>
+      </c>
+      <c r="J1190" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1190" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1190" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1190" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1190" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1190" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1191" s="1" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B1191" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1191" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1191" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1191" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1191" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1191" s="20">
+        <v>23859390</v>
+      </c>
+      <c r="H1191" s="1" t="s">
+        <v>2241</v>
+      </c>
+      <c r="J1191" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1191" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1191" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1191" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1191" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1191" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1192" s="1" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B1192" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1192" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1192" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1192" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1192" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1192" s="20">
+        <v>45981779</v>
+      </c>
+      <c r="H1192" s="1" t="s">
+        <v>2242</v>
+      </c>
+      <c r="J1192" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1192" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1192" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1192" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1192" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1192" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1193" s="1" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B1193" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1193" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1193" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1193" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1193" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1193" s="20">
+        <v>23815170</v>
+      </c>
+      <c r="H1193" s="1" t="s">
+        <v>2243</v>
+      </c>
+      <c r="J1193" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1193" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1193" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1193" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1193" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1193" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1194" s="1" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B1194" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1194" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1194" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1194" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1194" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1194" s="20">
+        <v>24884262</v>
+      </c>
+      <c r="H1194" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="J1194" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1194" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1194" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1194" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1194" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1194" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1195" s="1" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B1195" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1195" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1195" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1195" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1195" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1195" s="20">
+        <v>40809201</v>
+      </c>
+      <c r="H1195" s="1" t="s">
+        <v>2244</v>
+      </c>
+      <c r="J1195" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1195" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1195" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1195" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1195" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1195" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1196" s="1" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B1196" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1196" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1196" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1196" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1196" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1196" s="20">
+        <v>23885626</v>
+      </c>
+      <c r="H1196" s="1" t="s">
+        <v>2245</v>
+      </c>
+      <c r="J1196" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1196" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1196" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1196" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1196" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1196" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1197" s="1" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B1197" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1197" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1197" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1197" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1197" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1197" s="20">
+        <v>23837815</v>
+      </c>
+      <c r="H1197" s="1" t="s">
+        <v>2246</v>
+      </c>
+      <c r="J1197" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1197" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1197" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1197" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1197" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1197" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1198" s="1" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B1198" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1198" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1198" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1198" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1198" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1198" s="20">
+        <v>23841580</v>
+      </c>
+      <c r="H1198" s="1" t="s">
+        <v>2247</v>
+      </c>
+      <c r="J1198" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1198" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1198" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1198" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1198" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1198" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1199" s="1" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B1199" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1199" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1199" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1199" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1199" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1199" s="20">
+        <v>44249822</v>
+      </c>
+      <c r="H1199" s="1" t="s">
+        <v>2248</v>
+      </c>
+      <c r="J1199" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1199" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1199" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1199" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1199" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1199" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1200" s="1" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B1200" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1200" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1200" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1200" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1200" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1200" s="20">
+        <v>23839655</v>
+      </c>
+      <c r="H1200" s="1" t="s">
+        <v>2249</v>
+      </c>
+      <c r="J1200" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1200" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1200" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1200" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1200" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1200" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1201" s="1" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B1201" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1201" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1201" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1201" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1201" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1201" s="20">
+        <v>23815839</v>
+      </c>
+      <c r="H1201" s="1" t="s">
+        <v>2250</v>
+      </c>
+      <c r="J1201" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1201" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1201" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1201" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1201" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1201" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1202" s="1" t="s">
+        <v>2223</v>
+      </c>
+      <c r="B1202" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1202" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1202" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1202" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1202" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1202" s="20">
+        <v>23947542</v>
+      </c>
+      <c r="H1202" s="1" t="s">
+        <v>2251</v>
+      </c>
+      <c r="J1202" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1202" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1202" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1202" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1202" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1202" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1203" s="1" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B1203" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1203" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1203" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1203" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1203" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1203" s="20">
+        <v>23985843</v>
+      </c>
+      <c r="H1203" s="1" t="s">
+        <v>2252</v>
+      </c>
+      <c r="J1203" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1203" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1203" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1203" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1203" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1203" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1204" s="1" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B1204" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1204" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1204" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1204" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1204" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1204" s="20">
+        <v>45841374</v>
+      </c>
+      <c r="H1204" s="1" t="s">
+        <v>2253</v>
+      </c>
+      <c r="J1204" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1204" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1204" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1204" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1204" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1204" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1205" s="1" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B1205" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1205" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1205" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1205" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1205" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1205" s="20">
+        <v>23990823</v>
+      </c>
+      <c r="H1205" s="1" t="s">
+        <v>2254</v>
+      </c>
+      <c r="J1205" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1205" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1205" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1205" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1205" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1205" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1206" s="1" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1206" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1206" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1206" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1206" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1206" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1206" s="20">
+        <v>44926610</v>
+      </c>
+      <c r="H1206" s="1" t="s">
+        <v>2255</v>
+      </c>
+      <c r="J1206" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1206" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1206" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1206" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1206" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1206" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1207" s="1" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B1207" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1207" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1207" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1207" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1207" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1207" s="20">
+        <v>23856360</v>
+      </c>
+      <c r="H1207" s="1" t="s">
+        <v>2256</v>
+      </c>
+      <c r="J1207" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1207" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1207" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1207" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1207" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1207" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1208" s="1" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B1208" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1208" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1208" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1208" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1208" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1208" s="20">
+        <v>23986656</v>
+      </c>
+      <c r="H1208" s="1" t="s">
+        <v>2257</v>
+      </c>
+      <c r="J1208" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1208" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1208" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1208" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1208" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1208" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1209" s="1" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B1209" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1209" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1209" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1209" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1209" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1209" s="20">
+        <v>23860369</v>
+      </c>
+      <c r="H1209" s="1" t="s">
+        <v>2258</v>
+      </c>
+      <c r="J1209" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1209" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1209" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1209" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1209" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1209" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1210" s="1" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B1210" s="7" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C1210" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1210" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1210" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1210" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="G1210" s="20">
+        <v>23812194</v>
+      </c>
+      <c r="H1210" s="1" t="s">
+        <v>2259</v>
+      </c>
+      <c r="J1210" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1210" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1210" s="1" t="s">
+        <v>2201</v>
+      </c>
+      <c r="M1210" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1210" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1210" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1211" s="1" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B1211" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1211" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1211" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1211" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1211" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1211" s="20">
+        <v>43832608</v>
+      </c>
+      <c r="H1211" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J1211" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1211" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1211" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1211" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1211" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1211" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1212" s="1" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B1212" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1212" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1212" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1212" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1212" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1212" s="20">
+        <v>23830090</v>
+      </c>
+      <c r="H1212" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="J1212" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1212" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1212" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1212" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1212" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1212" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1213" s="1" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B1213" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1213" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1213" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1213" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1213" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1213" s="20">
+        <v>10473163450</v>
+      </c>
+      <c r="H1213" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J1213" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1213" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1213" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1213" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1213" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1213" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1214" s="1" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B1214" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1214" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1214" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1214" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1214" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1214" s="20">
+        <v>10248679081</v>
+      </c>
+      <c r="H1214" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1214" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1214" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1214" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1214" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1214" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1214" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1215" s="1" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B1215" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1215" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1215" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1215" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1215" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1215" s="20">
+        <v>10239510197</v>
+      </c>
+      <c r="H1215" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1215" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1215" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1215" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1215" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1215" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1215" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1216" s="1" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B1216" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1216" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1216" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1216" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1216" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1216" s="20">
+        <v>10238698362</v>
+      </c>
+      <c r="H1216" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="J1216" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1216" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1216" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1216" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1216" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1216" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1217" s="1" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B1217" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1217" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1217" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1217" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1217" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1217" s="20">
+        <v>10238089358</v>
+      </c>
+      <c r="H1217" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J1217" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1217" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1217" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1217" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1217" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1217" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1218" s="1" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B1218" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1218" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1218" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1218" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1218" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1218" s="20">
+        <v>10401531284</v>
+      </c>
+      <c r="H1218" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J1218" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1218" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1218" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1218" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1218" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1218" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1219" s="1" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B1219" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1219" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1219" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1219" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1219" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1219" s="20">
+        <v>10239791013</v>
+      </c>
+      <c r="H1219" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="J1219" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1219" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1219" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1219" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1219" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1219" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1220" s="1" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1220" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1220" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1220" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1220" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1220" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1220" s="20">
+        <v>10238657046</v>
+      </c>
+      <c r="H1220" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1220" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1220" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1220" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1220" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1220" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1220" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1221" s="1" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B1221" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1221" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1221" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1221" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1221" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1221" s="20">
+        <v>10468032738</v>
+      </c>
+      <c r="H1221" s="1" t="s">
+        <v>2286</v>
+      </c>
+      <c r="J1221" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1221" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1221" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1221" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1221" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1221" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1222" s="1" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B1222" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1222" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1222" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1222" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1222" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1222" s="20">
+        <v>10403471645</v>
+      </c>
+      <c r="H1222" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1222" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1222" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1222" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1222" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1222" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1222" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1223" s="1" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B1223" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1223" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1223" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1223" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1223" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1223" s="20">
+        <v>10403881363</v>
+      </c>
+      <c r="H1223" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1223" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1223" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1223" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1223" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1223" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1223" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1224" s="1" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B1224" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1224" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1224" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1224" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1224" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1224" s="20">
+        <v>10487664958</v>
+      </c>
+      <c r="H1224" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="J1224" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1224" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1224" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1224" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1224" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1224" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1225" s="1" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B1225" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1225" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1225" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1225" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1225" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1225" s="20">
+        <v>10239584115</v>
+      </c>
+      <c r="H1225" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J1225" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1225" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1225" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1225" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1225" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1225" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1226" s="1" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B1226" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1226" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1226" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1226" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1226" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1226" s="20">
+        <v>10240067566</v>
+      </c>
+      <c r="H1226" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J1226" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1226" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1226" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1226" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1226" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1226" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1227" s="1" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B1227" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1227" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1227" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1227" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1227" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1227" s="20">
+        <v>23938071</v>
+      </c>
+      <c r="H1227" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J1227" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1227" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1227" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1227" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1227" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1227" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1228" s="1" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B1228" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1228" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1228" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1228" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1228" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1228" s="20">
+        <v>23948637</v>
+      </c>
+      <c r="H1228" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1228" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1228" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1228" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1228" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1228" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1228" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1229" s="1" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B1229" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1229" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1229" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1229" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1229" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1229" s="20">
+        <v>10239128519</v>
+      </c>
+      <c r="H1229" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1229" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1229" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1229" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1229" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1229" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1229" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1230" s="1" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B1230" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1230" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1230" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1230" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1230" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1230" s="20">
+        <v>10238552589</v>
+      </c>
+      <c r="H1230" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="J1230" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1230" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1230" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1230" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1230" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1230" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1231" s="1" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B1231" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1231" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1231" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1231" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1231" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1231" s="20">
+        <v>10090021945</v>
+      </c>
+      <c r="H1231" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1231" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1231" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1231" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1231" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1231" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1231" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1232" s="1" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B1232" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1232" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1232" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1232" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1232" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1232" s="20">
+        <v>45449105</v>
+      </c>
+      <c r="H1232" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="J1232" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1232" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1232" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1232" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1232" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1232" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1233" s="1" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B1233" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1233" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1233" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1233" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1233" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1233" s="20">
+        <v>10238589458</v>
+      </c>
+      <c r="H1233" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="J1233" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1233" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1233" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1233" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1233" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1233" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1234" s="1" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B1234" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1234" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1234" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1234" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1234" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1234" s="20">
+        <v>23933131</v>
+      </c>
+      <c r="H1234" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="J1234" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1234" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1234" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1234" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1234" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1234" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1235" s="1" t="s">
+        <v>2285</v>
+      </c>
+      <c r="B1235" s="7" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C1235" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D1235" s="1">
+        <v>9</v>
+      </c>
+      <c r="E1235" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1235" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="G1235" s="20">
+        <v>10239106876</v>
+      </c>
+      <c r="H1235" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="J1235" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K1235" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="L1235" s="1" t="s">
+        <v>2260</v>
+      </c>
+      <c r="M1235" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="N1235" s="1">
+        <v>1</v>
+      </c>
+      <c r="O1235" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P727">
     <sortCondition ref="D709:D727"/>

--- a/data/ejecucion.xlsx
+++ b/data/ejecucion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROYECTOS - 2026 (DEV)\DEV - POI\Insights_POI\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74B8FC52-E97B-4875-A118-1C05E452B847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{018932BE-5E7D-4E49-970E-C3C2E4681A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8316,7 +8316,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -8359,7 +8359,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -62294,7 +62293,7 @@
       <c r="F1099" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1099" s="20">
+      <c r="G1099" s="1">
         <v>10706655307</v>
       </c>
       <c r="H1099" s="1" t="s">
@@ -62348,7 +62347,7 @@
       <c r="F1100" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1100" s="20">
+      <c r="G1100" s="1">
         <v>10443173639</v>
       </c>
       <c r="H1100" s="1" t="s">
@@ -62402,7 +62401,7 @@
       <c r="F1101" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1101" s="20">
+      <c r="G1101" s="1">
         <v>10445905955</v>
       </c>
       <c r="H1101" s="1" t="s">
@@ -62456,7 +62455,7 @@
       <c r="F1102" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1102" s="20">
+      <c r="G1102" s="1">
         <v>10800106937</v>
       </c>
       <c r="H1102" s="1" t="s">
@@ -62510,7 +62509,7 @@
       <c r="F1103" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1103" s="20">
+      <c r="G1103" s="1">
         <v>77709806</v>
       </c>
       <c r="H1103" s="1" t="s">
@@ -62564,7 +62563,7 @@
       <c r="F1104" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1104" s="20">
+      <c r="G1104" s="1">
         <v>74202742</v>
       </c>
       <c r="H1104" s="1" t="s">
@@ -62618,7 +62617,7 @@
       <c r="F1105" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1105" s="20">
+      <c r="G1105" s="1">
         <v>48019964</v>
       </c>
       <c r="H1105" s="1" t="s">
@@ -62672,7 +62671,7 @@
       <c r="F1106" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1106" s="20">
+      <c r="G1106" s="1">
         <v>25223309</v>
       </c>
       <c r="H1106" s="1" t="s">
@@ -62726,7 +62725,7 @@
       <c r="F1107" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1107" s="20">
+      <c r="G1107" s="1">
         <v>76085564</v>
       </c>
       <c r="H1107" s="1" t="s">
@@ -62780,7 +62779,7 @@
       <c r="F1108" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1108" s="20">
+      <c r="G1108" s="1">
         <v>74176831</v>
       </c>
       <c r="H1108" s="1" t="s">
@@ -62834,7 +62833,7 @@
       <c r="F1109" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1109" s="20">
+      <c r="G1109" s="1">
         <v>41551194</v>
       </c>
       <c r="H1109" s="1" t="s">
@@ -62888,7 +62887,7 @@
       <c r="F1110" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1110" s="20">
+      <c r="G1110" s="1">
         <v>76659819</v>
       </c>
       <c r="H1110" s="1" t="s">
@@ -62942,7 +62941,7 @@
       <c r="F1111" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1111" s="20">
+      <c r="G1111" s="1">
         <v>76724773</v>
       </c>
       <c r="H1111" s="1" t="s">
@@ -62996,7 +62995,7 @@
       <c r="F1112" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1112" s="20">
+      <c r="G1112" s="1">
         <v>46390613</v>
       </c>
       <c r="H1112" s="1" t="s">
@@ -63050,7 +63049,7 @@
       <c r="F1113" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1113" s="20">
+      <c r="G1113" s="1">
         <v>40306810</v>
       </c>
       <c r="H1113" s="1" t="s">
@@ -63104,7 +63103,7 @@
       <c r="F1114" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1114" s="20">
+      <c r="G1114" s="1">
         <v>40306210</v>
       </c>
       <c r="H1114" s="1" t="s">
@@ -63158,7 +63157,7 @@
       <c r="F1115" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1115" s="20">
+      <c r="G1115" s="1">
         <v>60120595</v>
       </c>
       <c r="H1115" s="1" t="s">
@@ -63212,7 +63211,7 @@
       <c r="F1116" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1116" s="20">
+      <c r="G1116" s="1">
         <v>25219001</v>
       </c>
       <c r="H1116" s="1" t="s">
@@ -63266,7 +63265,7 @@
       <c r="F1117" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1117" s="20">
+      <c r="G1117" s="1">
         <v>40787183</v>
       </c>
       <c r="H1117" s="1" t="s">
@@ -63320,7 +63319,7 @@
       <c r="F1118" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1118" s="20">
+      <c r="G1118" s="1">
         <v>10252190711</v>
       </c>
       <c r="H1118" s="1" t="s">
@@ -63374,7 +63373,7 @@
       <c r="F1119" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1119" s="20">
+      <c r="G1119" s="1">
         <v>75318942</v>
       </c>
       <c r="H1119" s="1" t="s">
@@ -63428,7 +63427,7 @@
       <c r="F1120" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1120" s="20">
+      <c r="G1120" s="1">
         <v>10428847585</v>
       </c>
       <c r="H1120" s="1" t="s">
@@ -63482,7 +63481,7 @@
       <c r="F1121" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1121" s="20">
+      <c r="G1121" s="1">
         <v>10401640741</v>
       </c>
       <c r="H1121" s="1" t="s">
@@ -63536,7 +63535,7 @@
       <c r="F1122" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1122" s="20">
+      <c r="G1122" s="1">
         <v>10457969967</v>
       </c>
       <c r="H1122" s="1" t="s">
@@ -63590,7 +63589,7 @@
       <c r="F1123" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1123" s="20">
+      <c r="G1123" s="1">
         <v>23956032</v>
       </c>
       <c r="H1123" s="1" t="s">
@@ -63644,7 +63643,7 @@
       <c r="F1124" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1124" s="20">
+      <c r="G1124" s="1">
         <v>25189609</v>
       </c>
       <c r="H1124" s="1" t="s">
@@ -63698,7 +63697,7 @@
       <c r="F1125" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1125" s="20">
+      <c r="G1125" s="1">
         <v>25190768</v>
       </c>
       <c r="H1125" s="1" t="s">
@@ -63752,7 +63751,7 @@
       <c r="F1126" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1126" s="20">
+      <c r="G1126" s="1">
         <v>42844656</v>
       </c>
       <c r="H1126" s="1" t="s">
@@ -63806,7 +63805,7 @@
       <c r="F1127" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1127" s="20">
+      <c r="G1127" s="1">
         <v>43830031</v>
       </c>
       <c r="H1127" s="1" t="s">
@@ -63860,7 +63859,7 @@
       <c r="F1128" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1128" s="20">
+      <c r="G1128" s="1">
         <v>44317363</v>
       </c>
       <c r="H1128" s="1" t="s">
@@ -63914,7 +63913,7 @@
       <c r="F1129" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1129" s="20">
+      <c r="G1129" s="1">
         <v>44323916</v>
       </c>
       <c r="H1129" s="1" t="s">
@@ -63968,7 +63967,7 @@
       <c r="F1130" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1130" s="20">
+      <c r="G1130" s="1">
         <v>45757914</v>
       </c>
       <c r="H1130" s="1" t="s">
@@ -64022,7 +64021,7 @@
       <c r="F1131" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1131" s="20">
+      <c r="G1131" s="1">
         <v>47278173</v>
       </c>
       <c r="H1131" s="1" t="s">
@@ -64076,7 +64075,7 @@
       <c r="F1132" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1132" s="20">
+      <c r="G1132" s="1">
         <v>48526709</v>
       </c>
       <c r="H1132" s="1" t="s">
@@ -64130,7 +64129,7 @@
       <c r="F1133" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1133" s="20">
+      <c r="G1133" s="1">
         <v>60387881</v>
       </c>
       <c r="H1133" s="1" t="s">
@@ -64184,7 +64183,7 @@
       <c r="F1134" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1134" s="20">
+      <c r="G1134" s="1">
         <v>60450012</v>
       </c>
       <c r="H1134" s="1" t="s">
@@ -64238,7 +64237,7 @@
       <c r="F1135" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1135" s="20">
+      <c r="G1135" s="1">
         <v>63346395</v>
       </c>
       <c r="H1135" s="1" t="s">
@@ -64292,7 +64291,7 @@
       <c r="F1136" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1136" s="20">
+      <c r="G1136" s="1">
         <v>74073764</v>
       </c>
       <c r="H1136" s="1" t="s">
@@ -64346,7 +64345,7 @@
       <c r="F1137" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1137" s="20">
+      <c r="G1137" s="1">
         <v>74488468</v>
       </c>
       <c r="H1137" s="1" t="s">
@@ -64400,7 +64399,7 @@
       <c r="F1138" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1138" s="20">
+      <c r="G1138" s="1">
         <v>75060472</v>
       </c>
       <c r="H1138" s="1" t="s">
@@ -64454,7 +64453,7 @@
       <c r="F1139" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="G1139" s="20">
+      <c r="G1139" s="1">
         <v>48343583</v>
       </c>
       <c r="H1139" s="1" t="s">
@@ -64508,7 +64507,7 @@
       <c r="F1140" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1140" s="20">
+      <c r="G1140" s="1">
         <v>48318063</v>
       </c>
       <c r="H1140" s="1" t="s">
@@ -64562,7 +64561,7 @@
       <c r="F1141" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1141" s="20">
+      <c r="G1141" s="1">
         <v>45717160</v>
       </c>
       <c r="H1141" s="1" t="s">
@@ -64616,7 +64615,7 @@
       <c r="F1142" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1142" s="20">
+      <c r="G1142" s="1">
         <v>44268677</v>
       </c>
       <c r="H1142" s="1" t="s">
@@ -64670,7 +64669,7 @@
       <c r="F1143" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1143" s="20">
+      <c r="G1143" s="1">
         <v>45757914</v>
       </c>
       <c r="H1143" s="1" t="s">
@@ -64724,7 +64723,7 @@
       <c r="F1144" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1144" s="20">
+      <c r="G1144" s="1">
         <v>46876336</v>
       </c>
       <c r="H1144" s="1" t="s">
@@ -64778,7 +64777,7 @@
       <c r="F1145" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1145" s="20">
+      <c r="G1145" s="1">
         <v>76698640</v>
       </c>
       <c r="H1145" s="1" t="s">
@@ -64832,7 +64831,7 @@
       <c r="F1146" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1146" s="20">
+      <c r="G1146" s="1">
         <v>80011154</v>
       </c>
       <c r="H1146" s="1" t="s">
@@ -64886,7 +64885,7 @@
       <c r="F1147" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1147" s="20">
+      <c r="G1147" s="1">
         <v>45718764</v>
       </c>
       <c r="H1147" s="1" t="s">
@@ -64940,7 +64939,7 @@
       <c r="F1148" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1148" s="20">
+      <c r="G1148" s="1">
         <v>45648002</v>
       </c>
       <c r="H1148" s="1" t="s">
@@ -64994,7 +64993,7 @@
       <c r="F1149" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1149" s="20">
+      <c r="G1149" s="1">
         <v>61753310</v>
       </c>
       <c r="H1149" s="1" t="s">
@@ -65048,7 +65047,7 @@
       <c r="F1150" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1150" s="20">
+      <c r="G1150" s="1">
         <v>25219551</v>
       </c>
       <c r="H1150" s="1" t="s">
@@ -65102,7 +65101,7 @@
       <c r="F1151" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1151" s="20">
+      <c r="G1151" s="1">
         <v>47658031</v>
       </c>
       <c r="H1151" s="1" t="s">
@@ -65156,7 +65155,7 @@
       <c r="F1152" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1152" s="20">
+      <c r="G1152" s="1">
         <v>80006214</v>
       </c>
       <c r="H1152" s="1" t="s">
@@ -65210,7 +65209,7 @@
       <c r="F1153" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1153" s="20">
+      <c r="G1153" s="1">
         <v>70505042</v>
       </c>
       <c r="H1153" s="1" t="s">
@@ -65264,7 +65263,7 @@
       <c r="F1154" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1154" s="20">
+      <c r="G1154" s="1">
         <v>44306849</v>
       </c>
       <c r="H1154" s="1" t="s">
@@ -65318,7 +65317,7 @@
       <c r="F1155" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1155" s="20">
+      <c r="G1155" s="1">
         <v>74488468</v>
       </c>
       <c r="H1155" s="1" t="s">
@@ -65372,7 +65371,7 @@
       <c r="F1156" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1156" s="20">
+      <c r="G1156" s="1">
         <v>45717138</v>
       </c>
       <c r="H1156" s="1" t="s">
@@ -65426,7 +65425,7 @@
       <c r="F1157" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1157" s="20">
+      <c r="G1157" s="1">
         <v>43801150</v>
       </c>
       <c r="H1157" s="1" t="s">
@@ -65480,7 +65479,7 @@
       <c r="F1158" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1158" s="20">
+      <c r="G1158" s="1">
         <v>47191259</v>
       </c>
       <c r="H1158" s="1" t="s">
@@ -65534,7 +65533,7 @@
       <c r="F1159" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1159" s="20">
+      <c r="G1159" s="1">
         <v>74209581</v>
       </c>
       <c r="H1159" s="1" t="s">
@@ -65588,7 +65587,7 @@
       <c r="F1160" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1160" s="20">
+      <c r="G1160" s="1">
         <v>25191266</v>
       </c>
       <c r="H1160" s="1" t="s">
@@ -65642,7 +65641,7 @@
       <c r="F1161" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1161" s="20">
+      <c r="G1161" s="1">
         <v>41448039</v>
       </c>
       <c r="H1161" s="1" t="s">
@@ -65696,7 +65695,7 @@
       <c r="F1162" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1162" s="20">
+      <c r="G1162" s="1">
         <v>25220487</v>
       </c>
       <c r="H1162" s="1" t="s">
@@ -65750,7 +65749,7 @@
       <c r="F1163" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1163" s="20">
+      <c r="G1163" s="1">
         <v>42592830</v>
       </c>
       <c r="H1163" s="1" t="s">
@@ -65804,7 +65803,7 @@
       <c r="F1164" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1164" s="20">
+      <c r="G1164" s="1">
         <v>42782239</v>
       </c>
       <c r="H1164" s="1" t="s">
@@ -65858,7 +65857,7 @@
       <c r="F1165" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1165" s="20">
+      <c r="G1165" s="1">
         <v>47714815</v>
       </c>
       <c r="H1165" s="1" t="s">
@@ -65912,7 +65911,7 @@
       <c r="F1166" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1166" s="20">
+      <c r="G1166" s="1">
         <v>46911926</v>
       </c>
       <c r="H1166" s="1" t="s">
@@ -65966,7 +65965,7 @@
       <c r="F1167" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1167" s="20">
+      <c r="G1167" s="1">
         <v>48318063</v>
       </c>
       <c r="H1167" s="1" t="s">
@@ -66020,7 +66019,7 @@
       <c r="F1168" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1168" s="20">
+      <c r="G1168" s="1">
         <v>45717160</v>
       </c>
       <c r="H1168" s="1" t="s">
@@ -66074,7 +66073,7 @@
       <c r="F1169" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1169" s="20">
+      <c r="G1169" s="1">
         <v>44268677</v>
       </c>
       <c r="H1169" s="1" t="s">
@@ -66128,7 +66127,7 @@
       <c r="F1170" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1170" s="20">
+      <c r="G1170" s="1">
         <v>45757914</v>
       </c>
       <c r="H1170" s="1" t="s">
@@ -66182,7 +66181,7 @@
       <c r="F1171" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1171" s="20">
+      <c r="G1171" s="1">
         <v>10766986400</v>
       </c>
       <c r="H1171" s="1" t="s">
@@ -66236,7 +66235,7 @@
       <c r="F1172" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1172" s="20">
+      <c r="G1172" s="1">
         <v>10468763368</v>
       </c>
       <c r="H1172" s="1" t="s">
@@ -66290,7 +66289,7 @@
       <c r="F1173" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1173" s="20">
+      <c r="G1173" s="1">
         <v>10800111540</v>
       </c>
       <c r="H1173" s="1" t="s">
@@ -66344,7 +66343,7 @@
       <c r="F1174" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1174" s="20">
+      <c r="G1174" s="1">
         <v>45718764</v>
       </c>
       <c r="H1174" s="1" t="s">
@@ -66398,7 +66397,7 @@
       <c r="F1175" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1175" s="20">
+      <c r="G1175" s="1">
         <v>46390613</v>
       </c>
       <c r="H1175" s="1" t="s">
@@ -66452,7 +66451,7 @@
       <c r="F1176" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1176" s="20">
+      <c r="G1176" s="1">
         <v>10252195519</v>
       </c>
       <c r="H1176" s="1" t="s">
@@ -66506,7 +66505,7 @@
       <c r="F1177" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1177" s="20">
+      <c r="G1177" s="1">
         <v>45648002</v>
       </c>
       <c r="H1177" s="1" t="s">
@@ -66560,7 +66559,7 @@
       <c r="F1178" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1178" s="20">
+      <c r="G1178" s="1">
         <v>70505042</v>
       </c>
       <c r="H1178" s="1" t="s">
@@ -66614,7 +66613,7 @@
       <c r="F1179" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1179" s="20">
+      <c r="G1179" s="1">
         <v>41551194</v>
       </c>
       <c r="H1179" s="1" t="s">
@@ -66668,7 +66667,7 @@
       <c r="F1180" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1180" s="20">
+      <c r="G1180" s="1">
         <v>10617533109</v>
       </c>
       <c r="H1180" s="1" t="s">
@@ -66722,7 +66721,7 @@
       <c r="F1181" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1181" s="20">
+      <c r="G1181" s="1">
         <v>74488468</v>
       </c>
       <c r="H1181" s="1" t="s">
@@ -66776,7 +66775,7 @@
       <c r="F1182" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1182" s="20">
+      <c r="G1182" s="1">
         <v>10476580311</v>
       </c>
       <c r="H1182" s="1" t="s">
@@ -66830,7 +66829,7 @@
       <c r="F1183" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1183" s="20">
+      <c r="G1183" s="1">
         <v>45717138</v>
       </c>
       <c r="H1183" s="1" t="s">
@@ -66884,7 +66883,7 @@
       <c r="F1184" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1184" s="20">
+      <c r="G1184" s="1">
         <v>77709806</v>
       </c>
       <c r="H1184" s="1" t="s">
@@ -66938,7 +66937,7 @@
       <c r="F1185" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1185" s="20">
+      <c r="G1185" s="1">
         <v>76726889</v>
       </c>
       <c r="H1185" s="1" t="s">
@@ -66992,7 +66991,7 @@
       <c r="F1186" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1186" s="20">
+      <c r="G1186" s="1">
         <v>48019964</v>
       </c>
       <c r="H1186" s="1" t="s">
@@ -67046,7 +67045,7 @@
       <c r="F1187" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1187" s="20">
+      <c r="G1187" s="1">
         <v>41349764</v>
       </c>
       <c r="H1187" s="1" t="s">
@@ -67100,7 +67099,7 @@
       <c r="F1188" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1188" s="20">
+      <c r="G1188" s="1">
         <v>25189724</v>
       </c>
       <c r="H1188" s="1" t="s">
@@ -67154,7 +67153,7 @@
       <c r="F1189" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1189" s="20">
+      <c r="G1189" s="1">
         <v>25216177</v>
       </c>
       <c r="H1189" s="1" t="s">
@@ -67208,7 +67207,7 @@
       <c r="F1190" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1190" s="20">
+      <c r="G1190" s="1">
         <v>25218821</v>
       </c>
       <c r="H1190" s="1" t="s">
@@ -67262,7 +67261,7 @@
       <c r="F1191" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1191" s="20">
+      <c r="G1191" s="1">
         <v>25189453</v>
       </c>
       <c r="H1191" s="1" t="s">
@@ -67316,7 +67315,7 @@
       <c r="F1192" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1192" s="20">
+      <c r="G1192" s="1">
         <v>10800062140</v>
       </c>
       <c r="H1192" s="1" t="s">
@@ -67370,7 +67369,7 @@
       <c r="F1193" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="G1193" s="20">
+      <c r="G1193" s="1">
         <v>47810496</v>
       </c>
       <c r="H1193" s="1" t="s">
@@ -67424,7 +67423,7 @@
       <c r="F1194" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1194" s="20">
+      <c r="G1194" s="1">
         <v>47191259</v>
       </c>
       <c r="H1194" s="1" t="s">
@@ -67478,7 +67477,7 @@
       <c r="F1195" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1195" s="20">
+      <c r="G1195" s="1">
         <v>44306849</v>
       </c>
       <c r="H1195" s="1" t="s">
@@ -67532,7 +67531,7 @@
       <c r="F1196" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1196" s="20">
+      <c r="G1196" s="1">
         <v>10251912667</v>
       </c>
       <c r="H1196" s="1" t="s">
@@ -67586,7 +67585,7 @@
       <c r="F1197" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1197" s="20">
+      <c r="G1197" s="1">
         <v>43801150</v>
       </c>
       <c r="H1197" s="1" t="s">
@@ -67640,7 +67639,7 @@
       <c r="F1198" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1198" s="20">
+      <c r="G1198" s="1">
         <v>25220487</v>
       </c>
       <c r="H1198" s="1" t="s">
@@ -67694,7 +67693,7 @@
       <c r="F1199" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1199" s="20">
+      <c r="G1199" s="1">
         <v>10742095810</v>
       </c>
       <c r="H1199" s="1" t="s">
@@ -67748,7 +67747,7 @@
       <c r="F1200" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1200" s="20">
+      <c r="G1200" s="1">
         <v>42592830</v>
       </c>
       <c r="H1200" s="1" t="s">
@@ -67802,7 +67801,7 @@
       <c r="F1201" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1201" s="20">
+      <c r="G1201" s="1">
         <v>10414480395</v>
       </c>
       <c r="H1201" s="1" t="s">
@@ -67856,7 +67855,7 @@
       <c r="F1202" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1202" s="20">
+      <c r="G1202" s="1">
         <v>47714815</v>
       </c>
       <c r="H1202" s="1" t="s">
@@ -67910,7 +67909,7 @@
       <c r="F1203" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1203" s="20">
+      <c r="G1203" s="1">
         <v>10427822392</v>
       </c>
       <c r="H1203" s="1" t="s">
@@ -67964,7 +67963,7 @@
       <c r="F1204" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1204" s="20">
+      <c r="G1204" s="1">
         <v>10427822392</v>
       </c>
       <c r="H1204" s="1" t="s">
@@ -68018,7 +68017,7 @@
       <c r="F1205" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1205" s="20">
+      <c r="G1205" s="1">
         <v>46911926</v>
       </c>
       <c r="H1205" s="1" t="s">
@@ -68072,7 +68071,7 @@
       <c r="F1206" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1206" s="20">
+      <c r="G1206" s="1">
         <v>77709806</v>
       </c>
       <c r="H1206" s="1" t="s">
@@ -68126,7 +68125,7 @@
       <c r="F1207" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1207" s="20">
+      <c r="G1207" s="1">
         <v>74202742</v>
       </c>
       <c r="H1207" s="1" t="s">
@@ -68180,7 +68179,7 @@
       <c r="F1208" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1208" s="20">
+      <c r="G1208" s="1">
         <v>48019964</v>
       </c>
       <c r="H1208" s="1" t="s">
@@ -68234,7 +68233,7 @@
       <c r="F1209" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1209" s="20">
+      <c r="G1209" s="1">
         <v>25223309</v>
       </c>
       <c r="H1209" s="1" t="s">
@@ -68288,7 +68287,7 @@
       <c r="F1210" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1210" s="20">
+      <c r="G1210" s="1">
         <v>76085564</v>
       </c>
       <c r="H1210" s="1" t="s">
@@ -68342,7 +68341,7 @@
       <c r="F1211" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1211" s="20">
+      <c r="G1211" s="1">
         <v>74176831</v>
       </c>
       <c r="H1211" s="1" t="s">
@@ -68396,7 +68395,7 @@
       <c r="F1212" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1212" s="20">
+      <c r="G1212" s="1">
         <v>41551194</v>
       </c>
       <c r="H1212" s="1" t="s">
@@ -68450,7 +68449,7 @@
       <c r="F1213" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1213" s="20">
+      <c r="G1213" s="1">
         <v>76659819</v>
       </c>
       <c r="H1213" s="1" t="s">
@@ -68504,7 +68503,7 @@
       <c r="F1214" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1214" s="20">
+      <c r="G1214" s="1">
         <v>25190308</v>
       </c>
       <c r="H1214" s="1" t="s">
@@ -68558,7 +68557,7 @@
       <c r="F1215" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1215" s="20">
+      <c r="G1215" s="1">
         <v>74078625</v>
       </c>
       <c r="H1215" s="1" t="s">
@@ -68612,7 +68611,7 @@
       <c r="F1216" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1216" s="20">
+      <c r="G1216" s="1">
         <v>60387881</v>
       </c>
       <c r="H1216" s="1" t="s">
@@ -68666,7 +68665,7 @@
       <c r="F1217" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1217" s="20">
+      <c r="G1217" s="1">
         <v>41098922</v>
       </c>
       <c r="H1217" s="1" t="s">
@@ -68720,7 +68719,7 @@
       <c r="F1218" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1218" s="20">
+      <c r="G1218" s="1">
         <v>48550474</v>
       </c>
       <c r="H1218" s="1" t="s">
@@ -68774,7 +68773,7 @@
       <c r="F1219" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1219" s="20">
+      <c r="G1219" s="1">
         <v>76724773</v>
       </c>
       <c r="H1219" s="1" t="s">
@@ -68828,7 +68827,7 @@
       <c r="F1220" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="G1220" s="20">
+      <c r="G1220" s="1">
         <v>46390613</v>
       </c>
       <c r="H1220" s="1" t="s">
@@ -68882,7 +68881,7 @@
       <c r="F1221" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1221" s="20">
+      <c r="G1221" s="1">
         <v>25190768</v>
       </c>
       <c r="H1221" s="1" t="s">
@@ -68936,7 +68935,7 @@
       <c r="F1222" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1222" s="20">
+      <c r="G1222" s="1">
         <v>25190922</v>
       </c>
       <c r="H1222" s="1" t="s">
@@ -68990,7 +68989,7 @@
       <c r="F1223" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1223" s="20">
+      <c r="G1223" s="1">
         <v>40394468</v>
       </c>
       <c r="H1223" s="1" t="s">
@@ -69044,7 +69043,7 @@
       <c r="F1224" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1224" s="20">
+      <c r="G1224" s="1">
         <v>43830031</v>
       </c>
       <c r="H1224" s="1" t="s">
@@ -69098,7 +69097,7 @@
       <c r="F1225" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1225" s="20">
+      <c r="G1225" s="1">
         <v>47278173</v>
       </c>
       <c r="H1225" s="1" t="s">
@@ -69152,7 +69151,7 @@
       <c r="F1226" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1226" s="20">
+      <c r="G1226" s="1">
         <v>60387881</v>
       </c>
       <c r="H1226" s="1" t="s">
@@ -69206,7 +69205,7 @@
       <c r="F1227" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1227" s="20">
+      <c r="G1227" s="1">
         <v>60450012</v>
       </c>
       <c r="H1227" s="1" t="s">
@@ -69260,7 +69259,7 @@
       <c r="F1228" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1228" s="20">
+      <c r="G1228" s="1">
         <v>63346395</v>
       </c>
       <c r="H1228" s="1" t="s">
@@ -69314,7 +69313,7 @@
       <c r="F1229" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1229" s="20">
+      <c r="G1229" s="1">
         <v>63374212</v>
       </c>
       <c r="H1229" s="1" t="s">
@@ -69368,7 +69367,7 @@
       <c r="F1230" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1230" s="20">
+      <c r="G1230" s="1">
         <v>70665530</v>
       </c>
       <c r="H1230" s="1" t="s">
@@ -69422,7 +69421,7 @@
       <c r="F1231" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1231" s="20">
+      <c r="G1231" s="1">
         <v>74073762</v>
       </c>
       <c r="H1231" s="1" t="s">
@@ -69476,7 +69475,7 @@
       <c r="F1232" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1232" s="20">
+      <c r="G1232" s="1">
         <v>74073764</v>
       </c>
       <c r="H1232" s="1" t="s">
@@ -69530,7 +69529,7 @@
       <c r="F1233" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1233" s="20">
+      <c r="G1233" s="1">
         <v>75060472</v>
       </c>
       <c r="H1233" s="1" t="s">
@@ -69584,7 +69583,7 @@
       <c r="F1234" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1234" s="20">
+      <c r="G1234" s="1">
         <v>77531519</v>
       </c>
       <c r="H1234" s="1" t="s">
@@ -69638,7 +69637,7 @@
       <c r="F1235" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1235" s="20">
+      <c r="G1235" s="1">
         <v>80010693</v>
       </c>
       <c r="H1235" s="1" t="s">
@@ -69692,7 +69691,7 @@
       <c r="F1236" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1236" s="20">
+      <c r="G1236" s="1">
         <v>80566378</v>
       </c>
       <c r="H1236" s="1" t="s">
@@ -69746,7 +69745,7 @@
       <c r="F1237" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1237" s="20">
+      <c r="G1237" s="1">
         <v>25216177</v>
       </c>
       <c r="H1237" s="1" t="s">
@@ -69800,7 +69799,7 @@
       <c r="F1238" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1238" s="20">
+      <c r="G1238" s="1">
         <v>25218821</v>
       </c>
       <c r="H1238" s="1" t="s">
@@ -69854,7 +69853,7 @@
       <c r="F1239" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1239" s="20">
+      <c r="G1239" s="1">
         <v>41551194</v>
       </c>
       <c r="H1239" s="1" t="s">
@@ -69908,7 +69907,7 @@
       <c r="F1240" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1240" s="20">
+      <c r="G1240" s="1">
         <v>42978959</v>
       </c>
       <c r="H1240" s="1" t="s">
@@ -69962,7 +69961,7 @@
       <c r="F1241" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1241" s="20">
+      <c r="G1241" s="1">
         <v>44649144</v>
       </c>
       <c r="H1241" s="1" t="s">
@@ -70016,7 +70015,7 @@
       <c r="F1242" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1242" s="20">
+      <c r="G1242" s="1">
         <v>46390613</v>
       </c>
       <c r="H1242" s="1" t="s">
@@ -70070,7 +70069,7 @@
       <c r="F1243" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1243" s="20">
+      <c r="G1243" s="1">
         <v>47810496</v>
       </c>
       <c r="H1243" s="1" t="s">
@@ -70124,7 +70123,7 @@
       <c r="F1244" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1244" s="20">
+      <c r="G1244" s="1">
         <v>48019964</v>
       </c>
       <c r="H1244" s="1" t="s">
@@ -70178,7 +70177,7 @@
       <c r="F1245" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1245" s="20">
+      <c r="G1245" s="1">
         <v>48484933</v>
       </c>
       <c r="H1245" s="1" t="s">
@@ -70232,7 +70231,7 @@
       <c r="F1246" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1246" s="20">
+      <c r="G1246" s="1">
         <v>76085564</v>
       </c>
       <c r="H1246" s="1" t="s">
@@ -70286,7 +70285,7 @@
       <c r="F1247" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1247" s="20">
+      <c r="G1247" s="1">
         <v>76207818</v>
       </c>
       <c r="H1247" s="1" t="s">
@@ -70340,7 +70339,7 @@
       <c r="F1248" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1248" s="20">
+      <c r="G1248" s="1">
         <v>76412365</v>
       </c>
       <c r="H1248" s="1" t="s">
@@ -70394,7 +70393,7 @@
       <c r="F1249" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1249" s="20">
+      <c r="G1249" s="1">
         <v>76726889</v>
       </c>
       <c r="H1249" s="1" t="s">
@@ -70448,7 +70447,7 @@
       <c r="F1250" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1250" s="20">
+      <c r="G1250" s="1">
         <v>77240676</v>
       </c>
       <c r="H1250" s="1" t="s">
@@ -70502,7 +70501,7 @@
       <c r="F1251" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1251" s="20">
+      <c r="G1251" s="1">
         <v>77709806</v>
       </c>
       <c r="H1251" s="1" t="s">
@@ -70556,7 +70555,7 @@
       <c r="F1252" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1252" s="20">
+      <c r="G1252" s="1">
         <v>23956032</v>
       </c>
       <c r="H1252" s="1" t="s">
@@ -70610,7 +70609,7 @@
       <c r="F1253" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1253" s="20">
+      <c r="G1253" s="1">
         <v>25189609</v>
       </c>
       <c r="H1253" s="1" t="s">
@@ -70664,7 +70663,7 @@
       <c r="F1254" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1254" s="20">
+      <c r="G1254" s="1">
         <v>25190768</v>
       </c>
       <c r="H1254" s="1" t="s">
@@ -70718,7 +70717,7 @@
       <c r="F1255" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1255" s="20">
+      <c r="G1255" s="1">
         <v>42844656</v>
       </c>
       <c r="H1255" s="1" t="s">
@@ -70772,7 +70771,7 @@
       <c r="F1256" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1256" s="20">
+      <c r="G1256" s="1">
         <v>43830031</v>
       </c>
       <c r="H1256" s="1" t="s">
@@ -70826,7 +70825,7 @@
       <c r="F1257" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1257" s="20">
+      <c r="G1257" s="1">
         <v>44317363</v>
       </c>
       <c r="H1257" s="1" t="s">
@@ -70880,7 +70879,7 @@
       <c r="F1258" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1258" s="20">
+      <c r="G1258" s="1">
         <v>44323916</v>
       </c>
       <c r="H1258" s="1" t="s">
@@ -70934,7 +70933,7 @@
       <c r="F1259" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1259" s="20">
+      <c r="G1259" s="1">
         <v>45757914</v>
       </c>
       <c r="H1259" s="1" t="s">
@@ -70988,7 +70987,7 @@
       <c r="F1260" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1260" s="20">
+      <c r="G1260" s="1">
         <v>47278173</v>
       </c>
       <c r="H1260" s="1" t="s">
@@ -71042,7 +71041,7 @@
       <c r="F1261" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1261" s="20">
+      <c r="G1261" s="1">
         <v>48526709</v>
       </c>
       <c r="H1261" s="1" t="s">
@@ -71096,7 +71095,7 @@
       <c r="F1262" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1262" s="20">
+      <c r="G1262" s="1">
         <v>60387881</v>
       </c>
       <c r="H1262" s="1" t="s">
@@ -71150,7 +71149,7 @@
       <c r="F1263" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1263" s="20">
+      <c r="G1263" s="1">
         <v>60450012</v>
       </c>
       <c r="H1263" s="1" t="s">
@@ -71204,7 +71203,7 @@
       <c r="F1264" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1264" s="20">
+      <c r="G1264" s="1">
         <v>63346395</v>
       </c>
       <c r="H1264" s="1" t="s">
@@ -71258,7 +71257,7 @@
       <c r="F1265" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1265" s="20">
+      <c r="G1265" s="1">
         <v>74073764</v>
       </c>
       <c r="H1265" s="1" t="s">
@@ -71312,7 +71311,7 @@
       <c r="F1266" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1266" s="20">
+      <c r="G1266" s="1">
         <v>74488468</v>
       </c>
       <c r="H1266" s="1" t="s">
@@ -71366,7 +71365,7 @@
       <c r="F1267" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="G1267" s="20">
+      <c r="G1267" s="1">
         <v>75060472</v>
       </c>
       <c r="H1267" s="1" t="s">
@@ -71420,7 +71419,7 @@
       <c r="F1268" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G1268" s="20">
+      <c r="G1268" s="1">
         <v>20614232596</v>
       </c>
       <c r="H1268" s="1" t="s">
@@ -71470,7 +71469,7 @@
       <c r="F1269" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1269" s="20">
+      <c r="G1269" s="1">
         <v>25189724</v>
       </c>
       <c r="H1269" s="1" t="s">
@@ -71524,7 +71523,7 @@
       <c r="F1270" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1270" s="20">
+      <c r="G1270" s="1">
         <v>25216177</v>
       </c>
       <c r="H1270" s="1" t="s">
@@ -71578,7 +71577,7 @@
       <c r="F1271" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1271" s="20">
+      <c r="G1271" s="1">
         <v>25218821</v>
       </c>
       <c r="H1271" s="1" t="s">
@@ -71632,7 +71631,7 @@
       <c r="F1272" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1272" s="20">
+      <c r="G1272" s="1">
         <v>25223309</v>
       </c>
       <c r="H1272" s="1" t="s">
@@ -71686,7 +71685,7 @@
       <c r="F1273" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1273" s="20">
+      <c r="G1273" s="1">
         <v>41164002</v>
       </c>
       <c r="H1273" s="1" t="s">
@@ -71740,7 +71739,7 @@
       <c r="F1274" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1274" s="20">
+      <c r="G1274" s="1">
         <v>41349764</v>
       </c>
       <c r="H1274" s="1" t="s">
@@ -71794,7 +71793,7 @@
       <c r="F1275" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1275" s="20">
+      <c r="G1275" s="1">
         <v>41551194</v>
       </c>
       <c r="H1275" s="1" t="s">
@@ -71848,7 +71847,7 @@
       <c r="F1276" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1276" s="20">
+      <c r="G1276" s="1">
         <v>46390613</v>
       </c>
       <c r="H1276" s="1" t="s">
@@ -71902,7 +71901,7 @@
       <c r="F1277" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1277" s="20">
+      <c r="G1277" s="1">
         <v>46605204</v>
       </c>
       <c r="H1277" s="1" t="s">
@@ -71956,7 +71955,7 @@
       <c r="F1278" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1278" s="20">
+      <c r="G1278" s="1">
         <v>47816496</v>
       </c>
       <c r="H1278" s="1" t="s">
@@ -72010,7 +72009,7 @@
       <c r="F1279" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1279" s="20">
+      <c r="G1279" s="1">
         <v>48019464</v>
       </c>
       <c r="H1279" s="1" t="s">
@@ -72064,7 +72063,7 @@
       <c r="F1280" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1280" s="20">
+      <c r="G1280" s="1">
         <v>71743082</v>
       </c>
       <c r="H1280" s="1" t="s">
@@ -72118,7 +72117,7 @@
       <c r="F1281" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1281" s="20">
+      <c r="G1281" s="1">
         <v>71828778</v>
       </c>
       <c r="H1281" s="1" t="s">
@@ -72172,7 +72171,7 @@
       <c r="F1282" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1282" s="20">
+      <c r="G1282" s="1">
         <v>74176881</v>
       </c>
       <c r="H1282" s="1" t="s">
@@ -72226,7 +72225,7 @@
       <c r="F1283" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1283" s="20">
+      <c r="G1283" s="1">
         <v>74202742</v>
       </c>
       <c r="H1283" s="1" t="s">
@@ -72280,7 +72279,7 @@
       <c r="F1284" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1284" s="20">
+      <c r="G1284" s="1">
         <v>76085564</v>
       </c>
       <c r="H1284" s="1" t="s">
@@ -72334,7 +72333,7 @@
       <c r="F1285" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1285" s="20">
+      <c r="G1285" s="1">
         <v>76659819</v>
       </c>
       <c r="H1285" s="1" t="s">
@@ -72388,7 +72387,7 @@
       <c r="F1286" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1286" s="20">
+      <c r="G1286" s="1">
         <v>76724770</v>
       </c>
       <c r="H1286" s="1" t="s">
@@ -72442,7 +72441,7 @@
       <c r="F1287" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1287" s="20">
+      <c r="G1287" s="1">
         <v>76724773</v>
       </c>
       <c r="H1287" s="1" t="s">
@@ -72496,7 +72495,7 @@
       <c r="F1288" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1288" s="20">
+      <c r="G1288" s="1">
         <v>76726889</v>
       </c>
       <c r="H1288" s="1" t="s">
@@ -72550,7 +72549,7 @@
       <c r="F1289" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1289" s="20">
+      <c r="G1289" s="1">
         <v>77709806</v>
       </c>
       <c r="H1289" s="1" t="s">
@@ -72604,7 +72603,7 @@
       <c r="F1290" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1290" s="20">
+      <c r="G1290" s="1">
         <v>25189453</v>
       </c>
       <c r="H1290" s="1" t="s">
@@ -72658,7 +72657,7 @@
       <c r="F1291" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1291" s="20">
+      <c r="G1291" s="1">
         <v>25219551</v>
       </c>
       <c r="H1291" s="1" t="s">
@@ -72712,7 +72711,7 @@
       <c r="F1292" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1292" s="20">
+      <c r="G1292" s="1">
         <v>25220487</v>
       </c>
       <c r="H1292" s="1" t="s">
@@ -72766,7 +72765,7 @@
       <c r="F1293" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1293" s="20">
+      <c r="G1293" s="1">
         <v>25315491</v>
       </c>
       <c r="H1293" s="1" t="s">
@@ -72820,7 +72819,7 @@
       <c r="F1294" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1294" s="20">
+      <c r="G1294" s="1">
         <v>40793868</v>
       </c>
       <c r="H1294" s="1" t="s">
@@ -72874,7 +72873,7 @@
       <c r="F1295" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1295" s="20">
+      <c r="G1295" s="1">
         <v>42782239</v>
       </c>
       <c r="H1295" s="1" t="s">
@@ -72928,7 +72927,7 @@
       <c r="F1296" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1296" s="20">
+      <c r="G1296" s="1">
         <v>43801150</v>
       </c>
       <c r="H1296" s="1" t="s">
@@ -72982,7 +72981,7 @@
       <c r="F1297" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1297" s="20">
+      <c r="G1297" s="1">
         <v>44306849</v>
       </c>
       <c r="H1297" s="1" t="s">
@@ -73036,7 +73035,7 @@
       <c r="F1298" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1298" s="20">
+      <c r="G1298" s="1">
         <v>45648002</v>
       </c>
       <c r="H1298" s="1" t="s">
@@ -73090,7 +73089,7 @@
       <c r="F1299" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1299" s="20">
+      <c r="G1299" s="1">
         <v>45717138</v>
       </c>
       <c r="H1299" s="1" t="s">
@@ -73144,7 +73143,7 @@
       <c r="F1300" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1300" s="20">
+      <c r="G1300" s="1">
         <v>46911926</v>
       </c>
       <c r="H1300" s="1" t="s">
@@ -73198,7 +73197,7 @@
       <c r="F1301" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1301" s="20">
+      <c r="G1301" s="1">
         <v>47191259</v>
       </c>
       <c r="H1301" s="1" t="s">
@@ -73252,7 +73251,7 @@
       <c r="F1302" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1302" s="20">
+      <c r="G1302" s="1">
         <v>47655031</v>
       </c>
       <c r="H1302" s="1" t="s">
@@ -73306,7 +73305,7 @@
       <c r="F1303" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1303" s="20">
+      <c r="G1303" s="1">
         <v>61753310</v>
       </c>
       <c r="H1303" s="1" t="s">
@@ -73360,7 +73359,7 @@
       <c r="F1304" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1304" s="20">
+      <c r="G1304" s="1">
         <v>70505042</v>
       </c>
       <c r="H1304" s="1" t="s">
@@ -73414,7 +73413,7 @@
       <c r="F1305" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1305" s="20">
+      <c r="G1305" s="1">
         <v>74205581</v>
       </c>
       <c r="H1305" s="1" t="s">
@@ -73468,7 +73467,7 @@
       <c r="F1306" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1306" s="20">
+      <c r="G1306" s="1">
         <v>74488468</v>
       </c>
       <c r="H1306" s="1" t="s">
@@ -73522,7 +73521,7 @@
       <c r="F1307" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1307" s="20">
+      <c r="G1307" s="1">
         <v>76810896</v>
       </c>
       <c r="H1307" s="1" t="s">
@@ -73576,7 +73575,7 @@
       <c r="F1308" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1308" s="20">
+      <c r="G1308" s="1">
         <v>80006214</v>
       </c>
       <c r="H1308" s="1" t="s">
@@ -73630,7 +73629,7 @@
       <c r="F1309" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1309" s="20">
+      <c r="G1309" s="1">
         <v>25181266</v>
       </c>
       <c r="H1309" s="1" t="s">
@@ -73684,7 +73683,7 @@
       <c r="F1310" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1310" s="20">
+      <c r="G1310" s="1">
         <v>25206671</v>
       </c>
       <c r="H1310" s="1" t="s">
@@ -73738,7 +73737,7 @@
       <c r="F1311" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1311" s="20">
+      <c r="G1311" s="1">
         <v>44268677</v>
       </c>
       <c r="H1311" s="1" t="s">
@@ -73792,7 +73791,7 @@
       <c r="F1312" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1312" s="20">
+      <c r="G1312" s="1">
         <v>44317363</v>
       </c>
       <c r="H1312" s="1" t="s">
@@ -73846,7 +73845,7 @@
       <c r="F1313" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1313" s="20">
+      <c r="G1313" s="1">
         <v>45717160</v>
       </c>
       <c r="H1313" s="1" t="s">
@@ -73900,7 +73899,7 @@
       <c r="F1314" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1314" s="20">
+      <c r="G1314" s="1">
         <v>45718764</v>
       </c>
       <c r="H1314" s="1" t="s">
@@ -73954,7 +73953,7 @@
       <c r="F1315" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1315" s="20">
+      <c r="G1315" s="1">
         <v>45718774</v>
       </c>
       <c r="H1315" s="1" t="s">
@@ -74008,7 +74007,7 @@
       <c r="F1316" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1316" s="20">
+      <c r="G1316" s="1">
         <v>45757914</v>
       </c>
       <c r="H1316" s="1" t="s">
@@ -74062,7 +74061,7 @@
       <c r="F1317" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1317" s="20">
+      <c r="G1317" s="1">
         <v>46876336</v>
       </c>
       <c r="H1317" s="1" t="s">
@@ -74116,7 +74115,7 @@
       <c r="F1318" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1318" s="20">
+      <c r="G1318" s="1">
         <v>48318063</v>
       </c>
       <c r="H1318" s="1" t="s">
@@ -74170,7 +74169,7 @@
       <c r="F1319" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1319" s="20">
+      <c r="G1319" s="1">
         <v>60387881</v>
       </c>
       <c r="H1319" s="1" t="s">
@@ -74224,7 +74223,7 @@
       <c r="F1320" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1320" s="20">
+      <c r="G1320" s="1">
         <v>74073764</v>
       </c>
       <c r="H1320" s="1" t="s">
@@ -74278,7 +74277,7 @@
       <c r="F1321" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1321" s="20">
+      <c r="G1321" s="1">
         <v>76698640</v>
       </c>
       <c r="H1321" s="1" t="s">
@@ -74332,7 +74331,7 @@
       <c r="F1322" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1322" s="20">
+      <c r="G1322" s="1">
         <v>77242609</v>
       </c>
       <c r="H1322" s="1" t="s">
@@ -74386,7 +74385,7 @@
       <c r="F1323" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1323" s="20">
+      <c r="G1323" s="1">
         <v>80011154</v>
       </c>
       <c r="H1323" s="1" t="s">
@@ -74440,7 +74439,7 @@
       <c r="F1324" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1324" s="20">
+      <c r="G1324" s="1">
         <v>23956032</v>
       </c>
       <c r="H1324" s="1" t="s">
@@ -74494,7 +74493,7 @@
       <c r="F1325" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1325" s="20">
+      <c r="G1325" s="1">
         <v>25205035</v>
       </c>
       <c r="H1325" s="1" t="s">
@@ -74548,7 +74547,7 @@
       <c r="F1326" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1326" s="20">
+      <c r="G1326" s="1">
         <v>25216191</v>
       </c>
       <c r="H1326" s="1" t="s">
@@ -74602,7 +74601,7 @@
       <c r="F1327" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1327" s="20">
+      <c r="G1327" s="1">
         <v>25219001</v>
       </c>
       <c r="H1327" s="1" t="s">
@@ -74656,7 +74655,7 @@
       <c r="F1328" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1328" s="20">
+      <c r="G1328" s="1">
         <v>25219535</v>
       </c>
       <c r="H1328" s="1" t="s">
@@ -74710,7 +74709,7 @@
       <c r="F1329" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1329" s="20">
+      <c r="G1329" s="1">
         <v>40306210</v>
       </c>
       <c r="H1329" s="1" t="s">
@@ -74764,7 +74763,7 @@
       <c r="F1330" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1330" s="20">
+      <c r="G1330" s="1">
         <v>40787183</v>
       </c>
       <c r="H1330" s="1" t="s">
@@ -74818,7 +74817,7 @@
       <c r="F1331" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1331" s="20">
+      <c r="G1331" s="1">
         <v>41798598</v>
       </c>
       <c r="H1331" s="1" t="s">
@@ -74872,7 +74871,7 @@
       <c r="F1332" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1332" s="20">
+      <c r="G1332" s="1">
         <v>44268677</v>
       </c>
       <c r="H1332" s="1" t="s">
@@ -74926,7 +74925,7 @@
       <c r="F1333" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1333" s="20">
+      <c r="G1333" s="1">
         <v>44424902</v>
       </c>
       <c r="H1333" s="1" t="s">
@@ -74980,7 +74979,7 @@
       <c r="F1334" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1334" s="20">
+      <c r="G1334" s="1">
         <v>45717160</v>
       </c>
       <c r="H1334" s="1" t="s">
@@ -75034,7 +75033,7 @@
       <c r="F1335" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1335" s="20">
+      <c r="G1335" s="1">
         <v>45718764</v>
       </c>
       <c r="H1335" s="1" t="s">
@@ -75088,7 +75087,7 @@
       <c r="F1336" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1336" s="20">
+      <c r="G1336" s="1">
         <v>45718774</v>
       </c>
       <c r="H1336" s="1" t="s">
@@ -75142,7 +75141,7 @@
       <c r="F1337" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1337" s="20">
+      <c r="G1337" s="1">
         <v>45757914</v>
       </c>
       <c r="H1337" s="1" t="s">
@@ -75196,7 +75195,7 @@
       <c r="F1338" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1338" s="20">
+      <c r="G1338" s="1">
         <v>46116552</v>
       </c>
       <c r="H1338" s="1" t="s">
@@ -75250,7 +75249,7 @@
       <c r="F1339" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1339" s="20">
+      <c r="G1339" s="1">
         <v>46876336</v>
       </c>
       <c r="H1339" s="1" t="s">
@@ -75304,7 +75303,7 @@
       <c r="F1340" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1340" s="20">
+      <c r="G1340" s="1">
         <v>48318063</v>
       </c>
       <c r="H1340" s="1" t="s">
@@ -75358,7 +75357,7 @@
       <c r="F1341" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1341" s="20">
+      <c r="G1341" s="1">
         <v>74159095</v>
       </c>
       <c r="H1341" s="1" t="s">
@@ -75412,7 +75411,7 @@
       <c r="F1342" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1342" s="20">
+      <c r="G1342" s="1">
         <v>76698640</v>
       </c>
       <c r="H1342" s="1" t="s">
@@ -75466,7 +75465,7 @@
       <c r="F1343" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1343" s="20">
+      <c r="G1343" s="1">
         <v>76913759</v>
       </c>
       <c r="H1343" s="1" t="s">
@@ -75520,7 +75519,7 @@
       <c r="F1344" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1344" s="20">
+      <c r="G1344" s="1">
         <v>77242609</v>
       </c>
       <c r="H1344" s="1" t="s">
@@ -75574,7 +75573,7 @@
       <c r="F1345" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1345" s="20">
+      <c r="G1345" s="1">
         <v>80011154</v>
       </c>
       <c r="H1345" s="1" t="s">
@@ -75628,7 +75627,7 @@
       <c r="F1346" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1346" s="20">
+      <c r="G1346" s="1">
         <v>80011295</v>
       </c>
       <c r="H1346" s="1" t="s">
@@ -75682,7 +75681,7 @@
       <c r="F1347" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G1347" s="20">
+      <c r="G1347" s="1">
         <v>23956032</v>
       </c>
       <c r="H1347" s="1" t="s">
@@ -79393,7 +79392,7 @@
         <v>27</v>
       </c>
       <c r="F1430" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1430" s="1">
         <v>71218324</v>
@@ -79437,7 +79436,7 @@
         <v>27</v>
       </c>
       <c r="F1431" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1431" s="1">
         <v>23915633</v>
@@ -79481,7 +79480,7 @@
         <v>27</v>
       </c>
       <c r="F1432" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1432" s="1">
         <v>23911269</v>
@@ -79525,7 +79524,7 @@
         <v>27</v>
       </c>
       <c r="F1433" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1433" s="1">
         <v>23982064</v>
@@ -79569,7 +79568,7 @@
         <v>27</v>
       </c>
       <c r="F1434" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1434" s="1">
         <v>23960156</v>
@@ -79613,7 +79612,7 @@
         <v>27</v>
       </c>
       <c r="F1435" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1435" s="1">
         <v>42047719</v>
@@ -79657,7 +79656,7 @@
         <v>27</v>
       </c>
       <c r="F1436" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1436" s="1">
         <v>23840825</v>
@@ -79701,7 +79700,7 @@
         <v>27</v>
       </c>
       <c r="F1437" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1437" s="1">
         <v>23811505</v>
@@ -79745,7 +79744,7 @@
         <v>27</v>
       </c>
       <c r="F1438" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1438" s="1">
         <v>42071025</v>
@@ -79789,7 +79788,7 @@
         <v>27</v>
       </c>
       <c r="F1439" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1439" s="1">
         <v>2403362</v>
@@ -79833,7 +79832,7 @@
         <v>27</v>
       </c>
       <c r="F1440" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1440" s="1">
         <v>23859390</v>
@@ -79877,7 +79876,7 @@
         <v>27</v>
       </c>
       <c r="F1441" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1441" s="1">
         <v>45981779</v>
@@ -79921,7 +79920,7 @@
         <v>27</v>
       </c>
       <c r="F1442" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1442" s="1">
         <v>23815170</v>
@@ -79965,7 +79964,7 @@
         <v>27</v>
       </c>
       <c r="F1443" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1443" s="1">
         <v>24884262</v>
@@ -80009,7 +80008,7 @@
         <v>27</v>
       </c>
       <c r="F1444" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1444" s="1">
         <v>40809201</v>
@@ -80053,7 +80052,7 @@
         <v>27</v>
       </c>
       <c r="F1445" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1445" s="1">
         <v>23885626</v>
@@ -80097,7 +80096,7 @@
         <v>27</v>
       </c>
       <c r="F1446" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1446" s="1">
         <v>23837815</v>
@@ -80141,7 +80140,7 @@
         <v>27</v>
       </c>
       <c r="F1447" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1447" s="1">
         <v>23841580</v>
@@ -80185,7 +80184,7 @@
         <v>27</v>
       </c>
       <c r="F1448" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1448" s="1">
         <v>44249822</v>
@@ -80229,7 +80228,7 @@
         <v>27</v>
       </c>
       <c r="F1449" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1449" s="1">
         <v>23839655</v>
@@ -80273,7 +80272,7 @@
         <v>27</v>
       </c>
       <c r="F1450" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1450" s="1">
         <v>23815839</v>
@@ -80317,7 +80316,7 @@
         <v>27</v>
       </c>
       <c r="F1451" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1451" s="1">
         <v>23947542</v>
@@ -80361,7 +80360,7 @@
         <v>27</v>
       </c>
       <c r="F1452" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1452" s="1">
         <v>23985843</v>
@@ -80405,7 +80404,7 @@
         <v>27</v>
       </c>
       <c r="F1453" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1453" s="1">
         <v>45841374</v>
@@ -80449,7 +80448,7 @@
         <v>27</v>
       </c>
       <c r="F1454" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1454" s="1">
         <v>23990823</v>
@@ -80493,7 +80492,7 @@
         <v>27</v>
       </c>
       <c r="F1455" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1455" s="1">
         <v>44926610</v>
@@ -80537,7 +80536,7 @@
         <v>27</v>
       </c>
       <c r="F1456" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1456" s="1">
         <v>23856360</v>
@@ -80581,7 +80580,7 @@
         <v>27</v>
       </c>
       <c r="F1457" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1457" s="1">
         <v>23986656</v>
@@ -80625,7 +80624,7 @@
         <v>27</v>
       </c>
       <c r="F1458" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1458" s="1">
         <v>23860369</v>
@@ -80669,7 +80668,7 @@
         <v>27</v>
       </c>
       <c r="F1459" s="1" t="s">
-        <v>594</v>
+        <v>1556</v>
       </c>
       <c r="G1459" s="1">
         <v>23812194</v>
